--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08ADE59-0125-4F0A-8722-796123F96A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF195D28-E0E1-4621-A983-DCDAFAA0B199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="825" yWindow="4905" windowWidth="24810" windowHeight="11820" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
     <sheet name="概要" sheetId="5" r:id="rId2"/>
     <sheet name="作業工数見積もり" sheetId="1" r:id="rId3"/>
-    <sheet name="メモ" sheetId="9" r:id="rId4"/>
-    <sheet name="カレンダー" sheetId="6" r:id="rId5"/>
-    <sheet name="雑用" sheetId="10" r:id="rId6"/>
+    <sheet name="日記" sheetId="12" r:id="rId4"/>
+    <sheet name="メモ" sheetId="9" r:id="rId5"/>
+    <sheet name="カレンダー" sheetId="6" r:id="rId6"/>
+    <sheet name="雑用" sheetId="10" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="235">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1586,6 +1587,56 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月日</t>
+    <rPh sb="0" eb="2">
+      <t>ツキヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8時間</t>
+    <rPh sb="1" eb="3">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンコントローラー、Input,とかの基盤を作った、Playerクラスの基底クラスの基盤を作った、PlayerのStatePatternを作っている途中</t>
+    <rPh sb="20" eb="22">
+      <t>キバン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>キテイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>キバン</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>トチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5265,6 +5316,54 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="127.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>46168</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -5286,7 +5385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C830D07-33E0-4A6A-A9E3-4F29F77EDCE6}">
   <dimension ref="C2:P37"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -5903,7 +6002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
   <dimension ref="C2:C7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -5945,6 +6044,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
@@ -5953,15 +6061,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6200,20 +6299,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
     <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF195D28-E0E1-4621-A983-DCDAFAA0B199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560D4A71-07DB-4CE1-BECE-008D7746ACC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="4905" windowWidth="24810" windowHeight="11820" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6915" yWindow="4965" windowWidth="24810" windowHeight="11820" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="237">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1637,6 +1637,35 @@
     </rPh>
     <rPh sb="75" eb="77">
       <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5時間</t>
+    <rPh sb="1" eb="3">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PlayerStateのattackState作ってた、次はattack中の移動時間を制限する</t>
+    <rPh sb="23" eb="24">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>セイゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5351,6 +5380,12 @@
       <c r="A3" s="1">
         <v>46167</v>
       </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1">
@@ -6044,15 +6079,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
@@ -6061,6 +6087,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6299,20 +6334,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
     <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560D4A71-07DB-4CE1-BECE-008D7746ACC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFB23BF-7316-4C78-A4E5-945E35A112A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="4965" windowWidth="24810" windowHeight="11820" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="645" yWindow="465" windowWidth="24075" windowHeight="14400" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$B$2:$G$62</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="255">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1232,10 +1232,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>5月</t>
     <rPh sb="1" eb="2">
       <t>ガツ</t>
@@ -1424,10 +1420,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>S</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・Idle</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1666,6 +1658,260 @@
     </rPh>
     <rPh sb="43" eb="45">
       <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだ当たり判定系はなにもしていない</t>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ハンテイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←必須ではなかった</t>
+    <rPh sb="1" eb="3">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力バッファの利点：爽快感が上がり、雑にコンボができるようになる</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>リテン</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ソウカイカン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ザツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在、0.2~0.8のがばでとっているため、あまり変わらない</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シビアになってきたときに輝く</t>
+    <rPh sb="12" eb="13">
+      <t>カガヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>just回避、just回避反撃のStateは行動が全然別なので、分けた方がよい</t>
+    <rPh sb="4" eb="6">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンゲキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゼンゼン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・Hit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・Dead</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡処理</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒット処理</t>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・Jump</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jump挙動</t>
+    <rPh sb="4" eb="6">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jump当たり判定</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定の取り方</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①攻撃との当たり判定&amp;物体同士の当たり判定</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ブッタイドウシ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②地形とのポリゴンとの当たり判定</t>
+    <rPh sb="1" eb="3">
+      <t>チケイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Set前に未来予測型の当たり判定をする</t>
+    <rPh sb="3" eb="4">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>ミライヨソクガタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(井上恋のプロジェクト参照)</t>
+    <rPh sb="1" eb="3">
+      <t>イノウエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>レン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>attack中の移動制限完了,PlayerStateParryのかけらを作った。次は、DashAttackを作ろうかなぁ。当たり判定を先にやってもいい</t>
+    <rPh sb="6" eb="7">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>イドウセイゲン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemyも作り始めたいけどさすがにPlayerがいろいろ終わった後かな</t>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1678,7 +1924,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1733,14 +1979,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="5" tint="0.59999389629810485"/>
       <name val="Yu Gothic"/>
@@ -1748,7 +1986,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1899,6 +2137,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -2027,19 +2271,17 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -2425,11 +2667,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>6.5920398009950254E-2</v>
+        <v>6.5756823821339946E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2469,7 +2711,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2534,11 +2776,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-371</v>
+        <v>-372</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.24797843665768193</v>
+        <v>-0.24731182795698925</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2565,11 +2807,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-351</v>
+        <v>-352</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.2621082621082621</v>
+        <v>-0.26136363636363635</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2596,11 +2838,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-340</v>
+        <v>-341</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.27058823529411763</v>
+        <v>-0.26979472140762462</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4128,8 +4370,8 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!F3:F84)</f>
-        <v>58</v>
+        <f>SUM(作業工数見積もり!E3:E91)</f>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4137,8 +4379,8 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!H3:H37,"完了",作業工数見積もり!F3:F37)</f>
-        <v>38</v>
+        <f>SUMIF(作業工数見積もり!G3:G44,"完了",作業工数見積もり!E3:E44)</f>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -4150,11 +4392,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>9.4527363184079602E-2</v>
+        <v>1.488833746898263E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4172,7 +4414,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4193,11 +4435,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-371</v>
+        <v>-372</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-5.3908355795148251E-2</v>
+        <v>-0.23118279569892472</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4210,11 +4452,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-351</v>
+        <v>-352</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-5.6980056980056981E-2</v>
+        <v>-0.24431818181818182</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4227,11 +4469,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-340</v>
+        <v>-341</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-5.8823529411764705E-2</v>
+        <v>-0.25219941348973607</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4315,1027 +4557,1394 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:M63"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="69.625" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.625" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.375" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.125" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="21"/>
-    <col min="10" max="10" width="18.125" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.5" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="21"/>
+    <col min="1" max="1" width="69.625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17.125" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="21"/>
+    <col min="9" max="9" width="18.125" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9" style="21"/>
+    <col min="16" max="16384" width="9" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="1:12">
+      <c r="A1" s="21" t="s">
+        <v>142</v>
+      </c>
       <c r="B1" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="21" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="2:13">
+    <row r="2" spans="1:12">
+      <c r="A2" s="26" t="s">
+        <v>129</v>
+      </c>
       <c r="B2" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="26" t="s">
         <v>130</v>
       </c>
+      <c r="C2" s="27" t="s">
+        <v>2</v>
+      </c>
       <c r="D2" s="27" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="27" t="s">
         <v>132</v>
       </c>
+      <c r="J2" s="21" t="s">
+        <v>171</v>
+      </c>
       <c r="K2" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="M2" s="21" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="29" t="s">
+    <row r="3" spans="1:12">
+      <c r="A3" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="21" t="s">
         <v>154</v>
       </c>
+      <c r="C3" s="28" t="s">
+        <v>9</v>
+      </c>
       <c r="D3" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>34</v>
+        <v>34</v>
+      </c>
+      <c r="E3" s="28">
+        <v>1</v>
       </c>
       <c r="F3" s="28">
         <v>1</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="J3" s="21">
+        <f ca="1">SUM(J4,J5,J6)</f>
+        <v>87</v>
+      </c>
+      <c r="K3" s="21">
+        <f>SUMIFS(E3:E61,G3:G61,"未着手")</f>
+        <v>80</v>
+      </c>
+      <c r="L3" s="21">
+        <f>SUM(F3:F61)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J4" s="41">
+        <f ca="1">SUMIF(D3:D59,I4,E3:E58)</f>
+        <v>85.5</v>
+      </c>
+      <c r="K4" s="21">
+        <f>SUMIFS($E$3:$E$61,$G$3:$G$61,"未着手",$D$3:$D$61,I4)</f>
+        <v>78.5</v>
+      </c>
+      <c r="L4" s="21">
+        <f>SUMIFS(F3:F61,D3:D61,I4)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="I5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="J5" s="41">
+        <f ca="1">SUMIF(D4:D61,I5,E4:E59)</f>
+        <v>1.5</v>
+      </c>
+      <c r="K5" s="21">
+        <f>SUMIFS($E$3:$E$61,$G$3:$G$61,"未着手",$D$3:$D$61,I5)</f>
+        <v>1.5</v>
+      </c>
+      <c r="L5" s="21">
+        <f>SUMIFS(F4:F62,D4:D62,I5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="J3" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="K3" s="21">
-        <f ca="1">SUM(K4,K5,K6)</f>
-        <v>53</v>
-      </c>
-      <c r="L3" s="21">
-        <f>SUMIFS(F3:F54,H3:H54,"未着手")</f>
-        <v>13.5</v>
-      </c>
-      <c r="M3" s="21">
-        <f>SUM(G3:G54)</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="28">
+      <c r="I6" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" s="41">
+        <f ca="1">SUMIF(D5:D62,I6,E5:E61)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="21">
+        <f>SUMIFS($E$3:$E$61,$G$3:$G$61,"未着手",$D$3:$D$61,I6)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="21">
+        <f>SUMIFS(F5:F62,D5:D62,I6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="28">
         <v>0.5</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="F7" s="28">
+        <v>2</v>
+      </c>
+      <c r="G7" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="J4" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="K4" s="42">
-        <f ca="1">SUMIF(E3:E52,J4,F3:F51)</f>
-        <v>39.5</v>
-      </c>
-      <c r="L4" s="21">
-        <f>SUMIFS($F$3:$F$54,$H$3:$H$54,"未着手",$E$3:$E$54,J4)</f>
+      <c r="I7" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="J7" s="21">
+        <f>COUNTIF(G3:G59,"作業中")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="28">
+        <v>2</v>
+      </c>
+      <c r="F8" s="28">
+        <v>3</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" outlineLevel="1">
+      <c r="A12" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="28">
         <v>1</v>
-      </c>
-      <c r="M4" s="21">
-        <f>SUMIFS(G3:G54,E3:E54,J4)</f>
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="J5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="42">
-        <f ca="1">SUMIF(E4:E54,J5,F4:F52)</f>
-        <v>13.5</v>
-      </c>
-      <c r="L5" s="21">
-        <f>SUMIFS($F$3:$F$54,$H$3:$H$54,"未着手",$E$3:$E$54,J5)</f>
-        <v>12.5</v>
-      </c>
-      <c r="M5" s="21">
-        <f>SUMIFS(G4:G55,E4:E55,J5)</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="J6" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="K6" s="42">
-        <f ca="1">SUMIF(E5:E55,J6,F5:F54)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="21">
-        <f>SUMIFS($F$3:$F$54,$H$3:$H$54,"未着手",$E$3:$E$54,J6)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="21">
-        <f>SUMIFS(G5:G55,E5:E55,J6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="28">
-        <v>2</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="K7" s="21">
-        <f>COUNTIF(H3:H52,"作業中")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="28">
-        <v>2</v>
-      </c>
-      <c r="G8" s="28">
-        <v>3</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" outlineLevel="1">
-      <c r="B12" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="28">
         <v>1</v>
       </c>
-      <c r="G12" s="28">
-        <v>5</v>
-      </c>
-      <c r="H12" s="28" t="s">
+      <c r="G12" s="28" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="2:13" outlineLevel="1">
-      <c r="B13" s="31" t="s">
+    <row r="13" spans="1:12" outlineLevel="1">
+      <c r="A13" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="B13" s="21" t="s">
         <v>167</v>
       </c>
+      <c r="C13" s="28" t="s">
+        <v>9</v>
+      </c>
       <c r="D13" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>34</v>
+        <v>34</v>
+      </c>
+      <c r="E13" s="28">
+        <v>1</v>
       </c>
       <c r="F13" s="28">
         <v>1</v>
       </c>
-      <c r="G13" s="28">
-        <v>7</v>
-      </c>
-      <c r="H13" s="28" t="s">
+      <c r="G13" s="28" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="31" t="s">
+    <row r="14" spans="1:12" outlineLevel="1">
+      <c r="A14" s="31"/>
+      <c r="B14" s="21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" outlineLevel="1">
+      <c r="A15" s="31"/>
+      <c r="B15" s="21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" outlineLevel="1">
+      <c r="A16" s="31"/>
+      <c r="B16" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="B17" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" outlineLevel="1">
+      <c r="A18" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="28">
+        <v>1</v>
+      </c>
+      <c r="F18" s="28">
+        <v>1</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" outlineLevel="1">
+      <c r="A19" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="28">
+        <v>1</v>
+      </c>
+      <c r="F19" s="28">
+        <v>1</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" outlineLevel="1">
+      <c r="A20" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="28">
+        <v>1</v>
+      </c>
+      <c r="F20" s="28">
+        <v>1</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" outlineLevel="1">
+      <c r="A21" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="E14" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" outlineLevel="1">
-      <c r="B15" s="31" t="s">
+      <c r="C22" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" outlineLevel="1">
+      <c r="A23" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="28">
+      <c r="B23" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="28">
+        <v>3</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" outlineLevel="1">
+      <c r="A25" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="28">
+        <v>24</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" outlineLevel="1">
+      <c r="A27" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="28">
+        <v>1</v>
+      </c>
+      <c r="F27" s="28">
+        <v>1</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" outlineLevel="1">
+      <c r="A28" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="28">
         <v>2</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G28" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" outlineLevel="1">
+      <c r="A29" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="28">
+        <v>4</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" outlineLevel="1">
+      <c r="A30" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="28">
+        <v>4</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" outlineLevel="1">
+      <c r="A32" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" outlineLevel="1">
+      <c r="A33" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" outlineLevel="1">
+      <c r="A34" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" outlineLevel="1">
+      <c r="A35" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" outlineLevel="1">
+      <c r="A36" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" outlineLevel="1">
+      <c r="A37" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B37" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" outlineLevel="1">
+      <c r="A38" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="28">
+        <v>1</v>
+      </c>
+      <c r="F39" s="28">
+        <v>4</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="28">
         <v>2</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="F40" s="28">
+        <v>2</v>
+      </c>
+      <c r="G40" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="28">
+        <v>2</v>
+      </c>
+      <c r="F41" s="28">
+        <v>3</v>
+      </c>
+      <c r="G41" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="28">
+        <v>8</v>
+      </c>
+      <c r="F42" s="28">
+        <v>3</v>
+      </c>
+      <c r="G42" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="F44" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="F45" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="G45" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G49" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E51" s="28">
+        <v>2</v>
+      </c>
+      <c r="G51" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B52" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G53" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" s="28">
+        <v>1</v>
+      </c>
+      <c r="F54" s="28">
+        <v>3</v>
+      </c>
+      <c r="G54" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" s="28">
+        <v>1</v>
+      </c>
+      <c r="F55" s="28">
+        <v>1</v>
+      </c>
+      <c r="G55" s="28" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="2:13" outlineLevel="1">
-      <c r="B16" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="28">
+    <row r="56" spans="1:7">
+      <c r="A56" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E56" s="28">
+        <v>12</v>
+      </c>
+      <c r="G56" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E57" s="28">
+        <v>6</v>
+      </c>
+      <c r="G57" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E58" s="28">
+        <v>3</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G60" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G62" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E63" s="28">
+        <v>3</v>
+      </c>
+      <c r="G63" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E64" s="28">
+        <v>2</v>
+      </c>
+      <c r="F64" s="28">
         <v>1</v>
       </c>
-      <c r="G16" s="28">
-        <v>1</v>
-      </c>
-      <c r="H16" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" outlineLevel="1">
-      <c r="B17" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="28">
-        <v>1</v>
-      </c>
-      <c r="G17" s="28">
-        <v>1</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" outlineLevel="1">
-      <c r="B18" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" outlineLevel="1">
-      <c r="B20" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="28">
-        <v>8</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" outlineLevel="1">
-      <c r="B22" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" outlineLevel="1">
-      <c r="B24" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="28">
-        <v>8</v>
-      </c>
-      <c r="G24" s="28">
-        <v>4</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" outlineLevel="1">
-      <c r="B25" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" outlineLevel="1">
-      <c r="B26" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" outlineLevel="1">
-      <c r="B27" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" outlineLevel="1">
-      <c r="B29" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" outlineLevel="1">
-      <c r="B30" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" outlineLevel="1">
-      <c r="B31" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="28">
-        <v>1</v>
-      </c>
-      <c r="G32" s="28">
-        <v>4</v>
-      </c>
-      <c r="H32" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="28">
-        <v>2</v>
-      </c>
-      <c r="G33" s="28">
-        <v>2</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D34" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="28">
-        <v>2</v>
-      </c>
-      <c r="G34" s="28">
-        <v>3</v>
-      </c>
-      <c r="H34" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="28">
-        <v>8</v>
-      </c>
-      <c r="G35" s="28">
-        <v>3</v>
-      </c>
-      <c r="H35" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="G37" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="H37" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="G38" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="H38" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="D44" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="28">
-        <v>2</v>
-      </c>
-      <c r="H44" s="28" t="s">
+      <c r="G64" s="28" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D47" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" s="28">
-        <v>1</v>
-      </c>
-      <c r="G47" s="28">
-        <v>3</v>
-      </c>
-      <c r="H47" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F50" s="28">
-        <v>8</v>
-      </c>
-      <c r="H50" s="28" t="s">
+    <row r="65" spans="1:7">
+      <c r="A65" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65" s="28" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" s="28">
-        <v>1</v>
-      </c>
-      <c r="H51" s="28" t="s">
+    <row r="66" spans="1:7">
+      <c r="A66" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G66" s="28" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="H52" s="28" t="s">
+    <row r="67" spans="1:7">
+      <c r="A67" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G67" s="28" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="35" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="H55" s="41"/>
-    </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="25" t="s">
+    <row r="68" spans="1:7">
+      <c r="A68" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D56" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F56" s="28">
-        <v>3</v>
-      </c>
-      <c r="H56" s="28" t="s">
+      <c r="B68" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G68" s="28" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="25" t="s">
+    <row r="69" spans="1:7">
+      <c r="A69" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="C57" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D57" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F57" s="28">
-        <v>2</v>
-      </c>
-      <c r="G57" s="28">
-        <v>1</v>
-      </c>
-      <c r="H57" s="28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
-      <c r="B58" s="25" t="s">
+      <c r="B69" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G69" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="21" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C59" s="21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
-      <c r="B60" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60" s="21" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8">
-      <c r="B61" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
-      <c r="B62" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="21" t="s">
+      <c r="B70" s="21" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="63" spans="2:8">
-      <c r="B63" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>221</v>
+      <c r="C70" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G70" s="28" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C2:H55" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H51">
-      <sortCondition ref="C2:C51"/>
+  <autoFilter ref="B2:G62" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G58">
+      <sortCondition ref="B2:B58"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D8 D56:D59 D12:D47 D50:D54" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C70" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E8 E56:E59 E11:E47 E50:E54" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D70" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H8 H56:H59 H12:H47 H50:H54" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G70" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5346,7 +5955,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -5356,13 +5965,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" t="s">
         <v>230</v>
-      </c>
-      <c r="B1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5370,10 +5979,10 @@
         <v>46166</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5381,15 +5990,21 @@
         <v>46167</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>46168</v>
+      <c r="A4" s="1"/>
+      <c r="C4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="C5" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -5400,7 +6015,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2"/>
+  <dimension ref="B2:D14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -5409,9 +6024,58 @@
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>229</v>
+        <v>227</v>
+      </c>
+      <c r="C2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="D3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -5427,12 +6091,12 @@
   <sheetData>
     <row r="2" spans="3:16">
       <c r="O2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="3:16">
       <c r="C3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="3:16">
@@ -5471,7 +6135,7 @@
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="3:16">
@@ -5499,7 +6163,7 @@
       <c r="K6" t="s">
         <v>126</v>
       </c>
-      <c r="L6" s="44"/>
+      <c r="L6" s="43"/>
       <c r="M6">
         <v>24</v>
       </c>
@@ -5529,7 +6193,7 @@
       <c r="K7" t="s">
         <v>1</v>
       </c>
-      <c r="L7" s="46"/>
+      <c r="L7" s="45"/>
       <c r="M7">
         <v>24</v>
       </c>
@@ -5553,7 +6217,7 @@
       <c r="G8" s="21">
         <v>21</v>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="50">
         <v>22</v>
       </c>
       <c r="I8" s="22">
@@ -5562,7 +6226,7 @@
       <c r="K8" t="s">
         <v>127</v>
       </c>
-      <c r="L8" s="50"/>
+      <c r="L8" s="49"/>
       <c r="M8">
         <v>24</v>
       </c>
@@ -5590,9 +6254,9 @@
         <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>179</v>
-      </c>
-      <c r="L9" s="47"/>
+        <v>178</v>
+      </c>
+      <c r="L9" s="46"/>
       <c r="M9">
         <v>7</v>
       </c>
@@ -5604,7 +6268,7 @@
     </row>
     <row r="12" spans="3:16">
       <c r="C12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="3:16">
@@ -5664,70 +6328,70 @@
       <c r="F15" s="21">
         <v>10</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="42">
         <v>11</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="43">
         <v>12</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="3:16">
-      <c r="C16" s="44">
+      <c r="C16" s="43">
         <v>14</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="43">
         <v>15</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="43">
         <v>16</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="43">
         <v>17</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="43">
         <v>18</v>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="43">
         <v>19</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="3:11">
-      <c r="C17" s="44">
+      <c r="C17" s="43">
         <v>21</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="43">
         <v>22</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="43">
         <v>23</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="43">
         <v>24</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="43">
         <v>25</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="43">
         <v>26</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="3:11">
-      <c r="C18" s="44">
+      <c r="C18" s="43">
         <v>28</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="43">
         <v>29</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="43">
         <v>30</v>
       </c>
       <c r="F18" s="21"/>
@@ -5740,7 +6404,7 @@
     </row>
     <row r="20" spans="3:11">
       <c r="C20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="3:11">
@@ -5770,24 +6434,24 @@
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="21"/>
-      <c r="F22" s="44">
+      <c r="F22" s="43">
         <v>1</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="43">
         <v>2</v>
       </c>
-      <c r="H22" s="44">
+      <c r="H22" s="43">
         <v>3</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="3:11">
-      <c r="C23" s="44">
+      <c r="C23" s="43">
         <v>5</v>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="43">
         <v>6</v>
       </c>
       <c r="E23" s="31">
@@ -5878,7 +6542,7 @@
     </row>
     <row r="30" spans="3:11">
       <c r="C30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="3:11">
@@ -5922,114 +6586,114 @@
       <c r="C33" s="31">
         <v>2</v>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="49">
         <v>3</v>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="49">
         <v>4</v>
       </c>
-      <c r="F33" s="50">
+      <c r="F33" s="49">
         <v>5</v>
       </c>
-      <c r="G33" s="50">
+      <c r="G33" s="49">
         <v>6</v>
       </c>
-      <c r="H33" s="50">
+      <c r="H33" s="49">
         <v>7</v>
       </c>
-      <c r="I33" s="50">
+      <c r="I33" s="49">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="3:9">
-      <c r="C34" s="50">
-        <v>9</v>
-      </c>
-      <c r="D34" s="50">
+      <c r="C34" s="49">
+        <v>9</v>
+      </c>
+      <c r="D34" s="49">
         <v>10</v>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="49">
         <v>11</v>
       </c>
-      <c r="F34" s="50">
+      <c r="F34" s="49">
         <v>12</v>
       </c>
-      <c r="G34" s="50">
+      <c r="G34" s="49">
         <v>13</v>
       </c>
-      <c r="H34" s="50">
+      <c r="H34" s="49">
         <v>14</v>
       </c>
-      <c r="I34" s="50">
+      <c r="I34" s="49">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="3:9">
-      <c r="C35" s="50">
+      <c r="C35" s="49">
         <v>16</v>
       </c>
-      <c r="D35" s="50">
+      <c r="D35" s="49">
         <v>17</v>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="49">
         <v>18</v>
       </c>
-      <c r="F35" s="50">
+      <c r="F35" s="49">
         <v>19</v>
       </c>
-      <c r="G35" s="50">
+      <c r="G35" s="49">
         <v>20</v>
       </c>
-      <c r="H35" s="50">
+      <c r="H35" s="49">
         <v>21</v>
       </c>
-      <c r="I35" s="50">
+      <c r="I35" s="49">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="3:9">
-      <c r="C36" s="50">
+      <c r="C36" s="49">
         <v>23</v>
       </c>
-      <c r="D36" s="50">
+      <c r="D36" s="49">
         <v>24</v>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="49">
         <v>25</v>
       </c>
-      <c r="F36" s="50">
+      <c r="F36" s="49">
         <v>26</v>
       </c>
-      <c r="G36" s="50">
+      <c r="G36" s="49">
         <v>27</v>
       </c>
-      <c r="H36" s="47">
+      <c r="H36" s="46">
         <v>28</v>
       </c>
-      <c r="I36" s="47">
+      <c r="I36" s="46">
         <v>29</v>
       </c>
     </row>
     <row r="37" spans="3:9">
-      <c r="C37" s="47">
+      <c r="C37" s="46">
         <v>30</v>
       </c>
-      <c r="D37" s="47">
+      <c r="D37" s="46">
         <v>31</v>
       </c>
-      <c r="E37" s="49">
+      <c r="E37" s="48">
         <v>1</v>
       </c>
-      <c r="F37" s="49">
+      <c r="F37" s="48">
         <v>2</v>
       </c>
-      <c r="G37" s="49">
+      <c r="G37" s="48">
         <v>3</v>
       </c>
-      <c r="H37" s="48">
+      <c r="H37" s="47">
         <v>4</v>
       </c>
-      <c r="I37" s="45"/>
+      <c r="I37" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -6044,32 +6708,32 @@
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -6079,17 +6743,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6098,7 +6751,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6333,18 +6986,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -6352,7 +7005,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6369,4 +7022,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFB23BF-7316-4C78-A4E5-945E35A112A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE146292-0727-44BF-AFB3-BB2552697419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="645" yWindow="465" windowWidth="24075" windowHeight="14400" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="257">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1912,6 +1912,23 @@
     </rPh>
     <rPh sb="33" eb="34">
       <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>playerのアニメーション名を再設定</t>
+    <rPh sb="14" eb="15">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>サイセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>playerのコンボノードを再設定</t>
+    <rPh sb="14" eb="17">
+      <t>サイセッテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2667,11 +2684,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>6.5756823821339946E-2</v>
+        <v>6.4792176039119798E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2711,7 +2728,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46167</v>
+        <v>46175</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2776,11 +2793,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-372</v>
+        <v>-378</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.24731182795698925</v>
+        <v>-0.24338624338624337</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2807,11 +2824,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-352</v>
+        <v>-358</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.26136363636363635</v>
+        <v>-0.25698324022346369</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2838,11 +2855,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-341</v>
+        <v>-347</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.26979472140762462</v>
+        <v>-0.26512968299711814</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4392,11 +4409,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.488833746898263E-2</v>
+        <v>1.4669926650366748E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4414,7 +4431,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46167</v>
+        <v>46175</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4435,11 +4452,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-372</v>
+        <v>-378</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.23118279569892472</v>
+        <v>-0.2275132275132275</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4452,11 +4469,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-352</v>
+        <v>-358</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.24431818181818182</v>
+        <v>-0.24022346368715083</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4469,11 +4486,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-341</v>
+        <v>-347</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.25219941348973607</v>
+        <v>-0.2478386167146974</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -6703,7 +6720,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
-  <dimension ref="C2:C7"/>
+  <dimension ref="C2:C11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="3:3">
@@ -6734,6 +6751,16 @@
     <row r="7" spans="3:3">
       <c r="C7" t="s">
         <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -6743,12 +6770,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6987,20 +7016,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7025,12 +7055,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE146292-0727-44BF-AFB3-BB2552697419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3C37C9-D8DB-41DD-9726-090DAC88B9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="259">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1929,6 +1929,26 @@
     <t>playerのコンボノードを再設定</t>
     <rPh sb="14" eb="17">
       <t>サイセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニメーション→</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dodge系、走り、歩きダサい、やり直し</t>
+    <rPh sb="5" eb="6">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ナオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6720,45 +6740,51 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
-  <dimension ref="C2:C11"/>
+  <dimension ref="C2:J11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="3:3">
+    <row r="2" spans="3:10">
       <c r="C2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="3" spans="3:3">
+    <row r="3" spans="3:10">
       <c r="C3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="3:3">
+    <row r="4" spans="3:10">
       <c r="C4" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="3:3">
+    <row r="5" spans="3:10">
       <c r="C5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="3:3">
+    <row r="6" spans="3:10">
       <c r="C6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="7" spans="3:3">
+    <row r="7" spans="3:10">
       <c r="C7" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="3:3">
+    <row r="10" spans="3:10">
       <c r="C10" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="11" spans="3:3">
+      <c r="H10" t="s">
+        <v>257</v>
+      </c>
+      <c r="J10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10">
       <c r="C11" t="s">
         <v>256</v>
       </c>
@@ -6770,17 +6796,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -7015,6 +7030,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -7025,17 +7051,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7054,6 +7069,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5B4DA2-253E-4664-BFBB-BAAD26468420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF97DD0-8280-4EE6-A0E4-A1FD6293C1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
     <sheet name="作業工数見積もり" sheetId="1" r:id="rId2"/>
-    <sheet name="日記" sheetId="12" r:id="rId3"/>
-    <sheet name="メモ" sheetId="9" r:id="rId4"/>
-    <sheet name="カレンダー" sheetId="6" r:id="rId5"/>
+    <sheet name="カレンダー" sheetId="6" r:id="rId3"/>
+    <sheet name="日記" sheetId="12" r:id="rId4"/>
+    <sheet name="メモ" sheetId="9" r:id="rId5"/>
     <sheet name="雑用" sheetId="10" r:id="rId6"/>
     <sheet name="仕様書" sheetId="13" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$63</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="183">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -670,10 +670,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スキル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ウルト</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -705,15 +701,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・Parry</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・Dash</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パリィ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -724,13 +712,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジャストパリィ反撃</t>
-    <rPh sb="7" eb="9">
-      <t>ハンゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ジャスト回避反撃</t>
     <rPh sb="4" eb="6">
       <t>カイヒ</t>
@@ -741,10 +722,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジャストパリィ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ダッシュ攻撃</t>
     <rPh sb="4" eb="6">
       <t>コウゲキ</t>
@@ -1473,6 +1450,36 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弱ボタン連携</t>
+    <rPh sb="0" eb="1">
+      <t>ジャク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>レンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強ボタン連携</t>
+    <rPh sb="0" eb="1">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>レンケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2087,7 +2094,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!E3:E91)</f>
+        <f>SUM(作業工数見積もり!E3:E92)</f>
         <v>92</v>
       </c>
     </row>
@@ -2096,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!G3:G44,"完了",作業工数見積もり!E3:E44)</f>
+        <f>SUMIF(作業工数見積もり!G3:G45,"完了",作業工数見積もり!E3:E45)</f>
         <v>6</v>
       </c>
       <c r="D4" t="s">
@@ -2109,11 +2116,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4634146341463415E-2</v>
+        <v>1.4563106796116505E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -2131,7 +2138,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46176</v>
+        <v>46179</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -2152,11 +2159,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-379</v>
+        <v>-381</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.22691292875989447</v>
+        <v>-0.22572178477690288</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -2169,11 +2176,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-359</v>
+        <v>-361</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23955431754874651</v>
+        <v>-0.23822714681440443</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -2186,11 +2193,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-348</v>
+        <v>-350</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.2471264367816092</v>
+        <v>-0.24571428571428572</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2274,7 +2281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="69.625" style="10" bestFit="1" customWidth="1"/>
@@ -2361,11 +2368,11 @@
         <v>87</v>
       </c>
       <c r="K3" s="10">
-        <f>SUMIFS(E3:E61,G3:G61,"未着手")</f>
+        <f>SUMIFS(E3:E62,G3:G62,"未着手")</f>
         <v>80</v>
       </c>
       <c r="L3" s="10">
-        <f>SUM(F3:F61)</f>
+        <f>SUM(F3:F62)</f>
         <v>29</v>
       </c>
     </row>
@@ -2392,15 +2399,15 @@
         <v>28</v>
       </c>
       <c r="J4" s="29">
-        <f ca="1">SUMIF(D3:D59,I4,E3:E58)</f>
+        <f ca="1">SUMIF(D3:D60,I4,E3:E59)</f>
         <v>85.5</v>
       </c>
       <c r="K4" s="10">
-        <f>SUMIFS($E$3:$E$61,$G$3:$G$61,"未着手",$D$3:$D$61,I4)</f>
+        <f>SUMIFS($E$3:$E$62,$G$3:$G$62,"未着手",$D$3:$D$62,I4)</f>
         <v>78.5</v>
       </c>
       <c r="L4" s="10">
-        <f>SUMIFS(F3:F61,D3:D61,I4)</f>
+        <f>SUMIFS(F3:F62,D3:D62,I4)</f>
         <v>29</v>
       </c>
     </row>
@@ -2427,15 +2434,15 @@
         <v>0</v>
       </c>
       <c r="J5" s="29">
-        <f ca="1">SUMIF(D4:D61,I5,E4:E59)</f>
+        <f ca="1">SUMIF(D4:D62,I5,E4:E60)</f>
         <v>1.5</v>
       </c>
       <c r="K5" s="10">
-        <f>SUMIFS($E$3:$E$61,$G$3:$G$61,"未着手",$D$3:$D$61,I5)</f>
+        <f>SUMIFS($E$3:$E$62,$G$3:$G$62,"未着手",$D$3:$D$62,I5)</f>
         <v>1.5</v>
       </c>
       <c r="L5" s="10">
-        <f>SUMIFS(F4:F62,D4:D62,I5)</f>
+        <f>SUMIFS(F4:F63,D4:D63,I5)</f>
         <v>0</v>
       </c>
     </row>
@@ -2462,15 +2469,15 @@
         <v>29</v>
       </c>
       <c r="J6" s="29">
-        <f ca="1">SUMIF(D5:D62,I6,E5:E61)</f>
+        <f ca="1">SUMIF(D5:D63,I6,E5:E62)</f>
         <v>0</v>
       </c>
       <c r="K6" s="10">
-        <f>SUMIFS($E$3:$E$61,$G$3:$G$61,"未着手",$D$3:$D$61,I6)</f>
+        <f>SUMIFS($E$3:$E$62,$G$3:$G$62,"未着手",$D$3:$D$62,I6)</f>
         <v>0</v>
       </c>
       <c r="L6" s="10">
-        <f>SUMIFS(F5:F62,D5:D62,I6)</f>
+        <f>SUMIFS(F5:F63,D5:D63,I6)</f>
         <v>0</v>
       </c>
     </row>
@@ -2500,7 +2507,7 @@
         <v>71</v>
       </c>
       <c r="J7" s="10">
-        <f>COUNTIF(G3:G59,"作業中")</f>
+        <f>COUNTIF(G3:G60,"作業中")</f>
         <v>0</v>
       </c>
     </row>
@@ -2566,7 +2573,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>5</v>
@@ -2627,19 +2634,19 @@
     <row r="14" spans="1:12" outlineLevel="1">
       <c r="A14" s="19"/>
       <c r="B14" s="10" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:12" outlineLevel="1">
       <c r="A15" s="19"/>
       <c r="B15" s="10" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:12" outlineLevel="1">
       <c r="A16" s="19"/>
       <c r="B16" s="10" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2647,7 +2654,7 @@
         <v>45</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5</v>
@@ -2732,6 +2739,9 @@
       <c r="A21" s="19" t="s">
         <v>45</v>
       </c>
+      <c r="B21" s="10" t="s">
+        <v>180</v>
+      </c>
       <c r="C21" s="16" t="s">
         <v>5</v>
       </c>
@@ -2747,7 +2757,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>5</v>
@@ -2764,7 +2774,7 @@
         <v>45</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>5</v>
@@ -2779,29 +2789,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" outlineLevel="1">
+    <row r="24" spans="1:7" outlineLevel="1">
+      <c r="A24" s="19"/>
+      <c r="B24" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>90</v>
+      <c r="B25" s="39" t="s">
+        <v>95</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>5</v>
@@ -2809,19 +2808,16 @@
       <c r="D25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="16">
-        <v>24</v>
-      </c>
       <c r="G25" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" outlineLevel="1">
       <c r="A26" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="39" t="s">
-        <v>98</v>
+      <c r="B26" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>5</v>
@@ -2829,16 +2825,19 @@
       <c r="D26" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E26" s="16">
+        <v>24</v>
+      </c>
       <c r="G26" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:7" outlineLevel="1">
+    <row r="27" spans="1:7">
       <c r="A27" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>91</v>
+      <c r="B27" s="39" t="s">
+        <v>96</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>5</v>
@@ -2846,14 +2845,8 @@
       <c r="D27" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="16">
-        <v>1</v>
-      </c>
-      <c r="F27" s="16">
-        <v>1</v>
-      </c>
       <c r="G27" s="16" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:7" outlineLevel="1">
@@ -2861,7 +2854,7 @@
         <v>45</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>5</v>
@@ -2870,10 +2863,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="16">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F28" s="16">
+        <v>1</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:7" outlineLevel="1">
@@ -2881,7 +2877,7 @@
         <v>45</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>5</v>
@@ -2890,7 +2886,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>39</v>
@@ -2901,7 +2897,7 @@
         <v>45</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>5</v>
@@ -2916,12 +2912,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" outlineLevel="1">
       <c r="A31" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="39" t="s">
-        <v>97</v>
+      <c r="B31" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>5</v>
@@ -2929,17 +2925,18 @@
       <c r="D31" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E31" s="16">
+        <v>4</v>
+      </c>
       <c r="G31" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:7" outlineLevel="1">
+    <row r="32" spans="1:7">
       <c r="A32" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>99</v>
-      </c>
+      <c r="B32" s="39"/>
       <c r="C32" s="16" t="s">
         <v>5</v>
       </c>
@@ -2954,9 +2951,6 @@
       <c r="A33" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>103</v>
-      </c>
       <c r="C33" s="16" t="s">
         <v>5</v>
       </c>
@@ -2971,9 +2965,6 @@
       <c r="A34" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>101</v>
-      </c>
       <c r="C34" s="16" t="s">
         <v>5</v>
       </c>
@@ -2988,22 +2979,22 @@
       <c r="A35" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="39" t="s">
-        <v>143</v>
-      </c>
       <c r="C35" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="16" t="s">
         <v>18</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:7" outlineLevel="1">
       <c r="A36" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>146</v>
+      <c r="B36" s="39" t="s">
+        <v>138</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5</v>
@@ -3016,8 +3007,8 @@
       <c r="A37" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="39" t="s">
-        <v>144</v>
+      <c r="B37" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>5</v>
@@ -3030,8 +3021,8 @@
       <c r="A38" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>145</v>
+      <c r="B38" s="39" t="s">
+        <v>139</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>5</v>
@@ -3040,27 +3031,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" outlineLevel="1">
       <c r="A39" s="19" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D39" s="16" t="s">
         <v>18</v>
-      </c>
-      <c r="E39" s="16">
-        <v>1</v>
-      </c>
-      <c r="F39" s="16">
-        <v>4</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3068,7 +3050,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>5</v>
@@ -3077,10 +3059,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>39</v>
@@ -3091,7 +3073,7 @@
         <v>45</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>5</v>
@@ -3103,7 +3085,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>39</v>
@@ -3114,7 +3096,7 @@
         <v>45</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>5</v>
@@ -3123,7 +3105,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F42" s="16">
         <v>3</v>
@@ -3133,17 +3115,23 @@
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="20" t="s">
-        <v>49</v>
+      <c r="A43" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>18</v>
+      </c>
+      <c r="E43" s="16">
+        <v>8</v>
+      </c>
+      <c r="F43" s="16">
+        <v>3</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>39</v>
@@ -3153,20 +3141,14 @@
       <c r="A44" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="39" t="s">
-        <v>105</v>
+      <c r="B44" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>18</v>
-      </c>
-      <c r="E44" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="F44" s="16">
-        <v>0.5</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>39</v>
@@ -3176,8 +3158,8 @@
       <c r="A45" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>43</v>
+      <c r="B45" s="39" t="s">
+        <v>100</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>5</v>
@@ -3199,14 +3181,20 @@
       <c r="A46" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="39" t="s">
-        <v>94</v>
+      <c r="B46" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D46" s="16" t="s">
         <v>18</v>
+      </c>
+      <c r="E46" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F46" s="16">
+        <v>0.5</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>39</v>
@@ -3216,8 +3204,8 @@
       <c r="A47" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>92</v>
+      <c r="B47" s="39" t="s">
+        <v>93</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>5</v>
@@ -3233,8 +3221,8 @@
       <c r="A48" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="39" t="s">
-        <v>106</v>
+      <c r="B48" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>5</v>
@@ -3250,8 +3238,8 @@
       <c r="A49" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>107</v>
+      <c r="B49" s="39" t="s">
+        <v>101</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>5</v>
@@ -3267,8 +3255,8 @@
       <c r="A50" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="39" t="s">
-        <v>108</v>
+      <c r="B50" s="10" t="s">
+        <v>102</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>5</v>
@@ -3284,17 +3272,14 @@
       <c r="A51" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>55</v>
+      <c r="B51" s="39" t="s">
+        <v>103</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D51" s="16" t="s">
         <v>18</v>
-      </c>
-      <c r="E51" s="16">
-        <v>2</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>39</v>
@@ -3304,14 +3289,17 @@
       <c r="A52" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B52" s="39" t="s">
-        <v>109</v>
+      <c r="B52" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D52" s="16" t="s">
         <v>18</v>
+      </c>
+      <c r="E52" s="16">
+        <v>2</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>39</v>
@@ -3321,8 +3309,8 @@
       <c r="A53" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="10" t="s">
-        <v>110</v>
+      <c r="B53" s="39" t="s">
+        <v>104</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>5</v>
@@ -3339,30 +3327,24 @@
         <v>49</v>
       </c>
       <c r="B54" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B55" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="16">
-        <v>1</v>
-      </c>
-      <c r="F54" s="16">
-        <v>3</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="C55" s="16" t="s">
         <v>5</v>
@@ -3374,10 +3356,10 @@
         <v>1</v>
       </c>
       <c r="F55" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3385,7 +3367,7 @@
         <v>40</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>5</v>
@@ -3394,10 +3376,13 @@
         <v>18</v>
       </c>
       <c r="E56" s="16">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="F56" s="16">
+        <v>1</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3405,7 +3390,7 @@
         <v>40</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>5</v>
@@ -3414,7 +3399,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>39</v>
@@ -3425,33 +3410,36 @@
         <v>40</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="16">
+        <v>6</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" s="16">
+      <c r="C59" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="16">
         <v>3</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>18</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>39</v>
@@ -3462,7 +3450,7 @@
         <v>41</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>5</v>
@@ -3475,48 +3463,45 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C61" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="10" t="s">
+      <c r="C62" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G62" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>52</v>
-      </c>
       <c r="C63" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>18</v>
-      </c>
-      <c r="E63" s="16">
-        <v>3</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>39</v>
@@ -3527,7 +3512,7 @@
         <v>38</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>5</v>
@@ -3536,10 +3521,7 @@
         <v>18</v>
       </c>
       <c r="E64" s="16">
-        <v>2</v>
-      </c>
-      <c r="F64" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64" s="16" t="s">
         <v>39</v>
@@ -3550,13 +3532,19 @@
         <v>38</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D65" s="16" t="s">
         <v>18</v>
+      </c>
+      <c r="E65" s="16">
+        <v>2</v>
+      </c>
+      <c r="F65" s="16">
+        <v>1</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>39</v>
@@ -3567,7 +3555,7 @@
         <v>38</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>5</v>
@@ -3584,7 +3572,7 @@
         <v>38</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>5</v>
@@ -3601,7 +3589,7 @@
         <v>38</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>5</v>
@@ -3618,7 +3606,7 @@
         <v>38</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>5</v>
@@ -3635,7 +3623,7 @@
         <v>38</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>5</v>
@@ -3647,21 +3635,38 @@
         <v>39</v>
       </c>
     </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:G62" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G58">
-      <sortCondition ref="B2:B58"/>
+  <autoFilter ref="B2:G63" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G59">
+      <sortCondition ref="B2:B59"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C70" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C71" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D70" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D71" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G70" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G71" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3671,6 +3676,623 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C830D07-33E0-4A6A-A9E3-4F29F77EDCE6}">
+  <dimension ref="C2:P37"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="3:16">
+      <c r="O2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="3:16">
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="3:16">
+      <c r="C4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11">
+        <v>2</v>
+      </c>
+      <c r="M5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16">
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="D6" s="10">
+        <v>4</v>
+      </c>
+      <c r="E6" s="10">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10">
+        <v>6</v>
+      </c>
+      <c r="G6" s="10">
+        <v>7</v>
+      </c>
+      <c r="H6" s="10">
+        <v>8</v>
+      </c>
+      <c r="I6" s="11">
+        <v>9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="31"/>
+      <c r="M6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16">
+      <c r="C7" s="10">
+        <v>10</v>
+      </c>
+      <c r="D7" s="10">
+        <v>11</v>
+      </c>
+      <c r="E7" s="10">
+        <v>12</v>
+      </c>
+      <c r="F7" s="10">
+        <v>13</v>
+      </c>
+      <c r="G7" s="10">
+        <v>14</v>
+      </c>
+      <c r="H7" s="10">
+        <v>15</v>
+      </c>
+      <c r="I7" s="11">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L7" s="33"/>
+      <c r="M7">
+        <v>24</v>
+      </c>
+      <c r="P7">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16">
+      <c r="C8" s="10">
+        <v>17</v>
+      </c>
+      <c r="D8" s="10">
+        <v>18</v>
+      </c>
+      <c r="E8" s="10">
+        <v>19</v>
+      </c>
+      <c r="F8" s="10">
+        <v>20</v>
+      </c>
+      <c r="G8" s="10">
+        <v>21</v>
+      </c>
+      <c r="H8" s="38">
+        <v>22</v>
+      </c>
+      <c r="I8" s="11">
+        <v>23</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="37"/>
+      <c r="M8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16">
+      <c r="C9" s="10">
+        <v>24</v>
+      </c>
+      <c r="D9" s="10">
+        <v>25</v>
+      </c>
+      <c r="E9" s="10">
+        <v>26</v>
+      </c>
+      <c r="F9" s="10">
+        <v>27</v>
+      </c>
+      <c r="G9" s="10">
+        <v>28</v>
+      </c>
+      <c r="H9" s="10">
+        <v>29</v>
+      </c>
+      <c r="I9" s="11">
+        <v>30</v>
+      </c>
+      <c r="K9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="34"/>
+      <c r="M9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="3:16">
+      <c r="C10" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="3:16">
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="3:16">
+      <c r="C13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="3:16">
+      <c r="C14" s="10"/>
+      <c r="D14" s="10">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10">
+        <v>2</v>
+      </c>
+      <c r="F14" s="10">
+        <v>3</v>
+      </c>
+      <c r="G14" s="10">
+        <v>4</v>
+      </c>
+      <c r="H14" s="10">
+        <v>5</v>
+      </c>
+      <c r="I14" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="3:16">
+      <c r="C15" s="10">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10">
+        <v>8</v>
+      </c>
+      <c r="E15" s="10">
+        <v>9</v>
+      </c>
+      <c r="F15" s="10">
+        <v>10</v>
+      </c>
+      <c r="G15" s="30">
+        <v>11</v>
+      </c>
+      <c r="H15" s="31">
+        <v>12</v>
+      </c>
+      <c r="I15" s="31">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="3:16">
+      <c r="C16" s="31">
+        <v>14</v>
+      </c>
+      <c r="D16" s="31">
+        <v>15</v>
+      </c>
+      <c r="E16" s="31">
+        <v>16</v>
+      </c>
+      <c r="F16" s="31">
+        <v>17</v>
+      </c>
+      <c r="G16" s="31">
+        <v>18</v>
+      </c>
+      <c r="H16" s="31">
+        <v>19</v>
+      </c>
+      <c r="I16" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11">
+      <c r="C17" s="31">
+        <v>21</v>
+      </c>
+      <c r="D17" s="31">
+        <v>22</v>
+      </c>
+      <c r="E17" s="31">
+        <v>23</v>
+      </c>
+      <c r="F17" s="31">
+        <v>24</v>
+      </c>
+      <c r="G17" s="31">
+        <v>25</v>
+      </c>
+      <c r="H17" s="31">
+        <v>26</v>
+      </c>
+      <c r="I17" s="31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11">
+      <c r="C18" s="31">
+        <v>28</v>
+      </c>
+      <c r="D18" s="31">
+        <v>29</v>
+      </c>
+      <c r="E18" s="31">
+        <v>30</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="K18">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="3:11">
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11">
+      <c r="C21" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11">
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="31">
+        <v>1</v>
+      </c>
+      <c r="G22" s="31">
+        <v>2</v>
+      </c>
+      <c r="H22" s="31">
+        <v>3</v>
+      </c>
+      <c r="I22" s="31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11">
+      <c r="C23" s="31">
+        <v>5</v>
+      </c>
+      <c r="D23" s="31">
+        <v>6</v>
+      </c>
+      <c r="E23" s="19">
+        <v>7</v>
+      </c>
+      <c r="F23" s="19">
+        <v>8</v>
+      </c>
+      <c r="G23" s="19">
+        <v>9</v>
+      </c>
+      <c r="H23" s="19">
+        <v>10</v>
+      </c>
+      <c r="I23" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11">
+      <c r="C24" s="19">
+        <v>12</v>
+      </c>
+      <c r="D24" s="19">
+        <v>13</v>
+      </c>
+      <c r="E24" s="19">
+        <v>14</v>
+      </c>
+      <c r="F24" s="19">
+        <v>15</v>
+      </c>
+      <c r="G24" s="19">
+        <v>16</v>
+      </c>
+      <c r="H24" s="19">
+        <v>17</v>
+      </c>
+      <c r="I24" s="19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11">
+      <c r="C25" s="19">
+        <v>19</v>
+      </c>
+      <c r="D25" s="19">
+        <v>20</v>
+      </c>
+      <c r="E25" s="19">
+        <v>21</v>
+      </c>
+      <c r="F25" s="19">
+        <v>22</v>
+      </c>
+      <c r="G25" s="19">
+        <v>23</v>
+      </c>
+      <c r="H25" s="19">
+        <v>24</v>
+      </c>
+      <c r="I25" s="19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11">
+      <c r="C26" s="19">
+        <v>26</v>
+      </c>
+      <c r="D26" s="19">
+        <v>27</v>
+      </c>
+      <c r="E26" s="19">
+        <v>28</v>
+      </c>
+      <c r="F26" s="19">
+        <v>29</v>
+      </c>
+      <c r="G26" s="19">
+        <v>30</v>
+      </c>
+      <c r="H26" s="19">
+        <v>31</v>
+      </c>
+      <c r="I26" s="11"/>
+      <c r="K26">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11">
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11">
+      <c r="C31" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11">
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="19">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9">
+      <c r="C33" s="19">
+        <v>2</v>
+      </c>
+      <c r="D33" s="37">
+        <v>3</v>
+      </c>
+      <c r="E33" s="37">
+        <v>4</v>
+      </c>
+      <c r="F33" s="37">
+        <v>5</v>
+      </c>
+      <c r="G33" s="37">
+        <v>6</v>
+      </c>
+      <c r="H33" s="37">
+        <v>7</v>
+      </c>
+      <c r="I33" s="37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9">
+      <c r="C34" s="37">
+        <v>9</v>
+      </c>
+      <c r="D34" s="37">
+        <v>10</v>
+      </c>
+      <c r="E34" s="37">
+        <v>11</v>
+      </c>
+      <c r="F34" s="37">
+        <v>12</v>
+      </c>
+      <c r="G34" s="37">
+        <v>13</v>
+      </c>
+      <c r="H34" s="37">
+        <v>14</v>
+      </c>
+      <c r="I34" s="37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9">
+      <c r="C35" s="37">
+        <v>16</v>
+      </c>
+      <c r="D35" s="37">
+        <v>17</v>
+      </c>
+      <c r="E35" s="37">
+        <v>18</v>
+      </c>
+      <c r="F35" s="37">
+        <v>19</v>
+      </c>
+      <c r="G35" s="37">
+        <v>20</v>
+      </c>
+      <c r="H35" s="37">
+        <v>21</v>
+      </c>
+      <c r="I35" s="37">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9">
+      <c r="C36" s="37">
+        <v>23</v>
+      </c>
+      <c r="D36" s="37">
+        <v>24</v>
+      </c>
+      <c r="E36" s="37">
+        <v>25</v>
+      </c>
+      <c r="F36" s="37">
+        <v>26</v>
+      </c>
+      <c r="G36" s="37">
+        <v>27</v>
+      </c>
+      <c r="H36" s="34">
+        <v>28</v>
+      </c>
+      <c r="I36" s="34">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9">
+      <c r="C37" s="34">
+        <v>30</v>
+      </c>
+      <c r="D37" s="34">
+        <v>31</v>
+      </c>
+      <c r="E37" s="36">
+        <v>1</v>
+      </c>
+      <c r="F37" s="36">
+        <v>2</v>
+      </c>
+      <c r="G37" s="36">
+        <v>3</v>
+      </c>
+      <c r="H37" s="35">
+        <v>4</v>
+      </c>
+      <c r="I37" s="32"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3682,13 +4304,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3696,10 +4318,10 @@
         <v>46166</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3707,21 +4329,21 @@
         <v>46167</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="C5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3730,7 +4352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
   <dimension ref="B2:D14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3743,674 +4365,57 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="D3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="B7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" t="s">
-        <v>154</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C830D07-33E0-4A6A-A9E3-4F29F77EDCE6}">
-  <dimension ref="C2:P37"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="2" spans="3:16">
-      <c r="O2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="3:16">
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="3:16">
-      <c r="C4" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="3:16">
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11">
-        <v>1</v>
-      </c>
-      <c r="I5" s="11">
-        <v>2</v>
-      </c>
-      <c r="M5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="3:16">
-      <c r="C6" s="10">
-        <v>3</v>
-      </c>
-      <c r="D6" s="10">
-        <v>4</v>
-      </c>
-      <c r="E6" s="10">
-        <v>5</v>
-      </c>
-      <c r="F6" s="10">
-        <v>6</v>
-      </c>
-      <c r="G6" s="10">
-        <v>7</v>
-      </c>
-      <c r="H6" s="10">
-        <v>8</v>
-      </c>
-      <c r="I6" s="11">
-        <v>9</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="31"/>
-      <c r="M6">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="3:16">
-      <c r="C7" s="10">
-        <v>10</v>
-      </c>
-      <c r="D7" s="10">
-        <v>11</v>
-      </c>
-      <c r="E7" s="10">
-        <v>12</v>
-      </c>
-      <c r="F7" s="10">
-        <v>13</v>
-      </c>
-      <c r="G7" s="10">
-        <v>14</v>
-      </c>
-      <c r="H7" s="10">
-        <v>15</v>
-      </c>
-      <c r="I7" s="11">
-        <v>16</v>
-      </c>
-      <c r="K7" t="s">
-        <v>0</v>
-      </c>
-      <c r="L7" s="33"/>
-      <c r="M7">
-        <v>24</v>
-      </c>
-      <c r="P7">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="3:16">
-      <c r="C8" s="10">
-        <v>17</v>
-      </c>
-      <c r="D8" s="10">
-        <v>18</v>
-      </c>
-      <c r="E8" s="10">
-        <v>19</v>
-      </c>
-      <c r="F8" s="10">
-        <v>20</v>
-      </c>
-      <c r="G8" s="10">
-        <v>21</v>
-      </c>
-      <c r="H8" s="38">
-        <v>22</v>
-      </c>
-      <c r="I8" s="11">
-        <v>23</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="37"/>
-      <c r="M8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="3:16">
-      <c r="C9" s="10">
-        <v>24</v>
-      </c>
-      <c r="D9" s="10">
-        <v>25</v>
-      </c>
-      <c r="E9" s="10">
-        <v>26</v>
-      </c>
-      <c r="F9" s="10">
-        <v>27</v>
-      </c>
-      <c r="G9" s="10">
-        <v>28</v>
-      </c>
-      <c r="H9" s="10">
-        <v>29</v>
-      </c>
-      <c r="I9" s="11">
-        <v>30</v>
-      </c>
-      <c r="K9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L9" s="34"/>
-      <c r="M9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="3:16">
-      <c r="C10" s="11">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="3:16">
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="3:16">
-      <c r="C13" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="3:16">
-      <c r="C14" s="10"/>
-      <c r="D14" s="10">
-        <v>1</v>
-      </c>
-      <c r="E14" s="10">
-        <v>2</v>
-      </c>
-      <c r="F14" s="10">
-        <v>3</v>
-      </c>
-      <c r="G14" s="10">
-        <v>4</v>
-      </c>
-      <c r="H14" s="10">
-        <v>5</v>
-      </c>
-      <c r="I14" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="3:16">
-      <c r="C15" s="10">
-        <v>7</v>
-      </c>
-      <c r="D15" s="10">
-        <v>8</v>
-      </c>
-      <c r="E15" s="10">
-        <v>9</v>
-      </c>
-      <c r="F15" s="10">
-        <v>10</v>
-      </c>
-      <c r="G15" s="30">
-        <v>11</v>
-      </c>
-      <c r="H15" s="31">
-        <v>12</v>
-      </c>
-      <c r="I15" s="31">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="3:16">
-      <c r="C16" s="31">
-        <v>14</v>
-      </c>
-      <c r="D16" s="31">
-        <v>15</v>
-      </c>
-      <c r="E16" s="31">
-        <v>16</v>
-      </c>
-      <c r="F16" s="31">
-        <v>17</v>
-      </c>
-      <c r="G16" s="31">
-        <v>18</v>
-      </c>
-      <c r="H16" s="31">
-        <v>19</v>
-      </c>
-      <c r="I16" s="31">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="3:11">
-      <c r="C17" s="31">
-        <v>21</v>
-      </c>
-      <c r="D17" s="31">
-        <v>22</v>
-      </c>
-      <c r="E17" s="31">
-        <v>23</v>
-      </c>
-      <c r="F17" s="31">
-        <v>24</v>
-      </c>
-      <c r="G17" s="31">
-        <v>25</v>
-      </c>
-      <c r="H17" s="31">
-        <v>26</v>
-      </c>
-      <c r="I17" s="31">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11">
-      <c r="C18" s="31">
-        <v>28</v>
-      </c>
-      <c r="D18" s="31">
-        <v>29</v>
-      </c>
-      <c r="E18" s="31">
-        <v>30</v>
-      </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="K18">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="3:11">
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11">
-      <c r="C21" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11">
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="31">
-        <v>1</v>
-      </c>
-      <c r="G22" s="31">
-        <v>2</v>
-      </c>
-      <c r="H22" s="31">
-        <v>3</v>
-      </c>
-      <c r="I22" s="31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11">
-      <c r="C23" s="31">
-        <v>5</v>
-      </c>
-      <c r="D23" s="31">
-        <v>6</v>
-      </c>
-      <c r="E23" s="19">
-        <v>7</v>
-      </c>
-      <c r="F23" s="19">
-        <v>8</v>
-      </c>
-      <c r="G23" s="19">
-        <v>9</v>
-      </c>
-      <c r="H23" s="19">
-        <v>10</v>
-      </c>
-      <c r="I23" s="19">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11">
-      <c r="C24" s="19">
-        <v>12</v>
-      </c>
-      <c r="D24" s="19">
-        <v>13</v>
-      </c>
-      <c r="E24" s="19">
-        <v>14</v>
-      </c>
-      <c r="F24" s="19">
-        <v>15</v>
-      </c>
-      <c r="G24" s="19">
-        <v>16</v>
-      </c>
-      <c r="H24" s="19">
-        <v>17</v>
-      </c>
-      <c r="I24" s="19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11">
-      <c r="C25" s="19">
-        <v>19</v>
-      </c>
-      <c r="D25" s="19">
-        <v>20</v>
-      </c>
-      <c r="E25" s="19">
-        <v>21</v>
-      </c>
-      <c r="F25" s="19">
-        <v>22</v>
-      </c>
-      <c r="G25" s="19">
-        <v>23</v>
-      </c>
-      <c r="H25" s="19">
-        <v>24</v>
-      </c>
-      <c r="I25" s="19">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="3:11">
-      <c r="C26" s="19">
-        <v>26</v>
-      </c>
-      <c r="D26" s="19">
-        <v>27</v>
-      </c>
-      <c r="E26" s="19">
-        <v>28</v>
-      </c>
-      <c r="F26" s="19">
-        <v>29</v>
-      </c>
-      <c r="G26" s="19">
-        <v>30</v>
-      </c>
-      <c r="H26" s="19">
-        <v>31</v>
-      </c>
-      <c r="I26" s="11"/>
-      <c r="K26">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11">
-      <c r="C30" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="3:11">
-      <c r="C31" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="3:11">
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="19">
-        <v>1</v>
-      </c>
-      <c r="K32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9">
-      <c r="C33" s="19">
-        <v>2</v>
-      </c>
-      <c r="D33" s="37">
-        <v>3</v>
-      </c>
-      <c r="E33" s="37">
-        <v>4</v>
-      </c>
-      <c r="F33" s="37">
-        <v>5</v>
-      </c>
-      <c r="G33" s="37">
-        <v>6</v>
-      </c>
-      <c r="H33" s="37">
-        <v>7</v>
-      </c>
-      <c r="I33" s="37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9">
-      <c r="C34" s="37">
-        <v>9</v>
-      </c>
-      <c r="D34" s="37">
-        <v>10</v>
-      </c>
-      <c r="E34" s="37">
-        <v>11</v>
-      </c>
-      <c r="F34" s="37">
-        <v>12</v>
-      </c>
-      <c r="G34" s="37">
-        <v>13</v>
-      </c>
-      <c r="H34" s="37">
-        <v>14</v>
-      </c>
-      <c r="I34" s="37">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="3:9">
-      <c r="C35" s="37">
-        <v>16</v>
-      </c>
-      <c r="D35" s="37">
-        <v>17</v>
-      </c>
-      <c r="E35" s="37">
-        <v>18</v>
-      </c>
-      <c r="F35" s="37">
-        <v>19</v>
-      </c>
-      <c r="G35" s="37">
-        <v>20</v>
-      </c>
-      <c r="H35" s="37">
-        <v>21</v>
-      </c>
-      <c r="I35" s="37">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9">
-      <c r="C36" s="37">
-        <v>23</v>
-      </c>
-      <c r="D36" s="37">
-        <v>24</v>
-      </c>
-      <c r="E36" s="37">
-        <v>25</v>
-      </c>
-      <c r="F36" s="37">
-        <v>26</v>
-      </c>
-      <c r="G36" s="37">
-        <v>27</v>
-      </c>
-      <c r="H36" s="34">
-        <v>28</v>
-      </c>
-      <c r="I36" s="34">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="3:9">
-      <c r="C37" s="34">
-        <v>30</v>
-      </c>
-      <c r="D37" s="34">
-        <v>31</v>
-      </c>
-      <c r="E37" s="36">
-        <v>1</v>
-      </c>
-      <c r="F37" s="36">
-        <v>2</v>
-      </c>
-      <c r="G37" s="36">
-        <v>3</v>
-      </c>
-      <c r="H37" s="35">
-        <v>4</v>
-      </c>
-      <c r="I37" s="32"/>
+        <v>149</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4425,48 +4430,48 @@
   <sheetData>
     <row r="2" spans="3:10">
       <c r="C2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="3:10">
       <c r="C3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="3:10">
       <c r="C4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="3:10">
       <c r="C5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="3:10">
       <c r="C6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="3:10">
       <c r="C7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="3:10">
       <c r="C10" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="3:10">
       <c r="C11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -4482,77 +4487,77 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="M1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="T1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="B2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="B3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="M3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="R3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="B4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="M4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="B5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="B6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="B7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="R7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="B8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="M9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -4562,42 +4567,42 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D14" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="D15" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F17" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4618,6 +4623,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -4852,15 +4866,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
@@ -4873,6 +4878,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4889,12 +4902,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF97DD0-8280-4EE6-A0E4-A1FD6293C1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A915D8B-5794-400D-9694-14D27089741E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="メモ" sheetId="9" r:id="rId5"/>
     <sheet name="雑用" sheetId="10" r:id="rId6"/>
     <sheet name="仕様書" sheetId="13" r:id="rId7"/>
+    <sheet name="クラス設計" sheetId="14" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$63</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="184">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -1480,6 +1481,16 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>レンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃仕様</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1817,6 +1828,418 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9976968F-90B1-9BAB-F8D7-355380CE457D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1504949" y="533400"/>
+          <a:ext cx="6276976" cy="2352675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>AttackBase</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>当たった敵のリスト</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>(Collidable)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>攻撃のノックバック距離、攻撃力←プレイヤーの</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>AttackData</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>から渡す、敵もどっかから渡す</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>生存時間などは迷い</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{955567FC-79AE-9F46-5366-81F2ADE8CAEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1095375" y="3724275"/>
+          <a:ext cx="1971675" cy="1952625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>PlayerAttack</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>具体的なデータをもらう</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>生存時間をきめる</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>195263</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>242887</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A033F718-35BA-3752-3F6E-75AFBC861E49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2081213" y="2886075"/>
+          <a:ext cx="2562224" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2543105A-5D70-964E-0AD0-C2362A7E31F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5848350" y="3705225"/>
+          <a:ext cx="1971675" cy="1952625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>EnemyAttack</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>具体的なデータをもらう</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>生存時間をもらう</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>242887</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>233363</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA140AA9-2668-66D5-D88F-CBF290BF3D79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4643437" y="2886075"/>
+          <a:ext cx="2190751" cy="819150"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2116,11 +2539,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4563106796116505E-2</v>
+        <v>1.4457831325301205E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -2138,7 +2561,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46179</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -2159,11 +2582,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-381</v>
+        <v>-384</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.22572178477690288</v>
+        <v>-0.22395833333333334</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -2176,11 +2599,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-361</v>
+        <v>-364</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23822714681440443</v>
+        <v>-0.23626373626373626</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -2193,11 +2616,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-350</v>
+        <v>-353</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.24571428571428572</v>
+        <v>-0.24362606232294617</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4611,6 +5034,23 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B1947F-A3A0-4027-965D-A484FB7F3C32}">
+  <dimension ref="C2"/>
+  <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="3:3">
+      <c r="C2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4623,15 +5063,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -4866,6 +5297,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
@@ -4878,14 +5318,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4902,4 +5334,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A915D8B-5794-400D-9694-14D27089741E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8340002A-AA44-4D8F-8F05-97C8D48338F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="199">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -1491,6 +1491,141 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル技</t>
+    <rPh sb="3" eb="4">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弱連携 2技</t>
+    <rPh sb="0" eb="1">
+      <t>ジャク</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強化状態</t>
+    <rPh sb="0" eb="1">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ため技で演出あり</t>
+    <rPh sb="2" eb="3">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>連携技でするかは考え中</t>
+    <rPh sb="0" eb="2">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>溜めモードはするか悩み</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弱の横一閃</t>
+    <rPh sb="0" eb="1">
+      <t>ジャク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イッセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X,X,X,X,X</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X,X,X,Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X,X,Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X,Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中で敵がいなかったら敵の方向に追従する</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ツイジュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2165,7 +2300,7 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>生存時間をもらう</a:t>
+            <a:t>生存時間をきめるスキル技</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
         </a:p>
@@ -2539,11 +2674,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4457831325301205E-2</v>
+        <v>1.4423076923076924E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -2561,7 +2696,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46183</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -2582,11 +2717,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-384</v>
+        <v>-385</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.22395833333333334</v>
+        <v>-0.22337662337662337</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -2599,11 +2734,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-364</v>
+        <v>-365</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23626373626373626</v>
+        <v>-0.23561643835616439</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -2616,11 +2751,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-353</v>
+        <v>-354</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.24362606232294617</v>
+        <v>-0.24293785310734464</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4905,26 +5040,32 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:AE21"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:31">
       <c r="M1" t="s">
         <v>161</v>
       </c>
       <c r="T1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="AE1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="B2" t="s">
         <v>156</v>
       </c>
       <c r="M2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="AE2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="B3" t="s">
         <v>157</v>
       </c>
@@ -4934,32 +5075,44 @@
       <c r="R3" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="AE3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
       <c r="B4" t="s">
         <v>158</v>
       </c>
       <c r="M4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="AE4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
       <c r="B5" t="s">
         <v>91</v>
       </c>
       <c r="M5" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="AE5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
       <c r="B6" t="s">
         <v>159</v>
       </c>
       <c r="M6" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="AE6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
       <c r="B7" t="s">
         <v>160</v>
       </c>
@@ -4969,8 +5122,11 @@
       <c r="R7" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="AE7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
       <c r="B8" t="s">
         <v>97</v>
       </c>
@@ -4978,17 +5134,30 @@
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:31">
       <c r="M9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="11" spans="1:31">
+      <c r="M11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
+      <c r="M12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
       <c r="B13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="M13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
         <v>170</v>
       </c>
@@ -4999,28 +5168,47 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:31">
       <c r="D15" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="17" spans="2:6">
+      <c r="M15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
+      <c r="M16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
       <c r="B17" t="s">
         <v>173</v>
       </c>
       <c r="F17" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="19" spans="2:6">
+      <c r="M17" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="M18" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
       <c r="B19" t="s">
         <v>176</v>
       </c>
       <c r="D19" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="21" spans="2:6">
+      <c r="M19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
       <c r="B21" t="s">
         <v>175</v>
       </c>
@@ -5052,17 +5240,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -5297,6 +5474,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5307,17 +5495,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5336,6 +5513,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8340002A-AA44-4D8F-8F05-97C8D48338F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7297A491-8689-45B1-8E52-252721E6C9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="2715" windowWidth="24810" windowHeight="17430" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="202">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -1626,6 +1626,21 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ツイジュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TODO:NEXT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプをする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ攻撃をする</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4912,7 +4927,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:D14"/>
+  <dimension ref="B2:D19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -4973,6 +4988,21 @@
     <row r="14" spans="2:4">
       <c r="B14" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -5240,6 +5270,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -5474,17 +5515,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5495,6 +5525,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5513,17 +5554,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7297A491-8689-45B1-8E52-252721E6C9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB092137-F1CE-4F72-9070-1C275D7F5FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="2715" windowWidth="24810" windowHeight="17430" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="212">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -1316,19 +1316,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>空中攻撃5段</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>空中強攻撃1段</t>
     <rPh sb="0" eb="2">
       <t>クウチュウ</t>
@@ -1390,13 +1377,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>放題</t>
-    <rPh sb="0" eb="2">
-      <t>ホウダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ちょっと強い敵</t>
     <rPh sb="4" eb="5">
       <t>ツヨ</t>
@@ -1591,10 +1571,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>X,X,X,X,X</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>X,X,X,Y</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1634,13 +1610,137 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジャンプをする</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ジャンプ攻撃をする</t>
     <rPh sb="4" eb="6">
       <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ攻撃のコンボノードを作る</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【血殺について】</t>
+    <rPh sb="1" eb="2">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レンダリングを分けてシェーダーする</t>
+    <rPh sb="7" eb="8">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①背景</t>
+    <rPh sb="1" eb="3">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②文字を描画</t>
+    <rPh sb="0" eb="3">
+      <t>2モジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ビョウガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③キャラクターを表示</t>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※エフェクトは白色に表示</t>
+    <rPh sb="7" eb="9">
+      <t>シロイロ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dxLibをForEffeckseerにしないといけない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中攻撃4段</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X,X,X,X</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いずなおとし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>砲台</t>
+    <rPh sb="0" eb="2">
+      <t>ホウダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中で攻撃を行ったら、カメラが前に近づく</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>チカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃を行ったら、カメラが斜め方向になる</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホウコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2689,11 +2789,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4423076923076924E-2</v>
+        <v>1.4388489208633094E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -2711,7 +2811,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -2732,11 +2832,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-385</v>
+        <v>-386</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.22337662337662337</v>
+        <v>-0.22279792746113988</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -2749,11 +2849,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-365</v>
+        <v>-366</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23561643835616439</v>
+        <v>-0.23497267759562843</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -2766,11 +2866,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-354</v>
+        <v>-355</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.24293785310734464</v>
+        <v>-0.24225352112676057</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -3313,7 +3413,7 @@
         <v>45</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>5</v>
@@ -3347,7 +3447,7 @@
         <v>45</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>5</v>
@@ -3365,7 +3465,7 @@
     <row r="24" spans="1:7" outlineLevel="1">
       <c r="A24" s="19"/>
       <c r="B24" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4927,7 +5027,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:D19"/>
+  <dimension ref="B2:D20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -4974,35 +5074,62 @@
       <c r="B10" t="s">
         <v>146</v>
       </c>
+      <c r="D10" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" t="s">
         <v>147</v>
       </c>
+      <c r="D11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="D12" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" t="s">
         <v>148</v>
       </c>
+      <c r="D13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" t="s">
         <v>149</v>
       </c>
+      <c r="D14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="D15" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>201</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -5070,21 +5197,21 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
-  <dimension ref="A1:AE21"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:33">
       <c r="M1" t="s">
         <v>161</v>
       </c>
       <c r="T1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AE1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33">
       <c r="B2" t="s">
         <v>156</v>
       </c>
@@ -5092,10 +5219,10 @@
         <v>162</v>
       </c>
       <c r="AE2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="B3" t="s">
         <v>157</v>
       </c>
@@ -5103,147 +5230,158 @@
         <v>163</v>
       </c>
       <c r="R3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AE3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31">
+        <v>191</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="B4" t="s">
         <v>158</v>
       </c>
       <c r="M4" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="AE4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="B5" t="s">
         <v>91</v>
       </c>
       <c r="M5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="B6" t="s">
         <v>159</v>
       </c>
       <c r="M6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="B7" t="s">
         <v>160</v>
       </c>
       <c r="M7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AE7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="B8" t="s">
         <v>97</v>
       </c>
       <c r="M8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="M9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="10" spans="1:33">
+      <c r="AE10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="M11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="M12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31">
+        <v>183</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="B13" t="s">
         <v>49</v>
       </c>
       <c r="M13" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" t="s">
         <v>170</v>
       </c>
-      <c r="B14" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31">
+    </row>
+    <row r="15" spans="1:33">
       <c r="D15" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="M15" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="M16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="M18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -5259,7 +5397,7 @@
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -5270,17 +5408,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -5515,6 +5642,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5525,17 +5663,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5554,6 +5681,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB092137-F1CE-4F72-9070-1C275D7F5FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFB8AA6-37C7-4E12-873C-C0C48F93FEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="2715" windowWidth="24810" windowHeight="17430" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -1346,16 +1346,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>もう一つ不明</t>
-    <rPh sb="2" eb="3">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>フメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2種</t>
     <rPh sb="1" eb="2">
       <t>シュ</t>
@@ -1408,16 +1398,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2段目切り上げ</t>
-    <rPh sb="1" eb="4">
-      <t>ダンメキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>X,Y,X,X,X,Y</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1610,23 +1590,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジャンプ攻撃をする</t>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャンプ攻撃のコンボノードを作る</t>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【血殺について】</t>
     <rPh sb="1" eb="2">
       <t>チ</t>
@@ -1741,6 +1704,79 @@
     </rPh>
     <rPh sb="14" eb="16">
       <t>ホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本的に弱攻撃からの強攻撃は空中攻撃を派生</t>
+    <rPh sb="0" eb="3">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジャクコウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2段目、3段目、4段目時切り上げ</t>
+    <rPh sb="1" eb="3">
+      <t>ダンメ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ダンメ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ダンメ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ攻撃の中身の実装</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ナカミ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ攻撃用にカメラを上対応にする</t>
+    <rPh sb="4" eb="5">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ウエタイオウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2811,7 +2847,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -3413,7 +3449,7 @@
         <v>45</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>5</v>
@@ -3447,7 +3483,7 @@
         <v>45</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>5</v>
@@ -3465,7 +3501,7 @@
     <row r="24" spans="1:7" outlineLevel="1">
       <c r="A24" s="19"/>
       <c r="B24" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5075,7 +5111,7 @@
         <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="2:4">
@@ -5083,12 +5119,12 @@
         <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="2:4">
@@ -5096,7 +5132,7 @@
         <v>148</v>
       </c>
       <c r="D13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="2:4">
@@ -5104,32 +5140,32 @@
         <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -5197,7 +5233,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
-  <dimension ref="A1:AG21"/>
+  <dimension ref="A1:AG22"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5205,10 +5241,10 @@
         <v>161</v>
       </c>
       <c r="T1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AE1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:33">
@@ -5219,7 +5255,7 @@
         <v>162</v>
       </c>
       <c r="AE2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -5230,13 +5266,13 @@
         <v>163</v>
       </c>
       <c r="R3" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="AE3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -5244,10 +5280,10 @@
         <v>158</v>
       </c>
       <c r="M4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AE4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -5258,7 +5294,7 @@
         <v>164</v>
       </c>
       <c r="AE5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -5269,7 +5305,7 @@
         <v>165</v>
       </c>
       <c r="AE6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -5280,10 +5316,10 @@
         <v>166</v>
       </c>
       <c r="R7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AE7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -5291,30 +5327,25 @@
         <v>97</v>
       </c>
       <c r="M8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33">
-      <c r="M9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:33">
       <c r="AE10" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:33">
       <c r="M11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:33">
       <c r="M12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AE12" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -5322,66 +5353,71 @@
         <v>49</v>
       </c>
       <c r="M13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="A14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" t="s">
         <v>169</v>
-      </c>
-      <c r="B14" t="s">
-        <v>168</v>
-      </c>
-      <c r="D14" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:33">
       <c r="D15" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="M15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:33">
       <c r="M16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
+        <v>170</v>
+      </c>
+      <c r="F17" t="s">
         <v>171</v>
       </c>
-      <c r="F17" t="s">
-        <v>172</v>
-      </c>
       <c r="M17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="M18" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="M22" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -5397,7 +5433,7 @@
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFB8AA6-37C7-4E12-873C-C0C48F93FEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3487F2A-452E-475C-B295-0E2B85A351D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="2715" windowWidth="24810" windowHeight="17430" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="日記" sheetId="12" r:id="rId4"/>
     <sheet name="メモ" sheetId="9" r:id="rId5"/>
     <sheet name="雑用" sheetId="10" r:id="rId6"/>
-    <sheet name="仕様書" sheetId="13" r:id="rId7"/>
-    <sheet name="クラス設計" sheetId="14" r:id="rId8"/>
+    <sheet name="仕様書①" sheetId="13" r:id="rId7"/>
+    <sheet name="仕様書②" sheetId="15" r:id="rId8"/>
+    <sheet name="クラス設計" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$63</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="251">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -835,54 +836,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>制作手順</t>
-    <rPh sb="0" eb="4">
-      <t>セイサクテジュン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シーン遷移の流れ</t>
-    <rPh sb="3" eb="5">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ナガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーを作る</t>
-    <rPh sb="6" eb="7">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>敵を作る</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>中ボス、ボスを作る</t>
-    <rPh sb="0" eb="1">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>キャラクタークラスをつくる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>必須：入力バッファのシステムがいる！！！</t>
     <rPh sb="0" eb="2">
       <t>ヒッス</t>
@@ -1226,47 +1179,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>playerのアニメーション名を再設定</t>
-    <rPh sb="14" eb="15">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>サイセッテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>playerのコンボノードを再設定</t>
-    <rPh sb="14" eb="17">
-      <t>サイセッテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アニメーション→</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>dodge系、走り、歩きダサい、やり直し</t>
-    <rPh sb="5" eb="6">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ハシ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>アル</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ナオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>playerのできること</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アイドル</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1755,28 +1667,299 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジャンプ攻撃の中身の実装</t>
+    <t>カメラを攻撃切り上げ時に空中にカメラが行くようにする</t>
     <rPh sb="4" eb="6">
       <t>コウゲキ</t>
     </rPh>
-    <rPh sb="7" eb="9">
-      <t>ナカミ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャンプ攻撃用にカメラを上対応にする</t>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CG要望</t>
+    <rPh sb="2" eb="4">
+      <t>ヨウボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地上5段</t>
+    <rPh sb="0" eb="2">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル3段攻撃</t>
     <rPh sb="4" eb="5">
-      <t>コウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ウエタイオウ</t>
+      <t>ダン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中は触ってみる</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル強攻撃（一旦一つ）</t>
+    <rPh sb="3" eb="6">
+      <t>キョウコウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>イッタンヒト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の仕様書</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>playerの仕様書</t>
+    <rPh sb="7" eb="10">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>忍者外電4　敵キャラ         攻撃種</t>
+  </si>
+  <si>
+    <t>・龍神党尖兵(大砲)</t>
+  </si>
+  <si>
+    <t>技1つ</t>
+  </si>
+  <si>
+    <t>・龍神党尖兵(なぎなた)　　　薙刀分回し(4連攻撃)、牙突攻撃(重め)</t>
+  </si>
+  <si>
+    <t>・龍神党尖兵(飛行)</t>
+  </si>
+  <si>
+    <t>・・龍神党兵長(銃)</t>
+  </si>
+  <si>
+    <t>・・龍神党兵長(手裏剣)</t>
+  </si>
+  <si>
+    <t>・飛天狗(銭杖)　　　　　　鎌の２連攻撃、空を飛ぶ</t>
+  </si>
+  <si>
+    <t>・飛天狗(扇)</t>
+  </si>
+  <si>
+    <t>遠距離キャラ、中身は銃と一緒</t>
+  </si>
+  <si>
+    <t>・大飛天狗</t>
+  </si>
+  <si>
+    <t>近距離6連撃、2連撃、牙突など龍神党兵長に似た感じ</t>
+  </si>
+  <si>
+    <t>・童子(鉈)　　　</t>
+  </si>
+  <si>
+    <t>4パターンぐらい、全部近接、3コンボ(蹴り飛ばし)、6コンボなど</t>
+  </si>
+  <si>
+    <t>・童子(刀)</t>
+  </si>
+  <si>
+    <t>大剣を持っている、大ぶりな攻撃がおおい</t>
+  </si>
+  <si>
+    <t>・龍神党尖兵(刀)　　　　　　2,4種ぐらい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍神党尖兵(刀)　</t>
+  </si>
+  <si>
+    <t>・雑魚敵</t>
+    <rPh sb="1" eb="4">
+      <t>ザコテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・中ボス</t>
+    <rPh sb="1" eb="2">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ちょっと強い敵</t>
+    <rPh sb="5" eb="6">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>童子</t>
+    <rPh sb="0" eb="1">
+      <t>ワラベ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・龍神党兵長(刀)　</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　遠距離技、近距離技2種(1combo,3comboの剣)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍神党兵長(刀)　</t>
+  </si>
+  <si>
+    <t>ボス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1-1のボス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・龍神党尖兵(銃)　　　　　　2種、近距離技一つと銃技1つ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>龍神党尖兵(銃)　</t>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の設計を作る</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のステートパターンまで作る</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EnemyBase</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>警戒態勢</t>
+    <rPh sb="0" eb="4">
+      <t>ケイカイタイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemy１</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離とり</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemy2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠距離攻撃</t>
+    <rPh sb="0" eb="5">
+      <t>エンキョリコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近距離攻撃</t>
+    <rPh sb="0" eb="3">
+      <t>キンキョリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemy3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近距離攻撃</t>
+    <rPh sb="0" eb="5">
+      <t>キンキョリコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pに近づく</t>
+    <rPh sb="2" eb="3">
+      <t>チカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1844,7 +2027,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1989,6 +2172,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -2035,7 +2230,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2082,6 +2277,8 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -3343,19 +3540,19 @@
     <row r="14" spans="1:12" outlineLevel="1">
       <c r="A14" s="19"/>
       <c r="B14" s="10" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:12" outlineLevel="1">
       <c r="A15" s="19"/>
       <c r="B15" s="10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:12" outlineLevel="1">
       <c r="A16" s="19"/>
       <c r="B16" s="10" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3449,7 +3646,7 @@
         <v>45</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>5</v>
@@ -3483,7 +3680,7 @@
         <v>45</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>5</v>
@@ -3501,7 +3698,7 @@
     <row r="24" spans="1:7" outlineLevel="1">
       <c r="A24" s="19"/>
       <c r="B24" s="10" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3703,7 +3900,7 @@
         <v>45</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5</v>
@@ -3717,7 +3914,7 @@
         <v>45</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>5</v>
@@ -3731,7 +3928,7 @@
         <v>45</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>5</v>
@@ -3745,7 +3942,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>5</v>
@@ -5013,13 +5210,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5027,10 +5224,10 @@
         <v>46166</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5038,21 +5235,21 @@
         <v>46167</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="C5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -5074,98 +5271,101 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="D3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="B7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D14" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
+        <v>183</v>
+      </c>
+      <c r="D17" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
       <c r="B18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
       <c r="B19" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -5176,53 +5376,95 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
-  <dimension ref="C2:J11"/>
+  <dimension ref="B3:F16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="3:10">
-      <c r="C2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="3:10">
+    <row r="3" spans="2:6">
       <c r="C3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="3:10">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
       <c r="C4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="3:10">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
       <c r="C5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="3:10">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
       <c r="C6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="3:10">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="C7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="3:10">
-      <c r="C10" t="s">
-        <v>152</v>
-      </c>
-      <c r="H10" t="s">
-        <v>154</v>
-      </c>
-      <c r="J10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="3:10">
-      <c r="C11" t="s">
-        <v>153</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" t="s">
+        <v>244</v>
+      </c>
+      <c r="F14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" t="s">
+        <v>242</v>
+      </c>
+      <c r="F15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="D16" t="s">
+        <v>250</v>
+      </c>
+      <c r="F16" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5233,57 +5475,60 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
-  <dimension ref="A1:AG22"/>
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:33">
       <c r="M1" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="T1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="AE1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:33">
-      <c r="B2" t="s">
-        <v>156</v>
-      </c>
+      <c r="B2" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="M2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="AE2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:33">
       <c r="B3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="M3" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="R3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="AE3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="AG3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:33">
       <c r="B4" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="M4" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AE4" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -5291,35 +5536,35 @@
         <v>91</v>
       </c>
       <c r="M5" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="AE5" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:33">
       <c r="B6" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="M6" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="AE6" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:33">
       <c r="B7" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="M7" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="R7" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="AE7" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -5332,20 +5577,20 @@
     </row>
     <row r="10" spans="1:33">
       <c r="AE10" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:33">
       <c r="M11" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:33">
       <c r="M12" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="AE12" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -5353,71 +5598,92 @@
         <v>49</v>
       </c>
       <c r="M13" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="A14" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:33">
       <c r="D15" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:33">
       <c r="M16" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13">
+        <v>172</v>
+      </c>
+      <c r="AF16" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="AG16" s="40"/>
+    </row>
+    <row r="17" spans="2:37">
       <c r="B17" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F17" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="M17" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13">
+        <v>176</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>201</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="2:37">
       <c r="M18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13">
+        <v>173</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="2:37">
       <c r="B19" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D19" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="M19" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13">
+        <v>174</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="2:37">
+      <c r="AF20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="2:37">
       <c r="B21" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="2:37">
       <c r="M22" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -5427,13 +5693,162 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015F96B1-EBF5-4BB2-93CD-A0906537FC8C}">
+  <dimension ref="C2:X16"/>
+  <sheetFormatPr defaultColWidth="3.875" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="25" max="25" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:24">
+      <c r="C2" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="Q2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="3:24">
+      <c r="C4" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="3:24">
+      <c r="C5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I5" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="3:24">
+      <c r="C6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I6" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>208</v>
+      </c>
+      <c r="S6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="3:24">
+      <c r="Q7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="3:24">
+      <c r="C8" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="3:24">
+      <c r="C9" t="s">
+        <v>231</v>
+      </c>
+      <c r="I9" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>229</v>
+      </c>
+      <c r="X9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="3:24">
+      <c r="C10" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" spans="3:24">
+      <c r="C11" t="s">
+        <v>228</v>
+      </c>
+      <c r="I11" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="3:24">
+      <c r="Q12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="3:24">
+      <c r="C13" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>215</v>
+      </c>
+      <c r="S13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="3:24">
+      <c r="C14" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>217</v>
+      </c>
+      <c r="S14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="3:24">
+      <c r="Q15" t="s">
+        <v>219</v>
+      </c>
+      <c r="R15" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="3:24">
+      <c r="Q16" t="s">
+        <v>221</v>
+      </c>
+      <c r="S16" t="s">
+        <v>222</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B1947F-A3A0-4027-965D-A484FB7F3C32}">
   <dimension ref="C2"/>
   <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5444,6 +5859,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -5678,27 +6113,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5715,23 +6149,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3487F2A-452E-475C-B295-0E2B85A351D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E29A83-320D-4337-86D4-E1D676F74A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="261">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -1880,29 +1880,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>敵の設計を作る</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>セッケイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>敵のステートパターンまで作る</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>EnemyBase</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1961,6 +1938,132 @@
     <rPh sb="2" eb="3">
       <t>チカ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追いかける</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ばくすて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃→ばくすて</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おいかける→攻撃</t>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>警戒→攻撃or追いかける</t>
+    <rPh sb="0" eb="2">
+      <t>ケイカイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃後、硬直あり</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウチョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイドル→</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃、警戒、バクステ、警戒のランダム</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケイカイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケイカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃のノックバックにXZ方面(正面)、Y軸(上方向)の二つを用意、それで切り上げ攻撃、切り下げ攻撃などを対応する</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ホウメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ショウメン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ジク</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ウエホウコウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃のデータ</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノックバック</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2185,7 +2288,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2223,6 +2326,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2230,7 +2413,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2279,6 +2462,15 @@
     <xf numFmtId="0" fontId="0" fillId="24" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -3044,7 +3236,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46186</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -5353,16 +5545,6 @@
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
-      <c r="B18" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" t="s">
-        <v>240</v>
-      </c>
-    </row>
     <row r="20" spans="2:4">
       <c r="B20" t="s">
         <v>190</v>
@@ -5376,95 +5558,222 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
-  <dimension ref="B3:F16"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="3" spans="2:6">
-      <c r="C3" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="47"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="45"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="47"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="45"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="47"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="45"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="47"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="45"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="47"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="45"/>
+      <c r="B9" s="46" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="C4" t="s">
+      <c r="C9" s="46"/>
+      <c r="D9" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="G9" s="47"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="45"/>
+      <c r="B10" s="46" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="C5" t="s">
+      <c r="C10" s="46"/>
+      <c r="D10" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="G10" s="47"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="45"/>
+      <c r="B11" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="47"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="45"/>
+      <c r="B12" s="46" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="C6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="C7" t="s">
+      <c r="C12" s="46"/>
+      <c r="D12" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="G12" s="47"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="45"/>
+      <c r="B13" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="G13" s="47"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49" t="s">
+        <v>248</v>
+      </c>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49" t="s">
+        <v>248</v>
+      </c>
+      <c r="G14" s="50"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>249</v>
+      </c>
+      <c r="D17" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" t="s">
-        <v>243</v>
-      </c>
-      <c r="D11" t="s">
-        <v>245</v>
-      </c>
-      <c r="F11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>246</v>
-      </c>
-      <c r="F12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" t="s">
-        <v>242</v>
-      </c>
-      <c r="D13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" t="s">
-        <v>244</v>
-      </c>
-      <c r="F14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" t="s">
-        <v>250</v>
-      </c>
-      <c r="D15" t="s">
-        <v>242</v>
-      </c>
-      <c r="F15" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="D16" t="s">
-        <v>250</v>
-      </c>
-      <c r="F16" t="s">
-        <v>250</v>
+      <c r="D20" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="D22" t="s">
+        <v>255</v>
+      </c>
+      <c r="F22" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -5843,12 +6152,37 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B1947F-A3A0-4027-965D-A484FB7F3C32}">
-  <dimension ref="C2"/>
+  <dimension ref="C1:AG9"/>
   <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="3:3">
+    <row r="1" spans="3:33" ht="19.5" thickBot="1"/>
+    <row r="2" spans="3:33">
       <c r="C2" t="s">
         <v>168</v>
+      </c>
+      <c r="AE2" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="44"/>
+    </row>
+    <row r="3" spans="3:33">
+      <c r="AE3" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="AF3" s="46"/>
+      <c r="AG3" s="47"/>
+    </row>
+    <row r="4" spans="3:33" ht="19.5" thickBot="1">
+      <c r="AE4" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="50"/>
+    </row>
+    <row r="9" spans="3:33">
+      <c r="AE9" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -5859,6 +6193,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
@@ -5867,15 +6210,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6114,20 +6448,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
     <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E29A83-320D-4337-86D4-E1D676F74A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063AE13E-1080-4B86-A8F1-9DBABB8A83F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="2520" windowWidth="21225" windowHeight="11295" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="263">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2064,6 +2064,32 @@
   </si>
   <si>
     <t>ノックバック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵との当たり判定をする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル、必殺技の演出を先にする</t>
+    <rPh sb="4" eb="7">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2413,7 +2439,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2466,7 +2492,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -2597,6 +2622,17 @@
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>生存時間などは迷い</a:t>
           </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>そもそもこれ一個でよさそう</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
         </a:p>
         <a:p>
@@ -2912,6 +2948,519 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>272142</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55C35913-0911-5F9E-CAC9-8CA6C39708E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9974035" y="3333750"/>
+          <a:ext cx="2245179" cy="1415143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Character</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>97972</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>125186</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>68036</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75F5DD45-549A-BE84-13E2-3113F25B4AFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10112829" y="6248400"/>
+          <a:ext cx="1534886" cy="813707"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>押し戻しの</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>当たり判定</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Collider</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>常にある</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ON/OFF</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>231321</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>201386</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>187778</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1D8097C-4633-4B47-80D4-EE8820FA9CC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12123964" y="6232071"/>
+          <a:ext cx="1534886" cy="813707"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>やられ</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>判定</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Collider</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>常にある</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>ON/OFF</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>59871</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A03EB29-5809-4A44-8689-CC90B57AA4F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="9" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11096625" y="4748893"/>
+          <a:ext cx="1794782" cy="1483178"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>239486</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>125186</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線矢印コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3F26736-F687-4F47-A3AF-255F380F201E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="6" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="10880272" y="4748893"/>
+          <a:ext cx="216353" cy="1499507"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>46265</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>81644</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{115D434C-23B9-4028-845D-04BACFD15C8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="21" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11096625" y="4748893"/>
+          <a:ext cx="3971926" cy="1455965"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>217715</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>81644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>187780</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>160565</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E6300D1-C695-421E-BF17-F42F0CB94819}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14301108" y="6204858"/>
+          <a:ext cx="1534886" cy="813707"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>攻撃</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>判定</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Collider</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>毎回作る</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3214,11 +3763,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4388489208633094E-2</v>
+        <v>1.4354066985645933E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -3236,7 +3785,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46187</v>
+        <v>46188</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -3257,11 +3806,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-386</v>
+        <v>-387</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.22279792746113988</v>
+        <v>-0.22222222222222221</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -3274,11 +3823,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-366</v>
+        <v>-367</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23497267759562843</v>
+        <v>-0.23433242506811988</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -3291,11 +3840,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-355</v>
+        <v>-356</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.24225352112676057</v>
+        <v>-0.24157303370786518</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -5545,6 +6094,16 @@
         <v>199</v>
       </c>
     </row>
+    <row r="18" spans="2:4">
+      <c r="B18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" t="s">
+        <v>262</v>
+      </c>
+    </row>
     <row r="20" spans="2:4">
       <c r="B20" t="s">
         <v>190</v>
@@ -5572,164 +6131,124 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="47"/>
+      <c r="G2" s="46"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46" t="s">
+      <c r="C3" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="G3" s="46"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46" t="s">
+      <c r="C4" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
+      <c r="G4" s="46"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="45"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46" t="s">
+      <c r="C5" t="s">
         <v>240</v>
       </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="47"/>
+      <c r="G5" s="46"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="47"/>
+      <c r="G6" s="46"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="45"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46" t="s">
+      <c r="C7" t="s">
         <v>248</v>
       </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="47"/>
+      <c r="G7" s="46"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="45"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="47"/>
+      <c r="G8" s="46"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="45"/>
-      <c r="B9" s="46" t="s">
+      <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46" t="s">
+      <c r="D9" t="s">
         <v>243</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46" t="s">
+      <c r="F9" t="s">
         <v>246</v>
       </c>
-      <c r="G9" s="47"/>
+      <c r="G9" s="46"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="45"/>
-      <c r="B10" s="46" t="s">
+      <c r="B10" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46" t="s">
+      <c r="D10" t="s">
         <v>244</v>
       </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46" t="s">
+      <c r="F10" t="s">
         <v>247</v>
       </c>
-      <c r="G10" s="47"/>
+      <c r="G10" s="46"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="45"/>
-      <c r="B11" s="46" t="s">
+      <c r="B11" t="s">
         <v>240</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46" t="s">
+      <c r="D11" t="s">
         <v>245</v>
       </c>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46" t="s">
+      <c r="F11" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="47"/>
+      <c r="G11" s="46"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="45"/>
-      <c r="B12" s="46" t="s">
+      <c r="B12" t="s">
         <v>242</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46" t="s">
+      <c r="D12" t="s">
         <v>242</v>
       </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46" t="s">
+      <c r="F12" t="s">
         <v>242</v>
       </c>
-      <c r="G12" s="47"/>
+      <c r="G12" s="46"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="45"/>
-      <c r="B13" s="46" t="s">
+      <c r="B13" t="s">
         <v>248</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46" t="s">
+      <c r="D13" t="s">
         <v>240</v>
       </c>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46" t="s">
+      <c r="F13" t="s">
         <v>240</v>
       </c>
-      <c r="G13" s="47"/>
+      <c r="G13" s="46"/>
     </row>
     <row r="14" spans="1:7" ht="19.5" thickBot="1">
-      <c r="A14" s="48"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49" t="s">
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49" t="s">
+      <c r="E14" s="48"/>
+      <c r="F14" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="G14" s="50"/>
+      <c r="G14" s="49"/>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
@@ -6170,15 +6689,14 @@
       <c r="AE3" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="AF3" s="46"/>
-      <c r="AG3" s="47"/>
+      <c r="AG3" s="46"/>
     </row>
     <row r="4" spans="3:33" ht="19.5" thickBot="1">
-      <c r="AE4" s="48" t="s">
+      <c r="AE4" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="AF4" s="49"/>
-      <c r="AG4" s="50"/>
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="49"/>
     </row>
     <row r="9" spans="3:33">
       <c r="AE9" t="s">
@@ -6202,17 +6720,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6447,6 +6954,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
@@ -6456,17 +6974,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6483,4 +6990,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063AE13E-1080-4B86-A8F1-9DBABB8A83F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C14A09-8266-4207-A0BB-4D1445FEB46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3915" yWindow="2520" windowWidth="21225" windowHeight="11295" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="274">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2090,6 +2090,125 @@
     <rPh sb="11" eb="12">
       <t>サキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HItColのクラスを持たせて</t>
+    <rPh sb="11" eb="12">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たったらPlayerに検知させる</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吹っ飛ばし方の種類</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それ用のクラスを作る</t>
+    <rPh sb="2" eb="3">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期装備</t>
+    <rPh sb="0" eb="4">
+      <t>ショキソウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃クラスを作る</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>派生図を作る</t>
+    <rPh sb="0" eb="2">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地上</t>
+    <rPh sb="0" eb="2">
+      <t>チジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵から離れるため終了</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そばに敵がいない場合、近くの敵に向かって急降下していく</t>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>キュウコウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それもいなかったらまっすぐ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2439,7 +2558,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2496,6 +2615,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -2529,6 +2650,2163 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21069168-72E0-17F6-5F38-A981ABEB9152}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="762000" y="6400800"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>地上</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43B6EF13-7DA7-18C1-630D-19824C6B48EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1400175" y="8791575"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>切り上げ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>4763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00638CB6-F325-8E7B-7ECC-5F5847C37312}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="3" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1400175" y="6672263"/>
+          <a:ext cx="228600" cy="2390775"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12742478-CC5B-66BF-73F2-526883B71271}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2266950" y="6410325"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>地上２</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F11E1F40-B7DE-95F5-3F47-6DB7B906B4C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3705225" y="6410325"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>地上</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{522792DE-2B6B-D8FA-7D6D-A1FC6F51D68F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5181600" y="6419850"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>地上４</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24F04BEB-2651-A94C-838E-F35301DB3DFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6657975" y="6400800"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>地上</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>5</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>4763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="直線矢印コネクタ 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{229FF8BB-DC7B-E01A-B37D-65E72D140BBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="10" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1628775" y="6672263"/>
+          <a:ext cx="638175" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4E61294-C862-FB9A-2433-733E2B00B6A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3124200" y="6681788"/>
+          <a:ext cx="571500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="直線矢印コネクタ 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86412CA0-E1D6-E681-F222-B2F523FD68D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="3"/>
+          <a:endCxn id="12" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4572000" y="6681788"/>
+          <a:ext cx="609600" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>4763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="直線矢印コネクタ 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEA6D135-07C8-9314-5B1D-EA46CF7F7EBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="12" idx="3"/>
+          <a:endCxn id="13" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6048375" y="6672263"/>
+          <a:ext cx="609600" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="正方形/長方形 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1317DEEE-A3A1-199F-983B-899D3F3CE9B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3124200" y="9934575"/>
+          <a:ext cx="1066800" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>切り上げ２</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="正方形/長方形 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A9FFD03-8C7F-7743-11D2-7D847FA17769}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4600575" y="11020425"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>切り上げ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="正方形/長方形 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D50A5F8E-B9CD-3C0F-4501-053DB1CBB01C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6638925" y="7258050"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>強３</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>204788</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="36" name="直線矢印コネクタ 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E95430B9-CDF7-920A-C218-5A2189E1E645}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="3"/>
+          <a:endCxn id="31" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3124200" y="6681788"/>
+          <a:ext cx="9525" cy="3524250"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>100013</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="39" name="直線矢印コネクタ 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F2F195-00EC-A427-8194-9F1C27530983}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="3"/>
+          <a:endCxn id="32" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4572000" y="6681788"/>
+          <a:ext cx="28575" cy="4610100"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>147638</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="直線矢印コネクタ 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20CDADD4-4A8F-B592-FC8D-9C1B6B16D2DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="12" idx="3"/>
+          <a:endCxn id="33" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6048375" y="6691313"/>
+          <a:ext cx="590550" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="正方形/長方形 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6D349A2-857C-39F7-F5E1-39D37E2198B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2705100" y="8791575"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>空中</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="正方形/長方形 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B53BF35-9B67-9560-4B4A-A4A4A32429F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3905250" y="8810625"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>空中</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="正方形/長方形 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59F1F595-6184-E83C-6E41-51145E43C18C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5057775" y="8791575"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>空中</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="正方形/長方形 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79ACAA13-B9E1-5D69-2D1E-16CCFB495E26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5886450" y="11029950"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>空中</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="正方形/長方形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01712D99-8CB6-2E24-3854-97E6273317F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7248525" y="11029950"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>空中</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>4</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="正方形/長方形 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95B0F2F2-3E98-619D-8D17-8EFEF9405B97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6381750" y="8772525"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>空中</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>4</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="直線矢印コネクタ 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ABCBD60-97B9-6E7D-9CC9-28D2F2F7B438}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="47" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2266950" y="9063038"/>
+          <a:ext cx="438150" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="直線矢印コネクタ 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9380E42-0E4F-448D-D5D0-A4DEBAFF8835}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="47" idx="3"/>
+          <a:endCxn id="51" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3571875" y="9063038"/>
+          <a:ext cx="333375" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="69" name="直線矢印コネクタ 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1C72B8D-91DF-C62E-2B63-2D13A38655A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="51" idx="3"/>
+          <a:endCxn id="52" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4772025" y="9063038"/>
+          <a:ext cx="285750" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>233363</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="72" name="直線矢印コネクタ 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{133170D3-2A24-B456-33E5-1EF74EEB2228}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="52" idx="3"/>
+          <a:endCxn id="58" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5924550" y="9043988"/>
+          <a:ext cx="457200" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>100013</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>109538</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="78" name="直線矢印コネクタ 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F5D9089-DC87-F94C-4AD2-7C49D3DE0A33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="32" idx="3"/>
+          <a:endCxn id="53" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5467350" y="11291888"/>
+          <a:ext cx="419100" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>109538</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>109538</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="直線矢印コネクタ 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2AE6844-E79D-C61E-C32D-B1585B3361FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="53" idx="3"/>
+          <a:endCxn id="55" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6753225" y="11301413"/>
+          <a:ext cx="495300" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="83" name="正方形/長方形 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F47593BE-2808-51D9-5F5A-A42BFBA65B8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="733425" y="7315200"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>強</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="84" name="正方形/長方形 83">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A8D576E-CA75-E84D-7423-98DEA41F6862}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7372350"/>
+          <a:ext cx="0" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="85" name="正方形/長方形 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C384BA8-378F-1537-45D6-455C564888A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2257425" y="7324725"/>
+          <a:ext cx="866775" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>強</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>204788</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>214313</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="87" name="直線矢印コネクタ 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CF3F4ED-EC41-2515-7DB8-28791575A9DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="83" idx="3"/>
+          <a:endCxn id="85" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="7586663"/>
+          <a:ext cx="657225" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="89" name="正方形/長方形 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3FABCD3-7056-5CA9-45CD-E34939AAF3F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7296150" y="9772650"/>
+          <a:ext cx="1085850" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>いずな落とし</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>42863</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="91" name="直線矢印コネクタ 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC6BF1CE-AE9D-C11F-FF1C-209F79DA1F71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="51" idx="3"/>
+          <a:endCxn id="89" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4772025" y="9082088"/>
+          <a:ext cx="2524125" cy="962025"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3763,11 +6041,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4354066985645933E-2</v>
+        <v>1.4319809069212411E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -3785,7 +6063,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -3806,11 +6084,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-387</v>
+        <v>-388</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.22222222222222221</v>
+        <v>-0.22164948453608246</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -3823,11 +6101,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-367</v>
+        <v>-368</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23433242506811988</v>
+        <v>-0.23369565217391305</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -3840,11 +6118,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-356</v>
+        <v>-357</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.24157303370786518</v>
+        <v>-0.24089635854341737</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -6303,7 +8581,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:33">
@@ -6457,7 +8735,7 @@
       </c>
       <c r="AG16" s="40"/>
     </row>
-    <row r="17" spans="2:37">
+    <row r="17" spans="1:37">
       <c r="B17" t="s">
         <v>159</v>
       </c>
@@ -6474,7 +8752,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="2:37">
+    <row r="18" spans="1:37">
       <c r="M18" t="s">
         <v>173</v>
       </c>
@@ -6482,7 +8760,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="19" spans="2:37">
+    <row r="19" spans="1:37">
       <c r="B19" t="s">
         <v>162</v>
       </c>
@@ -6496,12 +8774,12 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="2:37">
+    <row r="20" spans="1:37">
       <c r="AF20" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="21" spans="2:37">
+    <row r="21" spans="1:37">
       <c r="B21" t="s">
         <v>161</v>
       </c>
@@ -6509,14 +8787,45 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="2:37">
+    <row r="22" spans="1:37">
       <c r="M22" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="D24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37">
+      <c r="A28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="O43" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6671,11 +8980,11 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B1947F-A3A0-4027-965D-A484FB7F3C32}">
-  <dimension ref="C1:AG9"/>
+  <dimension ref="C1:AU33"/>
   <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="3:33" ht="19.5" thickBot="1"/>
-    <row r="2" spans="3:33">
+    <row r="1" spans="3:35" ht="19.5" thickBot="1"/>
+    <row r="2" spans="3:35">
       <c r="C2" t="s">
         <v>168</v>
       </c>
@@ -6683,24 +8992,61 @@
         <v>258</v>
       </c>
       <c r="AF2" s="43"/>
-      <c r="AG2" s="44"/>
-    </row>
-    <row r="3" spans="3:33">
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="44"/>
+    </row>
+    <row r="3" spans="3:35">
       <c r="AE3" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="AG3" s="46"/>
-    </row>
-    <row r="4" spans="3:33" ht="19.5" thickBot="1">
-      <c r="AE4" s="47" t="s">
+      <c r="AF3" s="50"/>
+      <c r="AG3" s="50"/>
+      <c r="AH3" s="50"/>
+      <c r="AI3" s="46"/>
+    </row>
+    <row r="4" spans="3:35">
+      <c r="AE4" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="49"/>
-    </row>
-    <row r="9" spans="3:33">
+      <c r="AF4" s="50"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="50"/>
+      <c r="AI4" s="46"/>
+    </row>
+    <row r="5" spans="3:35" ht="19.5" thickBot="1">
+      <c r="AE5" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="49"/>
+    </row>
+    <row r="9" spans="3:35">
       <c r="AE9" t="s">
         <v>257</v>
+      </c>
+    </row>
+    <row r="31" spans="34:47">
+      <c r="AN31" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU31" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="34:47">
+      <c r="AH32" t="s">
+        <v>267</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="40:40">
+      <c r="AN33" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -6711,15 +9057,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -6954,6 +9291,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6966,14 +9312,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6992,6 +9330,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C14A09-8266-4207-A0BB-4D1445FEB46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35115CAF-F849-4E75-9E0E-17E7957DC590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="275">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2209,6 +2209,49 @@
   </si>
   <si>
     <t>それもいなかったらまっすぐ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HItColとAttackColを作った。AttackColは途中、AttackColを作りつつ、終わったら、Player,Enemyに持たせて初期化させて使う。カプセル型Colliderの勉強や、Boxの当たり判定を使うことを考える</t>
+    <rPh sb="17" eb="18">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="72" eb="75">
+      <t>ショキカ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="109" eb="110">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>カンガ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2558,7 +2601,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2615,8 +2658,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -6041,11 +6082,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4319809069212411E-2</v>
+        <v>1.4285714285714285E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6063,7 +6104,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6084,11 +6125,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-388</v>
+        <v>-389</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.22164948453608246</v>
+        <v>-0.2210796915167095</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6101,11 +6142,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-368</v>
+        <v>-369</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23369565217391305</v>
+        <v>-0.23306233062330622</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6118,11 +6159,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-357</v>
+        <v>-358</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.24089635854341737</v>
+        <v>-0.24022346368715083</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8219,7 +8260,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8269,6 +8310,14 @@
     <row r="5" spans="1:3">
       <c r="C5" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
+        <v>46190</v>
+      </c>
+      <c r="C7" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -9000,22 +9049,16 @@
       <c r="AE3" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="AF3" s="50"/>
-      <c r="AG3" s="50"/>
-      <c r="AH3" s="50"/>
       <c r="AI3" s="46"/>
     </row>
     <row r="4" spans="3:35">
       <c r="AE4" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="AF4" s="50"/>
-      <c r="AG4" s="50"/>
-      <c r="AH4" s="50"/>
       <c r="AI4" s="46"/>
     </row>
     <row r="5" spans="3:35" ht="19.5" thickBot="1">
-      <c r="AE5" s="51" t="s">
+      <c r="AE5" s="47" t="s">
         <v>265</v>
       </c>
       <c r="AF5" s="48"/>
@@ -9057,6 +9100,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9291,27 +9354,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9328,23 +9390,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35115CAF-F849-4E75-9E0E-17E7957DC590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D807706C-210F-4753-8659-893A2BE92786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="2550" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="276">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2251,6 +2251,22 @@
     </rPh>
     <rPh sb="114" eb="115">
       <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ColのUpdateをCollsionManagerでやりたいけど、責務が重すぎるかなって思って、それぞれでやったがいいのか、悩む</t>
+    <rPh sb="34" eb="36">
+      <t>セキム</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ナヤ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6082,11 +6098,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4285714285714285E-2</v>
+        <v>1.4251781472684086E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6104,7 +6120,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6125,11 +6141,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-389</v>
+        <v>-390</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.2210796915167095</v>
+        <v>-0.22051282051282051</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6142,11 +6158,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-369</v>
+        <v>-370</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23306233062330622</v>
+        <v>-0.23243243243243245</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6159,11 +6175,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-358</v>
+        <v>-359</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.24022346368715083</v>
+        <v>-0.23955431754874651</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8260,7 +8276,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8318,6 +8334,14 @@
       </c>
       <c r="C7" t="s">
         <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
+        <v>46191</v>
+      </c>
+      <c r="C8" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -9100,26 +9124,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9354,26 +9358,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9390,4 +9395,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D807706C-210F-4753-8659-893A2BE92786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3804532E-2741-4B31-9899-99124AC7BBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="2550" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="480" windowWidth="21225" windowHeight="14325" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="277">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2267,6 +2267,16 @@
     </rPh>
     <rPh sb="63" eb="64">
       <t>ナヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollsionManagerのUpdateをする、コンボチェーンにいろいろ追加したけどプログラミングのほうでは追加してないからしないといけない、</t>
+    <rPh sb="38" eb="40">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8276,7 +8286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8342,6 +8352,14 @@
       </c>
       <c r="C8" t="s">
         <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
+        <v>46192</v>
+      </c>
+      <c r="C9" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -9124,6 +9142,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9358,27 +9396,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9395,23 +9432,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3804532E-2741-4B31-9899-99124AC7BBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EE5D75-65B7-4573-88F5-834F8BD9EE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="480" windowWidth="21225" windowHeight="14325" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="279">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2277,6 +2277,65 @@
     </rPh>
     <rPh sb="56" eb="58">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それは終わった、次は速度をmapにして、いろいろ修正、追加できるようにしている途中、unorderd_mapでvelをやってて、今CollisionManagerとの</t>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>イマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定の取り方をもう一度見直しているところ、そこが終わったら、敵が吹っ飛ばせるようになって、って感じ</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>イチドミナオ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>カン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6108,11 +6167,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4251781472684086E-2</v>
+        <v>1.4218009478672985E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6130,7 +6189,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46193</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6151,11 +6210,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-390</v>
+        <v>-391</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.22051282051282051</v>
+        <v>-0.21994884910485935</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6168,11 +6227,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-370</v>
+        <v>-371</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23243243243243245</v>
+        <v>-0.23180592991913745</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6185,11 +6244,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-359</v>
+        <v>-360</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.23955431754874651</v>
+        <v>-0.2388888888888889</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8286,7 +8345,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8360,6 +8419,16 @@
       </c>
       <c r="C9" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="C10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="C11" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -9142,26 +9211,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9396,26 +9445,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9432,4 +9482,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EE5D75-65B7-4573-88F5-834F8BD9EE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65658B95-9AC2-4AB8-B3B5-1F53B3C8C6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22575" yWindow="3195" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="281">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2335,6 +2335,50 @@
       <t>ト</t>
     </rPh>
     <rPh sb="50" eb="51">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑のやり方でやろうとしたけど、無理そうだったので、やめる（プロジェクト分けたので、研究用として後ほど）</t>
+    <rPh sb="4" eb="5">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ムリ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ケンキュウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ノチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のOnDamage内で、m_velじゃなくて、knockBackVelに入れて、減衰させる（プレイヤーと同じ感じでする）</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ゲンスイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
       <t>カン</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -6189,7 +6233,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46193</v>
+        <v>46194</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8345,7 +8389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8429,6 +8473,19 @@
     <row r="11" spans="1:3">
       <c r="C11" t="s">
         <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1">
+        <v>46193</v>
+      </c>
+      <c r="C12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="C13" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65658B95-9AC2-4AB8-B3B5-1F53B3C8C6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF7367E-E49C-47AB-B4F9-C30E57F9ABD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22575" yWindow="3195" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="283">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2380,6 +2380,47 @@
     </rPh>
     <rPh sb="55" eb="56">
       <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やられ判定がだんだん下方向にいっている→おそらくジャンプ着地後の挙動でm_pos.y = 0にしているせい</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>シタホウコウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>チャクチ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃が当たったとき、Playerを動かないようにするorEnemyを動かして、Playerの攻撃を当たるようにする</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6211,11 +6252,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4218009478672985E-2</v>
+        <v>1.4184397163120567E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6233,7 +6274,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6254,11 +6295,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-391</v>
+        <v>-392</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.21994884910485935</v>
+        <v>-0.21938775510204081</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6271,11 +6312,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-371</v>
+        <v>-372</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23180592991913745</v>
+        <v>-0.23118279569892472</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6288,11 +6329,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-360</v>
+        <v>-361</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.2388888888888889</v>
+        <v>-0.23822714681440443</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8389,7 +8430,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8486,6 +8527,19 @@
     <row r="13" spans="1:3">
       <c r="C13" t="s">
         <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="C15" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -9268,6 +9322,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9502,27 +9576,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9539,23 +9612,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF7367E-E49C-47AB-B4F9-C30E57F9ABD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F83A6F-9B12-4EB7-8A9F-A39688FDE832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22575" yWindow="3195" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="284">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2421,6 +2421,28 @@
     </rPh>
     <rPh sb="49" eb="50">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑敵側を動かすやり方が高速アクションゲームは多いらしい</t>
+    <rPh sb="1" eb="2">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウソク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8430,7 +8452,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8540,6 +8562,11 @@
     <row r="15" spans="1:3">
       <c r="C15" t="s">
         <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="C16" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -9322,26 +9349,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9576,26 +9583,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9612,4 +9620,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F83A6F-9B12-4EB7-8A9F-A39688FDE832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CBBEE6-945B-4E8A-AD02-6B32DB4237F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22575" yWindow="3195" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="288">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2443,6 +2443,58 @@
     </rPh>
     <rPh sb="22" eb="23">
       <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃判定をすぐに出さないようにする</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のknockバック距離はいったんやめる</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃に敵の当たり判定がついじゅうするようになった</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はcolliderがずれないように、posをずらしたときにm_hitColに0になるまでの上べくとるを足す</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>タ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8452,7 +8504,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8567,6 +8619,29 @@
     <row r="16" spans="1:3">
       <c r="C16" t="s">
         <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C17" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="C18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="C19" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="C20" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -9349,6 +9424,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9583,27 +9678,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9620,23 +9714,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CBBEE6-945B-4E8A-AD02-6B32DB4237F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146D3F26-8BB8-4B5B-9486-C60C2F613279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2745" yWindow="4980" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="289">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2495,6 +2495,13 @@
     </rPh>
     <rPh sb="52" eb="53">
       <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そもそもm_hitColをm_pos = GetPosにすれば即解決した</t>
+    <rPh sb="31" eb="34">
+      <t>ソクカイケツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8504,7 +8511,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8642,6 +8649,11 @@
     <row r="20" spans="1:3">
       <c r="C20" t="s">
         <v>287</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="C21" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -9424,26 +9436,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9678,26 +9670,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9714,4 +9707,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146D3F26-8BB8-4B5B-9486-C60C2F613279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB242894-CABB-48CF-911B-55DE971FCC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2745" yWindow="4980" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="291">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2502,6 +2502,41 @@
     <t>そもそもm_hitColをm_pos = GetPosにすれば即解決した</t>
     <rPh sb="31" eb="34">
       <t>ソクカイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、必殺技のシェーダーをする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップを追加、マップとの当たり判定(ポリゴンとの当たり判定を終わらせた後)</t>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>アト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8511,7 +8546,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8654,6 +8689,16 @@
     <row r="21" spans="1:3">
       <c r="C21" t="s">
         <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="C22" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="C23" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB242894-CABB-48CF-911B-55DE971FCC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF545AB-F47F-4446-B94E-A3C7E54BF701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2745" yWindow="4980" windowWidth="21135" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1290" yWindow="5385" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="293">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2537,6 +2537,44 @@
     </rPh>
     <rPh sb="35" eb="36">
       <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コライダー2つをもらって当たり判定をしてboolを返すクラスを作る、stageクラスにgethandleでモデルハンドルを取得できるようにする→</t>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もし、当たり判定がpolygonだったら当たり判定をするというのをCollisionManagerで作る</t>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6368,11 +6406,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4184397163120567E-2</v>
+        <v>1.4150943396226415E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6390,7 +6428,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6411,11 +6449,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-392</v>
+        <v>-393</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.21938775510204081</v>
+        <v>-0.21882951653944022</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6428,11 +6466,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-372</v>
+        <v>-373</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23118279569892472</v>
+        <v>-0.23056300268096513</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6445,11 +6483,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-361</v>
+        <v>-362</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.23822714681440443</v>
+        <v>-0.23756906077348067</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8546,7 +8584,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8699,6 +8737,19 @@
     <row r="23" spans="1:3">
       <c r="C23" t="s">
         <v>289</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C24" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="C25" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -9481,6 +9532,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -9715,15 +9775,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9736,6 +9787,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9754,14 +9813,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiraoTaiki\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF545AB-F47F-4446-B94E-A3C7E54BF701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B84918E-5329-4C30-8884-F03F422D4AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="5385" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="300">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2067,19 +2067,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>敵との当たり判定をする</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スキル、必殺技の演出を先にする</t>
     <rPh sb="4" eb="7">
       <t>ヒッサツワザ</t>
@@ -2575,6 +2562,146 @@
     </rPh>
     <rPh sb="50" eb="51">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの攻撃が当たったらプレイヤーの正面に来るように移動させる（これが吸着かも）</t>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ショウメン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>キュウチャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーが敵にコンボ中は追撃する仕様について</t>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広範囲内の敵のvectorを渡して、</t>
+    <rPh sb="0" eb="3">
+      <t>コウハンイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先順位を決める</t>
+    <rPh sb="0" eb="4">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①ロックオンしている敵&gt;入力している方向にいる敵&gt;1番近くにいる敵</t>
+    <rPh sb="10" eb="11">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>バンチカ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それでもいなかったら入力の向きに進むようにする</t>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その敵のほうに進む</t>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定を終わらせる→敵への攻撃のやつを終わらせる→スキル、必殺技の演出を実装する</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6406,11 +6533,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4150943396226415E-2</v>
+        <v>1.411764705882353E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6428,7 +6555,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6449,11 +6576,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-393</v>
+        <v>-394</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.21882951653944022</v>
+        <v>-0.21827411167512689</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6466,11 +6593,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-373</v>
+        <v>-374</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23056300268096513</v>
+        <v>-0.22994652406417113</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6483,11 +6610,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-362</v>
+        <v>-363</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.23756906077348067</v>
+        <v>-0.23691460055096419</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8584,7 +8711,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8641,7 +8768,7 @@
         <v>46190</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8649,7 +8776,7 @@
         <v>46191</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8657,17 +8784,17 @@
         <v>46192</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8675,12 +8802,12 @@
         <v>46193</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="C13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -8688,17 +8815,17 @@
         <v>46194</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="C15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="C16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8706,37 +8833,37 @@
         <v>46195</v>
       </c>
       <c r="C17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="C18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="C19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="C20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="C21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="C22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="C23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8744,11 +8871,19 @@
         <v>46196</v>
       </c>
       <c r="C24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="C25" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C26" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8760,7 +8895,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:D20"/>
+  <dimension ref="B2:D27"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -8855,17 +8990,45 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" t="s">
         <v>190</v>
+      </c>
+      <c r="D20" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="D22" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="D23" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="D24" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="D25" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="D27" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -9275,12 +9438,12 @@
     </row>
     <row r="24" spans="1:37">
       <c r="D24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:37">
       <c r="A28" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -9290,17 +9453,17 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="O43" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -9491,7 +9654,7 @@
     </row>
     <row r="5" spans="3:35" ht="19.5" thickBot="1">
       <c r="AE5" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AF5" s="48"/>
       <c r="AG5" s="48"/>
@@ -9505,23 +9668,23 @@
     </row>
     <row r="31" spans="34:47">
       <c r="AN31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="34:47">
       <c r="AH32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AN32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="40:40">
       <c r="AN33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF545AB-F47F-4446-B94E-A3C7E54BF701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C8D315-BCC2-42BF-8078-C7B71D0DDC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="5385" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="3285" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="294">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2575,6 +2575,16 @@
     </rPh>
     <rPh sb="50" eb="51">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionCheckerのクラスとFixNextPositionのクラスを作って、それをCollisionManagerに持たせる</t>
+    <rPh sb="41" eb="42">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>モ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6406,11 +6416,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.4150943396226415E-2</v>
+        <v>1.411764705882353E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6428,7 +6438,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6449,11 +6459,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-393</v>
+        <v>-394</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.21882951653944022</v>
+        <v>-0.21827411167512689</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6466,11 +6476,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-373</v>
+        <v>-374</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.23056300268096513</v>
+        <v>-0.22994652406417113</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6483,11 +6493,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-362</v>
+        <v>-363</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.23756906077348067</v>
+        <v>-0.23691460055096419</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8584,7 +8594,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8750,6 +8760,11 @@
     <row r="25" spans="1:3">
       <c r="C25" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="C26" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -9532,12 +9547,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9776,20 +9793,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9814,12 +9832,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C8D315-BCC2-42BF-8078-C7B71D0DDC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29C1033-8F52-4D82-9F21-158BDDA98581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7320" yWindow="3285" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="296">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2585,6 +2585,41 @@
     </rPh>
     <rPh sb="65" eb="66">
       <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionChecker食らうを作っている途中、fixedPosClassも同時平行でつくっていかないとこんがらがると思う</t>
+    <rPh sb="16" eb="17">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヘイコウ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だいぶ時間かかりそう、今週の日曜までにはおわらせたいなぁぁぁぁっぁ</t>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コンシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニチヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8594,7 +8629,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8765,6 +8800,19 @@
     <row r="26" spans="1:3">
       <c r="C26" t="s">
         <v>293</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C27" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="C28" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -9547,14 +9595,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9793,21 +9839,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9832,9 +9877,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29C1033-8F52-4D82-9F21-158BDDA98581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DAFD82-04E8-4194-BE18-B9ADD538827E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="3285" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11775" yWindow="3660" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="297">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2620,6 +2620,16 @@
     </rPh>
     <rPh sb="14" eb="16">
       <t>ニチヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FixedNextPosのFixNextposSPの途中、続きから</t>
+    <rPh sb="26" eb="28">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツヅ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6451,11 +6461,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.411764705882353E-2</v>
+        <v>1.405152224824356E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6473,7 +6483,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6494,11 +6504,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-394</v>
+        <v>-396</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.21827411167512689</v>
+        <v>-0.21717171717171718</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6511,11 +6521,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-374</v>
+        <v>-376</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.22994652406417113</v>
+        <v>-0.22872340425531915</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6528,11 +6538,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-363</v>
+        <v>-365</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.23691460055096419</v>
+        <v>-0.23561643835616439</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8629,7 +8639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8813,6 +8823,14 @@
     <row r="28" spans="1:3">
       <c r="C28" t="s">
         <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C29" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -9595,12 +9613,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9839,20 +9859,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9877,12 +9898,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DAFD82-04E8-4194-BE18-B9ADD538827E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2993C2CC-0FD2-4E9D-AF38-965E5D0E6533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11775" yWindow="3660" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="303">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2630,6 +2630,117 @@
     </rPh>
     <rPh sb="29" eb="30">
       <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定をどこまでやるのか問題はある、それによって、次何をやるか決める</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ツギナニ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残る課題は当たり判定、スキル、必殺技、ジャスト回避</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の当たり判定も変えたいかな</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の当たり判定変えた後、スキル、必殺技を作る</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LB押している間player.cppでモデルの追加とかをするLB&amp;技ボタンでスキル</t>
+    <rPh sb="2" eb="3">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PlayerStateAttackの中でスキルの詳細を書く</t>
+    <rPh sb="18" eb="19">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6483,7 +6594,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8639,7 +8750,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8831,6 +8942,36 @@
       </c>
       <c r="C29" t="s">
         <v>296</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="C30" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="C31" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="C32" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2993C2CC-0FD2-4E9D-AF38-965E5D0E6533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C43B50-5407-4414-9EEB-D0EBECAF9D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11775" yWindow="3660" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="305">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2732,7 +2732,23 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>PlayerStateAttackの中でスキルの詳細を書く</t>
+    <t>raven状態はplayer.cppで書くがplayerStateAttackの時は解除をさせないようにする</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PlayerStateAttackの中でスキルの詳細を書く←管理が面倒だからやっぱり分ける</t>
     <rPh sb="18" eb="19">
       <t>ナカ</t>
     </rPh>
@@ -2741,6 +2757,37 @@
     </rPh>
     <rPh sb="27" eb="28">
       <t>カ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>メンドウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑結局、PlayerStateAttackの中で書いた、また、raven状態はidle,move,run,(Attackの遷移時)にかえる</t>
+    <rPh sb="1" eb="3">
+      <t>ケッキョク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8750,7 +8797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8971,7 +9018,17 @@
     </row>
     <row r="35" spans="3:3">
       <c r="C35" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" t="s">
         <v>302</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -9754,14 +9811,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10000,21 +10055,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10039,9 +10093,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C43B50-5407-4414-9EEB-D0EBECAF9D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8110C39F-FFDF-455C-BC55-E77292874706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11775" yWindow="3660" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="クラス設計" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$40</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="303">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -348,16 +348,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>表示、移動</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1コスト1時間</t>
     <rPh sb="5" eb="7">
       <t>ジカン</t>
@@ -369,17 +359,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>移動アニメーション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃アニメーション</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>4/13まで</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -391,60 +370,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カメラの移動</t>
-    <rPh sb="4" eb="6">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>剣の表示</t>
-    <rPh sb="0" eb="1">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームループ用のシステム</t>
-    <rPh sb="6" eb="7">
-      <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージの表示</t>
-    <rPh sb="5" eb="7">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃と敵との当たり判定</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被弾アニメーション</t>
-    <rPh sb="0" eb="2">
-      <t>ヒダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>モデル探し</t>
     <rPh sb="3" eb="4">
       <t>サガ</t>
@@ -466,30 +391,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーと敵との当たり判定</t>
-    <rPh sb="6" eb="7">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>インゲーム中のシステム</t>
-    <rPh sb="5" eb="6">
-      <t>チュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>UX</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>日</t>
     <rPh sb="0" eb="1">
       <t>ニチ</t>
@@ -515,30 +416,7 @@
     <t>土</t>
   </si>
   <si>
-    <t>カメラに合わせたプレイヤーの移動、回転</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カイテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>完了</t>
-  </si>
-  <si>
-    <t>作業中(作業工数)</t>
-    <rPh sb="0" eb="3">
-      <t>サギョウチュウ</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>サギョウコウスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>実コスト</t>
@@ -615,23 +493,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>弱攻撃</t>
-    <rPh sb="0" eb="1">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>強攻撃</t>
-    <rPh sb="0" eb="3">
-      <t>キョウコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>コンボ攻撃</t>
     <rPh sb="3" eb="5">
       <t>コウゲキ</t>
@@ -639,29 +500,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃当たり判定</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップとの当たり判定</t>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>カメラの当たり判定</t>
     <rPh sb="4" eb="5">
       <t>ア</t>
@@ -672,14 +510,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ウルト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダッシュ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>攻撃</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
@@ -687,26 +517,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・Idle</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・Attack</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・Skill</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・Ult</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・Dash</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ジャスト回避</t>
     <rPh sb="4" eb="6">
       <t>カイヒ</t>
@@ -714,16 +524,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジャスト回避反撃</t>
-    <rPh sb="4" eb="6">
-      <t>カイヒ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハンゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ダッシュ攻撃</t>
     <rPh sb="4" eb="6">
       <t>コウゲキ</t>
@@ -731,14 +531,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・Idle</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・Caution</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>警戒</t>
     <rPh sb="0" eb="2">
       <t>ケイカイ</t>
@@ -746,46 +538,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・Hit</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・Dead</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡</t>
-    <rPh sb="0" eb="2">
-      <t>シボウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーのカメラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>player攻撃の演出カメラ</t>
-    <rPh sb="0" eb="8">
-      <t>プレイヤーコウゲキ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>エンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒットエフェクト、タイムスケール実装</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージの表示</t>
-    <rPh sb="5" eb="7">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ステージの当たり判定</t>
     <rPh sb="5" eb="6">
       <t>ア</t>
@@ -796,46 +548,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>シーン遷移</t>
-    <rPh sb="3" eb="5">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・タイトルシーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・ゲームシーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・リザルトシーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・セレクトシーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・チュートリアル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・雑魚敵、中ボス、大ボス</t>
-    <rPh sb="1" eb="4">
-      <t>ザコテキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>オオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>必須：入力バッファのシステムがいる！！！</t>
     <rPh sb="0" eb="2">
       <t>ヒッス</t>
@@ -1006,52 +718,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・Hit</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・Dead</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡処理</t>
-    <rPh sb="0" eb="2">
-      <t>シボウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒット処理</t>
-    <rPh sb="3" eb="5">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・Jump</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>jump挙動</t>
-    <rPh sb="4" eb="6">
-      <t>キョドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>jump当たり判定</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>当たり判定の取り方</t>
     <rPh sb="0" eb="1">
       <t>ア</t>
@@ -1327,36 +993,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>空中攻撃</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弱ボタン連携</t>
-    <rPh sb="0" eb="1">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>レンケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>強ボタン連携</t>
-    <rPh sb="0" eb="1">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>レンケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>攻撃仕様</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
@@ -2788,6 +2424,432 @@
     </rPh>
     <rPh sb="63" eb="64">
       <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルのエフェクト制作</t>
+    <rPh sb="9" eb="11">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技システム実装</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技シェーダー演出実装</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャスト回避</t>
+    <rPh sb="4" eb="6">
+      <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃時の細かい当たり判定の制御</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中での攻撃使用制限</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ため攻撃実装するか</t>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>剣を持たせる2種(モデル探しも含む)</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鴉状態での追加モデル(モデル探しも含む)</t>
+    <rPh sb="0" eb="1">
+      <t>カラス</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニメーション調整</t>
+    <rPh sb="7" eb="9">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデル、アニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>より詳しい攻撃</t>
+    <rPh sb="2" eb="3">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2体目作る</t>
+    <rPh sb="1" eb="4">
+      <t>タイメツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラクター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒット時のノックバック</t>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡判定</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージ処理</t>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイムスケール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットストップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃時に斜めに傾く奴</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナナ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カタム</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヤツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃時に少しズームアップするやつ</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキジ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なにか演出カメラ</t>
+    <rPh sb="3" eb="5">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃権のシステム</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スポーンシステム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ制作</t>
+    <rPh sb="4" eb="6">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作説明(コンボ表記、操作ボタン割り当てなど)</t>
+    <rPh sb="0" eb="4">
+      <t>ソウサセツメイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他設定で使うやつ</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーhpなど</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が現れるとき、死ぬときのディゾルブ</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技のエフェクト</t>
+    <rPh sb="0" eb="1">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他なにかあれば</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復アイテム</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーン制作</t>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプションシーン制作</t>
+    <rPh sb="8" eb="10">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクトシーン制作</t>
+    <rPh sb="11" eb="13">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトシーン制作</t>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバーシーン制作</t>
+    <rPh sb="10" eb="12">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアル制作</t>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラシステム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM,SE、ボイスいれ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ</t>
+  </si>
+  <si>
+    <t>残り日数</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニッスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>締め切り</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト締め切り</t>
+    <rPh sb="3" eb="4">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ締め切り</t>
+    <rPh sb="4" eb="5">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ締め切り</t>
+    <rPh sb="3" eb="4">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1日当たりのコスト</t>
+    <rPh sb="1" eb="3">
+      <t>ニチア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2855,7 +2917,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2996,12 +3058,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3009,6 +3065,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3138,7 +3206,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3184,9 +3252,8 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -3195,6 +3262,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -6597,8 +6668,8 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!E3:E92)</f>
-        <v>92</v>
+        <f>SUM(作業工数見積もり!E3:E69)</f>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -6606,8 +6677,8 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!G3:G45,"完了",作業工数見積もり!E3:E45)</f>
-        <v>6</v>
+        <f>SUMIF(作業工数見積もり!G3:G19,"完了",作業工数見積もり!E3:E19)</f>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -6623,7 +6694,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.405152224824356E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6641,7 +6712,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46200</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6666,7 +6737,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.21717171717171718</v>
+        <v>-0.45202020202020204</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6683,7 +6754,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.22872340425531915</v>
+        <v>-0.47606382978723405</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6700,7 +6771,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.23561643835616439</v>
+        <v>-0.49041095890410957</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -6784,7 +6855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="69.625" style="10" bestFit="1" customWidth="1"/>
@@ -6798,18 +6869,19 @@
     <col min="10" max="11" width="11.5" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.5" style="10" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="9" style="10"/>
+    <col min="15" max="15" width="9" style="11"/>
     <col min="16" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="14" t="s">
         <v>31</v>
       </c>
@@ -6832,21 +6904,27 @@
         <v>34</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>58</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="17" t="s">
         <v>35</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>5</v>
@@ -6855,36 +6933,37 @@
         <v>18</v>
       </c>
       <c r="E3" s="16">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>39</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="J3" s="10">
-        <f ca="1">SUM(J4,J5,J6)</f>
-        <v>87</v>
+        <f>SUM(J4,J5,J6)</f>
+        <v>179</v>
       </c>
       <c r="K3" s="10">
-        <f>SUMIFS(E3:E62,G3:G62,"未着手")</f>
-        <v>80</v>
+        <f>SUMIFS(E3:E36,G3:G36,"未着手")</f>
+        <v>107</v>
       </c>
       <c r="L3" s="10">
-        <f>SUM(F3:F62)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <f>SUM(F3:F36)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <f ca="1">INT(J11 - TODAY())</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="17" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>14</v>
@@ -6893,7 +6972,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>39</v>
@@ -6902,24 +6981,32 @@
         <v>28</v>
       </c>
       <c r="J4" s="29">
-        <f ca="1">SUMIF(D3:D60,I4,E3:E59)</f>
-        <v>85.5</v>
+        <f>SUMIF(D3:D48,I4,E3:E48)</f>
+        <v>104</v>
       </c>
       <c r="K4" s="10">
-        <f>SUMIFS($E$3:$E$62,$G$3:$G$62,"未着手",$D$3:$D$62,I4)</f>
-        <v>78.5</v>
+        <f>SUMIFS(E3:E48,G3:G48,"未着手",D3:D48,I4)</f>
+        <v>104</v>
       </c>
       <c r="L4" s="10">
-        <f>SUMIFS(F3:F62,D3:D62,I4)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <f>SUMIFS(F3:F36,D3:D36,I4)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="10">
+        <f ca="1">INT(J12-TODAY())</f>
+        <v>19</v>
+      </c>
+      <c r="N4" s="10">
+        <f ca="1">J4/M4</f>
+        <v>5.4736842105263159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="17" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>14</v>
@@ -6928,7 +7015,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>39</v>
@@ -6937,19 +7024,27 @@
         <v>0</v>
       </c>
       <c r="J5" s="29">
-        <f ca="1">SUMIF(D4:D62,I5,E4:E60)</f>
-        <v>1.5</v>
+        <f>SUMIF(D3:D48,I5,E3:E48)</f>
+        <v>59</v>
       </c>
       <c r="K5" s="10">
-        <f>SUMIFS($E$3:$E$62,$G$3:$G$62,"未着手",$D$3:$D$62,I5)</f>
-        <v>1.5</v>
+        <f>SUMIFS(E3:E48,G3:G48,"未着手",D3:D48,I5)</f>
+        <v>59</v>
       </c>
       <c r="L5" s="10">
-        <f>SUMIFS(F4:F63,D4:D63,I5)</f>
+        <f>SUMIFS(F4:F40,D4:D40,I5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="10">
+        <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
+        <v>43</v>
+      </c>
+      <c r="N5" s="10">
+        <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
+        <v>1.3720930232558139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="17" t="s">
         <v>35</v>
       </c>
@@ -6963,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>39</v>
@@ -6972,24 +7067,32 @@
         <v>29</v>
       </c>
       <c r="J6" s="29">
-        <f ca="1">SUMIF(D5:D63,I6,E5:E62)</f>
+        <f>SUMIF(D3:D48,I6,E3:E48)</f>
+        <v>16</v>
+      </c>
+      <c r="K6" s="10">
+        <f>SUMIFS(E3:E48,G3:G48,"未着手",D3:D48,I6)</f>
+        <v>16</v>
+      </c>
+      <c r="L6" s="10">
+        <f>SUMIFS(F5:F40,D5:D40,I6)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="10">
-        <f>SUMIFS($E$3:$E$62,$G$3:$G$62,"未着手",$D$3:$D$62,I6)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="10">
-        <f>SUMIFS(F5:F63,D5:D63,I6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="10">
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="N6" s="10">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.26666666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="18" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>5</v>
@@ -6998,28 +7101,18 @@
         <v>18</v>
       </c>
       <c r="E7" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="10">
-        <f>COUNTIF(G3:G60,"作業中")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="18" t="s">
-        <v>37</v>
+    </row>
+    <row r="8" spans="1:14" outlineLevel="1">
+      <c r="A8" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>59</v>
+        <v>253</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5</v>
@@ -7028,21 +7121,18 @@
         <v>18</v>
       </c>
       <c r="E8" s="16">
-        <v>2</v>
-      </c>
-      <c r="F8" s="16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="18" t="s">
-        <v>37</v>
+    <row r="9" spans="1:14" outlineLevel="1">
+      <c r="A9" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>87</v>
+        <v>254</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5</v>
@@ -7050,16 +7140,19 @@
       <c r="D9" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E9" s="16">
+        <v>2</v>
+      </c>
       <c r="G9" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="18" t="s">
-        <v>37</v>
+    <row r="10" spans="1:14" outlineLevel="1">
+      <c r="A10" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>88</v>
+        <v>255</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>5</v>
@@ -7067,56 +7160,74 @@
       <c r="D10" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E10" s="16">
+        <v>12</v>
+      </c>
       <c r="G10" s="16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="I10" s="19" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" outlineLevel="1">
       <c r="A11" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>92</v>
+        <v>44</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>256</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E11" s="16">
+        <v>3</v>
+      </c>
       <c r="G11" s="16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" outlineLevel="1">
+      <c r="I11" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="J11" s="51">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>43</v>
+        <v>257</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="16">
-        <v>1</v>
-      </c>
-      <c r="F12" s="16">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" outlineLevel="1">
+        <v>39</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J12" s="52">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>69</v>
+        <v>258</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5</v>
@@ -7127,37 +7238,85 @@
       <c r="E13" s="16">
         <v>1</v>
       </c>
-      <c r="F13" s="16">
-        <v>1</v>
-      </c>
       <c r="G13" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" outlineLevel="1">
-      <c r="A14" s="19"/>
+        <v>39</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="J13" s="52">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="19" t="s">
+        <v>44</v>
+      </c>
       <c r="B14" s="10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" outlineLevel="1">
-      <c r="A15" s="19"/>
+        <v>261</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="16">
+        <v>2</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J14" s="52">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="19" t="s">
+        <v>44</v>
+      </c>
       <c r="B15" s="10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" outlineLevel="1">
-      <c r="A16" s="19"/>
+        <v>262</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="16">
+        <v>2</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="19" t="s">
+        <v>44</v>
+      </c>
       <c r="B16" s="10" t="s">
-        <v>138</v>
+        <v>259</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>93</v>
+        <v>44</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>263</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5</v>
@@ -7165,16 +7324,19 @@
       <c r="D17" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E17" s="16">
+        <v>8</v>
+      </c>
       <c r="G17" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:7" outlineLevel="1">
-      <c r="A18" s="19" t="s">
-        <v>45</v>
+    <row r="18" spans="1:7">
+      <c r="A18" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>5</v>
@@ -7183,67 +7345,58 @@
         <v>18</v>
       </c>
       <c r="E18" s="16">
-        <v>1</v>
-      </c>
-      <c r="F18" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" outlineLevel="1">
-      <c r="A19" s="19" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="16">
-        <v>1</v>
-      </c>
-      <c r="F19" s="16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" outlineLevel="1">
-      <c r="A20" s="19" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>85</v>
+        <v>277</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="16">
-        <v>1</v>
-      </c>
-      <c r="F20" s="16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" outlineLevel="1">
-      <c r="A21" s="19" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>165</v>
+        <v>278</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>5</v>
@@ -7251,33 +7404,39 @@
       <c r="D21" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E21" s="16">
+        <v>4</v>
+      </c>
       <c r="G21" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>94</v>
+      <c r="A22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>266</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E22" s="16">
+        <v>8</v>
+      </c>
       <c r="G22" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:7" outlineLevel="1">
-      <c r="A23" s="19" t="s">
-        <v>45</v>
+    <row r="23" spans="1:7">
+      <c r="A23" s="50" t="s">
+        <v>267</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>5</v>
@@ -7292,18 +7451,32 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:7" outlineLevel="1">
-      <c r="A24" s="19"/>
+    <row r="24" spans="1:7">
+      <c r="A24" s="50" t="s">
+        <v>267</v>
+      </c>
       <c r="B24" s="10" t="s">
-        <v>167</v>
+        <v>269</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="16">
+        <v>2</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>95</v>
+      <c r="A25" s="50" t="s">
+        <v>267</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>270</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>5</v>
@@ -7311,16 +7484,19 @@
       <c r="D25" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E25" s="16">
+        <v>1</v>
+      </c>
       <c r="G25" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:7" outlineLevel="1">
-      <c r="A26" s="19" t="s">
-        <v>45</v>
+    <row r="26" spans="1:7">
+      <c r="A26" s="50" t="s">
+        <v>267</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>89</v>
+        <v>271</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>5</v>
@@ -7329,18 +7505,18 @@
         <v>18</v>
       </c>
       <c r="E26" s="16">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>96</v>
+      <c r="A27" s="50" t="s">
+        <v>267</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>272</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>5</v>
@@ -7348,16 +7524,19 @@
       <c r="D27" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E27" s="16">
+        <v>2</v>
+      </c>
       <c r="G27" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:7" outlineLevel="1">
-      <c r="A28" s="19" t="s">
-        <v>45</v>
+    <row r="28" spans="1:7">
+      <c r="A28" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>90</v>
+        <v>273</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>5</v>
@@ -7366,21 +7545,18 @@
         <v>18</v>
       </c>
       <c r="E28" s="16">
-        <v>1</v>
-      </c>
-      <c r="F28" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" outlineLevel="1">
-      <c r="A29" s="19" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>99</v>
+        <v>274</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>5</v>
@@ -7389,18 +7565,18 @@
         <v>18</v>
       </c>
       <c r="E29" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:7" outlineLevel="1">
-      <c r="A30" s="19" t="s">
-        <v>45</v>
+    <row r="30" spans="1:7">
+      <c r="A30" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>97</v>
+        <v>294</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>5</v>
@@ -7409,18 +7585,18 @@
         <v>18</v>
       </c>
       <c r="E30" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:7" outlineLevel="1">
-      <c r="A31" s="19" t="s">
-        <v>45</v>
+    <row r="31" spans="1:7">
+      <c r="A31" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>98</v>
+        <v>275</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>5</v>
@@ -7429,30 +7605,38 @@
         <v>18</v>
       </c>
       <c r="E31" s="16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="39"/>
+      <c r="A32" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>276</v>
+      </c>
       <c r="C32" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D32" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E32" s="16">
+        <v>6</v>
+      </c>
       <c r="G32" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:7" outlineLevel="1">
-      <c r="A33" s="19" t="s">
-        <v>45</v>
+    <row r="33" spans="1:7">
+      <c r="A33" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>279</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>5</v>
@@ -7460,13 +7644,19 @@
       <c r="D33" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E33" s="16">
+        <v>3</v>
+      </c>
       <c r="G33" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:7" outlineLevel="1">
-      <c r="A34" s="19" t="s">
-        <v>45</v>
+    <row r="34" spans="1:7">
+      <c r="A34" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>5</v>
@@ -7474,703 +7664,295 @@
       <c r="D34" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="E34" s="16">
+        <v>0</v>
+      </c>
       <c r="G34" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" outlineLevel="1">
-      <c r="A35" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>5</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>281</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>18</v>
+        <v>296</v>
+      </c>
+      <c r="E35" s="16">
+        <v>2</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:7" outlineLevel="1">
-      <c r="A36" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>132</v>
+    <row r="36" spans="1:7">
+      <c r="A36" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>282</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" outlineLevel="1">
-      <c r="A37" s="19" t="s">
-        <v>45</v>
+        <v>296</v>
+      </c>
+      <c r="E36" s="16">
+        <v>1</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" outlineLevel="1">
-      <c r="A38" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>5</v>
+        <v>296</v>
+      </c>
+      <c r="E37" s="16">
+        <v>1</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>284</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" outlineLevel="1">
-      <c r="A39" s="19" t="s">
-        <v>45</v>
+        <v>10</v>
+      </c>
+      <c r="E38" s="16">
+        <v>6</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="10" t="s">
+        <v>280</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>5</v>
+        <v>285</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="E39" s="16">
+        <v>6</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="19" t="s">
-        <v>45</v>
+      <c r="A40" s="10" t="s">
+        <v>280</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="16">
-        <v>1</v>
-      </c>
-      <c r="F40" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="19" t="s">
-        <v>45</v>
+      <c r="A41" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>46</v>
+        <v>287</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E41" s="16">
-        <v>2</v>
-      </c>
-      <c r="F41" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="19" t="s">
-        <v>45</v>
+      <c r="A42" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>47</v>
+        <v>288</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E42" s="16">
-        <v>2</v>
-      </c>
-      <c r="F42" s="16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="19" t="s">
-        <v>45</v>
+      <c r="A43" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>51</v>
+        <v>289</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E43" s="16">
-        <v>8</v>
-      </c>
-      <c r="F43" s="16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="20" t="s">
-        <v>49</v>
+      <c r="A44" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="E44" s="16">
+        <v>8</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>100</v>
+      <c r="A45" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>291</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E45" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="F45" s="16">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="20" t="s">
-        <v>49</v>
+      <c r="A46" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>43</v>
+        <v>292</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E46" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="F46" s="16">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="39" t="s">
-        <v>93</v>
+      <c r="A47" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>293</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="E47" s="16">
+        <v>12</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="20" t="s">
-        <v>49</v>
+      <c r="A48" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>18</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="E48" s="16">
+        <v>12</v>
+      </c>
+      <c r="F48" s="10"/>
       <c r="G48" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="16">
-        <v>2</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" s="16">
-        <v>1</v>
-      </c>
-      <c r="F55" s="16">
-        <v>3</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" s="16">
-        <v>1</v>
-      </c>
-      <c r="F56" s="16">
-        <v>1</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" s="16">
-        <v>12</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" s="16">
-        <v>6</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" s="16">
-        <v>3</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G62" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64" s="16">
-        <v>3</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" s="16">
-        <v>2</v>
-      </c>
-      <c r="F65" s="16">
-        <v>1</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G66" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G70" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G71" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B2:G63" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G59">
-      <sortCondition ref="B2:B59"/>
+  <autoFilter ref="B2:G40" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G32">
+      <sortCondition ref="B2:B32"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C71" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
-      <formula1>"S,A,B,C"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D71" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+  <dataValidations disablePrompts="1" count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D48" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G71" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G48" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C48" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+      <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8185,35 +7967,35 @@
   <sheetData>
     <row r="2" spans="3:16">
       <c r="O2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="3:16">
       <c r="C3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="3:16">
       <c r="C4" s="11" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="3:16">
@@ -8229,7 +8011,7 @@
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="3:16">
@@ -8289,7 +8071,7 @@
       </c>
       <c r="L7" s="33"/>
       <c r="M7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P7">
         <v>74</v>
@@ -8322,7 +8104,7 @@
       </c>
       <c r="L8" s="37"/>
       <c r="M8">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="3:16">
@@ -8348,7 +8130,7 @@
         <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="L9" s="34"/>
       <c r="M9">
@@ -8362,30 +8144,30 @@
     </row>
     <row r="12" spans="3:16">
       <c r="C12" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="3:16">
       <c r="C13" s="11" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="3:16">
@@ -8455,7 +8237,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="3:11">
+    <row r="17" spans="3:13">
       <c r="C17" s="31">
         <v>21</v>
       </c>
@@ -8478,7 +8260,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:11">
+    <row r="18" spans="3:13">
       <c r="C18" s="31">
         <v>28</v>
       </c>
@@ -8496,35 +8278,35 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="3:11">
+    <row r="20" spans="3:13">
       <c r="C20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13">
       <c r="C21" s="11" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13">
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
@@ -8541,53 +8323,53 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:11">
+    <row r="23" spans="3:13">
       <c r="C23" s="31">
         <v>5</v>
       </c>
       <c r="D23" s="31">
         <v>6</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="31">
         <v>7</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="31">
         <v>8</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="31">
         <v>9</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="31">
         <v>10</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="31">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="3:11">
-      <c r="C24" s="19">
+    <row r="24" spans="3:13">
+      <c r="C24" s="31">
         <v>12</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="31">
         <v>13</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="31">
         <v>14</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="31">
         <v>15</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="31">
         <v>16</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="31">
         <v>17</v>
       </c>
       <c r="I24" s="19">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="3:11">
+    <row r="25" spans="3:13">
       <c r="C25" s="19">
         <v>19</v>
       </c>
@@ -8610,23 +8392,23 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="3:11">
-      <c r="C26" s="19">
+    <row r="26" spans="3:13">
+      <c r="C26" s="49">
         <v>26</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="49">
         <v>27</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="49">
         <v>28</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="49">
         <v>29</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="49">
         <v>30</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="49">
         <v>31</v>
       </c>
       <c r="I26" s="11"/>
@@ -8634,42 +8416,47 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="3:11">
+    <row r="29" spans="3:13">
+      <c r="M29">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13">
       <c r="C30" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="3:11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13">
       <c r="C31" s="11" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="3:11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13">
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
-      <c r="I32" s="19">
+      <c r="I32" s="49">
         <v>1</v>
       </c>
       <c r="K32">
@@ -8680,30 +8467,30 @@
       <c r="C33" s="19">
         <v>2</v>
       </c>
-      <c r="D33" s="37">
+      <c r="D33" s="19">
         <v>3</v>
       </c>
-      <c r="E33" s="37">
+      <c r="E33" s="19">
         <v>4</v>
       </c>
-      <c r="F33" s="37">
+      <c r="F33" s="19">
         <v>5</v>
       </c>
-      <c r="G33" s="37">
+      <c r="G33" s="19">
         <v>6</v>
       </c>
-      <c r="H33" s="37">
+      <c r="H33" s="19">
         <v>7</v>
       </c>
-      <c r="I33" s="37">
+      <c r="I33" s="19">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="3:9">
-      <c r="C34" s="37">
+      <c r="C34" s="19">
         <v>9</v>
       </c>
-      <c r="D34" s="37">
+      <c r="D34" s="19">
         <v>10</v>
       </c>
       <c r="E34" s="37">
@@ -8807,13 +8594,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8821,10 +8608,10 @@
         <v>46166</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8832,21 +8619,21 @@
         <v>46167</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="C5" t="s">
-        <v>145</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8854,7 +8641,7 @@
         <v>46190</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8862,7 +8649,7 @@
         <v>46191</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8870,17 +8657,17 @@
         <v>46192</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8888,12 +8675,12 @@
         <v>46193</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="C13" t="s">
-        <v>280</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -8901,17 +8688,17 @@
         <v>46194</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="C15" t="s">
-        <v>282</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="C16" t="s">
-        <v>283</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8919,37 +8706,37 @@
         <v>46195</v>
       </c>
       <c r="C17" t="s">
-        <v>284</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="C18" t="s">
-        <v>285</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="C19" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="C20" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="C21" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="C22" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="C23" t="s">
-        <v>289</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8957,17 +8744,17 @@
         <v>46196</v>
       </c>
       <c r="C24" t="s">
-        <v>291</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="C25" t="s">
-        <v>292</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="C26" t="s">
-        <v>293</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8975,12 +8762,12 @@
         <v>46197</v>
       </c>
       <c r="C27" t="s">
-        <v>294</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="C28" t="s">
-        <v>295</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8988,47 +8775,47 @@
         <v>46198</v>
       </c>
       <c r="C29" t="s">
-        <v>296</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="C30" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="C31" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="C32" t="s">
-        <v>299</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>300</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
-        <v>301</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" t="s">
-        <v>303</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="3:3">
       <c r="C36" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" t="s">
-        <v>304</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -9050,101 +8837,101 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="D3" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="B7" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>184</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>185</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>186</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>188</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>189</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="2:4">
       <c r="B18" t="s">
-        <v>261</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" t="s">
-        <v>262</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -9159,178 +8946,178 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="42"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="44"/>
+      <c r="A1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="45"/>
-      <c r="G2" s="46"/>
+      <c r="A2" s="44"/>
+      <c r="G2" s="45"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="45"/>
+      <c r="A3" s="44"/>
       <c r="C3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G3" s="46"/>
+        <v>187</v>
+      </c>
+      <c r="G3" s="45"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="45"/>
+      <c r="A4" s="44"/>
       <c r="C4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G4" s="46"/>
+        <v>71</v>
+      </c>
+      <c r="G4" s="45"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="45"/>
+      <c r="A5" s="44"/>
       <c r="C5" t="s">
-        <v>240</v>
-      </c>
-      <c r="G5" s="46"/>
+        <v>188</v>
+      </c>
+      <c r="G5" s="45"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="45"/>
+      <c r="A6" s="44"/>
       <c r="C6" t="s">
-        <v>242</v>
-      </c>
-      <c r="G6" s="46"/>
+        <v>190</v>
+      </c>
+      <c r="G6" s="45"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="45"/>
+      <c r="A7" s="44"/>
       <c r="C7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G7" s="46"/>
+        <v>196</v>
+      </c>
+      <c r="G7" s="45"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="45"/>
-      <c r="G8" s="46"/>
+      <c r="A8" s="44"/>
+      <c r="G8" s="45"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="45"/>
+      <c r="A9" s="44"/>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="F9" t="s">
-        <v>246</v>
-      </c>
-      <c r="G9" s="46"/>
+        <v>194</v>
+      </c>
+      <c r="G9" s="45"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="45"/>
+      <c r="A10" s="44"/>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="F10" t="s">
-        <v>247</v>
-      </c>
-      <c r="G10" s="46"/>
+        <v>195</v>
+      </c>
+      <c r="G10" s="45"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="45"/>
+      <c r="A11" s="44"/>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>193</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="46"/>
+        <v>69</v>
+      </c>
+      <c r="G11" s="45"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="45"/>
+      <c r="A12" s="44"/>
       <c r="B12" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="F12" t="s">
-        <v>242</v>
-      </c>
-      <c r="G12" s="46"/>
+        <v>190</v>
+      </c>
+      <c r="G12" s="45"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="45"/>
+      <c r="A13" s="44"/>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>196</v>
       </c>
       <c r="D13" t="s">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="F13" t="s">
-        <v>240</v>
-      </c>
-      <c r="G13" s="46"/>
+        <v>188</v>
+      </c>
+      <c r="G13" s="45"/>
     </row>
     <row r="14" spans="1:7" ht="19.5" thickBot="1">
-      <c r="A14" s="47"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48" t="s">
-        <v>248</v>
-      </c>
-      <c r="G14" s="49"/>
+      <c r="A14" s="46"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" s="48"/>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>249</v>
+        <v>197</v>
       </c>
       <c r="D17" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>253</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="D20" t="s">
-        <v>254</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="D22" t="s">
-        <v>255</v>
+        <v>203</v>
       </c>
       <c r="F22" t="s">
-        <v>256</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -9346,240 +9133,240 @@
   <sheetData>
     <row r="1" spans="1:33">
       <c r="M1" t="s">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="T1" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="AE1" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:33">
-      <c r="B2" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
+      <c r="B2" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
       <c r="M2" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="AE2" t="s">
-        <v>192</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:33">
       <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M3" t="s">
+        <v>103</v>
+      </c>
+      <c r="R3" t="s">
         <v>146</v>
       </c>
-      <c r="M3" t="s">
-        <v>152</v>
-      </c>
-      <c r="R3" t="s">
-        <v>198</v>
-      </c>
       <c r="AE3" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="AG3" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:33">
       <c r="B4" t="s">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="AE4" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:33">
       <c r="B5" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="AE5" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:33">
       <c r="B6" t="s">
-        <v>148</v>
+        <v>99</v>
       </c>
       <c r="M6" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="AE6" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:33">
       <c r="B7" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="R7" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="AE7" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:33">
       <c r="B8" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="M8" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:33">
       <c r="AE10" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:33">
       <c r="M11" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:33">
       <c r="M12" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="AE12" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:33">
       <c r="B13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:33">
       <c r="D15" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="M15" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:33">
       <c r="M16" t="s">
-        <v>172</v>
-      </c>
-      <c r="AF16" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="AG16" s="40"/>
+        <v>120</v>
+      </c>
+      <c r="AF16" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG16" s="39"/>
     </row>
     <row r="17" spans="1:37">
       <c r="B17" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="F17" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="M17" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="AF17" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="AK17" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:37">
       <c r="M18" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="AF18" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:37">
       <c r="B19" t="s">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="M19" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="AF19" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:37">
       <c r="AF20" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:37">
       <c r="B21" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:37">
       <c r="M22" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:37">
       <c r="D24" t="s">
-        <v>269</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:37">
       <c r="A28" t="s">
-        <v>270</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>272</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>273</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="O43" t="s">
-        <v>271</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -9598,138 +9385,138 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:24">
-      <c r="C2" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
+      <c r="C2" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
       <c r="Q2" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="3:24">
       <c r="C4" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="Q4" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="3:24">
       <c r="C5" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="I5" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="Q5" t="s">
-        <v>234</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="3:24">
       <c r="C6" t="s">
-        <v>235</v>
+        <v>183</v>
       </c>
       <c r="I6" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="Q6" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="S6" t="s">
-        <v>209</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="3:24">
       <c r="Q7" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="3:24">
       <c r="C8" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c r="Q8" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="3:24">
       <c r="C9" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="I9" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="Q9" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="X9" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="3:24">
       <c r="C10" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
       <c r="Q10" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="3:24">
       <c r="C11" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="I11" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="Q11" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="3:24">
       <c r="Q12" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="3:24">
       <c r="C13" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="Q13" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="S13" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="3:24">
       <c r="C14" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="I14" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="Q14" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="S14" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="3:24">
       <c r="Q15" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="R15" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="3:24">
       <c r="Q16" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="S16" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -9746,61 +9533,61 @@
     <row r="1" spans="3:35" ht="19.5" thickBot="1"/>
     <row r="2" spans="3:35">
       <c r="C2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE2" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="44"/>
+        <v>116</v>
+      </c>
+      <c r="AE2" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="43"/>
     </row>
     <row r="3" spans="3:35">
-      <c r="AE3" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="AI3" s="46"/>
+      <c r="AE3" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI3" s="45"/>
     </row>
     <row r="4" spans="3:35">
-      <c r="AE4" s="45" t="s">
-        <v>260</v>
-      </c>
-      <c r="AI4" s="46"/>
+      <c r="AE4" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI4" s="45"/>
     </row>
     <row r="5" spans="3:35" ht="19.5" thickBot="1">
-      <c r="AE5" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="49"/>
+      <c r="AE5" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="48"/>
     </row>
     <row r="9" spans="3:35">
       <c r="AE9" t="s">
-        <v>257</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="34:47">
       <c r="AN31" t="s">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AU31" t="s">
-        <v>268</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="34:47">
       <c r="AH32" t="s">
-        <v>267</v>
+        <v>215</v>
       </c>
       <c r="AN32" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="40:40">
       <c r="AN33" t="s">
-        <v>266</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -9811,12 +9598,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10055,20 +9844,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10093,12 +9883,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8110C39F-FFDF-455C-BC55-E77292874706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62602C97-0F9B-48E6-8073-CE78F56E5B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="304">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -2850,6 +2850,13 @@
     <t>1日当たりのコスト</t>
     <rPh sb="1" eb="3">
       <t>ニチア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今日はノックバックをする</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6946,12 +6953,12 @@
         <v>179</v>
       </c>
       <c r="K3" s="10">
-        <f>SUMIFS(E3:E36,G3:G36,"未着手")</f>
-        <v>107</v>
+        <f>SUMIFS(E3:E48,G3:G48,"未着手")</f>
+        <v>176</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
@@ -6986,11 +6993,11 @@
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E48,G3:G48,"未着手",D3:D48,I4)</f>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F36,D3:D36,I4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
@@ -7447,8 +7454,11 @@
       <c r="E23" s="16">
         <v>3</v>
       </c>
+      <c r="F23" s="16">
+        <v>1</v>
+      </c>
       <c r="G23" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7944,7 +7954,7 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D48" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
@@ -8584,7 +8594,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8793,29 +8803,40 @@
         <v>247</v>
       </c>
     </row>
-    <row r="33" spans="3:3">
+    <row r="33" spans="1:3">
       <c r="C33" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="34" spans="3:3">
+    <row r="34" spans="1:3">
       <c r="C34" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="35" spans="3:3">
+    <row r="35" spans="1:3">
       <c r="C35" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="36" spans="3:3">
+    <row r="36" spans="1:3">
       <c r="C36" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="37" spans="3:3">
+    <row r="37" spans="1:3">
+      <c r="A37" s="1">
+        <v>46200</v>
+      </c>
       <c r="C37" t="s">
         <v>252</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1">
+        <v>46201</v>
+      </c>
+      <c r="C38" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -9598,14 +9619,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9844,21 +9863,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9883,9 +9901,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62602C97-0F9B-48E6-8073-CE78F56E5B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1374A707-6858-4135-8401-FF1C9F178422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="3840" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="308">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -1155,13 +1155,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>①背景</t>
-    <rPh sb="1" eb="3">
-      <t>ハイケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>②文字を描画</t>
     <rPh sb="0" eb="3">
       <t>2モジ</t>
@@ -2857,6 +2850,101 @@
     <t>今日はノックバックをする</t>
     <rPh sb="0" eb="2">
       <t>キョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①背景(赤色に)</t>
+    <rPh sb="1" eb="3">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>アカイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②エフェクトを描画(白色に)</t>
+    <rPh sb="7" eb="9">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シロイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノックバック終わったので、必殺技の演出を作る</t>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技のレンダーターゲットを分けて、マップを赤くしたところ、けっこういい感じだから次は剣のエフェクトをとりあえず作って出す</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、血殺の文字を入れて、完成させる、エフェクトは先輩に聞いて一緒に作る</t>
+    <rPh sb="5" eb="6">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6697,7 +6785,7 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
@@ -6719,7 +6807,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6740,11 +6828,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-396</v>
+        <v>-397</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.45202020202020204</v>
+        <v>-0.45088161209068012</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6757,11 +6845,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-376</v>
+        <v>-377</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.47606382978723405</v>
+        <v>-0.47480106100795755</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6774,11 +6862,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-365</v>
+        <v>-366</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.49041095890410957</v>
+        <v>-0.48907103825136611</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -6920,10 +7008,10 @@
         <v>58</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -6962,7 +7050,7 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7001,11 +7089,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>5.4736842105263159</v>
+        <v>5.7777777777777777</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7044,11 +7132,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>1.3720930232558139</v>
+        <v>1.4047619047619047</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7087,11 +7175,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.26666666666666666</v>
+        <v>0.2711864406779661</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7119,7 +7207,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5</v>
@@ -7139,7 +7227,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5</v>
@@ -7159,7 +7247,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>5</v>
@@ -7174,7 +7262,7 @@
         <v>39</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:14" outlineLevel="1">
@@ -7182,10 +7270,10 @@
         <v>44</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>18</v>
@@ -7197,7 +7285,7 @@
         <v>39</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J11" s="51">
         <v>46265</v>
@@ -7208,10 +7296,10 @@
         <v>44</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>18</v>
@@ -7223,7 +7311,7 @@
         <v>39</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J12" s="52">
         <v>46220</v>
@@ -7234,7 +7322,7 @@
         <v>44</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5</v>
@@ -7249,7 +7337,7 @@
         <v>39</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J13" s="52">
         <v>46244</v>
@@ -7260,7 +7348,7 @@
         <v>44</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>5</v>
@@ -7275,7 +7363,7 @@
         <v>39</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J14" s="52">
         <v>46261</v>
@@ -7286,7 +7374,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>5</v>
@@ -7306,7 +7394,7 @@
         <v>44</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>14</v>
@@ -7323,7 +7411,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5</v>
@@ -7343,7 +7431,7 @@
         <v>46</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>5</v>
@@ -7363,10 +7451,10 @@
         <v>46</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>18</v>
@@ -7383,10 +7471,10 @@
         <v>46</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>18</v>
@@ -7403,7 +7491,7 @@
         <v>46</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>5</v>
@@ -7423,10 +7511,10 @@
         <v>46</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>18</v>
@@ -7440,10 +7528,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="50" t="s">
+        <v>266</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>268</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>5</v>
@@ -7463,10 +7551,10 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>5</v>
@@ -7483,10 +7571,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>5</v>
@@ -7503,10 +7591,10 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>5</v>
@@ -7523,10 +7611,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>5</v>
@@ -7546,7 +7634,7 @@
         <v>40</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>5</v>
@@ -7566,7 +7654,7 @@
         <v>40</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>5</v>
@@ -7586,7 +7674,7 @@
         <v>40</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>5</v>
@@ -7606,7 +7694,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>5</v>
@@ -7626,7 +7714,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>5</v>
@@ -7646,7 +7734,7 @@
         <v>41</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>5</v>
@@ -7686,10 +7774,10 @@
         <v>42</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E35" s="16">
         <v>2</v>
@@ -7703,13 +7791,13 @@
         <v>42</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E36" s="16">
         <v>1</v>
@@ -7723,10 +7811,10 @@
         <v>42</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E37" s="16">
         <v>1</v>
@@ -7737,10 +7825,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>10</v>
@@ -7754,10 +7842,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D39" s="16" t="s">
         <v>10</v>
@@ -7771,10 +7859,10 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>18</v>
@@ -7791,10 +7879,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>10</v>
@@ -7811,7 +7899,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>5</v>
@@ -7831,7 +7919,7 @@
         <v>38</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>5</v>
@@ -7851,7 +7939,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>5</v>
@@ -7871,7 +7959,7 @@
         <v>38</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>5</v>
@@ -7891,7 +7979,7 @@
         <v>38</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>5</v>
@@ -7911,7 +7999,7 @@
         <v>38</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>5</v>
@@ -7931,13 +8019,13 @@
         <v>38</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E48" s="16">
         <v>12</v>
@@ -8594,7 +8682,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -8651,7 +8739,7 @@
         <v>46190</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8659,7 +8747,7 @@
         <v>46191</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8667,17 +8755,17 @@
         <v>46192</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8685,12 +8773,12 @@
         <v>46193</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="C13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -8698,17 +8786,17 @@
         <v>46194</v>
       </c>
       <c r="C14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="C15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="C16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8716,37 +8804,37 @@
         <v>46195</v>
       </c>
       <c r="C17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="C18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="C19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="C20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="C21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="C22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="C23" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8754,17 +8842,17 @@
         <v>46196</v>
       </c>
       <c r="C24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="C25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="C26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8772,12 +8860,12 @@
         <v>46197</v>
       </c>
       <c r="C27" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="C28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8785,42 +8873,42 @@
         <v>46198</v>
       </c>
       <c r="C29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="C30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="C31" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="C32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="C33" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="C34" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="C35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="C36" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -8828,7 +8916,7 @@
         <v>46200</v>
       </c>
       <c r="C37" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -8836,7 +8924,22 @@
         <v>46201</v>
       </c>
       <c r="C38" t="s">
-        <v>303</v>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="C39" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="C40" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="C41" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -8908,7 +9011,7 @@
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>134</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="2:4">
@@ -8916,7 +9019,7 @@
         <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="2:4">
@@ -8924,12 +9027,17 @@
         <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="D16" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -8937,22 +9045,22 @@
         <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="2:4">
       <c r="B18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -8982,7 +9090,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="44"/>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G3" s="45"/>
     </row>
@@ -8996,21 +9104,21 @@
     <row r="5" spans="1:7">
       <c r="A5" s="44"/>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G5" s="45"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="44"/>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G6" s="45"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="44"/>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G7" s="45"/>
     </row>
@@ -9021,13 +9129,13 @@
     <row r="9" spans="1:7">
       <c r="A9" s="44"/>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G9" s="45"/>
     </row>
@@ -9037,20 +9145,20 @@
         <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G10" s="45"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="44"/>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F11" t="s">
         <v>69</v>
@@ -9060,26 +9168,26 @@
     <row r="12" spans="1:7">
       <c r="A12" s="44"/>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G12" s="45"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="44"/>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G13" s="45"/>
     </row>
@@ -9088,20 +9196,20 @@
       <c r="B14" s="47"/>
       <c r="C14" s="47"/>
       <c r="D14" s="47" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E14" s="47"/>
       <c r="F14" s="47" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G14" s="48"/>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -9109,7 +9217,7 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:6">
@@ -9117,15 +9225,15 @@
         <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="2:6">
@@ -9135,10 +9243,10 @@
     </row>
     <row r="22" spans="2:6">
       <c r="D22" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" t="s">
         <v>203</v>
-      </c>
-      <c r="F22" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -9165,7 +9273,7 @@
     </row>
     <row r="2" spans="1:33">
       <c r="B2" s="40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -9174,7 +9282,7 @@
         <v>102</v>
       </c>
       <c r="AE2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -9185,13 +9293,13 @@
         <v>103</v>
       </c>
       <c r="R3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AE3" t="s">
         <v>126</v>
       </c>
       <c r="AG3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -9199,7 +9307,7 @@
         <v>98</v>
       </c>
       <c r="M4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AE4" t="s">
         <v>127</v>
@@ -9251,7 +9359,7 @@
     </row>
     <row r="10" spans="1:33">
       <c r="AE10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -9264,7 +9372,7 @@
         <v>118</v>
       </c>
       <c r="AE12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -9288,7 +9396,7 @@
     </row>
     <row r="15" spans="1:33">
       <c r="D15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M15" t="s">
         <v>119</v>
@@ -9299,7 +9407,7 @@
         <v>120</v>
       </c>
       <c r="AF16" s="39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG16" s="39"/>
     </row>
@@ -9314,10 +9422,10 @@
         <v>124</v>
       </c>
       <c r="AF17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AK17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -9325,7 +9433,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -9339,12 +9447,12 @@
         <v>122</v>
       </c>
       <c r="AF19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:37">
       <c r="AF20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -9357,17 +9465,17 @@
     </row>
     <row r="22" spans="1:37">
       <c r="M22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:37">
       <c r="D24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:37">
       <c r="A28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -9377,17 +9485,17 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="O43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -9407,137 +9515,137 @@
   <sheetData>
     <row r="2" spans="3:24">
       <c r="C2" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D2" s="40"/>
       <c r="E2" s="40"/>
       <c r="Q2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="3:24">
       <c r="C4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="3:24">
       <c r="C5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="3:24">
       <c r="C6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q6" t="s">
+        <v>155</v>
+      </c>
+      <c r="S6" t="s">
         <v>156</v>
-      </c>
-      <c r="S6" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="7" spans="3:24">
       <c r="Q7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="3:24">
       <c r="C8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="3:24">
       <c r="C9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q9" t="s">
+        <v>176</v>
+      </c>
+      <c r="X9" t="s">
         <v>177</v>
-      </c>
-      <c r="X9" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="10" spans="3:24">
       <c r="C10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="3:24">
       <c r="C11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="3:24">
       <c r="Q12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="3:24">
       <c r="C13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q13" t="s">
+        <v>162</v>
+      </c>
+      <c r="S13" t="s">
         <v>163</v>
-      </c>
-      <c r="S13" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="14" spans="3:24">
       <c r="C14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q14" t="s">
+        <v>164</v>
+      </c>
+      <c r="S14" t="s">
         <v>165</v>
-      </c>
-      <c r="S14" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="15" spans="3:24">
       <c r="Q15" t="s">
+        <v>166</v>
+      </c>
+      <c r="R15" t="s">
         <v>167</v>
-      </c>
-      <c r="R15" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="16" spans="3:24">
       <c r="Q16" t="s">
+        <v>168</v>
+      </c>
+      <c r="S16" t="s">
         <v>169</v>
-      </c>
-      <c r="S16" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -9557,7 +9665,7 @@
         <v>116</v>
       </c>
       <c r="AE2" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AF2" s="42"/>
       <c r="AG2" s="42"/>
@@ -9566,19 +9674,19 @@
     </row>
     <row r="3" spans="3:35">
       <c r="AE3" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI3" s="45"/>
     </row>
     <row r="4" spans="3:35">
       <c r="AE4" s="44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI4" s="45"/>
     </row>
     <row r="5" spans="3:35" ht="19.5" thickBot="1">
       <c r="AE5" s="46" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AF5" s="47"/>
       <c r="AG5" s="47"/>
@@ -9587,28 +9695,28 @@
     </row>
     <row r="9" spans="3:35">
       <c r="AE9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="34:47">
       <c r="AN31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AU31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="34:47">
       <c r="AH32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="40:40">
       <c r="AN33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -9619,12 +9727,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9863,20 +9973,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9901,12 +10012,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1374A707-6858-4135-8401-FF1C9F178422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079DC6EA-03C0-408D-9A15-AE5FF59074B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="3840" windowWidth="24000" windowHeight="15165" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -3301,7 +3301,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3361,6 +3361,7 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -6785,7 +6786,7 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
@@ -6807,7 +6808,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6828,11 +6829,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-397</v>
+        <v>-399</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.45088161209068012</v>
+        <v>-0.44862155388471175</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6845,11 +6846,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-377</v>
+        <v>-379</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.47480106100795755</v>
+        <v>-0.47229551451187335</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6862,11 +6863,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-366</v>
+        <v>-368</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.48907103825136611</v>
+        <v>-0.48641304347826086</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -6963,7 +6964,8 @@
     <col min="9" max="9" width="18.125" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="11.5" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9" style="10"/>
+    <col min="13" max="13" width="9" style="10"/>
+    <col min="14" max="14" width="9.625" style="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="11"/>
     <col min="16" max="16384" width="9" style="10"/>
   </cols>
@@ -7050,7 +7052,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="N3" s="53">
+        <f ca="1">K3/M3</f>
+        <v>2.8852459016393444</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7089,11 +7095,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>5.7777777777777777</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7132,11 +7138,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>1.4047619047619047</v>
+        <v>1.4750000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7175,11 +7181,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2711864406779661</v>
+        <v>0.2807017543859649</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9727,14 +9733,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9973,21 +9977,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10012,9 +10015,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079DC6EA-03C0-408D-9A15-AE5FF59074B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF3B3DC-E6B8-413F-B9F9-3A029D137FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="クラス設計" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$42</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="319">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -1182,10 +1182,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>dxLibをForEffeckseerにしないといけない</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>空中攻撃4段</t>
     <rPh sb="0" eb="2">
       <t>クウチュウ</t>
@@ -1696,19 +1692,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>敵との当たり判定をする</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スキル、必殺技の演出を先にする</t>
     <rPh sb="4" eb="7">
       <t>ヒッサツワザ</t>
@@ -2945,6 +2928,147 @@
     </rPh>
     <rPh sb="36" eb="37">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業中</t>
+  </si>
+  <si>
+    <t>被ダメ周りの処理</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミーマネージャーを作ってそこで管理</t>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やりたいこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シェーダーのエミッションを鴉に適用など</t>
+    <rPh sb="13" eb="14">
+      <t>カラス</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の死に方を雑にしているからいずれ修正必須</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ザツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の死に方</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吹き飛ぶとき</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぶっ飛びながら死ぬ</t>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吹き飛ばないとき</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡アニメーションで死ぬ</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中攻撃時</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後まで食らった後、死ぬ</t>
+    <rPh sb="0" eb="2">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3301,7 +3425,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3361,7 +3485,6 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -6764,8 +6887,8 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!E3:E69)</f>
-        <v>179</v>
+        <f>SUM(作業工数見積もり!E3:E71)</f>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -6773,8 +6896,8 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!G3:G19,"完了",作業工数見積もり!E3:E19)</f>
-        <v>0</v>
+        <f>SUMIF(作業工数見積もり!G3:G20,"完了",作業工数見積もり!E3:E20)</f>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -6790,7 +6913,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>0</v>
+        <v>4.6511627906976744E-3</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6833,7 +6956,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.44862155388471175</v>
+        <v>-0.45363408521303256</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6850,7 +6973,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.47229551451187335</v>
+        <v>-0.47757255936675463</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6867,7 +6990,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.48641304347826086</v>
+        <v>-0.49184782608695654</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -6951,7 +7074,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="69.625" style="10" bestFit="1" customWidth="1"/>
@@ -7010,10 +7133,10 @@
         <v>58</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7040,23 +7163,23 @@
       </c>
       <c r="J3" s="10">
         <f>SUM(J4,J5,J6)</f>
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K3" s="10">
-        <f>SUMIFS(E3:E48,G3:G48,"未着手")</f>
-        <v>176</v>
+        <f>SUMIFS(E3:E50,G3:G50,"未着手")</f>
+        <v>155</v>
       </c>
       <c r="L3" s="10">
-        <f>SUM(F3:F36)</f>
-        <v>1</v>
+        <f>SUM(F3:F38)</f>
+        <v>5</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
         <v>61</v>
       </c>
-      <c r="N3" s="53">
+      <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.8852459016393444</v>
+        <v>2.540983606557377</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7082,16 +7205,16 @@
         <v>28</v>
       </c>
       <c r="J4" s="29">
-        <f>SUMIF(D3:D48,I4,E3:E48)</f>
-        <v>104</v>
+        <f>SUMIF(D3:D50,I4,E3:E50)</f>
+        <v>108</v>
       </c>
       <c r="K4" s="10">
-        <f>SUMIFS(E3:E48,G3:G48,"未着手",D3:D48,I4)</f>
-        <v>101</v>
+        <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I4)</f>
+        <v>80</v>
       </c>
       <c r="L4" s="10">
-        <f>SUMIFS(F3:F36,D3:D36,I4)</f>
-        <v>1</v>
+        <f>SUMIFS(F3:F38,D3:D38,I4)</f>
+        <v>5</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
@@ -7099,7 +7222,7 @@
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7125,15 +7248,15 @@
         <v>0</v>
       </c>
       <c r="J5" s="29">
-        <f>SUMIF(D3:D48,I5,E3:E48)</f>
+        <f>SUMIF(D3:D50,I5,E3:E50)</f>
         <v>59</v>
       </c>
       <c r="K5" s="10">
-        <f>SUMIFS(E3:E48,G3:G48,"未着手",D3:D48,I5)</f>
+        <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I5)</f>
         <v>59</v>
       </c>
       <c r="L5" s="10">
-        <f>SUMIFS(F4:F40,D4:D40,I5)</f>
+        <f>SUMIFS(F4:F42,D4:D42,I5)</f>
         <v>0</v>
       </c>
       <c r="M5" s="10">
@@ -7168,15 +7291,15 @@
         <v>29</v>
       </c>
       <c r="J6" s="29">
-        <f>SUMIF(D3:D48,I6,E3:E48)</f>
+        <f>SUMIF(D3:D50,I6,E3:E50)</f>
         <v>16</v>
       </c>
       <c r="K6" s="10">
-        <f>SUMIFS(E3:E48,G3:G48,"未着手",D3:D48,I6)</f>
+        <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I6)</f>
         <v>16</v>
       </c>
       <c r="L6" s="10">
-        <f>SUMIFS(F5:F40,D5:D40,I6)</f>
+        <f>SUMIFS(F5:F42,D5:D42,I6)</f>
         <v>0</v>
       </c>
       <c r="M6" s="10">
@@ -7213,7 +7336,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>5</v>
@@ -7225,7 +7348,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:14" outlineLevel="1">
@@ -7233,7 +7356,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>5</v>
@@ -7253,7 +7376,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>5</v>
@@ -7265,10 +7388,10 @@
         <v>12</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:14" outlineLevel="1">
@@ -7276,10 +7399,10 @@
         <v>44</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>18</v>
@@ -7291,7 +7414,7 @@
         <v>39</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J11" s="51">
         <v>46265</v>
@@ -7302,10 +7425,10 @@
         <v>44</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>18</v>
@@ -7317,7 +7440,7 @@
         <v>39</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J12" s="52">
         <v>46220</v>
@@ -7328,7 +7451,7 @@
         <v>44</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>5</v>
@@ -7343,7 +7466,7 @@
         <v>39</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J13" s="52">
         <v>46244</v>
@@ -7354,7 +7477,7 @@
         <v>44</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>5</v>
@@ -7366,10 +7489,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J14" s="52">
         <v>46261</v>
@@ -7380,7 +7503,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>5</v>
@@ -7391,8 +7514,11 @@
       <c r="E15" s="16">
         <v>2</v>
       </c>
+      <c r="F15" s="16">
+        <v>2</v>
+      </c>
       <c r="G15" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7400,7 +7526,7 @@
         <v>44</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>14</v>
@@ -7417,7 +7543,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5</v>
@@ -7426,18 +7552,18 @@
         <v>18</v>
       </c>
       <c r="E17" s="16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="20" t="s">
-        <v>46</v>
+      <c r="A18" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>5</v>
@@ -7446,7 +7572,7 @@
         <v>18</v>
       </c>
       <c r="E18" s="16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>39</v>
@@ -7457,16 +7583,16 @@
         <v>46</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>259</v>
+        <v>5</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>39</v>
@@ -7477,16 +7603,16 @@
         <v>46</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>39</v>
@@ -7497,16 +7623,16 @@
         <v>46</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>39</v>
@@ -7517,27 +7643,27 @@
         <v>46</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>259</v>
+        <v>5</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="16">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="50" t="s">
-        <v>266</v>
+      <c r="A23" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>5</v>
@@ -7546,30 +7672,30 @@
         <v>18</v>
       </c>
       <c r="E23" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="16">
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>57</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="50" t="s">
-        <v>266</v>
+      <c r="A24" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="16">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>39</v>
@@ -7577,10 +7703,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="50" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>5</v>
@@ -7589,18 +7715,21 @@
         <v>18</v>
       </c>
       <c r="E25" s="16">
+        <v>3</v>
+      </c>
+      <c r="F25" s="16">
         <v>1</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>266</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>270</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>5</v>
@@ -7617,10 +7746,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="50" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>5</v>
@@ -7629,18 +7758,21 @@
         <v>18</v>
       </c>
       <c r="E27" s="16">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F27" s="16">
+        <v>1</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="21" t="s">
-        <v>40</v>
+      <c r="A28" s="50" t="s">
+        <v>264</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>5</v>
@@ -7656,11 +7788,11 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="21" t="s">
-        <v>40</v>
+      <c r="A29" s="50" t="s">
+        <v>264</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>5</v>
@@ -7669,7 +7801,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>39</v>
@@ -7680,7 +7812,7 @@
         <v>40</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>5</v>
@@ -7700,7 +7832,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>5</v>
@@ -7709,7 +7841,7 @@
         <v>18</v>
       </c>
       <c r="E31" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>39</v>
@@ -7720,7 +7852,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>5</v>
@@ -7729,18 +7861,18 @@
         <v>18</v>
       </c>
       <c r="E32" s="16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="22" t="s">
-        <v>41</v>
+      <c r="A33" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>5</v>
@@ -7756,11 +7888,11 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="22" t="s">
-        <v>41</v>
+      <c r="A34" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>5</v>
@@ -7769,47 +7901,50 @@
         <v>18</v>
       </c>
       <c r="E34" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="23" t="s">
-        <v>42</v>
+      <c r="A35" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>280</v>
+        <v>276</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>295</v>
+        <v>18</v>
       </c>
       <c r="E35" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="23" t="s">
-        <v>42</v>
+      <c r="A36" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>281</v>
+        <v>75</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>295</v>
+        <v>18</v>
       </c>
       <c r="E36" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -7817,47 +7952,50 @@
         <v>42</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E37" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>283</v>
+      <c r="C38" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="E38" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="10" t="s">
-        <v>279</v>
+      <c r="A39" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="E39" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>39</v>
@@ -7865,56 +8003,50 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E40" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="13" t="s">
-        <v>38</v>
+      <c r="A41" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="13" t="s">
-        <v>38</v>
+      <c r="A42" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E42" s="16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>39</v>
@@ -7925,16 +8057,16 @@
         <v>38</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>39</v>
@@ -7945,7 +8077,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>5</v>
@@ -7965,7 +8097,7 @@
         <v>38</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>5</v>
@@ -7974,7 +8106,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>39</v>
@@ -7985,7 +8117,7 @@
         <v>38</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>5</v>
@@ -7994,7 +8126,7 @@
         <v>10</v>
       </c>
       <c r="E46" s="16">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>39</v>
@@ -8005,7 +8137,7 @@
         <v>38</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>5</v>
@@ -8014,7 +8146,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>39</v>
@@ -8025,37 +8157,85 @@
         <v>38</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>295</v>
+        <v>10</v>
       </c>
       <c r="E48" s="16">
-        <v>12</v>
-      </c>
-      <c r="F48" s="10"/>
+        <v>4</v>
+      </c>
       <c r="G48" s="16" t="s">
         <v>39</v>
       </c>
     </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="16">
+        <v>12</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E50" s="16">
+        <v>12</v>
+      </c>
+      <c r="F50" s="10"/>
+      <c r="G50" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:G40" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G32">
-      <sortCondition ref="B2:B32"/>
+  <autoFilter ref="B2:G42" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G34">
+      <sortCondition ref="B2:B34"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D48" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D50" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G48" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G50" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C48" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C50" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8745,7 +8925,7 @@
         <v>46190</v>
       </c>
       <c r="C7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8753,7 +8933,7 @@
         <v>46191</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8761,17 +8941,17 @@
         <v>46192</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -8779,12 +8959,12 @@
         <v>46193</v>
       </c>
       <c r="C12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="C13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -8792,17 +8972,17 @@
         <v>46194</v>
       </c>
       <c r="C14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="C15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="C16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8810,37 +8990,37 @@
         <v>46195</v>
       </c>
       <c r="C17" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="C18" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="C19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="C20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="C21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="C22" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="C23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8848,17 +9028,17 @@
         <v>46196</v>
       </c>
       <c r="C24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="C25" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="C26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8866,12 +9046,12 @@
         <v>46197</v>
       </c>
       <c r="C27" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="C28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8879,42 +9059,42 @@
         <v>46198</v>
       </c>
       <c r="C29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="C30" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="C31" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="C32" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="C33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="C34" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="C35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="C36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -8922,7 +9102,7 @@
         <v>46200</v>
       </c>
       <c r="C37" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -8930,22 +9110,22 @@
         <v>46201</v>
       </c>
       <c r="C38" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="C39" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="C40" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="C41" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -8956,7 +9136,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:D20"/>
+  <dimension ref="B2:E23"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -9017,7 +9197,7 @@
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="2:4">
@@ -9025,7 +9205,7 @@
         <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="2:4">
@@ -9046,27 +9226,49 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:5">
       <c r="B17" t="s">
         <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
       <c r="B19" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>137</v>
+        <v>311</v>
+      </c>
+      <c r="D20" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="D21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E21" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="D22" t="s">
+        <v>315</v>
+      </c>
+      <c r="E22" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="D23" t="s">
+        <v>317</v>
+      </c>
+      <c r="E23" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -9096,7 +9298,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="44"/>
       <c r="C3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G3" s="45"/>
     </row>
@@ -9110,21 +9312,21 @@
     <row r="5" spans="1:7">
       <c r="A5" s="44"/>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G5" s="45"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="44"/>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G6" s="45"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="44"/>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G7" s="45"/>
     </row>
@@ -9135,13 +9337,13 @@
     <row r="9" spans="1:7">
       <c r="A9" s="44"/>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G9" s="45"/>
     </row>
@@ -9151,20 +9353,20 @@
         <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G10" s="45"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="44"/>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F11" t="s">
         <v>69</v>
@@ -9174,26 +9376,26 @@
     <row r="12" spans="1:7">
       <c r="A12" s="44"/>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G12" s="45"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="44"/>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G13" s="45"/>
     </row>
@@ -9202,20 +9404,20 @@
       <c r="B14" s="47"/>
       <c r="C14" s="47"/>
       <c r="D14" s="47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E14" s="47"/>
       <c r="F14" s="47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G14" s="48"/>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -9223,7 +9425,7 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="2:6">
@@ -9231,15 +9433,15 @@
         <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:6">
@@ -9249,10 +9451,10 @@
     </row>
     <row r="22" spans="2:6">
       <c r="D22" t="s">
+        <v>201</v>
+      </c>
+      <c r="F22" t="s">
         <v>202</v>
-      </c>
-      <c r="F22" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -9279,7 +9481,7 @@
     </row>
     <row r="2" spans="1:33">
       <c r="B2" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -9288,7 +9490,7 @@
         <v>102</v>
       </c>
       <c r="AE2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -9299,13 +9501,13 @@
         <v>103</v>
       </c>
       <c r="R3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AE3" t="s">
         <v>126</v>
       </c>
       <c r="AG3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -9313,7 +9515,7 @@
         <v>98</v>
       </c>
       <c r="M4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AE4" t="s">
         <v>127</v>
@@ -9365,7 +9567,7 @@
     </row>
     <row r="10" spans="1:33">
       <c r="AE10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -9378,7 +9580,7 @@
         <v>118</v>
       </c>
       <c r="AE12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -9402,7 +9604,7 @@
     </row>
     <row r="15" spans="1:33">
       <c r="D15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M15" t="s">
         <v>119</v>
@@ -9413,7 +9615,7 @@
         <v>120</v>
       </c>
       <c r="AF16" s="39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG16" s="39"/>
     </row>
@@ -9428,10 +9630,10 @@
         <v>124</v>
       </c>
       <c r="AF17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AK17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -9439,7 +9641,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -9453,12 +9655,12 @@
         <v>122</v>
       </c>
       <c r="AF19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:37">
       <c r="AF20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -9471,17 +9673,17 @@
     </row>
     <row r="22" spans="1:37">
       <c r="M22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:37">
       <c r="D24" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="1:37">
       <c r="A28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -9491,17 +9693,17 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="O43" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -9521,137 +9723,137 @@
   <sheetData>
     <row r="2" spans="3:24">
       <c r="C2" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D2" s="40"/>
       <c r="E2" s="40"/>
       <c r="Q2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="3:24">
       <c r="C4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="3:24">
       <c r="C5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="3:24">
       <c r="C6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q6" t="s">
+        <v>154</v>
+      </c>
+      <c r="S6" t="s">
         <v>155</v>
-      </c>
-      <c r="S6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="3:24">
       <c r="Q7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="3:24">
       <c r="C8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="3:24">
       <c r="C9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q9" t="s">
+        <v>175</v>
+      </c>
+      <c r="X9" t="s">
         <v>176</v>
-      </c>
-      <c r="X9" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="10" spans="3:24">
       <c r="C10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="3:24">
       <c r="C11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="3:24">
       <c r="Q12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="3:24">
       <c r="C13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q13" t="s">
+        <v>161</v>
+      </c>
+      <c r="S13" t="s">
         <v>162</v>
-      </c>
-      <c r="S13" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="14" spans="3:24">
       <c r="C14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q14" t="s">
+        <v>163</v>
+      </c>
+      <c r="S14" t="s">
         <v>164</v>
-      </c>
-      <c r="S14" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="15" spans="3:24">
       <c r="Q15" t="s">
+        <v>165</v>
+      </c>
+      <c r="R15" t="s">
         <v>166</v>
-      </c>
-      <c r="R15" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="16" spans="3:24">
       <c r="Q16" t="s">
+        <v>167</v>
+      </c>
+      <c r="S16" t="s">
         <v>168</v>
-      </c>
-      <c r="S16" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -9671,7 +9873,7 @@
         <v>116</v>
       </c>
       <c r="AE2" s="41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AF2" s="42"/>
       <c r="AG2" s="42"/>
@@ -9680,19 +9882,19 @@
     </row>
     <row r="3" spans="3:35">
       <c r="AE3" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AI3" s="45"/>
     </row>
     <row r="4" spans="3:35">
       <c r="AE4" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI4" s="45"/>
     </row>
     <row r="5" spans="3:35" ht="19.5" thickBot="1">
       <c r="AE5" s="46" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AF5" s="47"/>
       <c r="AG5" s="47"/>
@@ -9701,28 +9903,28 @@
     </row>
     <row r="9" spans="3:35">
       <c r="AE9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="34:47">
       <c r="AN31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AU31" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="34:47">
       <c r="AH32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN32" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="40:40">
       <c r="AN33" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -9733,12 +9935,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9977,20 +10181,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10015,12 +10220,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fugedaku!\Desktop\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF3B3DC-E6B8-413F-B9F9-3A029D137FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E602F6BF-C057-45DC-8221-B09700B1C525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!E3:E71)</f>
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.45363408521303256</v>
+        <v>-0.45112781954887216</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.47757255936675463</v>
+        <v>-0.47493403693931396</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.49184782608695654</v>
+        <v>-0.4891304347826087</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -7163,11 +7163,11 @@
       </c>
       <c r="J3" s="10">
         <f>SUM(J4,J5,J6)</f>
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手")</f>
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F38)</f>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.540983606557377</v>
+        <v>2.5245901639344264</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7206,11 +7206,11 @@
       </c>
       <c r="J4" s="29">
         <f>SUMIF(D3:D50,I4,E3:E50)</f>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I4)</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F38,D3:D38,I4)</f>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>6.75</v>
+        <v>6.6875</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7408,7 +7408,7 @@
         <v>18</v>
       </c>
       <c r="E11" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>39</v>
@@ -7815,7 +7815,7 @@
         <v>270</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>18</v>
@@ -7835,7 +7835,7 @@
         <v>271</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>18</v>
@@ -7895,7 +7895,7 @@
         <v>273</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>18</v>
@@ -9935,14 +9935,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10181,21 +10179,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10220,9 +10217,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fugedaku!\Desktop\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E602F6BF-C057-45DC-8221-B09700B1C525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D03C4F-9BCE-4CF6-AECD-81B622B34DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手")</f>
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F38)</f>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.5245901639344264</v>
+        <v>2.442622950819672</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I4)</f>
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F38,D3:D38,I4)</f>
@@ -7328,7 +7328,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:14" outlineLevel="1">
@@ -7824,7 +7824,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -9935,12 +9935,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10179,20 +10181,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10217,12 +10220,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D03C4F-9BCE-4CF6-AECD-81B622B34DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D01A12-D2BD-46EB-B122-52FEEB67AA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="328">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3070,6 +3070,135 @@
     <rPh sb="10" eb="11">
       <t>シ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ挙動</t>
+    <rPh sb="3" eb="5">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンはプレイヤーから一番近い敵をロックオン</t>
+    <rPh sb="13" eb="16">
+      <t>イチバンチカ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンした敵の方向にプレイヤーは攻撃する</t>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また、普通の攻撃した時も内部的にはロックオンし、別の入力があった場合は、切り替える</t>
+    <rPh sb="3" eb="5">
+      <t>フツウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ナイブテキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンした時はプレイヤーと敵の中間点をカメラは見続ける</t>
+    <rPh sb="7" eb="8">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>チュウカンテン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ミツヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラの方向とかプレイヤーの方向とかもいろいろありそう</t>
+    <rPh sb="4" eb="6">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>案2</t>
+    <rPh sb="0" eb="1">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rayvecとenemyVecの角度を取り、その角度差が小さいところを取る（範囲指定して奥行ってしまうバグをなくす）</t>
+    <rPh sb="16" eb="18">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="38" eb="42">
+      <t>ハンイシテイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラをしている</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6909,11 +7038,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>4.6511627906976744E-3</v>
+        <v>4.6403712296983757E-3</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6931,7 +7060,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -6952,11 +7081,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-399</v>
+        <v>-400</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.45112781954887216</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -6969,11 +7098,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-379</v>
+        <v>-380</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.47493403693931396</v>
+        <v>-0.47368421052631576</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6986,11 +7115,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-368</v>
+        <v>-369</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.4891304347826087</v>
+        <v>-0.48780487804878048</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -7175,11 +7304,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.442622950819672</v>
+        <v>2.4833333333333334</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7218,11 +7347,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>6.6875</v>
+        <v>7.1333333333333337</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7261,11 +7390,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>1.4750000000000001</v>
+        <v>1.5128205128205128</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7304,11 +7433,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2807017543859649</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9136,7 +9265,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:E23"/>
+  <dimension ref="B2:P33"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -9226,7 +9355,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:16">
       <c r="B17" t="s">
         <v>131</v>
       </c>
@@ -9234,12 +9363,17 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="18" spans="2:16">
+      <c r="B18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16">
       <c r="B19" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:16">
       <c r="B20" t="s">
         <v>311</v>
       </c>
@@ -9247,7 +9381,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:16">
       <c r="D21" t="s">
         <v>313</v>
       </c>
@@ -9255,7 +9389,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:16">
       <c r="D22" t="s">
         <v>315</v>
       </c>
@@ -9263,12 +9397,46 @@
         <v>316</v>
       </c>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:16">
       <c r="D23" t="s">
         <v>317</v>
       </c>
       <c r="E23" t="s">
         <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16">
+      <c r="D27" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16">
+      <c r="D29" t="s">
+        <v>320</v>
+      </c>
+      <c r="H29" t="s">
+        <v>324</v>
+      </c>
+      <c r="O29" t="s">
+        <v>325</v>
+      </c>
+      <c r="P29" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16">
+      <c r="D30" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16">
+      <c r="D31" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -9935,14 +10103,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10181,21 +10347,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10220,9 +10385,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D01A12-D2BD-46EB-B122-52FEEB67AA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3435ACE-E226-44E1-A3BE-21D46FC0E007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="クラス設計" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$50</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="333">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3198,7 +3198,99 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カメラをしている</t>
+    <t>ロックオンしている敵に攻撃がむかうようにする</t>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンしている敵が死んだら次のやつを探す</t>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右スティックの左か右の入力があったら、ロックオンしている敵を変更</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑cosΘのやつを大きい順に並び変えてて、変更や、消えたりしたら次のものに変更させる</t>
+    <rPh sb="9" eb="10">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>配列ごと渡してもいい（まだわからんけど）</t>
+    <rPh sb="0" eb="2">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵をモデルちゃんと作る</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3265,7 +3357,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3428,6 +3520,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -3554,7 +3652,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3614,6 +3712,7 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -7038,11 +7137,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>4.6403712296983757E-3</v>
+        <v>4.6296296296296294E-3</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7060,7 +7159,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -7081,11 +7180,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-400</v>
+        <v>-401</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.45</v>
+        <v>-0.44887780548628431</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -7098,11 +7197,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-380</v>
+        <v>-381</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.47368421052631576</v>
+        <v>-0.47244094488188976</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -7115,11 +7214,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-369</v>
+        <v>-370</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.48780487804878048</v>
+        <v>-0.48648648648648651</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -7203,6 +7302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
@@ -7296,22 +7396,22 @@
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手")</f>
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F38)</f>
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.4833333333333334</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>2.4310344827586206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" hidden="1">
       <c r="A4" s="17" t="s">
         <v>35</v>
       </c>
@@ -7335,26 +7435,26 @@
       </c>
       <c r="J4" s="29">
         <f>SUMIF(D3:D50,I4,E3:E50)</f>
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I4)</f>
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F38,D3:D38,I4)</f>
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>7.1333333333333337</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>6.8461538461538458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" hidden="1">
       <c r="A5" s="17" t="s">
         <v>35</v>
       </c>
@@ -7378,7 +7478,7 @@
       </c>
       <c r="J5" s="29">
         <f>SUMIF(D3:D50,I5,E3:E50)</f>
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="K5" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I5)</f>
@@ -7390,14 +7490,14 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>1.5128205128205128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>2.0810810810810811</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" hidden="1">
       <c r="A6" s="17" t="s">
         <v>35</v>
       </c>
@@ -7433,11 +7533,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2857142857142857</v>
+        <v>0.29629629629629628</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7460,7 +7560,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="8" spans="1:14" outlineLevel="1">
+    <row r="8" spans="1:14" hidden="1" outlineLevel="1">
       <c r="A8" s="19" t="s">
         <v>44</v>
       </c>
@@ -7471,7 +7571,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E8" s="16">
         <v>6</v>
@@ -7500,7 +7600,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:14" outlineLevel="1">
+    <row r="10" spans="1:14" hidden="1" outlineLevel="1">
       <c r="A10" s="19" t="s">
         <v>44</v>
       </c>
@@ -7511,7 +7611,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E10" s="16">
         <v>12</v>
@@ -7992,8 +8092,11 @@
       <c r="E32" s="16">
         <v>2</v>
       </c>
+      <c r="F32" s="16">
+        <v>12</v>
+      </c>
       <c r="G32" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -8032,8 +8135,11 @@
       <c r="E34" s="16">
         <v>6</v>
       </c>
+      <c r="F34" s="16">
+        <v>6</v>
+      </c>
       <c r="G34" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -8076,7 +8182,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" s="23" t="s">
         <v>42</v>
       </c>
@@ -8093,7 +8199,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" s="23" t="s">
         <v>42</v>
       </c>
@@ -8113,7 +8219,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" s="23" t="s">
         <v>42</v>
       </c>
@@ -8130,7 +8236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" s="10" t="s">
         <v>277</v>
       </c>
@@ -8147,7 +8253,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" s="10" t="s">
         <v>277</v>
       </c>
@@ -8181,7 +8287,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="13" t="s">
         <v>38</v>
       </c>
@@ -8201,7 +8307,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" s="13" t="s">
         <v>38</v>
       </c>
@@ -8221,7 +8327,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" s="13" t="s">
         <v>38</v>
       </c>
@@ -8241,7 +8347,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" s="13" t="s">
         <v>38</v>
       </c>
@@ -8261,7 +8367,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" s="13" t="s">
         <v>38</v>
       </c>
@@ -8281,7 +8387,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" s="13" t="s">
         <v>38</v>
       </c>
@@ -8301,7 +8407,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" s="13" t="s">
         <v>38</v>
       </c>
@@ -8321,7 +8427,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" s="13" t="s">
         <v>38</v>
       </c>
@@ -8351,7 +8457,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G42" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="B2:G50" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="プロト"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G34">
       <sortCondition ref="B2:B34"/>
     </sortState>
@@ -9370,18 +9481,21 @@
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>207</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="D20" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="21" spans="2:16">
+      <c r="B21" t="s">
+        <v>330</v>
+      </c>
       <c r="D21" t="s">
         <v>313</v>
       </c>
@@ -9390,6 +9504,9 @@
       </c>
     </row>
     <row r="22" spans="2:16">
+      <c r="B22" t="s">
+        <v>331</v>
+      </c>
       <c r="D22" t="s">
         <v>315</v>
       </c>
@@ -9405,9 +9522,22 @@
         <v>318</v>
       </c>
     </row>
+    <row r="24" spans="2:16">
+      <c r="B24" s="53" t="s">
+        <v>332</v>
+      </c>
+    </row>
     <row r="27" spans="2:16">
+      <c r="B27" t="s">
+        <v>207</v>
+      </c>
       <c r="D27" t="s">
         <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16">
+      <c r="B28" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -10103,12 +10233,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10347,20 +10479,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10385,12 +10518,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3435ACE-E226-44E1-A3BE-21D46FC0E007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AB1DE4-C455-421E-9292-CC1881D8CB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="338">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3290,6 +3290,77 @@
     </rPh>
     <rPh sb="9" eb="10">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃がおそらく単体にしか当たっていない</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵について</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃を2種類にするできれば</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃の範囲をもっと広くして、攻撃時移動するようにする</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>コウゲキジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃クールタイムの時は、追いかけ続けず、別のステートに移行させる</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>イコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9376,7 +9447,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:P33"/>
+  <dimension ref="B2:P36"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -9560,13 +9631,34 @@
       </c>
     </row>
     <row r="31" spans="2:16">
+      <c r="B31" t="s">
+        <v>333</v>
+      </c>
       <c r="D31" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="33" spans="4:4">
+    <row r="33" spans="2:4">
+      <c r="B33" t="s">
+        <v>334</v>
+      </c>
       <c r="D33" t="s">
         <v>323</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AB1DE4-C455-421E-9292-CC1881D8CB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFB21D0-CAB3-4C39-A1CA-D316E6EC2B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="341">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3361,6 +3361,51 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上下さがある攻撃の時は地面についたとき、さらに吹っ飛ぶようにする</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウゲ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル攻撃の後の通常攻撃はもっと早くでるようにしたほうが操作感がいい</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>ソウサカン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7196,7 +7241,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!G3:G20,"完了",作業工数見積もり!E3:E20)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -7212,7 +7257,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>4.6296296296296294E-3</v>
+        <v>9.2592592592592587E-3</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7230,7 +7275,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46207</v>
+        <v>46208</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -7255,7 +7300,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.44887780548628431</v>
+        <v>-0.44389027431421446</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -7272,7 +7317,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.47244094488188976</v>
+        <v>-0.46719160104986879</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -7289,7 +7334,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.48648648648648651</v>
+        <v>-0.48108108108108111</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -7475,11 +7520,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.4310344827586206</v>
+        <v>2.4736842105263159</v>
       </c>
     </row>
     <row r="4" spans="1:14" hidden="1">
@@ -7518,11 +7563,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>6.8461538461538458</v>
+        <v>7.416666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:14" hidden="1">
@@ -7561,11 +7606,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.0810810810810811</v>
+        <v>2.1388888888888888</v>
       </c>
     </row>
     <row r="6" spans="1:14" hidden="1">
@@ -7604,11 +7649,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.29629629629629628</v>
+        <v>0.30188679245283018</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7789,7 +7834,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>306</v>
+        <v>57</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>298</v>
@@ -9447,7 +9492,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:P36"/>
+  <dimension ref="B2:P41"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -9659,6 +9704,21 @@
     <row r="36" spans="2:4">
       <c r="B36" t="s">
         <v>335</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -10325,14 +10385,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10571,21 +10629,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10610,9 +10667,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFB21D0-CAB3-4C39-A1CA-D316E6EC2B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A1C9D5-04FD-4F3E-A74A-946E6BE35D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -3284,16 +3284,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>敵をモデルちゃんと作る</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>攻撃がおそらく単体にしか当たっていない</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
@@ -3406,6 +3396,19 @@
     </rPh>
     <rPh sb="28" eb="31">
       <t>ソウサカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はスポナーの仕組みを作る</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3473,7 +3476,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3636,12 +3639,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -3768,7 +3765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3828,7 +3825,6 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -8160,7 +8156,7 @@
         <v>270</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>18</v>
@@ -8223,7 +8219,7 @@
         <v>272</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>18</v>
@@ -9592,17 +9588,17 @@
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D20" t="s">
         <v>312</v>
@@ -9610,7 +9606,7 @@
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D21" t="s">
         <v>313</v>
@@ -9621,7 +9617,7 @@
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D22" t="s">
         <v>315</v>
@@ -9631,6 +9627,9 @@
       </c>
     </row>
     <row r="23" spans="2:16">
+      <c r="B23" t="s">
+        <v>331</v>
+      </c>
       <c r="D23" t="s">
         <v>317</v>
       </c>
@@ -9638,10 +9637,8 @@
         <v>318</v>
       </c>
     </row>
-    <row r="24" spans="2:16">
-      <c r="B24" s="53" t="s">
-        <v>332</v>
-      </c>
+    <row r="25" spans="2:16">
+      <c r="B25" s="32"/>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
@@ -9677,7 +9674,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D31" t="s">
         <v>322</v>
@@ -9685,7 +9682,7 @@
     </row>
     <row r="33" spans="2:4">
       <c r="B33" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D33" t="s">
         <v>323</v>
@@ -9693,32 +9690,32 @@
     </row>
     <row r="34" spans="2:4">
       <c r="B34" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -10385,12 +10382,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10629,20 +10628,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10667,12 +10667,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A1C9D5-04FD-4F3E-A74A-946E6BE35D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A23CE0-6C21-4290-B9FC-AD9969C2E61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -7249,11 +7249,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>9.2592592592592587E-3</v>
+        <v>9.2378752886836026E-3</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -7292,11 +7292,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-401</v>
+        <v>-402</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.44389027431421446</v>
+        <v>-0.44278606965174128</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -7309,11 +7309,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-381</v>
+        <v>-382</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.46719160104986879</v>
+        <v>-0.46596858638743455</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -7326,11 +7326,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-370</v>
+        <v>-371</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.48108108108108111</v>
+        <v>-0.47978436657681939</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -7508,19 +7508,19 @@
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手")</f>
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F38)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.4736842105263159</v>
+        <v>2.4464285714285716</v>
       </c>
     </row>
     <row r="4" spans="1:14" hidden="1">
@@ -7551,19 +7551,19 @@
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I4)</f>
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F38,D3:D38,I4)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>7.416666666666667</v>
+        <v>8.0909090909090917</v>
       </c>
     </row>
     <row r="5" spans="1:14" hidden="1">
@@ -7602,11 +7602,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.1388888888888888</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:14" hidden="1">
@@ -7645,11 +7645,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.30188679245283018</v>
+        <v>0.30769230769230771</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7995,8 +7995,11 @@
       <c r="E22" s="16">
         <v>4</v>
       </c>
+      <c r="F22" s="16">
+        <v>2</v>
+      </c>
       <c r="G22" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -10382,14 +10385,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10628,21 +10629,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10667,9 +10667,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A23CE0-6C21-4290-B9FC-AD9969C2E61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89B8505-0EC9-42AA-8414-2540F22929EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="342">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3409,6 +3409,25 @@
     </rPh>
     <rPh sb="11" eb="12">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今、ジャスト回避を作っていて、ジャスト回避用のColliderをつくるところ</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9223,7 +9242,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -9481,6 +9500,14 @@
     <row r="41" spans="1:3">
       <c r="C41" t="s">
         <v>305</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C43" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -10385,12 +10412,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10629,20 +10658,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10667,12 +10697,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89B8505-0EC9-42AA-8414-2540F22929EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B7D84C-F9BB-4C7E-81D2-7EE469D7E348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="クラス設計" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$52</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="349">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3428,6 +3428,100 @@
     </rPh>
     <rPh sb="21" eb="22">
       <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の方向に攻撃が向かうようにする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技時のタイムスケールが変</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャスト回避の優先順位を下げた</t>
+    <rPh sb="4" eb="6">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル攻撃からの通常攻撃をスムーズになるようにした</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中での攻撃回数を制限しないといけない</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>コウゲキカイスウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終わらせた。次は、いよいよプレイヤーの攻撃方向、内部ロックオン関連かなー</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それか必殺技、スキルのシステム</t>
+    <rPh sb="3" eb="6">
+      <t>ヒッサツワザ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7246,7 +7340,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!E3:E71)</f>
+        <f>SUM(作業工数見積もり!E3:E73)</f>
         <v>182</v>
       </c>
     </row>
@@ -7255,7 +7349,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!G3:G20,"完了",作業工数見積もり!E3:E20)</f>
+        <f>SUMIF(作業工数見積もり!G3:G22,"完了",作業工数見積もり!E3:E22)</f>
         <v>4</v>
       </c>
       <c r="D4" t="s">
@@ -7268,11 +7362,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>9.2378752886836026E-3</v>
+        <v>9.2165898617511521E-3</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7290,7 +7384,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -7311,11 +7405,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-402</v>
+        <v>-403</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.44278606965174128</v>
+        <v>-0.44168734491315137</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -7328,11 +7422,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-382</v>
+        <v>-383</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.46596858638743455</v>
+        <v>-0.46475195822454307</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -7345,11 +7439,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-371</v>
+        <v>-372</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.47978436657681939</v>
+        <v>-0.478494623655914</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -7434,7 +7528,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="69.625" style="10" bestFit="1" customWidth="1"/>
@@ -7526,20 +7620,20 @@
         <v>182</v>
       </c>
       <c r="K3" s="10">
-        <f>SUMIFS(E3:E50,G3:G50,"未着手")</f>
+        <f>SUMIFS(E3:E52,G3:G52,"未着手")</f>
         <v>137</v>
       </c>
       <c r="L3" s="10">
-        <f>SUM(F3:F38)</f>
+        <f>SUM(F3:F40)</f>
         <v>25</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.4464285714285716</v>
+        <v>2.4909090909090907</v>
       </c>
     </row>
     <row r="4" spans="1:14" hidden="1">
@@ -7565,24 +7659,24 @@
         <v>28</v>
       </c>
       <c r="J4" s="29">
-        <f>SUMIF(D3:D50,I4,E3:E50)</f>
+        <f>SUMIF(D3:D52,I4,E3:E52)</f>
         <v>89</v>
       </c>
       <c r="K4" s="10">
-        <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I4)</f>
+        <f>SUMIFS(E3:E52,G3:G52,"未着手",D3:D52,I4)</f>
         <v>62</v>
       </c>
       <c r="L4" s="10">
-        <f>SUMIFS(F3:F38,D3:D38,I4)</f>
+        <f>SUMIFS(F3:F40,D3:D40,I4)</f>
         <v>25</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>8.0909090909090917</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:14" hidden="1">
@@ -7608,24 +7702,24 @@
         <v>0</v>
       </c>
       <c r="J5" s="29">
-        <f>SUMIF(D3:D50,I5,E3:E50)</f>
+        <f>SUMIF(D3:D52,I5,E3:E52)</f>
         <v>77</v>
       </c>
       <c r="K5" s="10">
-        <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I5)</f>
+        <f>SUMIFS(E3:E52,G3:G52,"未着手",D3:D52,I5)</f>
         <v>59</v>
       </c>
       <c r="L5" s="10">
-        <f>SUMIFS(F4:F42,D4:D42,I5)</f>
+        <f>SUMIFS(F4:F44,D4:D44,I5)</f>
         <v>0</v>
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.2000000000000002</v>
+        <v>2.2647058823529411</v>
       </c>
     </row>
     <row r="6" spans="1:14" hidden="1">
@@ -7651,24 +7745,24 @@
         <v>29</v>
       </c>
       <c r="J6" s="29">
-        <f>SUMIF(D3:D50,I6,E3:E50)</f>
+        <f>SUMIF(D3:D52,I6,E3:E52)</f>
         <v>16</v>
       </c>
       <c r="K6" s="10">
-        <f>SUMIFS(E3:E50,G3:G50,"未着手",D3:D50,I6)</f>
+        <f>SUMIFS(E3:E52,G3:G52,"未着手",D3:D52,I6)</f>
         <v>16</v>
       </c>
       <c r="L6" s="10">
-        <f>SUMIFS(F5:F42,D5:D42,I6)</f>
+        <f>SUMIFS(F5:F44,D5:D44,I6)</f>
         <v>0</v>
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.30769230769230771</v>
+        <v>0.31372549019607843</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7923,7 +8017,7 @@
         <v>44</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>5</v>
@@ -7931,19 +8025,13 @@
       <c r="D18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="16">
-        <v>8</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="20" t="s">
-        <v>46</v>
+      <c r="A19" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>261</v>
+        <v>343</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>5</v>
@@ -7951,28 +8039,22 @@
       <c r="D19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="16">
-        <v>3</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="20" t="s">
-        <v>46</v>
+      <c r="A20" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>39</v>
@@ -7983,16 +8065,16 @@
         <v>46</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>39</v>
@@ -8003,22 +8085,19 @@
         <v>46</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="16">
-        <v>4</v>
-      </c>
-      <c r="F22" s="16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>306</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -8026,22 +8105,19 @@
         <v>46</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="16">
-        <v>2</v>
-      </c>
-      <c r="F23" s="16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>306</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -8049,27 +8125,30 @@
         <v>46</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="16">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="F24" s="16">
+        <v>2</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="50" t="s">
-        <v>264</v>
+      <c r="A25" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>265</v>
+        <v>308</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>5</v>
@@ -8078,30 +8157,30 @@
         <v>18</v>
       </c>
       <c r="E25" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="16">
         <v>1</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>57</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="50" t="s">
-        <v>264</v>
+      <c r="A26" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D26" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="16">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>39</v>
@@ -8112,7 +8191,7 @@
         <v>264</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>5</v>
@@ -8121,7 +8200,7 @@
         <v>18</v>
       </c>
       <c r="E27" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" s="16">
         <v>1</v>
@@ -8135,7 +8214,7 @@
         <v>264</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>5</v>
@@ -8155,7 +8234,7 @@
         <v>264</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>5</v>
@@ -8164,18 +8243,21 @@
         <v>18</v>
       </c>
       <c r="E29" s="16">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F29" s="16">
+        <v>1</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="21" t="s">
-        <v>40</v>
+      <c r="A30" s="50" t="s">
+        <v>264</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>5</v>
@@ -8187,24 +8269,24 @@
         <v>2</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>306</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="21" t="s">
-        <v>40</v>
+      <c r="A31" s="50" t="s">
+        <v>264</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>39</v>
@@ -8215,7 +8297,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>5</v>
@@ -8226,11 +8308,8 @@
       <c r="E32" s="16">
         <v>2</v>
       </c>
-      <c r="F32" s="16">
-        <v>12</v>
-      </c>
       <c r="G32" s="16" t="s">
-        <v>57</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -8238,7 +8317,7 @@
         <v>40</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>257</v>
@@ -8247,7 +8326,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" s="16" t="s">
         <v>39</v>
@@ -8258,33 +8337,33 @@
         <v>40</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F34" s="16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="22" t="s">
-        <v>41</v>
+      <c r="A35" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D35" s="16" t="s">
         <v>18</v>
@@ -8297,60 +8376,66 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="22" t="s">
-        <v>41</v>
+      <c r="A36" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D36" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="16">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="F36" s="16">
+        <v>6</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
-      <c r="A37" s="23" t="s">
-        <v>42</v>
+    <row r="37" spans="1:7">
+      <c r="A37" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>293</v>
+        <v>18</v>
       </c>
       <c r="E37" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
-      <c r="A38" s="23" t="s">
-        <v>42</v>
+    <row r="38" spans="1:7">
+      <c r="A38" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>279</v>
+        <v>75</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>293</v>
+        <v>18</v>
       </c>
       <c r="E38" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:7" hidden="1">
@@ -8358,104 +8443,101 @@
         <v>42</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D39" s="16" t="s">
         <v>293</v>
       </c>
       <c r="E39" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:7" hidden="1">
-      <c r="A40" s="10" t="s">
-        <v>277</v>
+      <c r="A40" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="E40" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:7" hidden="1">
-      <c r="A41" s="10" t="s">
-        <v>277</v>
+      <c r="A41" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="E41" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="10" t="s">
         <v>277</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E42" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:7" hidden="1">
-      <c r="A43" s="13" t="s">
-        <v>38</v>
+      <c r="A43" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
-      <c r="A44" s="13" t="s">
-        <v>38</v>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E44" s="16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>39</v>
@@ -8466,16 +8548,16 @@
         <v>38</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D45" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>39</v>
@@ -8486,7 +8568,7 @@
         <v>38</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>5</v>
@@ -8506,7 +8588,7 @@
         <v>38</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>5</v>
@@ -8515,7 +8597,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>39</v>
@@ -8526,7 +8608,7 @@
         <v>38</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>5</v>
@@ -8535,7 +8617,7 @@
         <v>10</v>
       </c>
       <c r="E48" s="16">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>39</v>
@@ -8546,7 +8628,7 @@
         <v>38</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>5</v>
@@ -8555,7 +8637,7 @@
         <v>10</v>
       </c>
       <c r="E49" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>39</v>
@@ -8566,50 +8648,90 @@
         <v>38</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>293</v>
+        <v>10</v>
       </c>
       <c r="E50" s="16">
-        <v>12</v>
-      </c>
-      <c r="F50" s="10"/>
+        <v>4</v>
+      </c>
       <c r="G50" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="10" t="s">
+    <row r="51" spans="1:7" hidden="1">
+      <c r="A51" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="16">
+        <v>12</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" hidden="1">
+      <c r="A52" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E52" s="16">
+        <v>12</v>
+      </c>
+      <c r="F52" s="10"/>
+      <c r="G52" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B54" s="10" t="s">
         <v>310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G50" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="B2:G52" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
         <filter val="プロト"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G34">
-      <sortCondition ref="B2:B34"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G36">
+      <sortCondition ref="B2:B36"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D50" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D52" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G50" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G52" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C50" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C52" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9242,7 +9364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -9508,6 +9630,31 @@
       </c>
       <c r="C43" t="s">
         <v>341</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="C44" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="C45" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="C46" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="C47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="C48" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -10412,14 +10559,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10658,21 +10803,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10697,9 +10841,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B7D84C-F9BB-4C7E-81D2-7EE469D7E348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01307486-1730-4D77-8049-C7604A9AC9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3450" yWindow="2190" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="351">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3522,6 +3522,44 @@
     <t>それか必殺技、スキルのシステム</t>
     <rPh sb="3" eb="6">
       <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドロップ攻撃の終わり際に攻撃判定をつけて、ドロップ攻撃後、周囲は吹き飛ぶようにする</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>オワリギワ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>コウゲキハンテイ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>コウゲキゴ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、プレイヤーの攻撃方向、内部ロックオン関連をやる</t>
+    <rPh sb="11" eb="15">
+      <t>コウゲキホウコウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カンレン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9364,7 +9402,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -9655,6 +9693,19 @@
     <row r="48" spans="1:3">
       <c r="C48" t="s">
         <v>348</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1">
+        <v>46210</v>
+      </c>
+      <c r="C49" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="C50" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -10559,12 +10610,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10803,20 +10856,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10841,12 +10895,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01307486-1730-4D77-8049-C7604A9AC9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="2190" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -10610,14 +10610,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10856,21 +10854,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10895,9 +10892,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01307486-1730-4D77-8049-C7604A9AC9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C536A648-C5B5-45C4-84C7-8344AD7685E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="4035" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="355">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3560,6 +3560,94 @@
     </rPh>
     <rPh sb="23" eb="25">
       <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドロップ攻撃の吹き飛ばし終わった、敵が吹き飛ばした後、すぐに動くより、吹っ飛んだ後、起き上がる時間、寝ている時間があったほうがいいと思うからそうしたい</t>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ネ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>でも、それは後回しでいいと思う</t>
+    <rPh sb="6" eb="8">
+      <t>アトマワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ステージをもとにちゃんとwave制にする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>セイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、攻撃の操作改善をやる</t>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ソウサカイゼン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7400,11 +7488,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>9.2165898617511521E-3</v>
+        <v>9.1954022988505746E-3</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7422,7 +7510,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -7443,11 +7531,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-403</v>
+        <v>-404</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.44168734491315137</v>
+        <v>-0.4405940594059406</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -7460,11 +7548,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-383</v>
+        <v>-384</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.46475195822454307</v>
+        <v>-0.46354166666666669</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -7477,11 +7565,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-372</v>
+        <v>-373</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.478494623655914</v>
+        <v>-0.47721179624664878</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -7667,11 +7755,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.4909090909090907</v>
+        <v>2.5370370370370372</v>
       </c>
     </row>
     <row r="4" spans="1:14" hidden="1">
@@ -7710,11 +7798,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>8.9</v>
+        <v>9.8888888888888893</v>
       </c>
     </row>
     <row r="5" spans="1:14" hidden="1">
@@ -7753,11 +7841,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.2647058823529411</v>
+        <v>2.3333333333333335</v>
       </c>
     </row>
     <row r="6" spans="1:14" hidden="1">
@@ -7796,11 +7884,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.31372549019607843</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9402,7 +9490,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -9706,6 +9794,29 @@
     <row r="50" spans="1:3">
       <c r="C50" t="s">
         <v>350</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1">
+        <v>46211</v>
+      </c>
+      <c r="C52" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="C53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="C54" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="C55" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -10610,12 +10721,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10854,20 +10967,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10892,12 +11006,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C536A648-C5B5-45C4-84C7-8344AD7685E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F51A5A4-8B58-44FD-8C33-6B87583A0A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="4035" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="クラス設計" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$53</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="359">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3648,6 +3648,52 @@
     </rPh>
     <rPh sb="8" eb="12">
       <t>ソウサカイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>血殺シーン、やっぱり敵も黒く描画したいかも、シェーダーで。（敵が目立ってあんまりな感じがした）</t>
+    <rPh sb="0" eb="1">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>サツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>メダ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スカイボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インターン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>be-ta最終が27日</t>
+    <rPh sb="5" eb="7">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ニチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3660,7 +3706,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3710,6 +3756,13 @@
     <font>
       <sz val="11"/>
       <color theme="5" tint="0.59999389629810485"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3868,13 +3921,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4004,7 +4057,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4061,9 +4114,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -7466,8 +7520,8 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!E3:E73)</f>
-        <v>182</v>
+        <f>SUM(作業工数見積もり!E3:E74)</f>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -7476,7 +7530,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!G3:G22,"完了",作業工数見積もり!E3:E22)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -7492,7 +7546,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>9.1954022988505746E-3</v>
+        <v>1.1494252873563218E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7654,7 +7708,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="69.625" style="10" bestFit="1" customWidth="1"/>
@@ -7743,15 +7797,15 @@
       </c>
       <c r="J3" s="10">
         <f>SUM(J4,J5,J6)</f>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K3" s="10">
-        <f>SUMIFS(E3:E52,G3:G52,"未着手")</f>
-        <v>137</v>
+        <f>SUMIFS(E3:E53,G3:G53,"未着手")</f>
+        <v>136</v>
       </c>
       <c r="L3" s="10">
-        <f>SUM(F3:F40)</f>
-        <v>25</v>
+        <f>SUM(F3:F41)</f>
+        <v>27</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
@@ -7759,7 +7813,7 @@
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.5370370370370372</v>
+        <v>2.5185185185185186</v>
       </c>
     </row>
     <row r="4" spans="1:14" hidden="1">
@@ -7785,16 +7839,16 @@
         <v>28</v>
       </c>
       <c r="J4" s="29">
-        <f>SUMIF(D3:D52,I4,E3:E52)</f>
-        <v>89</v>
+        <f>SUMIF(D3:D53,I4,E3:E53)</f>
+        <v>90</v>
       </c>
       <c r="K4" s="10">
-        <f>SUMIFS(E3:E52,G3:G52,"未着手",D3:D52,I4)</f>
-        <v>62</v>
+        <f>SUMIFS(E3:E53,G3:G53,"未着手",D3:D53,I4)</f>
+        <v>61</v>
       </c>
       <c r="L4" s="10">
-        <f>SUMIFS(F3:F40,D3:D40,I4)</f>
-        <v>25</v>
+        <f>SUMIFS(F3:F41,D3:D41,I4)</f>
+        <v>27</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
@@ -7802,7 +7856,7 @@
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>9.8888888888888893</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:14" hidden="1">
@@ -7828,15 +7882,15 @@
         <v>0</v>
       </c>
       <c r="J5" s="29">
-        <f>SUMIF(D3:D52,I5,E3:E52)</f>
+        <f>SUMIF(D3:D53,I5,E3:E53)</f>
         <v>77</v>
       </c>
       <c r="K5" s="10">
-        <f>SUMIFS(E3:E52,G3:G52,"未着手",D3:D52,I5)</f>
+        <f>SUMIFS(E3:E53,G3:G53,"未着手",D3:D53,I5)</f>
         <v>59</v>
       </c>
       <c r="L5" s="10">
-        <f>SUMIFS(F4:F44,D4:D44,I5)</f>
+        <f>SUMIFS(F4:F45,D4:D45,I5)</f>
         <v>0</v>
       </c>
       <c r="M5" s="10">
@@ -7871,15 +7925,15 @@
         <v>29</v>
       </c>
       <c r="J6" s="29">
-        <f>SUMIF(D3:D52,I6,E3:E52)</f>
+        <f>SUMIF(D3:D53,I6,E3:E53)</f>
         <v>16</v>
       </c>
       <c r="K6" s="10">
-        <f>SUMIFS(E3:E52,G3:G52,"未着手",D3:D52,I6)</f>
+        <f>SUMIFS(E3:E53,G3:G53,"未着手",D3:D53,I6)</f>
         <v>16</v>
       </c>
       <c r="L6" s="10">
-        <f>SUMIFS(F5:F44,D5:D44,I6)</f>
+        <f>SUMIFS(F5:F45,D5:D45,I6)</f>
         <v>0</v>
       </c>
       <c r="M6" s="10">
@@ -7996,7 +8050,7 @@
       <c r="I11" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="J11" s="51">
+      <c r="J11" s="50">
         <v>46265</v>
       </c>
     </row>
@@ -8022,7 +8076,7 @@
       <c r="I12" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12" s="51">
         <v>46220</v>
       </c>
     </row>
@@ -8042,13 +8096,16 @@
       <c r="E13" s="16">
         <v>1</v>
       </c>
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
       <c r="G13" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="J13" s="52">
+      <c r="J13" s="51">
         <v>46244</v>
       </c>
     </row>
@@ -8074,7 +8131,7 @@
       <c r="I14" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="J14" s="52">
+      <c r="J14" s="51">
         <v>46261</v>
       </c>
     </row>
@@ -8313,7 +8370,7 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="50" t="s">
+      <c r="A27" s="49" t="s">
         <v>264</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -8336,7 +8393,7 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="49" t="s">
         <v>264</v>
       </c>
       <c r="B28" s="10" t="s">
@@ -8356,7 +8413,7 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="50" t="s">
+      <c r="A29" s="49" t="s">
         <v>264</v>
       </c>
       <c r="B29" s="10" t="s">
@@ -8379,7 +8436,7 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="50" t="s">
+      <c r="A30" s="49" t="s">
         <v>264</v>
       </c>
       <c r="B30" s="10" t="s">
@@ -8399,7 +8456,7 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="49" t="s">
         <v>264</v>
       </c>
       <c r="B31" s="10" t="s">
@@ -8549,7 +8606,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>5</v>
@@ -8558,27 +8615,33 @@
         <v>18</v>
       </c>
       <c r="E38" s="16">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F38" s="16">
+        <v>1</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
-      <c r="A39" s="23" t="s">
-        <v>42</v>
+    <row r="39" spans="1:7">
+      <c r="A39" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>278</v>
+        <v>75</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>293</v>
+        <v>18</v>
       </c>
       <c r="E39" s="16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:7" hidden="1">
@@ -8586,16 +8649,13 @@
         <v>42</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>5</v>
+        <v>278</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>293</v>
       </c>
       <c r="E40" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>39</v>
@@ -8606,7 +8666,10 @@
         <v>42</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>293</v>
@@ -8619,17 +8682,17 @@
       </c>
     </row>
     <row r="42" spans="1:7" hidden="1">
-      <c r="A42" s="10" t="s">
-        <v>277</v>
+      <c r="A42" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="E42" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>39</v>
@@ -8640,7 +8703,7 @@
         <v>277</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>10</v>
@@ -8652,38 +8715,35 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" s="10" t="s">
         <v>277</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E44" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
-      <c r="A45" s="13" t="s">
-        <v>38</v>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E45" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>39</v>
@@ -8694,16 +8754,16 @@
         <v>38</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D46" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="16">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>39</v>
@@ -8714,7 +8774,7 @@
         <v>38</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>5</v>
@@ -8723,7 +8783,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>39</v>
@@ -8734,7 +8794,7 @@
         <v>38</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>5</v>
@@ -8743,7 +8803,7 @@
         <v>10</v>
       </c>
       <c r="E48" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>39</v>
@@ -8754,7 +8814,7 @@
         <v>38</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>5</v>
@@ -8774,7 +8834,7 @@
         <v>38</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>5</v>
@@ -8783,7 +8843,7 @@
         <v>10</v>
       </c>
       <c r="E50" s="16">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>39</v>
@@ -8794,7 +8854,7 @@
         <v>38</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>5</v>
@@ -8803,7 +8863,7 @@
         <v>10</v>
       </c>
       <c r="E51" s="16">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>39</v>
@@ -8814,32 +8874,52 @@
         <v>38</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>293</v>
+        <v>10</v>
       </c>
       <c r="E52" s="16">
         <v>12</v>
       </c>
-      <c r="F52" s="10"/>
       <c r="G52" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="10" t="s">
+    <row r="53" spans="1:7" hidden="1">
+      <c r="A53" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E53" s="16">
+        <v>12</v>
+      </c>
+      <c r="F53" s="10"/>
+      <c r="G53" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B55" s="10" t="s">
         <v>310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G52" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="B2:G53" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
         <filter val="プロト"/>
@@ -8851,13 +8931,13 @@
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D52" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D53" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G52" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G53" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C52" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C53" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9048,6 +9128,12 @@
         <v>31</v>
       </c>
     </row>
+    <row r="11" spans="3:16">
+      <c r="K11" t="s">
+        <v>357</v>
+      </c>
+      <c r="L11" s="53"/>
+    </row>
     <row r="12" spans="3:16">
       <c r="C12" t="s">
         <v>63</v>
@@ -9143,7 +9229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="3:13">
+    <row r="17" spans="3:9">
       <c r="C17" s="31">
         <v>21</v>
       </c>
@@ -9166,7 +9252,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:13">
+    <row r="18" spans="3:9">
       <c r="C18" s="31">
         <v>28</v>
       </c>
@@ -9180,16 +9266,13 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
-      <c r="K18">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="3:13">
+    </row>
+    <row r="20" spans="3:9">
       <c r="C20" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="3:13">
+    <row r="21" spans="3:9">
       <c r="C21" s="11" t="s">
         <v>50</v>
       </c>
@@ -9212,7 +9295,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:13">
+    <row r="22" spans="3:9">
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
@@ -9229,7 +9312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:13">
+    <row r="23" spans="3:9">
       <c r="C23" s="31">
         <v>5</v>
       </c>
@@ -9252,7 +9335,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="3:13">
+    <row r="24" spans="3:9">
       <c r="C24" s="31">
         <v>12</v>
       </c>
@@ -9275,7 +9358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="3:13">
+    <row r="25" spans="3:9">
       <c r="C25" s="19">
         <v>19</v>
       </c>
@@ -9298,41 +9381,33 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="3:13">
-      <c r="C26" s="49">
+    <row r="26" spans="3:9">
+      <c r="C26" s="52">
         <v>26</v>
       </c>
-      <c r="D26" s="49">
+      <c r="D26" s="52">
         <v>27</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="52">
         <v>28</v>
       </c>
-      <c r="F26" s="49">
+      <c r="F26" s="52">
         <v>29</v>
       </c>
-      <c r="G26" s="49">
+      <c r="G26" s="52">
         <v>30</v>
       </c>
-      <c r="H26" s="49">
+      <c r="H26" s="52">
         <v>31</v>
       </c>
       <c r="I26" s="11"/>
-      <c r="K26">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="3:13">
-      <c r="M29">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="3:13">
+    </row>
+    <row r="30" spans="3:9">
       <c r="C30" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="3:13">
+    <row r="31" spans="3:9">
       <c r="C31" s="11" t="s">
         <v>50</v>
       </c>
@@ -9355,28 +9430,25 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="3:13">
+    <row r="32" spans="3:9">
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
-      <c r="I32" s="49">
+      <c r="I32" s="52">
         <v>1</v>
       </c>
-      <c r="K32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9">
+    </row>
+    <row r="33" spans="3:11">
       <c r="C33" s="19">
         <v>2</v>
       </c>
       <c r="D33" s="19">
         <v>3</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="52">
         <v>4</v>
       </c>
       <c r="F33" s="19">
@@ -9392,7 +9464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="3:9">
+    <row r="34" spans="3:11">
       <c r="C34" s="19">
         <v>9</v>
       </c>
@@ -9415,7 +9487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="3:9">
+    <row r="35" spans="3:11">
       <c r="C35" s="37">
         <v>16</v>
       </c>
@@ -9438,30 +9510,33 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="3:9">
+    <row r="36" spans="3:11">
       <c r="C36" s="37">
         <v>23</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="52">
         <v>24</v>
       </c>
-      <c r="E36" s="37">
+      <c r="E36" s="52">
         <v>25</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="52">
         <v>26</v>
       </c>
-      <c r="G36" s="37">
+      <c r="G36" s="52">
         <v>27</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="52">
         <v>28</v>
       </c>
       <c r="I36" s="34">
         <v>29</v>
       </c>
-    </row>
-    <row r="37" spans="3:9">
+      <c r="K36" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="37" spans="3:11">
       <c r="C37" s="34">
         <v>30</v>
       </c>
@@ -9490,7 +9565,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -9817,6 +9892,11 @@
     <row r="55" spans="1:3">
       <c r="C55" t="s">
         <v>354</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="C56" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -10721,14 +10801,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10967,21 +11045,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11006,9 +11083,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F51A5A4-8B58-44FD-8C33-6B87583A0A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC75D20E-CD4F-4EB7-8AA0-CA034A80C57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -7711,18 +7711,18 @@
   <dimension ref="A1:O55"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="69.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.375" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.25" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.25" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="10"/>
-    <col min="9" max="9" width="18.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="11.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="10" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="10"/>
-    <col min="14" max="14" width="9.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.375" style="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="11"/>
     <col min="16" max="16384" width="9" style="10"/>
   </cols>
@@ -7773,7 +7773,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" s="17" t="s">
         <v>35</v>
       </c>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E53,G3:G53,"未着手")</f>
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F41)</f>
@@ -7813,10 +7813,10 @@
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.5185185185185186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" hidden="1">
+        <v>2.425925925925926</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
       <c r="A4" s="17" t="s">
         <v>35</v>
       </c>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E53,G3:G53,"未着手",D3:D53,I4)</f>
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F41,D3:D41,I4)</f>
@@ -7859,7 +7859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1">
+    <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
       <c r="A5" s="17" t="s">
         <v>35</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1">
+    <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
       <c r="A6" s="17" t="s">
         <v>35</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>306</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8346,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>306</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -8452,7 +8452,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -8598,7 +8598,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:7">

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC75D20E-CD4F-4EB7-8AA0-CA034A80C57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7850A35F-27FD-482F-A51F-D2417DB0A792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="360">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3694,6 +3694,28 @@
     </rPh>
     <rPh sb="10" eb="11">
       <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が死んだときの配列の消去などをしていないので、旗を立ててそれをする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ショウキョ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ハタ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>タ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9565,7 +9587,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -9897,6 +9919,11 @@
     <row r="56" spans="1:3">
       <c r="C56" t="s">
         <v>355</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="C58" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -10801,12 +10828,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11045,20 +11074,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11083,12 +11113,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,23 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7850A35F-27FD-482F-A51F-D2417DB0A792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1C780F-33EB-460F-A374-38920CA3B648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
     <sheet name="作業工数見積もり" sheetId="1" r:id="rId2"/>
     <sheet name="カレンダー" sheetId="6" r:id="rId3"/>
     <sheet name="日記" sheetId="12" r:id="rId4"/>
-    <sheet name="メモ" sheetId="9" r:id="rId5"/>
-    <sheet name="雑用" sheetId="10" r:id="rId6"/>
-    <sheet name="仕様書①" sheetId="13" r:id="rId7"/>
-    <sheet name="仕様書②" sheetId="15" r:id="rId8"/>
-    <sheet name="クラス設計" sheetId="14" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId5"/>
+    <sheet name="メモ" sheetId="9" r:id="rId6"/>
+    <sheet name="雑用" sheetId="10" r:id="rId7"/>
+    <sheet name="仕様書①" sheetId="13" r:id="rId8"/>
+    <sheet name="仕様書②" sheetId="15" r:id="rId9"/>
+    <sheet name="クラス設計" sheetId="14" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$53</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="385">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3716,6 +3717,187 @@
     </rPh>
     <rPh sb="26" eb="27">
       <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地上5段完成している</t>
+    <rPh sb="0" eb="2">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ダン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>x,y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xx,y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxxy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>切り上げ攻撃3種</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル3種</t>
+    <rPh sb="4" eb="5">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>できたらうれしい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全部担当</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>たいき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩き</t>
+    <rPh sb="0" eb="1">
+      <t>アル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はしり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かいひ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バック回避</t>
+    <rPh sb="3" eb="5">
+      <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>らっか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動系</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃1</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンボ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弱4種</t>
+    <rPh sb="0" eb="1">
+      <t>ジャク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強1種</t>
+    <rPh sb="0" eb="1">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地上強攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>切り上げ攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデル切り替えてアニメーションする仕組みを作る</t>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3790,7 +3972,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3953,6 +4135,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -4079,7 +4267,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4140,6 +4328,7 @@
     <xf numFmtId="56" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -7727,6 +7916,78 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B1947F-A3A0-4027-965D-A484FB7F3C32}">
+  <dimension ref="C1:AU33"/>
+  <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="3:35" ht="19.5" thickBot="1"/>
+    <row r="2" spans="3:35">
+      <c r="C2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE2" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="43"/>
+    </row>
+    <row r="3" spans="3:35">
+      <c r="AE3" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI3" s="45"/>
+    </row>
+    <row r="4" spans="3:35">
+      <c r="AE4" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI4" s="45"/>
+    </row>
+    <row r="5" spans="3:35" ht="19.5" thickBot="1">
+      <c r="AE5" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="48"/>
+    </row>
+    <row r="9" spans="3:35">
+      <c r="AE9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="34:47">
+      <c r="AN31" t="s">
+        <v>208</v>
+      </c>
+      <c r="AU31" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="34:47">
+      <c r="AH32" t="s">
+        <v>212</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="40:40">
+      <c r="AN33" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
@@ -9933,6 +10194,133 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{885D8AAA-735E-4C60-B6AA-AFC225D5AECF}">
+  <dimension ref="D2:R17"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:18">
+      <c r="D2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="3" spans="4:18">
+      <c r="D3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="4:18">
+      <c r="D4" t="s">
+        <v>364</v>
+      </c>
+      <c r="H4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="4:18">
+      <c r="D5" t="s">
+        <v>365</v>
+      </c>
+      <c r="H5" t="s">
+        <v>362</v>
+      </c>
+      <c r="N5" t="s">
+        <v>375</v>
+      </c>
+      <c r="O5" t="s">
+        <v>376</v>
+      </c>
+      <c r="P5" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>376</v>
+      </c>
+      <c r="R5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="6" spans="4:18">
+      <c r="H6" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="4:18">
+      <c r="D9" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="10" spans="4:18">
+      <c r="D10" t="s">
+        <v>368</v>
+      </c>
+      <c r="E10" t="s">
+        <v>369</v>
+      </c>
+      <c r="F10" t="s">
+        <v>371</v>
+      </c>
+      <c r="G10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" t="s">
+        <v>374</v>
+      </c>
+      <c r="K10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="12" spans="4:18">
+      <c r="D12" s="54" t="s">
+        <v>379</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="13" spans="4:18">
+      <c r="D13" s="54"/>
+      <c r="E13" s="54" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="15" spans="4:18">
+      <c r="D15" t="s">
+        <v>382</v>
+      </c>
+      <c r="E15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K15" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="17" spans="14:16">
+      <c r="N17" t="s">
+        <v>277</v>
+      </c>
+      <c r="P17" t="s">
+        <v>383</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
   <dimension ref="B2:P41"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -10170,7 +10558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -10356,7 +10744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
   <dimension ref="A1:AK43"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
@@ -10606,7 +10994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015F96B1-EBF5-4BB2-93CD-A0906537FC8C}">
   <dimension ref="C2:X16"/>
   <sheetFormatPr defaultColWidth="3.875" defaultRowHeight="18.75"/>
@@ -10755,87 +11143,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B1947F-A3A0-4027-965D-A484FB7F3C32}">
-  <dimension ref="C1:AU33"/>
-  <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="3:35" ht="19.5" thickBot="1"/>
-    <row r="2" spans="3:35">
-      <c r="C2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE2" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="43"/>
-    </row>
-    <row r="3" spans="3:35">
-      <c r="AE3" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="AI3" s="45"/>
-    </row>
-    <row r="4" spans="3:35">
-      <c r="AE4" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="AI4" s="45"/>
-    </row>
-    <row r="5" spans="3:35" ht="19.5" thickBot="1">
-      <c r="AE5" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="48"/>
-    </row>
-    <row r="9" spans="3:35">
-      <c r="AE9" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="31" spans="34:47">
-      <c r="AN31" t="s">
-        <v>208</v>
-      </c>
-      <c r="AU31" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="34:47">
-      <c r="AH32" t="s">
-        <v>212</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="33" spans="40:40">
-      <c r="AN33" t="s">
-        <v>211</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11074,21 +11388,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11113,9 +11426,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1C780F-33EB-460F-A374-38920CA3B648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06BFE3A-1F8C-4B96-B871-5A91C2ECDDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="4035" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="387">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3897,6 +3897,56 @@
       <t>シク</t>
     </rPh>
     <rPh sb="21" eb="22">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウルトの当たり判定、ステートを作る、そこでのみ確殺が起こるようにする</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクサツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、攻撃の操作改善orアニメーション切り替え時のモデル切り替えの仕組みを作る</t>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ソウサカイゼン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="39" eb="40">
       <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -7753,11 +7803,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.1494252873563218E-2</v>
+        <v>1.1467889908256881E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7775,7 +7825,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -7796,11 +7846,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-404</v>
+        <v>-405</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.4405940594059406</v>
+        <v>-0.43950617283950616</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -7813,11 +7863,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-384</v>
+        <v>-385</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.46354166666666669</v>
+        <v>-0.46233766233766233</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -7830,11 +7880,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-373</v>
+        <v>-374</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.47721179624664878</v>
+        <v>-0.47593582887700536</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8092,11 +8142,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.425925925925926</v>
+        <v>2.4716981132075473</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -8135,11 +8185,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>10</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -8178,11 +8228,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.3333333333333335</v>
+        <v>2.40625</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -8221,11 +8271,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.32</v>
+        <v>0.32653061224489793</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9848,7 +9898,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -10185,6 +10235,16 @@
     <row r="58" spans="1:3">
       <c r="C58" t="s">
         <v>359</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="C60" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="C61" t="s">
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -11144,12 +11204,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11388,20 +11450,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11426,12 +11489,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06BFE3A-1F8C-4B96-B871-5A91C2ECDDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72D9DA8-DBC7-460D-A78C-7224C8C3F3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="4035" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="-12825" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="389">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3948,6 +3948,50 @@
     </rPh>
     <rPh sb="39" eb="40">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先にプロトを完成させてから、攻撃操作改善などをする</t>
+    <rPh sb="0" eb="1">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はプレイヤーの被弾の仕組みを作った後、プレイヤーのhpなどを表示して、、っていう風にする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒダン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>フウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9898,7 +9942,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -10245,6 +10289,19 @@
     <row r="61" spans="1:3">
       <c r="C61" t="s">
         <v>386</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="1">
+        <v>46212</v>
+      </c>
+      <c r="C63" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="C64" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -11204,14 +11261,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11450,21 +11505,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11489,9 +11543,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72D9DA8-DBC7-460D-A78C-7224C8C3F3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDCE61F-ECFC-4E38-991E-4FE83415DA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="-12825" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="465" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="391">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3992,6 +3992,35 @@
     </rPh>
     <rPh sb="41" eb="42">
       <t>フウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被弾を作った、今、プレイヤーが死ぬステートを作ってる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それが終わったらプロとほぼ終わり</t>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9942,7 +9971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -10302,6 +10331,16 @@
     <row r="64" spans="1:3">
       <c r="C64" t="s">
         <v>388</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3">
+      <c r="C65" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3">
+      <c r="C66" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -11261,12 +11300,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11505,20 +11546,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11543,12 +11585,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDCE61F-ECFC-4E38-991E-4FE83415DA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5939EE-841D-4EA9-B429-E59DEA4F3F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="465" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="394">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4021,6 +4021,54 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本的なプロトは完成</t>
+    <rPh sb="0" eb="3">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不安要素は、残り時間と、アニメーション</t>
+    <rPh sb="0" eb="4">
+      <t>フアンヨウソ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次やることは攻撃の改善か、攻撃の際にモデルを切り替えること</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7876,11 +7924,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.1467889908256881E-2</v>
+        <v>1.1441647597254004E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7898,7 +7946,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -7919,11 +7967,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-405</v>
+        <v>-406</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.43950617283950616</v>
+        <v>-0.43842364532019706</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -7936,11 +7984,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-385</v>
+        <v>-386</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.46233766233766233</v>
+        <v>-0.46113989637305697</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -7953,11 +8001,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-374</v>
+        <v>-375</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.47593582887700536</v>
+        <v>-0.47466666666666668</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8215,11 +8263,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.4716981132075473</v>
+        <v>2.5192307692307692</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -8258,11 +8306,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>11.25</v>
+        <v>12.857142857142858</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -8301,11 +8349,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.40625</v>
+        <v>2.4838709677419355</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -8344,11 +8392,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.32653061224489793</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9971,7 +10019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -10333,14 +10381,32 @@
         <v>388</v>
       </c>
     </row>
-    <row r="65" spans="3:3">
+    <row r="65" spans="1:3">
       <c r="C65" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="66" spans="3:3">
+    <row r="66" spans="1:3">
       <c r="C66" t="s">
         <v>390</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1">
+        <v>46213</v>
+      </c>
+      <c r="C68" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="C69" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="C70" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -11300,14 +11366,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11546,21 +11610,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11585,9 +11648,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5939EE-841D-4EA9-B429-E59DEA4F3F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D948AD-8D3B-40E4-986F-A716B224E093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="0" windowWidth="21600" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="クラス設計" sheetId="14" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$55</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="396">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4069,6 +4069,32 @@
     </rPh>
     <rPh sb="24" eb="25">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル、ウルトゲージ周り</t>
+    <rPh sb="10" eb="11">
+      <t>マワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンカメラ切り替え、死亡時の自動切換え</t>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>シボウジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キリカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7902,8 +7928,8 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!E3:E74)</f>
-        <v>183</v>
+        <f>SUM(作業工数見積もり!E3:E76)</f>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -7911,8 +7937,8 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!G3:G22,"完了",作業工数見積もり!E3:E22)</f>
-        <v>5</v>
+        <f>SUMIF(作業工数見積もり!G3:G23,"完了",作業工数見積もり!E3:E23)</f>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -7928,7 +7954,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.1441647597254004E-2</v>
+        <v>1.8306636155606407E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -7971,7 +7997,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.43842364532019706</v>
+        <v>-0.43349753694581283</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -7988,7 +8014,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.46113989637305697</v>
+        <v>-0.45595854922279794</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8005,7 +8031,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.47466666666666668</v>
+        <v>-0.46933333333333332</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8162,7 +8188,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.125" style="10" bestFit="1" customWidth="1"/>
@@ -8251,15 +8277,15 @@
       </c>
       <c r="J3" s="10">
         <f>SUM(J4,J5,J6)</f>
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K3" s="10">
-        <f>SUMIFS(E3:E53,G3:G53,"未着手")</f>
-        <v>131</v>
+        <f>SUMIFS(E3:E55,G3:G55,"未着手")</f>
+        <v>127</v>
       </c>
       <c r="L3" s="10">
-        <f>SUM(F3:F41)</f>
-        <v>27</v>
+        <f>SUM(F3:F43)</f>
+        <v>32</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
@@ -8267,7 +8293,7 @@
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.5192307692307692</v>
+        <v>2.4423076923076925</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -8293,16 +8319,16 @@
         <v>28</v>
       </c>
       <c r="J4" s="29">
-        <f>SUMIF(D3:D53,I4,E3:E53)</f>
-        <v>90</v>
+        <f>SUMIF(D3:D55,I4,E3:E55)</f>
+        <v>91</v>
       </c>
       <c r="K4" s="10">
-        <f>SUMIFS(E3:E53,G3:G53,"未着手",D3:D53,I4)</f>
-        <v>56</v>
+        <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I4)</f>
+        <v>52</v>
       </c>
       <c r="L4" s="10">
-        <f>SUMIFS(F3:F41,D3:D41,I4)</f>
-        <v>27</v>
+        <f>SUMIFS(F3:F43,D3:D43,I4)</f>
+        <v>32</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
@@ -8310,7 +8336,7 @@
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>12.857142857142858</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -8336,15 +8362,15 @@
         <v>0</v>
       </c>
       <c r="J5" s="29">
-        <f>SUMIF(D3:D53,I5,E3:E53)</f>
+        <f>SUMIF(D3:D55,I5,E3:E55)</f>
         <v>77</v>
       </c>
       <c r="K5" s="10">
-        <f>SUMIFS(E3:E53,G3:G53,"未着手",D3:D53,I5)</f>
+        <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I5)</f>
         <v>59</v>
       </c>
       <c r="L5" s="10">
-        <f>SUMIFS(F4:F45,D4:D45,I5)</f>
+        <f>SUMIFS(F4:F47,D4:D47,I5)</f>
         <v>0</v>
       </c>
       <c r="M5" s="10">
@@ -8379,15 +8405,15 @@
         <v>29</v>
       </c>
       <c r="J6" s="29">
-        <f>SUMIF(D3:D53,I6,E3:E53)</f>
+        <f>SUMIF(D3:D55,I6,E3:E55)</f>
         <v>16</v>
       </c>
       <c r="K6" s="10">
-        <f>SUMIFS(E3:E53,G3:G53,"未着手",D3:D53,I6)</f>
+        <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I6)</f>
         <v>16</v>
       </c>
       <c r="L6" s="10">
-        <f>SUMIFS(F5:F45,D5:D45,I6)</f>
+        <f>SUMIFS(F5:F47,D5:D47,I6)</f>
         <v>0</v>
       </c>
       <c r="M6" s="10">
@@ -8534,7 +8560,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" hidden="1">
       <c r="A13" s="19" t="s">
         <v>44</v>
       </c>
@@ -8563,7 +8589,7 @@
         <v>46244</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" hidden="1">
       <c r="A14" s="19" t="s">
         <v>44</v>
       </c>
@@ -8589,7 +8615,7 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" hidden="1">
       <c r="A15" s="19" t="s">
         <v>44</v>
       </c>
@@ -8634,7 +8660,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>307</v>
+        <v>394</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5</v>
@@ -8643,10 +8669,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="16">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F17" s="16">
+        <v>1</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -8654,7 +8683,7 @@
         <v>44</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>5</v>
@@ -8662,13 +8691,22 @@
       <c r="D18" s="16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="E18" s="16">
+        <v>2</v>
+      </c>
+      <c r="F18" s="16">
+        <v>2</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" s="19" t="s">
         <v>44</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>5</v>
@@ -8677,12 +8715,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" s="19" t="s">
         <v>44</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>5</v>
@@ -8690,19 +8728,13 @@
       <c r="D20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="16">
-        <v>8</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="20" t="s">
-        <v>46</v>
+      <c r="A21" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>5</v>
@@ -8711,7 +8743,7 @@
         <v>18</v>
       </c>
       <c r="E21" s="16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>39</v>
@@ -8722,16 +8754,16 @@
         <v>46</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>39</v>
@@ -8742,7 +8774,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>257</v>
@@ -8751,7 +8783,7 @@
         <v>18</v>
       </c>
       <c r="E23" s="16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>39</v>
@@ -8762,30 +8794,27 @@
         <v>46</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="16">
-        <v>4</v>
-      </c>
-      <c r="F24" s="16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" s="20" t="s">
         <v>46</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>5</v>
@@ -8794,64 +8823,64 @@
         <v>18</v>
       </c>
       <c r="E25" s="16">
+        <v>4</v>
+      </c>
+      <c r="F25" s="16">
         <v>2</v>
-      </c>
-      <c r="F25" s="16">
-        <v>1</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" s="20" t="s">
         <v>46</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D26" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="16">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="F26" s="16">
+        <v>1</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="49" t="s">
-        <v>264</v>
+      <c r="A27" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D27" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="16">
-        <v>3</v>
-      </c>
-      <c r="F27" s="16">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" s="49" t="s">
         <v>264</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>5</v>
@@ -8860,10 +8889,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="16">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F28" s="16">
+        <v>1</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -8871,7 +8903,7 @@
         <v>264</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>5</v>
@@ -8880,21 +8912,21 @@
         <v>18</v>
       </c>
       <c r="E29" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" s="49" t="s">
         <v>264</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>5</v>
@@ -8903,10 +8935,13 @@
         <v>18</v>
       </c>
       <c r="E30" s="16">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F30" s="16">
+        <v>1</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>306</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -8914,7 +8949,7 @@
         <v>264</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>5</v>
@@ -8926,15 +8961,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="21" t="s">
-        <v>40</v>
+      <c r="A32" s="49" t="s">
+        <v>264</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>5</v>
@@ -8946,7 +8981,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>306</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -8954,19 +8989,19 @@
         <v>40</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -8974,42 +9009,42 @@
         <v>40</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="16">
-        <v>2</v>
-      </c>
-      <c r="F34" s="16">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" s="21" t="s">
         <v>40</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D35" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="16">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F35" s="16">
+        <v>12</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -9017,33 +9052,18 @@
         <v>40</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="C36" s="16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>257</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="16">
-        <v>6</v>
-      </c>
-      <c r="F36" s="16">
-        <v>6</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>5</v>
       </c>
       <c r="D37" s="16" t="s">
         <v>18</v>
@@ -9052,27 +9072,27 @@
         <v>3</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1">
+      <c r="A38" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F38" s="16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>57</v>
@@ -9083,7 +9103,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>5</v>
@@ -9092,47 +9112,53 @@
         <v>18</v>
       </c>
       <c r="E39" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G39" s="16" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1">
+      <c r="A40" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="16">
+        <v>1</v>
+      </c>
+      <c r="F40" s="16">
+        <v>1</v>
+      </c>
+      <c r="G40" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
-      <c r="A40" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="E40" s="16">
-        <v>2</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
     <row r="41" spans="1:7" hidden="1">
-      <c r="A41" s="23" t="s">
-        <v>42</v>
+      <c r="A41" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>279</v>
+        <v>75</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>293</v>
+        <v>18</v>
       </c>
       <c r="E41" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:7" hidden="1">
@@ -9140,104 +9166,101 @@
         <v>42</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>293</v>
       </c>
       <c r="E42" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:7" hidden="1">
-      <c r="A43" s="10" t="s">
-        <v>277</v>
+      <c r="A43" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="E43" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:7" hidden="1">
-      <c r="A44" s="10" t="s">
-        <v>277</v>
+      <c r="A44" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="E44" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" s="10" t="s">
         <v>277</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E45" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:7" hidden="1">
-      <c r="A46" s="13" t="s">
-        <v>38</v>
+      <c r="A46" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="D46" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
-      <c r="A47" s="13" t="s">
-        <v>38</v>
+    <row r="47" spans="1:7">
+      <c r="A47" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E47" s="16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>39</v>
@@ -9248,16 +9271,16 @@
         <v>38</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D48" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>39</v>
@@ -9268,7 +9291,7 @@
         <v>38</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>5</v>
@@ -9288,7 +9311,7 @@
         <v>38</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>5</v>
@@ -9297,7 +9320,7 @@
         <v>10</v>
       </c>
       <c r="E50" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>39</v>
@@ -9308,7 +9331,7 @@
         <v>38</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>5</v>
@@ -9317,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="E51" s="16">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>39</v>
@@ -9328,7 +9351,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>5</v>
@@ -9337,7 +9360,7 @@
         <v>10</v>
       </c>
       <c r="E52" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>39</v>
@@ -9348,50 +9371,96 @@
         <v>38</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>293</v>
+        <v>10</v>
       </c>
       <c r="E53" s="16">
-        <v>12</v>
-      </c>
-      <c r="F53" s="10"/>
+        <v>4</v>
+      </c>
       <c r="G53" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="10" t="s">
+    <row r="54" spans="1:7" hidden="1">
+      <c r="A54" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="16">
+        <v>12</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1">
+      <c r="A55" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E55" s="16">
+        <v>12</v>
+      </c>
+      <c r="F55" s="10"/>
+      <c r="G55" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B57" s="10" t="s">
         <v>310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G53" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="B2:G55" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
         <filter val="プロト"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G36">
-      <sortCondition ref="B2:B36"/>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="作業中"/>
+        <filter val="未着手"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G38">
+      <sortCondition ref="B2:B38"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D53" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D55" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G53" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G55" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C53" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C55" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D948AD-8D3B-40E4-986F-A716B224E093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC344CE6-6908-4C9D-A979-CE75D719A46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="0" windowWidth="21600" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC344CE6-6908-4C9D-A979-CE75D719A46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC49878B-E2DD-4D2C-B24A-508738438593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="0" windowWidth="21600" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$55</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="415">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3401,19 +3402,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>次はスポナーの仕組みを作る</t>
-    <rPh sb="0" eb="1">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>今、ジャスト回避を作っていて、ジャスト回避用のColliderをつくるところ</t>
     <rPh sb="0" eb="1">
       <t>イマ</t>
@@ -4095,6 +4083,410 @@
     </rPh>
     <rPh sb="19" eb="21">
       <t>キリカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ時のカメラの改善終わり、</t>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が空中で死ぬの変だし、攻撃をした敵の空中-&gt;地面のノックバックが変</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヘン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が吹っ飛ばされた後は、しばらく動けない状態にしたい</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次やることは、攻撃の操作感改善のための、ロックオンシステムの改善</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ソウサカン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンの切り替えはできるようになった。</t>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ロックオンしている敵が死んだとき、自動でターゲットが切り替わる仕組み</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終わったので、ターゲットしている敵に向かって攻撃する仕組みを作る</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンの時のターゲットもプレイヤーカメラ同様にプレイヤーの高さに応じて、割合を決めて変えるようにする</t>
+    <rPh sb="6" eb="7">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ワリアイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンしていないとき、の内部的なターゲットについて</t>
+    <rPh sb="14" eb="17">
+      <t>ナイブテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力方向の先に敵がいたらそいつに切り替わる</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃して当たった敵をターゲットにする</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>多段ヒットした場合</t>
+    <rPh sb="0" eb="2">
+      <t>タダン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初の敵をターゲットする？</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内部ロックオンの基盤は完成→現在は、攻撃したら内部ロックオンの設定を完了</t>
+    <rPh sb="0" eb="2">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キバン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、攻撃の時に入力があったら、その方向に敵がいたら内部ターゲットを切り替える、いなかったらそのまま</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また、内部ターゲットがいなかったらその敵を探す仕組みがあってもいい</t>
+    <rPh sb="3" eb="5">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃が当たったタイミングで新しいカメラ(攻撃中にカッコいい角度のするカメラ)に切り替えて、右スティックの入力があったら、PlayerCameraに戻すs</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>コウゲキチュウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PlayerStateAttackでgamesceneの関数を呼び出す-&gt;入力方向に敵がいたら内部ターゲットをきりかえる</t>
+    <rPh sb="28" eb="30">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="37" eb="41">
+      <t>ニュウリョクホウコウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ナイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内部ロックオンの仕組み終わった！すべて終わったと思う</t>
+    <rPh sb="0" eb="2">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後は、内部ロックオンした時にカッコいいカメラに行くように自然とカメラの位置を変える（攻撃が当たったタイミングで）</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シゼン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7929,7 +8321,7 @@
       </c>
       <c r="C3">
         <f>SUM(作業工数見積もり!E3:E76)</f>
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -7972,7 +8364,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -7997,7 +8389,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.43349753694581283</v>
+        <v>-0.44088669950738918</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8014,7 +8406,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.45595854922279794</v>
+        <v>-0.46373056994818651</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8031,7 +8423,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.46933333333333332</v>
+        <v>-0.47733333333333333</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8277,11 +8669,11 @@
       </c>
       <c r="J3" s="10">
         <f>SUM(J4,J5,J6)</f>
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E55,G3:G55,"未着手")</f>
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F43)</f>
@@ -8289,11 +8681,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.4423076923076925</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -8320,11 +8712,11 @@
       </c>
       <c r="J4" s="29">
         <f>SUMIF(D3:D55,I4,E3:E55)</f>
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I4)</f>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F43,D3:D43,I4)</f>
@@ -8332,11 +8724,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>13</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -8375,11 +8767,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.4838709677419355</v>
+        <v>2.6551724137931036</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -8418,11 +8810,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.34782608695652173</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -8660,7 +9052,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5</v>
@@ -8706,7 +9098,7 @@
         <v>44</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>5</v>
@@ -8720,7 +9112,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>5</v>
@@ -9052,7 +9444,19 @@
         <v>40</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="16">
+        <v>3</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -9123,7 +9527,7 @@
         <v>41</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>5</v>
@@ -9653,7 +10057,7 @@
     </row>
     <row r="11" spans="3:16">
       <c r="K11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L11" s="53"/>
     </row>
@@ -10056,7 +10460,7 @@
         <v>29</v>
       </c>
       <c r="K36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37" spans="3:11">
@@ -10088,7 +10492,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -10353,32 +10757,32 @@
         <v>46209</v>
       </c>
       <c r="C43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="C45" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="C46" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="C47" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="C48" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -10386,12 +10790,12 @@
         <v>46210</v>
       </c>
       <c r="C49" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="C50" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -10399,42 +10803,42 @@
         <v>46211</v>
       </c>
       <c r="C52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="C53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="C54" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="C55" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="C56" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="C58" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="C60" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="C61" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -10442,22 +10846,22 @@
         <v>46212</v>
       </c>
       <c r="C63" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="C64" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="C65" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="C66" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -10465,17 +10869,95 @@
         <v>46213</v>
       </c>
       <c r="C68" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="C69" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="C70" t="s">
-        <v>393</v>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1">
+        <v>46214</v>
+      </c>
+      <c r="C72" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="C73" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="C74" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="C76" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="C77" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="C78" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="C79" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
+      <c r="C81" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3">
+      <c r="C83" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3">
+      <c r="C84" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3">
+      <c r="C85" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3">
+      <c r="C90" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3">
+      <c r="C91" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -10497,104 +10979,104 @@
   <sheetData>
     <row r="2" spans="4:18">
       <c r="D2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="4:18">
       <c r="D3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="4:18">
       <c r="D4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="4:18">
       <c r="D5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N5" t="s">
+        <v>374</v>
+      </c>
+      <c r="O5" t="s">
         <v>375</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>376</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
+        <v>375</v>
+      </c>
+      <c r="R5" t="s">
         <v>377</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>376</v>
-      </c>
-      <c r="R5" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="6" spans="4:18">
       <c r="H6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="4:18">
       <c r="D9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="4:18">
       <c r="D10" t="s">
+        <v>367</v>
+      </c>
+      <c r="E10" t="s">
         <v>368</v>
       </c>
-      <c r="E10" t="s">
-        <v>369</v>
-      </c>
       <c r="F10" t="s">
+        <v>370</v>
+      </c>
+      <c r="G10" t="s">
         <v>371</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>372</v>
-      </c>
-      <c r="H10" t="s">
-        <v>373</v>
       </c>
       <c r="I10" t="s">
         <v>99</v>
       </c>
       <c r="J10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="4:18">
       <c r="D12" s="54" t="s">
+        <v>378</v>
+      </c>
+      <c r="E12" s="54" t="s">
         <v>379</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="13" spans="4:18">
       <c r="D13" s="54"/>
       <c r="E13" s="54" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="4:18">
       <c r="D15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E15" t="s">
         <v>107</v>
       </c>
       <c r="K15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" spans="14:16">
@@ -10602,7 +11084,7 @@
         <v>277</v>
       </c>
       <c r="P17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -10613,7 +11095,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:P41"/>
+  <dimension ref="B2:P45"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -10713,17 +11195,17 @@
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D20" t="s">
         <v>312</v>
@@ -10731,7 +11213,7 @@
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D21" t="s">
         <v>313</v>
@@ -10742,7 +11224,7 @@
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D22" t="s">
         <v>315</v>
@@ -10752,9 +11234,6 @@
       </c>
     </row>
     <row r="23" spans="2:16">
-      <c r="B23" t="s">
-        <v>331</v>
-      </c>
       <c r="D23" t="s">
         <v>317</v>
       </c>
@@ -10805,7 +11284,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" spans="2:12">
       <c r="B33" t="s">
         <v>333</v>
       </c>
@@ -10813,34 +11292,53 @@
         <v>323</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
+    <row r="34" spans="2:12">
       <c r="B34" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" spans="2:12">
       <c r="B35" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="2:12">
       <c r="B36" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:12">
       <c r="B37" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
+    <row r="40" spans="2:12">
       <c r="B40" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
+    <row r="41" spans="2:12">
       <c r="B41" t="s">
         <v>339</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="D44" t="s">
+        <v>405</v>
+      </c>
+      <c r="I44" t="s">
+        <v>406</v>
+      </c>
+      <c r="L44" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="B45" t="s">
+        <v>403</v>
+      </c>
+      <c r="D45" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -11435,12 +11933,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11679,20 +12179,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11717,12 +12218,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC49878B-E2DD-4D2C-B24A-508738438593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC8F9A1-9F9F-4A02-9377-92A73011A367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="421">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4487,6 +4487,114 @@
     </rPh>
     <rPh sb="45" eb="46">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自然と変えるやつは、その左右の切り替えが変だからよくわからない</t>
+    <rPh sb="0" eb="2">
+      <t>シゼン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今から、ロックオンした時のカメラの注視点の位置を割合にする</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>チュウシテン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ワリアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なんかあんまりうまくいかなかった、もっと研究が必要(血殺の時の角度について)</t>
+    <rPh sb="20" eb="22">
+      <t>ケンキュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>サツ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これで基本的にやりたいことは終わった</t>
+    <rPh sb="3" eb="6">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、カプセルコライダーとかボックスコライダーを足す</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>orモデル切り替えや、例キャストで地面との当たり判定を常にとるなど</t>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツネ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8330,7 +8438,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!G3:G23,"完了",作業工数見積もり!E3:E23)</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -8346,7 +8454,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.8306636155606407E-2</v>
+        <v>5.0343249427917618E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8389,7 +8497,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.44088669950738918</v>
+        <v>-0.40640394088669951</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8406,7 +8514,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.46373056994818651</v>
+        <v>-0.42746113989637308</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8423,7 +8531,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.47733333333333333</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8673,11 +8781,11 @@
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E55,G3:G55,"未着手")</f>
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F43)</f>
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
@@ -8685,7 +8793,7 @@
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.6</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -8716,11 +8824,11 @@
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I4)</f>
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F43,D3:D43,I4)</f>
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
@@ -8873,8 +8981,11 @@
       <c r="E9" s="16">
         <v>2</v>
       </c>
+      <c r="F9" s="16">
+        <v>2</v>
+      </c>
       <c r="G9" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:14" hidden="1" outlineLevel="1">
@@ -8942,8 +9053,11 @@
       <c r="E12" s="16">
         <v>12</v>
       </c>
+      <c r="F12" s="16">
+        <v>4</v>
+      </c>
       <c r="G12" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>296</v>
@@ -9455,8 +9569,11 @@
       <c r="E36" s="16">
         <v>3</v>
       </c>
+      <c r="F36" s="16">
+        <v>4</v>
+      </c>
       <c r="G36" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -10492,7 +10609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -10958,6 +11075,36 @@
     <row r="91" spans="3:3">
       <c r="C91" t="s">
         <v>414</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3">
+      <c r="C92" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3">
+      <c r="C93" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3">
+      <c r="C94" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3">
+      <c r="C95" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3">
+      <c r="C96" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3">
+      <c r="C97" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC8F9A1-9F9F-4A02-9377-92A73011A367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB61ED6-8BC1-4798-855D-A15C84E4ED1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$55</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="428">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4595,6 +4594,76 @@
     </rPh>
     <rPh sb="27" eb="28">
       <t>ツネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の吹っ飛んだ後、ダウン状態にするようにした</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、カプセルコライダーorレイキャストで地面との当たり判定をとる、血殺のシェーダーのどれか</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>サツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レイキャストかな</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあとシェーダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レイキャスト終了、カプセルコライダーのdxLibのほうは慣れたからそれやってもいい</t>
+    <rPh sb="6" eb="8">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もしくは、シェーダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まずはステージ制作のリメイクをする</t>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8438,7 +8507,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!G3:G23,"完了",作業工数見積もり!E3:E23)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -8454,7 +8523,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.0343249427917618E-2</v>
+        <v>5.7208237986270026E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8497,7 +8566,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.40640394088669951</v>
+        <v>-0.39901477832512317</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8514,7 +8583,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.42746113989637308</v>
+        <v>-0.41968911917098445</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8531,7 +8600,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.44</v>
+        <v>-0.432</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8781,11 +8850,11 @@
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E55,G3:G55,"未着手")</f>
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F43)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
@@ -8793,7 +8862,7 @@
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.2599999999999998</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -8824,11 +8893,11 @@
       </c>
       <c r="K4" s="10">
         <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I4)</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F43,D3:D43,I4)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
@@ -8965,7 +9034,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="1:14" outlineLevel="1">
+    <row r="9" spans="1:14" hidden="1" outlineLevel="1">
       <c r="A9" s="19" t="s">
         <v>44</v>
       </c>
@@ -9037,7 +9106,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" hidden="1">
       <c r="A12" s="19" t="s">
         <v>44</v>
       </c>
@@ -9161,7 +9230,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" s="19" t="s">
         <v>44</v>
       </c>
@@ -9184,7 +9253,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" s="19" t="s">
         <v>44</v>
       </c>
@@ -9271,8 +9340,11 @@
       <c r="E22" s="16">
         <v>3</v>
       </c>
+      <c r="F22" s="16">
+        <v>3</v>
+      </c>
       <c r="G22" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -9404,7 +9476,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" s="49" t="s">
         <v>264</v>
       </c>
@@ -9553,7 +9625,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" s="21" t="s">
         <v>40</v>
       </c>
@@ -10609,7 +10681,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11102,9 +11174,47 @@
         <v>419</v>
       </c>
     </row>
-    <row r="97" spans="3:3">
+    <row r="97" spans="1:3">
       <c r="C97" t="s">
         <v>420</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1">
+        <v>46215</v>
+      </c>
+      <c r="C99" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="C100" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="C101" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="C102" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="C103" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="C104" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="C105" t="s">
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -12080,14 +12190,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12326,21 +12434,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12365,9 +12472,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB61ED6-8BC1-4798-855D-A15C84E4ED1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B04967D-F765-4C0E-85E3-002C826A6233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="430">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4664,6 +4664,53 @@
     <t>まずはステージ制作のリメイクをする</t>
     <rPh sb="7" eb="9">
       <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>階段（段差）や、斜めの床、高台を追加した。なぜか、カメラ周りの処理や、壁付近でジャンプした時どうなっているのかがわからない</t>
+    <rPh sb="0" eb="2">
+      <t>カイダン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダンサ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナナ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タカダイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>カベフキン</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その辺をする、一旦聞いて、無理そうだったらシェーダーとかをする</t>
+    <rPh sb="2" eb="3">
+      <t>ヘン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>イッタンキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ムリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10681,7 +10728,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11215,6 +11262,16 @@
     <row r="105" spans="1:3">
       <c r="C105" t="s">
         <v>427</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="C106" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="C107" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -12190,12 +12247,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12434,20 +12493,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12472,12 +12532,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B04967D-F765-4C0E-85E3-002C826A6233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E53A85B-85B1-4836-9965-6650F7BD975C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="431">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4711,6 +4711,31 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>ムリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのモデル切り替えの仕組みと、ポリゴンとの当たり判定を同時進行で進めている</t>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>ドウジシンコウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>スス</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8566,11 +8591,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.7208237986270026E-2</v>
+        <v>5.7077625570776253E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8588,7 +8613,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8609,11 +8634,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-406</v>
+        <v>-407</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39901477832512317</v>
+        <v>-0.39803439803439805</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8626,11 +8651,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-386</v>
+        <v>-387</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.41968911917098445</v>
+        <v>-0.41860465116279072</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8643,11 +8668,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-375</v>
+        <v>-376</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.432</v>
+        <v>-0.43085106382978722</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8905,11 +8930,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.2000000000000002</v>
+        <v>2.2448979591836733</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -8948,11 +8973,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>18.8</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -8991,11 +9016,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.6551724137931036</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -9034,11 +9059,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.34782608695652173</v>
+        <v>0.35555555555555557</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -10728,7 +10753,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11272,6 +11297,14 @@
     <row r="107" spans="1:3">
       <c r="C107" t="s">
         <v>429</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1">
+        <v>46216</v>
+      </c>
+      <c r="C109" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -12247,14 +12280,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12493,21 +12524,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12532,9 +12562,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E53A85B-85B1-4836-9965-6650F7BD975C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9912D7-1498-4EDC-9510-345EC0F6161B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="0" windowWidth="22110" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="438">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4736,6 +4736,103 @@
     </rPh>
     <rPh sb="36" eb="37">
       <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先にk2用にアルファを進めることにした</t>
+    <rPh sb="0" eb="1">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、↑のプレイヤーのモデル切り替えの仕組みとポリゴンとの当たり判定をしようかなと思っている</t>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファの次にすること</t>
+    <rPh sb="5" eb="6">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>waveごとにプレイヤーの動ける範囲を制限する</t>
+    <rPh sb="13" eb="14">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあとは、コンボノードや、操作Uiを追加する</t>
+    <rPh sb="14" eb="16">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正直、あんまり思いついていない→先輩に都度きく</t>
+    <rPh sb="0" eb="2">
+      <t>ショウジキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>24日までの10日間、アルファを進めるという認識でいい</t>
+    <rPh sb="2" eb="3">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニチカン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ニンシキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8591,11 +8688,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.7077625570776253E-2</v>
+        <v>5.6947608200455579E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8613,7 +8710,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8634,11 +8731,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-407</v>
+        <v>-408</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39803439803439805</v>
+        <v>-0.39705882352941174</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8651,11 +8748,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-387</v>
+        <v>-388</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.41860465116279072</v>
+        <v>-0.4175257731958763</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8668,11 +8765,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-376</v>
+        <v>-377</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.43085106382978722</v>
+        <v>-0.42970822281167109</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8922,7 +9019,7 @@
       </c>
       <c r="K3" s="10">
         <f>SUMIFS(E3:E55,G3:G55,"未着手")</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F43)</f>
@@ -8930,14 +9027,14 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.2448979591836733</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
+        <v>2.2708333333333335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="26.25" customHeight="1">
       <c r="A4" s="17" t="s">
         <v>35</v>
       </c>
@@ -8973,14 +9070,14 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
+        <v>31.333333333333332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16.5" customHeight="1">
       <c r="A5" s="17" t="s">
         <v>35</v>
       </c>
@@ -9016,14 +9113,14 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
+        <v>2.8518518518518516</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="19.5" customHeight="1">
       <c r="A6" s="17" t="s">
         <v>35</v>
       </c>
@@ -9051,19 +9148,19 @@
       </c>
       <c r="K6" s="10">
         <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I6)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L6" s="10">
         <f>SUMIFS(F5:F47,D5:D47,I6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.35555555555555557</v>
+        <v>0.36363636363636365</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9086,7 +9183,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="8" spans="1:14" hidden="1" outlineLevel="1">
+    <row r="8" spans="1:14" outlineLevel="1">
       <c r="A8" s="19" t="s">
         <v>44</v>
       </c>
@@ -9129,7 +9226,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" outlineLevel="1">
+    <row r="10" spans="1:14" outlineLevel="1">
       <c r="A10" s="19" t="s">
         <v>44</v>
       </c>
@@ -9396,7 +9493,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" s="20" t="s">
         <v>46</v>
       </c>
@@ -9826,7 +9923,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" s="23" t="s">
         <v>42</v>
       </c>
@@ -9843,7 +9940,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" s="23" t="s">
         <v>42</v>
       </c>
@@ -9863,7 +9960,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" s="23" t="s">
         <v>42</v>
       </c>
@@ -9876,11 +9973,14 @@
       <c r="E44" s="16">
         <v>1</v>
       </c>
+      <c r="F44" s="16">
+        <v>1</v>
+      </c>
       <c r="G44" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" hidden="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="10" t="s">
         <v>277</v>
       </c>
@@ -9897,7 +9997,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" s="10" t="s">
         <v>277</v>
       </c>
@@ -9931,7 +10031,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" s="13" t="s">
         <v>38</v>
       </c>
@@ -9951,7 +10051,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" s="13" t="s">
         <v>38</v>
       </c>
@@ -9971,7 +10071,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" s="13" t="s">
         <v>38</v>
       </c>
@@ -9991,7 +10091,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" s="13" t="s">
         <v>38</v>
       </c>
@@ -10011,7 +10111,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" s="13" t="s">
         <v>38</v>
       </c>
@@ -10031,7 +10131,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" s="13" t="s">
         <v>38</v>
       </c>
@@ -10051,7 +10151,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" s="13" t="s">
         <v>38</v>
       </c>
@@ -10071,7 +10171,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1">
+    <row r="55" spans="1:7">
       <c r="A55" s="13" t="s">
         <v>38</v>
       </c>
@@ -10102,11 +10202,6 @@
     </row>
   </sheetData>
   <autoFilter ref="B2:G55" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="プロト"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="5">
       <filters>
         <filter val="作業中"/>
@@ -10753,7 +10848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11305,6 +11400,41 @@
       </c>
       <c r="C109" t="s">
         <v>430</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="C110" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="C111" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="C112" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="113" spans="3:3">
+      <c r="C113" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3">
+      <c r="C114" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3">
+      <c r="C115" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3">
+      <c r="C116" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -12280,12 +12410,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12524,20 +12656,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12562,12 +12695,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9912D7-1498-4EDC-9510-345EC0F6161B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C35EBA-AAFA-4ADC-8B73-09C8226FA5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="0" windowWidth="22110" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="435">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3081,60 +3081,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ロックオンはプレイヤーから一番近い敵をロックオン</t>
-    <rPh sb="13" eb="16">
-      <t>イチバンチカ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ロックオンした敵の方向にプレイヤーは攻撃する</t>
-    <rPh sb="7" eb="8">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホウコウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>また、普通の攻撃した時も内部的にはロックオンし、別の入力があった場合は、切り替える</t>
-    <rPh sb="3" eb="5">
-      <t>フツウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ナイブテキ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ロックオンした時はプレイヤーと敵の中間点をカメラは見続ける</t>
     <rPh sb="7" eb="8">
       <t>トキ</t>
@@ -3151,54 +3097,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カメラの方向とかプレイヤーの方向とかもいろいろありそう</t>
-    <rPh sb="4" eb="6">
-      <t>ホウコウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ホウコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>案2</t>
-    <rPh sb="0" eb="1">
-      <t>アン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>rayvecとenemyVecの角度を取り、その角度差が小さいところを取る（範囲指定して奥行ってしまうバグをなくす）</t>
-    <rPh sb="16" eb="18">
-      <t>カクド</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>カクド</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>サ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>チイ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="38" eb="42">
-      <t>ハンイシテイ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ロックオンしている敵に攻撃がむかうようにする</t>
     <rPh sb="9" eb="10">
       <t>テキ</t>
@@ -4260,55 +4158,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>入力方向の先に敵がいたらそいつに切り替わる</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ホウコウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃して当たった敵をターゲットにする</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>多段ヒットした場合</t>
-    <rPh sb="0" eb="2">
-      <t>タダン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>最初の敵をターゲットする？</t>
-    <rPh sb="0" eb="2">
-      <t>サイショ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>内部ロックオンの基盤は完成→現在は、攻撃したら内部ロックオンの設定を完了</t>
     <rPh sb="0" eb="2">
       <t>ナイブ</t>
@@ -4833,6 +4682,91 @@
     </rPh>
     <rPh sb="22" eb="24">
       <t>ニンシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデルの分離が意外といけそう</t>
+    <rPh sb="4" eb="6">
+      <t>ブンリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデルのそこからの子フレームをすべて取得して、</t>
+    <rPh sb="9" eb="10">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行列でスケールなどをゼロにする</t>
+    <rPh sb="0" eb="2">
+      <t>ギョウレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そしたらないように見える</t>
+    <rPh sb="9" eb="10">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そこに、新しくもう1つのモデルを用意して、それを飛ばすことで、分離しているように見せれる</t>
+    <rPh sb="4" eb="5">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ブンリ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデルの分離方法を川野先生に教わった</t>
+    <rPh sb="4" eb="8">
+      <t>ブンリホウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カワ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やることステージをちゃんと作る(れお先輩のステージを参考にする)</t>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サンコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8688,11 +8622,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.6947608200455579E-2</v>
+        <v>5.6818181818181816E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8710,7 +8644,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8731,11 +8665,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-408</v>
+        <v>-409</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39705882352941174</v>
+        <v>-0.39608801955990219</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8748,11 +8682,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-388</v>
+        <v>-389</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.4175257731958763</v>
+        <v>-0.41645244215938304</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8765,11 +8699,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-377</v>
+        <v>-378</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42970822281167109</v>
+        <v>-0.42857142857142855</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9027,11 +8961,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.2708333333333335</v>
+        <v>2.3191489361702127</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" customHeight="1">
@@ -9070,11 +9004,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>31.333333333333332</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -9113,11 +9047,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.8518518518518516</v>
+        <v>2.9615384615384617</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1">
@@ -9156,11 +9090,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.36363636363636365</v>
+        <v>0.37209302325581395</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9404,7 +9338,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5</v>
@@ -9450,7 +9384,7 @@
         <v>44</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>5</v>
@@ -9464,7 +9398,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>5</v>
@@ -9799,7 +9733,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5</v>
@@ -9885,7 +9819,7 @@
         <v>41</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>5</v>
@@ -10413,7 +10347,7 @@
     </row>
     <row r="11" spans="3:16">
       <c r="K11" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="L11" s="53"/>
     </row>
@@ -10816,7 +10750,7 @@
         <v>29</v>
       </c>
       <c r="K36" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="37" spans="3:11">
@@ -10848,7 +10782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11113,32 +11047,32 @@
         <v>46209</v>
       </c>
       <c r="C43" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="C45" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="C46" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="C47" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="C48" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -11146,12 +11080,12 @@
         <v>46210</v>
       </c>
       <c r="C49" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="C50" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -11159,42 +11093,42 @@
         <v>46211</v>
       </c>
       <c r="C52" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="C53" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="C54" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="C55" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="C56" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="C58" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="C60" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="C61" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -11202,22 +11136,22 @@
         <v>46212</v>
       </c>
       <c r="C63" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="C64" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="C65" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="C66" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -11225,17 +11159,17 @@
         <v>46213</v>
       </c>
       <c r="C68" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="C69" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="C70" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -11243,107 +11177,107 @@
         <v>46214</v>
       </c>
       <c r="C72" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="C73" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="C74" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="C76" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="C77" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="C78" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="C79" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
     </row>
     <row r="96" spans="3:3">
       <c r="C96" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="C97" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -11351,47 +11285,47 @@
         <v>46215</v>
       </c>
       <c r="C99" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="C100" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="C101" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="C102" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="C103" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="C104" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="C105" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="C106" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="C107" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -11399,42 +11333,55 @@
         <v>46216</v>
       </c>
       <c r="C109" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="C110" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="C111" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="C112" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="C113" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="C114" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="C115" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="C116" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C118" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="113" spans="3:3">
-      <c r="C113" t="s">
+    <row r="119" spans="1:3">
+      <c r="C119" t="s">
         <v>434</v>
-      </c>
-    </row>
-    <row r="114" spans="3:3">
-      <c r="C114" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="115" spans="3:3">
-      <c r="C115" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="116" spans="3:3">
-      <c r="C116" t="s">
-        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -11456,104 +11403,104 @@
   <sheetData>
     <row r="2" spans="4:18">
       <c r="D2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="4:18">
       <c r="D3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="4:18">
       <c r="D4" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="H4" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="4:18">
       <c r="D5" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="H5" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="N5" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="O5" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="P5" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="Q5" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="R5" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="4:18">
       <c r="H6" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="4:18">
       <c r="D9" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="4:18">
       <c r="D10" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="E10" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="F10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="G10" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="H10" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="I10" t="s">
         <v>99</v>
       </c>
       <c r="J10" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="K10" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="4:18">
       <c r="D12" s="54" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E12" s="54" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" spans="4:18">
       <c r="D13" s="54"/>
       <c r="E13" s="54" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="4:18">
       <c r="D15" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E15" t="s">
         <v>107</v>
       </c>
       <c r="K15" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="14:16">
@@ -11561,7 +11508,7 @@
         <v>277</v>
       </c>
       <c r="P17" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -11572,7 +11519,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:P45"/>
+  <dimension ref="B2:E51"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -11662,7 +11609,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="2:16">
+    <row r="17" spans="2:5">
       <c r="B17" t="s">
         <v>131</v>
       </c>
@@ -11670,27 +11617,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="2:16">
+    <row r="18" spans="2:5">
       <c r="B18" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
       <c r="B19" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D20" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="21" spans="2:16">
+    <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D21" t="s">
         <v>313</v>
@@ -11699,9 +11646,9 @@
         <v>314</v>
       </c>
     </row>
-    <row r="22" spans="2:16">
+    <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D22" t="s">
         <v>315</v>
@@ -11710,7 +11657,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="23" spans="2:16">
+    <row r="23" spans="2:5">
       <c r="D23" t="s">
         <v>317</v>
       </c>
@@ -11718,10 +11665,10 @@
         <v>318</v>
       </c>
     </row>
-    <row r="25" spans="2:16">
+    <row r="25" spans="2:5">
       <c r="B25" s="32"/>
     </row>
-    <row r="27" spans="2:16">
+    <row r="27" spans="2:5">
       <c r="B27" t="s">
         <v>207</v>
       </c>
@@ -11729,93 +11676,82 @@
         <v>319</v>
       </c>
     </row>
-    <row r="28" spans="2:16">
+    <row r="28" spans="2:5">
       <c r="B28" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="29" spans="2:16">
-      <c r="D29" t="s">
+      <c r="D28" t="s">
         <v>320</v>
       </c>
-      <c r="H29" t="s">
-        <v>324</v>
-      </c>
-      <c r="O29" t="s">
-        <v>325</v>
-      </c>
-      <c r="P29" t="s">
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="30" spans="2:16">
-      <c r="D30" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16">
-      <c r="B31" t="s">
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
         <v>332</v>
       </c>
-      <c r="D31" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12">
-      <c r="B33" t="s">
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" t="s">
         <v>333</v>
       </c>
-      <c r="D33" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
-      <c r="B34" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12">
-      <c r="B35" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12">
-      <c r="B36" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12">
-      <c r="B37" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12">
-      <c r="B40" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12">
-      <c r="B41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12">
-      <c r="D44" t="s">
-        <v>405</v>
-      </c>
-      <c r="I44" t="s">
-        <v>406</v>
-      </c>
-      <c r="L44" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12">
+    </row>
+    <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>403</v>
-      </c>
-      <c r="D45" t="s">
-        <v>404</v>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -12410,14 +12346,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12656,21 +12590,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12695,9 +12628,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C35EBA-AAFA-4ADC-8B73-09C8226FA5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E8AAAD-229D-4985-9BCA-8DB0073D3452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="437">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4767,6 +4767,26 @@
     </rPh>
     <rPh sb="26" eb="28">
       <t>サンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>playerの移動制限をした後、ヒットストップ、カメラシェイクを作る</t>
+    <rPh sb="7" eb="11">
+      <t>イドウセイゲン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、しっかりとしたステージを作る</t>
+    <rPh sb="17" eb="18">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10782,7 +10802,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11382,6 +11402,16 @@
     <row r="119" spans="1:3">
       <c r="C119" t="s">
         <v>434</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="C121" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="C122" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -12346,12 +12376,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12590,20 +12622,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12628,12 +12661,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E8AAAD-229D-4985-9BCA-8DB0073D3452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B954AD-43CB-4B3D-BAA3-63C855A1F4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="438">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4787,6 +4787,19 @@
     <t>そのあと、しっかりとしたステージを作る</t>
     <rPh sb="17" eb="18">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動制限、あとは数値をいじるだけ、次はヒットストップとカメラシェイクをする</t>
+    <rPh sb="0" eb="4">
+      <t>イドウセイゲン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10802,7 +10815,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11412,6 +11425,11 @@
     <row r="122" spans="1:3">
       <c r="C122" t="s">
         <v>436</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="C123" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -12376,14 +12394,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12622,21 +12638,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12661,9 +12676,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B954AD-43CB-4B3D-BAA3-63C855A1F4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9508C764-9158-491F-8240-511F06021EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="444">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4800,6 +4800,66 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動制限終了、アニメーション、ヒットストップ、カメラシェイクに入る</t>
+    <rPh sb="0" eb="4">
+      <t>イドウセイゲン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モーションによるモデルの切り替えいい感じ</t>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>続いて、ヒットストップをする</t>
+    <rPh sb="0" eb="1">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>orエフェクトを作るorシェーダー、ステージ制作</t>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットストップ→あとはアニメーションクラスに所有者のタイムスケールを持ってきて、かけてあげる</t>
+    <rPh sb="22" eb="25">
+      <t>ショユウシャ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ColUpdateで初期化してる</t>
+    <rPh sb="10" eb="13">
+      <t>ショキカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8655,11 +8715,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.6818181818181816E-2</v>
+        <v>5.6561085972850679E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8677,7 +8737,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8698,11 +8758,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-409</v>
+        <v>-411</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39608801955990219</v>
+        <v>-0.39416058394160586</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8715,11 +8775,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-389</v>
+        <v>-391</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.41645244215938304</v>
+        <v>-0.41432225063938621</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8732,11 +8792,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-378</v>
+        <v>-380</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42857142857142855</v>
+        <v>-0.4263157894736842</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -8994,11 +9054,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.3191489361702127</v>
+        <v>2.4222222222222221</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" customHeight="1">
@@ -9037,11 +9097,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>2</v>
-      </c>
-      <c r="N4" s="10">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="e">
         <f ca="1">J4/M4</f>
-        <v>47</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -9080,11 +9140,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>2.9615384615384617</v>
+        <v>3.2083333333333335</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1">
@@ -9123,11 +9183,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.37209302325581395</v>
+        <v>0.3902439024390244</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -10815,7 +10875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11430,6 +11490,42 @@
     <row r="123" spans="1:3">
       <c r="C123" t="s">
         <v>437</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="1">
+        <v>46219</v>
+      </c>
+      <c r="C124" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="1">
+        <v>46220</v>
+      </c>
+      <c r="C125" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="C126" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="C127" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="C128" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3">
+      <c r="C129" t="s">
+        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9508C764-9158-491F-8240-511F06021EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28801699-B598-40DE-9FB7-B249F0D7406F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="446">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4860,6 +4860,26 @@
     <t>ColUpdateで初期化してる</t>
     <rPh sb="10" eb="13">
       <t>ショキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクトがなんかあまりうまく表示されないが、一旦これでいく</t>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イッタン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>川野先生に解決してもらう</t>
+    <rPh sb="0" eb="4">
+      <t>カワノセンセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイケツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8737,7 +8757,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9054,11 +9074,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.4222222222222221</v>
+        <v>2.5348837209302326</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" customHeight="1">
@@ -9097,11 +9117,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="10" t="e">
+        <v>-2</v>
+      </c>
+      <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>#DIV/0!</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -9140,11 +9160,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>3.2083333333333335</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1">
@@ -9183,11 +9203,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.3902439024390244</v>
+        <v>0.41025641025641024</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -10875,7 +10895,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11523,9 +11543,22 @@
         <v>442</v>
       </c>
     </row>
-    <row r="129" spans="3:3">
+    <row r="129" spans="1:3">
       <c r="C129" t="s">
         <v>443</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="1">
+        <v>46221</v>
+      </c>
+      <c r="C130" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="C131" t="s">
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -12490,12 +12523,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12734,20 +12769,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12772,12 +12808,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28801699-B598-40DE-9FB7-B249F0D7406F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A17590-3369-43E4-B4AF-CE4A6D0F11E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$55</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="461">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -4880,6 +4881,156 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージの制作をする</t>
+    <rPh sb="5" eb="7">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一旦見た目を作ったので、大きさの確認をする</t>
+    <rPh sb="0" eb="2">
+      <t>イッタン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大きさの確認終了</t>
+    <rPh sb="0" eb="1">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>カクニンシュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見た目の整理終わり</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>元の作業に戻る</t>
+    <rPh sb="0" eb="1">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はカメラシェイク、orrカメラが変なので、修正</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヘン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>orシェーダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーンのあん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルがまずぱっと出てきて、プレイヤーがけって、正しい位置にずらして剣をとりだす</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スコア型</t>
+    <rPh sb="3" eb="4">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aって出てきた後、剣で切ってSをだす</t>
+    <rPh sb="3" eb="4">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その際、ブレンダーで作ったモデルでばらばらにする表現をする</t>
+    <rPh sb="2" eb="3">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非同期ロードをする</t>
+    <rPh sb="0" eb="3">
+      <t>ヒドウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、タイトルシーンなどを作り始める</t>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10895,7 +11046,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11559,6 +11710,51 @@
     <row r="131" spans="1:3">
       <c r="C131" t="s">
         <v>445</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="C132" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="C133" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="C134" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="C135" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="C136" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="C137" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="C138" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="C139" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="C140" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -11696,7 +11892,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:E51"/>
+  <dimension ref="B2:E60"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -11929,6 +12125,36 @@
     <row r="51" spans="2:2">
       <c r="B51" t="s">
         <v>432</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" t="s">
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A17590-3369-43E4-B4AF-CE4A6D0F11E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9014899B-55C9-4B38-A2C3-28CB3D8CDB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="4380" windowWidth="22110" windowHeight="11100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23970" yWindow="4455" windowWidth="22110" windowHeight="11025" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$55</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="462">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5031,6 +5030,13 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルがシェーダーででてくる→プレイヤーがおりてくる→文字をけってずらす</t>
+    <rPh sb="28" eb="30">
+      <t>モジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8886,11 +8892,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.6561085972850679E-2</v>
+        <v>5.6433408577878104E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8908,7 +8914,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8929,11 +8935,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-411</v>
+        <v>-412</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39416058394160586</v>
+        <v>-0.39320388349514562</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8946,11 +8952,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-391</v>
+        <v>-392</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.41432225063938621</v>
+        <v>-0.41326530612244899</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8963,11 +8969,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-380</v>
+        <v>-381</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.4263157894736842</v>
+        <v>-0.42519685039370081</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9225,11 +9231,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.5348837209302326</v>
+        <v>2.5952380952380953</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" customHeight="1">
@@ -9268,11 +9274,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-47</v>
+        <v>-31.333333333333332</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -9311,11 +9317,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>3.5</v>
+        <v>3.6666666666666665</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1">
@@ -9354,11 +9360,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.41025641025641024</v>
+        <v>0.42105263157894735</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -11892,7 +11898,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
-  <dimension ref="B2:E60"/>
+  <dimension ref="B2:E64"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="42.75" bestFit="1" customWidth="1"/>
@@ -12134,26 +12140,31 @@
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="57" spans="2:2">
-      <c r="B57" t="s">
+    <row r="61" spans="2:2">
+      <c r="B61" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="58" spans="2:2">
-      <c r="B58" t="s">
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="59" spans="2:2">
-      <c r="B59" t="s">
+    <row r="63" spans="2:2">
+      <c r="B63" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="60" spans="2:2">
-      <c r="B60" t="s">
+    <row r="64" spans="2:2">
+      <c r="B64" t="s">
         <v>458</v>
       </c>
     </row>
@@ -12749,14 +12760,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12995,21 +13004,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13034,9 +13042,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9014899B-55C9-4B38-A2C3-28CB3D8CDB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0EAD4E-E8E8-4998-8727-D57DDB5C12B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23970" yWindow="4455" windowWidth="22110" windowHeight="11025" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="4680" windowWidth="22110" windowHeight="11025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="465">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5037,6 +5037,57 @@
     <t>タイトルがシェーダーででてくる→プレイヤーがおりてくる→文字をけってずらす</t>
     <rPh sb="28" eb="30">
       <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シェーダーをやっている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のアニメーションが動かない問題は自作のVSシェーダーを使うのではなく、DxLibの既存のVSシェーダを使うことで解決するらしい</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジサク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それは川野先生のProjectから持ってくる、そして、カメラ行列の適用はいらないらしい、自動でやるらしい</t>
+    <rPh sb="3" eb="7">
+      <t>カワノセンセイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ギョウレツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ジドウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8892,11 +8943,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.6433408577878104E-2</v>
+        <v>5.6306306306306307E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8914,7 +8965,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8935,11 +8986,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-412</v>
+        <v>-413</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39320388349514562</v>
+        <v>-0.39225181598062953</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8952,11 +9003,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-392</v>
+        <v>-393</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.41326530612244899</v>
+        <v>-0.41221374045801529</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8969,11 +9020,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-381</v>
+        <v>-382</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42519685039370081</v>
+        <v>-0.42408376963350786</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9231,11 +9282,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.5952380952380953</v>
+        <v>2.6585365853658538</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" customHeight="1">
@@ -9274,11 +9325,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-31.333333333333332</v>
+        <v>-23.5</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -9317,11 +9368,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>3.6666666666666665</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1">
@@ -9360,11 +9411,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.42105263157894735</v>
+        <v>0.43243243243243246</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -11052,7 +11103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11761,6 +11812,24 @@
     <row r="140" spans="1:3">
       <c r="C140" t="s">
         <v>460</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="1">
+        <v>46224</v>
+      </c>
+      <c r="C142" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="C143" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="C144" t="s">
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -12760,12 +12829,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13004,20 +13075,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13042,12 +13114,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0EAD4E-E8E8-4998-8727-D57DDB5C12B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEFFB46-32DB-4061-A6E2-56B22968464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="4680" windowWidth="22110" windowHeight="11025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="21600" windowHeight="13590" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="469">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5088,6 +5088,52 @@
     </rPh>
     <rPh sb="44" eb="46">
       <t>ジドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シェーダーは何かバグったので、川野先生の質問まち</t>
+    <rPh sb="6" eb="7">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>カワノセンセイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>シツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵座標をもう一度入れなおして、そのあと、タイトルシーンをする</t>
+    <rPh sb="0" eb="3">
+      <t>テキザヒョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵座標入れなおした</t>
+    <rPh sb="0" eb="3">
+      <t>テキザヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非同期ロードのメモリを削除した</t>
+    <rPh sb="0" eb="3">
+      <t>ヒドウキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -11103,7 +11149,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11830,6 +11876,26 @@
     <row r="144" spans="1:3">
       <c r="C144" t="s">
         <v>464</v>
+      </c>
+    </row>
+    <row r="145" spans="3:3">
+      <c r="C145" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3">
+      <c r="C146" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3">
+      <c r="C147" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="148" spans="3:3">
+      <c r="C148" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -12829,14 +12895,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13075,21 +13139,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13114,9 +13177,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEFFB46-32DB-4061-A6E2-56B22968464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626CBDFD-85DA-494D-AA50-DA3911E8E3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="21600" windowHeight="13590" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="4680" windowWidth="22110" windowHeight="11025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="471">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5135,6 +5135,23 @@
     <rPh sb="11" eb="13">
       <t>サクジョ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はカメラ揺らすのと、ヒットエフェクトを出す</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ユ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、タイトルシーンとかやっていきたい</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8989,11 +9006,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.6306306306306307E-2</v>
+        <v>5.6179775280898875E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -9011,7 +9028,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9032,11 +9049,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-413</v>
+        <v>-414</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39225181598062953</v>
+        <v>-0.39130434782608697</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9049,11 +9066,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-393</v>
+        <v>-394</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.41221374045801529</v>
+        <v>-0.41116751269035534</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9066,11 +9083,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-382</v>
+        <v>-383</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42408376963350786</v>
+        <v>-0.42297650130548303</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9328,11 +9345,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.6585365853658538</v>
+        <v>2.7250000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" customHeight="1">
@@ -9371,11 +9388,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-23.5</v>
+        <v>-18.8</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -9414,11 +9431,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>3.85</v>
+        <v>4.0526315789473681</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1">
@@ -9457,11 +9474,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.43243243243243246</v>
+        <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -11149,7 +11166,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11896,6 +11913,16 @@
     <row r="148" spans="3:3">
       <c r="C148" t="s">
         <v>468</v>
+      </c>
+    </row>
+    <row r="149" spans="3:3">
+      <c r="C149" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="150" spans="3:3">
+      <c r="C150" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -12895,12 +12922,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13139,20 +13168,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13177,12 +13207,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626CBDFD-85DA-494D-AA50-DA3911E8E3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2CF9A0-B146-4FCF-8011-E5253EDBDD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="4680" windowWidth="22110" windowHeight="11025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4095" yWindow="1770" windowWidth="21600" windowHeight="13590" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="472">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5152,6 +5152,19 @@
   </si>
   <si>
     <t>そのあと、タイトルシーンとかやっていきたい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵がy座標マイナスになったら死ぬようにする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11166,7 +11179,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11923,6 +11936,11 @@
     <row r="150" spans="3:3">
       <c r="C150" t="s">
         <v>470</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3">
+      <c r="C152" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -12922,14 +12940,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13168,21 +13184,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13207,9 +13222,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2CF9A0-B146-4FCF-8011-E5253EDBDD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CDEC4A-DB10-466D-919B-45C74053AE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4095" yWindow="1770" windowWidth="21600" windowHeight="13590" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="476">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5164,6 +5164,52 @@
     </rPh>
     <rPh sb="14" eb="15">
       <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラクターの移動量を調整する</t>
+    <rPh sb="7" eb="10">
+      <t>イドウリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>24日までにヒットエフェクトを実装する</t>
+    <rPh sb="2" eb="3">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>24日までにカメラの揺れやヒットストップを実装する</t>
+    <rPh sb="2" eb="3">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ユ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の移動量を制限する</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>イドウリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -11179,7 +11225,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11908,39 +11954,62 @@
         <v>464</v>
       </c>
     </row>
-    <row r="145" spans="3:3">
+    <row r="145" spans="1:3">
       <c r="C145" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="146" spans="3:3">
+    <row r="146" spans="1:3">
       <c r="C146" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="147" spans="3:3">
+    <row r="147" spans="1:3">
       <c r="C147" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="148" spans="3:3">
+    <row r="148" spans="1:3">
       <c r="C148" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="149" spans="3:3">
+    <row r="149" spans="1:3">
       <c r="C149" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="150" spans="3:3">
+    <row r="150" spans="1:3">
       <c r="C150" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="152" spans="3:3">
+    <row r="152" spans="1:3">
       <c r="C152" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="1">
+        <v>46225</v>
+      </c>
+      <c r="C153" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="C154" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="C155" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="C156" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -12940,12 +13009,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13184,20 +13255,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13222,12 +13294,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CDEC4A-DB10-466D-919B-45C74053AE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0667D6-D87A-404F-8200-F84C9C688904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="0" windowWidth="22110" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="477">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -3183,19 +3183,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃がおそらく単体にしか当たっていない</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>タンタイ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>敵について</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -5210,6 +5197,29 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃がおそらく単体にしか当たっていない←解決</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionのOnTrigger、OnPress,OnExitを作る</t>
+    <rPh sb="35" eb="36">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9065,11 +9075,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.6179775280898875E-2</v>
+        <v>5.5928411633109618E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -9087,7 +9097,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9108,11 +9118,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-414</v>
+        <v>-416</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39130434782608697</v>
+        <v>-0.38942307692307693</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9125,11 +9135,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-394</v>
+        <v>-396</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.41116751269035534</v>
+        <v>-0.40909090909090912</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9142,11 +9152,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-383</v>
+        <v>-385</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42297650130548303</v>
+        <v>-0.42077922077922075</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9404,11 +9414,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.7250000000000001</v>
+        <v>2.9459459459459461</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" customHeight="1">
@@ -9447,11 +9457,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-18.8</v>
+        <v>-11.75</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -9490,11 +9500,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>4.0526315789473681</v>
+        <v>4.8125</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1">
@@ -9533,11 +9543,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.44444444444444442</v>
+        <v>0.48484848484848486</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9781,7 +9791,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>5</v>
@@ -9827,7 +9837,7 @@
         <v>44</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>5</v>
@@ -9841,7 +9851,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>5</v>
@@ -10176,7 +10186,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>5</v>
@@ -10262,7 +10272,7 @@
         <v>41</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>5</v>
@@ -10790,7 +10800,7 @@
     </row>
     <row r="11" spans="3:16">
       <c r="K11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L11" s="53"/>
     </row>
@@ -11193,7 +11203,7 @@
         <v>29</v>
       </c>
       <c r="K36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="3:11">
@@ -11225,7 +11235,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -11490,32 +11500,32 @@
         <v>46209</v>
       </c>
       <c r="C43" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="C45" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="C46" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="C47" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="C48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -11523,12 +11533,12 @@
         <v>46210</v>
       </c>
       <c r="C49" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="C50" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -11536,42 +11546,42 @@
         <v>46211</v>
       </c>
       <c r="C52" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="C53" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="C54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="C55" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="C56" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="C58" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="C60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="C61" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -11579,22 +11589,22 @@
         <v>46212</v>
       </c>
       <c r="C63" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="C64" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="C65" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="C66" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -11602,17 +11612,17 @@
         <v>46213</v>
       </c>
       <c r="C68" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="C69" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="C70" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -11620,107 +11630,107 @@
         <v>46214</v>
       </c>
       <c r="C72" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="C73" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="C74" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="C76" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="C77" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="C78" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="C79" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="96" spans="3:3">
       <c r="C96" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="C97" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -11728,47 +11738,47 @@
         <v>46215</v>
       </c>
       <c r="C99" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="C100" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="C101" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="C102" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="C103" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="C104" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="C105" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="C106" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="C107" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -11776,42 +11786,42 @@
         <v>46216</v>
       </c>
       <c r="C109" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="C110" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="C111" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="C112" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="C113" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="C114" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="C115" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="C116" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -11819,27 +11829,27 @@
         <v>46218</v>
       </c>
       <c r="C118" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="C119" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="C121" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="C122" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="C123" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -11847,7 +11857,7 @@
         <v>46219</v>
       </c>
       <c r="C124" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -11855,27 +11865,27 @@
         <v>46220</v>
       </c>
       <c r="C125" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="C126" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="C127" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="C128" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="C129" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -11883,57 +11893,57 @@
         <v>46221</v>
       </c>
       <c r="C130" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="C131" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="C132" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="C133" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="C134" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="C135" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="C136" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="C137" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="C138" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="C139" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="C140" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -11941,52 +11951,52 @@
         <v>46224</v>
       </c>
       <c r="C142" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="C143" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="C144" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="C145" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="C146" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="C147" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="C148" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="C149" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="C150" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="C152" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -11994,22 +12004,30 @@
         <v>46225</v>
       </c>
       <c r="C153" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="C154" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="C155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="C156" t="s">
-        <v>475</v>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="1">
+        <v>46226</v>
+      </c>
+      <c r="C158" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -12031,104 +12049,104 @@
   <sheetData>
     <row r="2" spans="4:18">
       <c r="D2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="4:18">
       <c r="D3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="4:18">
       <c r="D4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="4:18">
       <c r="D5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N5" t="s">
+        <v>367</v>
+      </c>
+      <c r="O5" t="s">
         <v>368</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>369</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
+        <v>368</v>
+      </c>
+      <c r="R5" t="s">
         <v>370</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>369</v>
-      </c>
-      <c r="R5" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="6" spans="4:18">
       <c r="H6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="4:18">
       <c r="D9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="4:18">
       <c r="D10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E10" t="s">
         <v>361</v>
       </c>
-      <c r="E10" t="s">
-        <v>362</v>
-      </c>
       <c r="F10" t="s">
+        <v>363</v>
+      </c>
+      <c r="G10" t="s">
         <v>364</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>365</v>
-      </c>
-      <c r="H10" t="s">
-        <v>366</v>
       </c>
       <c r="I10" t="s">
         <v>99</v>
       </c>
       <c r="J10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="4:18">
       <c r="D12" s="54" t="s">
+        <v>371</v>
+      </c>
+      <c r="E12" s="54" t="s">
         <v>372</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="13" spans="4:18">
       <c r="D13" s="54"/>
       <c r="E13" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="4:18">
       <c r="D15" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E15" t="s">
         <v>107</v>
       </c>
       <c r="K15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="14:16">
@@ -12136,7 +12154,7 @@
         <v>277</v>
       </c>
       <c r="P17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -12314,107 +12332,107 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" t="s">
-        <v>326</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -13009,14 +13027,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13255,21 +13271,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13294,9 +13309,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0667D6-D87A-404F-8200-F84C9C688904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44E27AC-1154-4979-ABB1-1E0B30B29902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="0" windowWidth="22110" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8265" yWindow="5355" windowWidth="22110" windowHeight="11025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="クラス設計" sheetId="14" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$57</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="482">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5221,6 +5221,47 @@
     <rPh sb="35" eb="36">
       <t>ツク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剣のスキルエフェクトを追加する</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剣のエフェクト三種</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サンシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技のエフェクト1種</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未着手</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9053,8 +9094,8 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!E3:E76)</f>
-        <v>187</v>
+        <f>SUM(作業工数見積もり!E3:E78)</f>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -9122,7 +9163,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.38942307692307693</v>
+        <v>-0.40144230769230771</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9139,7 +9180,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.40909090909090912</v>
+        <v>-0.42171717171717171</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9156,7 +9197,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42077922077922075</v>
+        <v>-0.43376623376623374</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9313,7 +9354,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.125" style="10" bestFit="1" customWidth="1"/>
@@ -9395,18 +9436,18 @@
         <v>0</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>61</v>
       </c>
       <c r="J3" s="10">
         <f>SUM(J4,J5,J6)</f>
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K3" s="10">
-        <f>SUMIFS(E3:E55,G3:G55,"未着手")</f>
-        <v>109</v>
+        <f>SUMIFS(E3:E57,G3:G57,"未着手")</f>
+        <v>101</v>
       </c>
       <c r="L3" s="10">
         <f>SUM(F3:F43)</f>
@@ -9418,10 +9459,10 @@
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.9459459459459461</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="26.25" customHeight="1">
+        <v>2.7297297297297298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
       <c r="A4" s="17" t="s">
         <v>35</v>
       </c>
@@ -9444,12 +9485,12 @@
         <v>28</v>
       </c>
       <c r="J4" s="29">
-        <f>SUMIF(D3:D55,I4,E3:E55)</f>
+        <f>SUMIF(D3:D57,I4,E3:E57)</f>
         <v>94</v>
       </c>
       <c r="K4" s="10">
-        <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I4)</f>
-        <v>35</v>
+        <f>SUMIFS(E3:E57,G3:G57,"未着手",D3:D57,I4)</f>
+        <v>27</v>
       </c>
       <c r="L4" s="10">
         <f>SUMIFS(F3:F43,D3:D43,I4)</f>
@@ -9464,7 +9505,7 @@
         <v>-11.75</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1">
+    <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
       <c r="A5" s="17" t="s">
         <v>35</v>
       </c>
@@ -9487,15 +9528,15 @@
         <v>0</v>
       </c>
       <c r="J5" s="29">
-        <f>SUMIF(D3:D55,I5,E3:E55)</f>
-        <v>77</v>
+        <f>SUMIF(D3:D57,I5,E3:E57)</f>
+        <v>82</v>
       </c>
       <c r="K5" s="10">
-        <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I5)</f>
+        <f>SUMIFS(E3:E57,G3:G57,"未着手",D3:D57,I5)</f>
         <v>59</v>
       </c>
       <c r="L5" s="10">
-        <f>SUMIFS(F4:F47,D4:D47,I5)</f>
+        <f>SUMIFS(F4:F49,D4:D49,I5)</f>
         <v>0</v>
       </c>
       <c r="M5" s="10">
@@ -9504,10 +9545,10 @@
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>4.8125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="19.5" customHeight="1">
+        <v>5.125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
       <c r="A6" s="17" t="s">
         <v>35</v>
       </c>
@@ -9530,15 +9571,15 @@
         <v>29</v>
       </c>
       <c r="J6" s="29">
-        <f>SUMIF(D3:D55,I6,E3:E55)</f>
+        <f>SUMIF(D3:D57,I6,E3:E57)</f>
         <v>16</v>
       </c>
       <c r="K6" s="10">
-        <f>SUMIFS(E3:E55,G3:G55,"未着手",D3:D55,I6)</f>
+        <f>SUMIFS(E3:E57,G3:G57,"未着手",D3:D57,I6)</f>
         <v>15</v>
       </c>
       <c r="L6" s="10">
-        <f>SUMIFS(F5:F47,D5:D47,I6)</f>
+        <f>SUMIFS(F5:F49,D5:D49,I6)</f>
         <v>1</v>
       </c>
       <c r="M6" s="10">
@@ -9570,7 +9611,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="8" spans="1:14" outlineLevel="1">
+    <row r="8" spans="1:14" hidden="1" outlineLevel="1">
       <c r="A8" s="19" t="s">
         <v>44</v>
       </c>
@@ -9590,7 +9631,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="1:14" hidden="1" outlineLevel="1">
+    <row r="9" spans="1:14" outlineLevel="1">
       <c r="A9" s="19" t="s">
         <v>44</v>
       </c>
@@ -9613,7 +9654,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:14" outlineLevel="1">
+    <row r="10" spans="1:14" hidden="1" outlineLevel="1">
       <c r="A10" s="19" t="s">
         <v>44</v>
       </c>
@@ -9652,8 +9693,11 @@
       <c r="E11" s="16">
         <v>2</v>
       </c>
+      <c r="F11" s="16" t="s">
+        <v>480</v>
+      </c>
       <c r="G11" s="16" t="s">
-        <v>39</v>
+        <v>481</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>295</v>
@@ -9662,7 +9706,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1">
+    <row r="12" spans="1:14">
       <c r="A12" s="19" t="s">
         <v>44</v>
       </c>
@@ -9691,7 +9735,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1">
+    <row r="13" spans="1:14">
       <c r="A13" s="19" t="s">
         <v>44</v>
       </c>
@@ -9720,7 +9764,7 @@
         <v>46244</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1">
+    <row r="14" spans="1:14">
       <c r="A14" s="19" t="s">
         <v>44</v>
       </c>
@@ -9746,7 +9790,7 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1">
+    <row r="15" spans="1:14">
       <c r="A15" s="19" t="s">
         <v>44</v>
       </c>
@@ -9782,11 +9826,14 @@
       <c r="D16" s="16" t="s">
         <v>18</v>
       </c>
+      <c r="F16" s="16" t="s">
+        <v>480</v>
+      </c>
       <c r="G16" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" s="19" t="s">
         <v>44</v>
       </c>
@@ -9809,7 +9856,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" s="19" t="s">
         <v>44</v>
       </c>
@@ -9832,7 +9879,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" s="19" t="s">
         <v>44</v>
       </c>
@@ -9845,8 +9892,11 @@
       <c r="D19" s="16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" hidden="1">
+      <c r="G19" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="19" t="s">
         <v>44</v>
       </c>
@@ -9858,6 +9908,9 @@
       </c>
       <c r="D20" s="16" t="s">
         <v>18</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -9877,10 +9930,10 @@
         <v>8</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" hidden="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="20" t="s">
         <v>46</v>
       </c>
@@ -9943,7 +9996,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" s="20" t="s">
         <v>46</v>
       </c>
@@ -9966,7 +10019,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" s="20" t="s">
         <v>46</v>
       </c>
@@ -10009,7 +10062,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" s="49" t="s">
         <v>264</v>
       </c>
@@ -10032,7 +10085,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7">
       <c r="A29" s="49" t="s">
         <v>264</v>
       </c>
@@ -10055,7 +10108,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7">
       <c r="A30" s="49" t="s">
         <v>264</v>
       </c>
@@ -10158,7 +10211,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" s="21" t="s">
         <v>40</v>
       </c>
@@ -10181,7 +10234,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" s="21" t="s">
         <v>40</v>
       </c>
@@ -10224,7 +10277,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" s="21" t="s">
         <v>40</v>
       </c>
@@ -10267,7 +10320,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" s="22" t="s">
         <v>41</v>
       </c>
@@ -10290,7 +10343,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" s="22" t="s">
         <v>41</v>
       </c>
@@ -10310,7 +10363,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="23" t="s">
         <v>42</v>
       </c>
@@ -10327,7 +10380,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="23" t="s">
         <v>42</v>
       </c>
@@ -10347,7 +10400,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" s="23" t="s">
         <v>42</v>
       </c>
@@ -10367,7 +10420,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" s="10" t="s">
         <v>277</v>
       </c>
@@ -10384,13 +10437,16 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" s="10" t="s">
         <v>277</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>282</v>
       </c>
+      <c r="C46" s="16" t="s">
+        <v>5</v>
+      </c>
       <c r="D46" s="16" t="s">
         <v>10</v>
       </c>
@@ -10401,89 +10457,89 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" s="10" t="s">
         <v>277</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>283</v>
+        <v>478</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E47" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="13" t="s">
-        <v>38</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1">
+      <c r="A48" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>284</v>
+        <v>479</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
       <c r="D48" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="13" t="s">
-        <v>38</v>
+      <c r="A49" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E49" s="16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" s="13" t="s">
         <v>38</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="16">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" s="13" t="s">
         <v>38</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>5</v>
@@ -10498,12 +10554,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" s="13" t="s">
         <v>38</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>5</v>
@@ -10512,18 +10568,18 @@
         <v>10</v>
       </c>
       <c r="E52" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" s="13" t="s">
         <v>38</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>5</v>
@@ -10532,18 +10588,18 @@
         <v>10</v>
       </c>
       <c r="E53" s="16">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" s="13" t="s">
         <v>38</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C54" s="16" t="s">
         <v>5</v>
@@ -10552,47 +10608,86 @@
         <v>10</v>
       </c>
       <c r="E54" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" hidden="1">
       <c r="A55" s="13" t="s">
         <v>38</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C55" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>293</v>
+        <v>10</v>
       </c>
       <c r="E55" s="16">
-        <v>12</v>
-      </c>
-      <c r="F55" s="10"/>
+        <v>4</v>
+      </c>
       <c r="G55" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="10" t="s">
+    <row r="56" spans="1:7" hidden="1">
+      <c r="A56" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="16">
+        <v>12</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1">
+      <c r="A57" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E57" s="16">
+        <v>12</v>
+      </c>
+      <c r="F57" s="10"/>
+      <c r="G57" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B59" s="10" t="s">
         <v>310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G55" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
+  <autoFilter ref="B2:G57" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
       <filters>
-        <filter val="作業中"/>
-        <filter val="未着手"/>
+        <filter val="プロト"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G38">
@@ -10601,13 +10696,13 @@
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D55" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D57" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G55" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G57" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C55" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C57" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11235,7 +11330,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -12028,6 +12123,11 @@
       </c>
       <c r="C158" t="s">
         <v>476</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="C159" t="s">
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44E27AC-1154-4979-ABB1-1E0B30B29902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75AC8CB-DE3C-4562-B53F-ADE513DF4842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8265" yWindow="5355" windowWidth="22110" windowHeight="11025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="489">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5262,6 +5262,106 @@
   </si>
   <si>
     <t>未着手</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題点</t>
+    <rPh sb="0" eb="3">
+      <t>モンダイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内部ターゲットを攻撃の当たった敵に毎回登録しているので、ふくすうの敵に当たった場合、カメラががくがくになる</t>
+    <rPh sb="0" eb="2">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>マイカイトウロク</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技の時用に敵のやられエフェクトの白色を作る</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シロイロ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル技のエフェクトを残り二つにつける</t>
+    <rPh sb="3" eb="4">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>フタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットストップなどを外部ファイル化して、ヒットストップ、カメラシェイクするかを業ごとに決める</t>
+    <rPh sb="10" eb="12">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーン、リザルトシーンなどをしっかりとつける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあとは音、SEのベータ作業</t>
+    <rPh sb="5" eb="6">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サギョウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9116,11 +9216,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.5928411633109618E-2</v>
+        <v>5.5309734513274339E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -9138,7 +9238,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46228</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9159,11 +9259,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-416</v>
+        <v>-421</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.40144230769230771</v>
+        <v>-0.39667458432304037</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9176,11 +9276,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-396</v>
+        <v>-401</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.42171717171717171</v>
+        <v>-0.41645885286783041</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9193,11 +9293,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-385</v>
+        <v>-390</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.43376623376623374</v>
+        <v>-0.42820512820512818</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9455,11 +9555,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>2.7297297297297298</v>
+        <v>3.4827586206896552</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -9498,11 +9598,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-11.75</v>
+        <v>-5.875</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -9541,11 +9641,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>5.125</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -9584,11 +9684,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.48484848484848486</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -11330,7 +11430,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -12128,6 +12228,44 @@
     <row r="159" spans="1:3">
       <c r="C159" t="s">
         <v>477</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" s="1">
+        <v>46236</v>
+      </c>
+      <c r="C161" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="C162" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="C163" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="C164" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="C165" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="C166" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="C167" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -13127,12 +13265,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13371,20 +13511,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13409,12 +13550,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75AC8CB-DE3C-4562-B53F-ADE513DF4842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DC42A4-FE1E-4651-AF14-F4C68AC3AD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8265" yWindow="5355" windowWidth="22110" windowHeight="11025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="493">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5361,6 +5361,49 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>サギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnTrigger機能の追加完了</t>
+    <rPh sb="9" eb="11">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ツイカカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だいぶさぼって進捗おそい</t>
+    <rPh sb="7" eb="9">
+      <t>シンチョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インターンもあるしやばいよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、その最後の締めをした後、残りエフェクトの追加をする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9216,11 +9259,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.5309734513274339E-2</v>
+        <v>5.518763796909492E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -9238,7 +9281,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9259,11 +9302,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-421</v>
+        <v>-422</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39667458432304037</v>
+        <v>-0.39573459715639808</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9276,11 +9319,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-401</v>
+        <v>-402</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.41645885286783041</v>
+        <v>-0.4154228855721393</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9293,11 +9336,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-390</v>
+        <v>-391</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42820512820512818</v>
+        <v>-0.42710997442455245</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9555,11 +9598,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>3.4827586206896552</v>
+        <v>3.6071428571428572</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -9598,11 +9641,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-5.875</v>
+        <v>-5.5294117647058822</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -9641,11 +9684,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>10.25</v>
+        <v>11.714285714285714</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -9684,11 +9727,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.64</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -11430,7 +11473,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C172"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -12266,6 +12309,26 @@
     <row r="167" spans="1:3">
       <c r="C167" t="s">
         <v>488</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="C169" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="C170" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="C171" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="C172" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -13265,14 +13328,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13511,21 +13572,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13550,9 +13610,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DC42A4-FE1E-4651-AF14-F4C68AC3AD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3BFF88-7F9C-4FF8-89C9-5D55AFC916A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8265" yWindow="5355" windowWidth="22110" windowHeight="11025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9015" yWindow="3075" windowWidth="20625" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="518">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5404,6 +5404,316 @@
     </rPh>
     <rPh sb="23" eb="25">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エリア制限実装完了</t>
+    <rPh sb="3" eb="5">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ついgは、エフェクトをいろいろ追加するために、エフェクトマネージャーを作る</t>
+    <rPh sb="15" eb="17">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル技のエフェクトを作る、血殺の時のエフェクトを作る</t>
+    <rPh sb="3" eb="4">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーン、リザルトシーンをつくる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間が余ったらボス、チュートリアルを作れる</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクトの修正は恋先輩に手伝ってもらう</t>
+    <rPh sb="6" eb="8">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>レン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テツダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクトマネージャー作成終了、スキルエフェクト、血殺のエフェクトも作り終えた</t>
+    <rPh sb="11" eb="15">
+      <t>サクセイシュウリョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クオリティが鬼微妙</t>
+    <rPh sb="6" eb="9">
+      <t>オニビミョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はタイトルシーンを作る</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なにつくろうとしてたかちょっとしかおもいだせない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今のところペルソナ風</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>フウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーン作成手順</t>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラを表示→キャラをフレームでコマンドで動かす→カメラを動かす→シェーダーでペルソナ風にする</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>フウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フレームで動かす仕組みまでできた。次は、キャラを動かすところ</t>
+    <rPh sb="5" eb="6">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラとオブジェクトとの当たり判定をしないといけない</t>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラを動かすところまでできたけど、モーションがダサすぎてむずそう</t>
+    <rPh sb="4" eb="5">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゼンゼロのような足だけ移す→剣を拾う→タイトル</t>
+    <rPh sb="8" eb="9">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵を倒したりしてもいいかも</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩く→剣にもたれかかる→スタートしたら剣にいろいろ選択肢が出てくる→ゲームシーンへ</t>
+    <rPh sb="0" eb="1">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剣を映す→足を映す→足からぜんたいへ→剣を取る→走る→キャラが止まる→タイトルを映す</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ウツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゼンゼロ風</t>
+    <rPh sb="4" eb="5">
+      <t>フウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラがとまった後、カメラを動かして、世界を見せる→タイトルロゴ</t>
+    <rPh sb="8" eb="9">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後は、キャラクターのモーションに合わせて剣を表示、非表示などをさせる</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ヒヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9259,11 +9569,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.518763796909492E-2</v>
+        <v>5.4466230936819175E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -9281,7 +9591,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9302,11 +9612,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-422</v>
+        <v>-428</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39573459715639808</v>
+        <v>-0.39018691588785048</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9319,11 +9629,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-402</v>
+        <v>-408</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.4154228855721393</v>
+        <v>-0.40931372549019607</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9336,11 +9646,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-391</v>
+        <v>-397</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42710997442455245</v>
+        <v>-0.42065491183879095</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9598,11 +9908,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>3.6071428571428572</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -9641,11 +9951,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-17</v>
+        <v>-25</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-5.5294117647058822</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -9684,11 +9994,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>11.714285714285714</v>
+        <v>-82</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -9727,11 +10037,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -11473,7 +11783,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:C197"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -12329,6 +12639,137 @@
     <row r="172" spans="1:3">
       <c r="C172" t="s">
         <v>492</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C173" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="C174" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="C175" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="C176" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="C177" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C179" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="C180" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="C181" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="C182" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="C183" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="C184" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="C186" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="C187" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="C188" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="C189" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="C191" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="B192" t="s">
+        <v>511</v>
+      </c>
+      <c r="C192" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="B193" t="s">
+        <v>511</v>
+      </c>
+      <c r="C193" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
+        <v>515</v>
+      </c>
+      <c r="B194" t="s">
+        <v>513</v>
+      </c>
+      <c r="C194" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="B195" t="s">
+        <v>511</v>
+      </c>
+      <c r="C195" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="C196" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="C197" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3BFF88-7F9C-4FF8-89C9-5D55AFC916A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCCBEB4-380F-4D24-B354-E136ED07C15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9015" yWindow="3075" windowWidth="20625" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="530">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5714,6 +5714,183 @@
     </rPh>
     <rPh sb="25" eb="28">
       <t>ヒヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、ステージを作って、それらをうまく組み合わせて作る感じ</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ作りまで終わった、あとは白い線を出して疾走感をつけるだけ</t>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シッソウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネズミとぶつかったら血殺！って出す</t>
+    <rPh sb="10" eb="11">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーンいったん完成、次は、リザルト画面</t>
+    <rPh sb="11" eb="13">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルト画面案</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーンのラストヒットを血殺のみで倒せるようにする→血殺からのリザルト画面演出</t>
+    <rPh sb="14" eb="16">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スコアが出る→血殺→スコア変更→ペルソナみたいな画角で終わり</t>
+    <rPh sb="4" eb="5">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガカク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルト画面→時間→スコアを表示</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sだのそんな感じのやつ</t>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトはモデルを切るようにする</t>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スコアのモデルはダウンロードに作ったので、一旦、それを回転しながら表示させるなどをする</t>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イッタン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、切るアニメーションなどをして、モデルを切り崩すようにする</t>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>クズ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9569,11 +9746,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.4466230936819175E-2</v>
+        <v>5.4112554112554112E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -9591,7 +9768,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9612,11 +9789,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-428</v>
+        <v>-431</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.39018691588785048</v>
+        <v>-0.38747099767981441</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9629,11 +9806,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-408</v>
+        <v>-411</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.40931372549019607</v>
+        <v>-0.40632603406326034</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9646,11 +9823,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.42065491183879095</v>
+        <v>-0.41749999999999998</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9908,11 +10085,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>5.05</v>
+        <v>6.3125</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -9951,11 +10128,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-25</v>
+        <v>-29</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-3.76</v>
+        <v>-3.2413793103448274</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -9994,11 +10171,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-82</v>
+        <v>-16.399999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -10037,11 +10214,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -11783,7 +11960,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C197"/>
+  <dimension ref="A1:C211"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -12770,6 +12947,66 @@
     <row r="197" spans="1:3">
       <c r="C197" t="s">
         <v>517</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="C198" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="C199" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="C200" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="C202" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="C203" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="C204" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="C205" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="C207" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="C208" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="209" spans="3:3">
+      <c r="C209" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="210" spans="3:3">
+      <c r="C210" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="211" spans="3:3">
+      <c r="C211" t="s">
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -13769,12 +14006,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14013,20 +14252,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14051,12 +14291,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCCBEB4-380F-4D24-B354-E136ED07C15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D184C8FD-9FC9-498C-A4D1-1EFF54506EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9015" yWindow="3075" windowWidth="20625" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="539">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -5892,6 +5892,141 @@
     <rPh sb="26" eb="27">
       <t>クズ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトシーンは触、学校でやった、キャラクターを赤単色で表示まで終わっている(あんまり進んでいないため、強硬してもよい</t>
+    <rPh sb="8" eb="9">
+      <t>サワ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>タンショク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キョウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスを作る、そのあとは、ゲームシーンでやることをする(バグ直しorポーズシーンの追加等)</t>
+    <rPh sb="3" eb="4">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="40" eb="43">
+      <t>ツイカトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bossを作りたいなーー</t>
+    <rPh sb="5" eb="6">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bossの攻撃方法</t>
+    <rPh sb="5" eb="9">
+      <t>コウゲキホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法近距離攻撃、魔法遠距離攻撃、雑魚敵召喚</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="2" eb="7">
+      <t>キンキョリコウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>エンキョリコウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ザコ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ショウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EnemySwordManと同じつくりのStatePatternは実装したから、今からするのは、攻撃の中身の実装をしていく、↑三つのやつ</t>
+    <rPh sb="14" eb="15">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ナカミ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ミッ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、それら攻撃の当たり判定を生成する仕組み、そのあと、エフェクト制作</t>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ハン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、でかいからカメラをいろいろしたりとかかなー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9746,11 +9881,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.4112554112554112E-2</v>
+        <v>5.353319057815846E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -9768,7 +9903,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46249</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9789,11 +9924,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-431</v>
+        <v>-436</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.38747099767981441</v>
+        <v>-0.3830275229357798</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9806,11 +9941,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-411</v>
+        <v>-416</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.40632603406326034</v>
+        <v>-0.40144230769230771</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9823,11 +9958,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-400</v>
+        <v>-405</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.41749999999999998</v>
+        <v>-0.4123456790123457</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -10085,11 +10220,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>6.3125</v>
+        <v>11.222222222222221</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -10128,11 +10263,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-29</v>
+        <v>-36</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-3.2413793103448274</v>
+        <v>-2.6111111111111112</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -10171,11 +10306,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-16.399999999999999</v>
+        <v>-6.833333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -10214,11 +10349,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3333333333333333</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -11960,7 +12095,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C211"/>
+  <dimension ref="A1:C220"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -12994,19 +13129,67 @@
         <v>526</v>
       </c>
     </row>
-    <row r="209" spans="3:3">
+    <row r="209" spans="1:3">
       <c r="C209" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="210" spans="3:3">
+    <row r="210" spans="1:3">
       <c r="C210" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="211" spans="3:3">
+    <row r="211" spans="1:3">
       <c r="C211" t="s">
         <v>529</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" s="1">
+        <v>46255</v>
+      </c>
+      <c r="C212" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="C213" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="C214" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="C215" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="C216" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="C217" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="C218" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="C219" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="C220" t="s">
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D184C8FD-9FC9-498C-A4D1-1EFF54506EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91299C60-BE36-483A-B1D0-D179F9CCA999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9015" yWindow="3075" windowWidth="20625" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="20625" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="541">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -6027,6 +6027,26 @@
   </si>
   <si>
     <t>そのあと、でかいからカメラをいろいろしたりとかかなー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠距離攻撃、いったん完成</t>
+    <rPh sb="0" eb="5">
+      <t>エンキョリコウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、近距離攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="3" eb="8">
+      <t>キンキョリコウゲキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -12095,7 +12115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C220"/>
+  <dimension ref="A1:C222"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -13190,6 +13210,16 @@
     <row r="220" spans="1:3">
       <c r="C220" t="s">
         <v>538</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="C221" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="C222" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -14200,6 +14230,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -14434,15 +14473,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
@@ -14455,6 +14485,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14471,12 +14509,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91299C60-BE36-483A-B1D0-D179F9CCA999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C31603A-2993-4050-8687-09783C848137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="20625" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6525" yWindow="2055" windowWidth="20625" windowHeight="15585" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="仕様書①" sheetId="13" r:id="rId8"/>
     <sheet name="仕様書②" sheetId="15" r:id="rId9"/>
     <sheet name="クラス設計" sheetId="14" r:id="rId10"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$57</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="563">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -6047,6 +6048,184 @@
     <rPh sb="3" eb="8">
       <t>キンキョリコウゲキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近距離も、雑魚敵召喚も終わった</t>
+    <rPh sb="0" eb="3">
+      <t>キンキョリ</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>ザコテキショウカン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後は、ボスを丁寧に動かす、出現させる、スタンステート、ラストヒット演出って感じ</t>
+    <rPh sb="0" eb="1">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テイネイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音をだす</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameOverSceneの実装がまだだった</t>
+    <rPh sb="14" eb="16">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残りタスク洗い出し</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスを動かす</t>
+    <rPh sb="3" eb="4">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス用の血殺を作る(最後の)</t>
+    <rPh sb="2" eb="3">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>boss登場時のカメラ演出</t>
+    <rPh sb="4" eb="7">
+      <t>トウジョウジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIをしっかりしたのに変える</t>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズシーンを作る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズシーンを作る(LT押したら、ボタンガイドが出るとかでも全然いい)</t>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ゼンゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音をつける</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバーシーン(死でいい)</t>
+    <rPh sb="11" eb="12">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3日</t>
+    <rPh sb="1" eb="2">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回避を消す</t>
+    <rPh sb="0" eb="2">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスステート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Idle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stun</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9923,7 +10102,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -10133,6 +10312,37 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AB6BCA-2C55-4226-858C-6FF0248D7A91}">
+  <dimension ref="B2:B5"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10240,11 +10450,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>11.222222222222221</v>
+        <v>12.625</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -10283,11 +10493,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-2.6111111111111112</v>
+        <v>-2.5405405405405403</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -10326,11 +10536,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-6.833333333333333</v>
+        <v>-6.3076923076923075</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -10369,11 +10579,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -12115,7 +12325,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:C222"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -13220,6 +13430,109 @@
     <row r="222" spans="1:3">
       <c r="C222" t="s">
         <v>540</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="C223" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" s="1">
+        <v>46257</v>
+      </c>
+      <c r="C224" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="C225" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4">
+      <c r="C226" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="C228" t="s">
+        <v>545</v>
+      </c>
+      <c r="D228" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="B229" t="s">
+        <v>555</v>
+      </c>
+      <c r="C229" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="B230" t="s">
+        <v>554</v>
+      </c>
+      <c r="C230" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="B231" t="s">
+        <v>554</v>
+      </c>
+      <c r="C231" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4">
+      <c r="B232" t="s">
+        <v>556</v>
+      </c>
+      <c r="C232" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="B233" t="s">
+        <v>556</v>
+      </c>
+      <c r="C233" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="B234" t="s">
+        <v>555</v>
+      </c>
+      <c r="C234" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="B235" t="s">
+        <v>555</v>
+      </c>
+      <c r="C235" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="B236" t="s">
+        <v>556</v>
+      </c>
+      <c r="C236" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="B237" t="s">
+        <v>555</v>
+      </c>
+      <c r="C237" t="s">
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -14219,26 +14532,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -14473,26 +14766,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14509,4 +14803,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -1,29 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C31603A-2993-4050-8687-09783C848137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFC3E55-861F-4371-8EF3-F8E4B6FAE338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6525" yWindow="2055" windowWidth="20625" windowHeight="15585" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="435" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
     <sheet name="作業工数見積もり" sheetId="1" r:id="rId2"/>
     <sheet name="カレンダー" sheetId="6" r:id="rId3"/>
     <sheet name="日記" sheetId="12" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="16" r:id="rId5"/>
-    <sheet name="メモ" sheetId="9" r:id="rId6"/>
-    <sheet name="雑用" sheetId="10" r:id="rId7"/>
-    <sheet name="仕様書①" sheetId="13" r:id="rId8"/>
-    <sheet name="仕様書②" sheetId="15" r:id="rId9"/>
-    <sheet name="クラス設計" sheetId="14" r:id="rId10"/>
-    <sheet name="Sheet2" sheetId="17" r:id="rId11"/>
+    <sheet name="インターン中気になったこと" sheetId="18" r:id="rId5"/>
+    <sheet name="フィードバック" sheetId="19" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId7"/>
+    <sheet name="メモ" sheetId="9" r:id="rId8"/>
+    <sheet name="雑用" sheetId="10" r:id="rId9"/>
+    <sheet name="仕様書①" sheetId="13" r:id="rId10"/>
+    <sheet name="仕様書②" sheetId="15" r:id="rId11"/>
+    <sheet name="クラス設計" sheetId="14" r:id="rId12"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$57</definedName>
@@ -49,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="610">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -6226,6 +6228,398 @@
   </si>
   <si>
     <t>Stun</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LockOnManagerをつくる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CameraシステムをUnityのものからStatePatternのものにUpgradeする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定周りの修正案について</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>シュウセイアン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現状shared_ptrで管理しているせいで、参照が増えて、消したり登録したりが面倒</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>メンドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録したり、登録解除したりが面倒</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>トウロクカイジョ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>メンドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプの時のカメラ挙動はどういう風にしているのか気になる</t>
+    <rPh sb="5" eb="6">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>フウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンの時の注視点はどうしているのか気になる</t>
+    <rPh sb="6" eb="7">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>チュウシ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>playerにロックオンマネージャーを持たす</t>
+    <rPh sb="19" eb="20">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そこからゲットさせる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【フィードバック内容】</t>
+  </si>
+  <si>
+    <t>・カメラの切り替えが急すぎるため補間を入れる（ロックオン周りなど）</t>
+  </si>
+  <si>
+    <t>・キャラクターがとった行動に対してのリアクションが薄い</t>
+  </si>
+  <si>
+    <t>・Bボタンのアクションが何か分からない</t>
+  </si>
+  <si>
+    <t>・空中でのアクションは出るのが正しい？</t>
+  </si>
+  <si>
+    <t>・ポーズの機能</t>
+  </si>
+  <si>
+    <t>・ロックオンカーソル</t>
+  </si>
+  <si>
+    <t>・敵がどれくらいで倒せるのかが分からない</t>
+  </si>
+  <si>
+    <t>・モーションとアクションが合っていない（足が滑っている）</t>
+  </si>
+  <si>
+    <t>・画面が止まっている時間がある（タイトル）</t>
+  </si>
+  <si>
+    <t>・必殺で片翼を出した時、プレイヤーに対して何かしらのフィードバックが欲しい</t>
+  </si>
+  <si>
+    <t>・必殺でリソースが足りなかった時、足りなかったことが分からない</t>
+  </si>
+  <si>
+    <t>・ゲージが分かり辛い（表現の工夫？）</t>
+  </si>
+  <si>
+    <t>・ゲームの目的が分かる演出を入れる</t>
+  </si>
+  <si>
+    <t>・次のウェーブに進んだことが分かる演出を入れる</t>
+  </si>
+  <si>
+    <t>・歩き、ジャンプ、攻撃の踏み込みにエフェクトを入れる</t>
+  </si>
+  <si>
+    <t>・敵死亡時、パッと消えないようにする</t>
+  </si>
+  <si>
+    <t>・移動手段が歩きのみ（ステップやダッシュは不要？）</t>
+  </si>
+  <si>
+    <t>・モーションと当たり判定が合っていない</t>
+  </si>
+  <si>
+    <t>・打撃と斬撃で同じエフェクトが出ている</t>
+  </si>
+  <si>
+    <t>・当たり判定を大きい球ではなく、複数の球を持つようにする</t>
+  </si>
+  <si>
+    <t>GameSceneのロックオン処理は3つ</t>
+    <rPh sb="15" eb="17">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーン終了、次はplayerからattackColに渡したりしているところの変更</t>
+    <rPh sb="6" eb="8">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンボノードは一定時間攻撃していなかったら出す</t>
+    <rPh sb="7" eb="11">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>案</t>
+    <rPh sb="0" eb="1">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の色が体力によって変わっていくと、敵がhpを減っていってるのがわかりやすい</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヘ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>翼をゲージないときは出さない</t>
+    <rPh sb="0" eb="1">
+      <t>ツバサ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定を攻撃ごとに調整は優先度高い</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃アニメーションの当たり判定を出すタイミングは割合ではなく、フレームで管理したほうがいい</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ワリアイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そっちのほうが直感的だから</t>
+    <rPh sb="7" eb="10">
+      <t>チョッカンテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃の当たり判定はしっかり剣に沿わせたほうがいい</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あたった位置をとれるというのと、見た目に忠実に沿っているから、</t>
+    <rPh sb="4" eb="6">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チュウジツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やられ判定は</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やられ判定は球で、押し戻しをシリンダー</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理由は球同士の当たり判定が一番軽いから</t>
+    <rPh sb="0" eb="2">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>キュウドウシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>イチバンカル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扱いやすいならカプセルでもいいが、</t>
+    <rPh sb="0" eb="1">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本円柱とか球でいい</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンチュウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6237,7 +6631,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6297,6 +6691,19 @@
       <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="29">
@@ -6594,7 +7001,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -6656,6 +7063,8 @@
     <xf numFmtId="0" fontId="7" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -10080,11 +10489,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.353319057815846E-2</v>
+        <v>5.3418803418803416E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -10102,7 +10511,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -10123,11 +10532,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-436</v>
+        <v>-437</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.3830275229357798</v>
+        <v>-0.38215102974828374</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -10140,11 +10549,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-416</v>
+        <v>-417</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.40144230769230771</v>
+        <v>-0.40047961630695444</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -10157,11 +10566,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-405</v>
+        <v>-406</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.4123456790123457</v>
+        <v>-0.41133004926108374</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -10244,6 +10653,405 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
+  <dimension ref="A1:AK43"/>
+  <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:33">
+      <c r="M1" t="s">
+        <v>101</v>
+      </c>
+      <c r="T1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33">
+      <c r="B2" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="M2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M3" t="s">
+        <v>103</v>
+      </c>
+      <c r="R3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="M7" t="s">
+        <v>106</v>
+      </c>
+      <c r="R7" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
+      <c r="AE10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
+      <c r="M11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
+      <c r="M12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
+      <c r="A14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
+      <c r="D15" t="s">
+        <v>140</v>
+      </c>
+      <c r="M15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
+      <c r="M16" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF16" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG16" s="39"/>
+    </row>
+    <row r="17" spans="1:37">
+      <c r="B17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" t="s">
+        <v>111</v>
+      </c>
+      <c r="M17" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
+      <c r="M18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>111</v>
+      </c>
+      <c r="M19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="AF20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="B21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="M22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="D24" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37">
+      <c r="A28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="O43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015F96B1-EBF5-4BB2-93CD-A0906537FC8C}">
+  <dimension ref="C2:X16"/>
+  <sheetFormatPr defaultColWidth="3.875" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="25" max="25" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:24">
+      <c r="C2" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="Q2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="3:24">
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="3:24">
+      <c r="C5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="3:24">
+      <c r="C6" t="s">
+        <v>181</v>
+      </c>
+      <c r="I6" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>154</v>
+      </c>
+      <c r="S6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="3:24">
+      <c r="Q7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="3:24">
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="3:24">
+      <c r="C9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I9" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>175</v>
+      </c>
+      <c r="X9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="3:24">
+      <c r="C10" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="3:24">
+      <c r="C11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="3:24">
+      <c r="Q12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="3:24">
+      <c r="C13" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>161</v>
+      </c>
+      <c r="S13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="3:24">
+      <c r="C14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I14" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>163</v>
+      </c>
+      <c r="S14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="3:24">
+      <c r="Q15" t="s">
+        <v>165</v>
+      </c>
+      <c r="R15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="3:24">
+      <c r="Q16" t="s">
+        <v>167</v>
+      </c>
+      <c r="S16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B1947F-A3A0-4027-965D-A484FB7F3C32}">
   <dimension ref="C1:AU33"/>
   <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
@@ -10315,7 +11123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AB6BCA-2C55-4226-858C-6FF0248D7A91}">
   <dimension ref="B2:B5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -10450,11 +11258,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>12.625</v>
+        <v>14.428571428571429</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -10493,11 +11301,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-2.5405405405405403</v>
+        <v>-2.4736842105263159</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -10536,11 +11344,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-6.3076923076923075</v>
+        <v>-5.8571428571428568</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -10579,11 +11387,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -12325,7 +13133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D237"/>
+  <dimension ref="A1:D246"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -13445,17 +14253,17 @@
         <v>542</v>
       </c>
     </row>
-    <row r="225" spans="2:4">
+    <row r="225" spans="1:4">
       <c r="C225" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="226" spans="2:4">
+    <row r="226" spans="1:4">
       <c r="C226" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="228" spans="2:4">
+    <row r="228" spans="1:4">
       <c r="C228" t="s">
         <v>545</v>
       </c>
@@ -13463,7 +14271,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="229" spans="2:4">
+    <row r="229" spans="1:4">
       <c r="B229" t="s">
         <v>555</v>
       </c>
@@ -13471,7 +14279,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="230" spans="2:4">
+    <row r="230" spans="1:4">
       <c r="B230" t="s">
         <v>554</v>
       </c>
@@ -13479,7 +14287,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="231" spans="2:4">
+    <row r="231" spans="1:4">
       <c r="B231" t="s">
         <v>554</v>
       </c>
@@ -13487,7 +14295,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="232" spans="2:4">
+    <row r="232" spans="1:4">
       <c r="B232" t="s">
         <v>556</v>
       </c>
@@ -13495,7 +14303,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="233" spans="2:4">
+    <row r="233" spans="1:4">
       <c r="B233" t="s">
         <v>556</v>
       </c>
@@ -13503,7 +14311,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="234" spans="2:4">
+    <row r="234" spans="1:4">
       <c r="B234" t="s">
         <v>555</v>
       </c>
@@ -13511,7 +14319,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="235" spans="2:4">
+    <row r="235" spans="1:4">
       <c r="B235" t="s">
         <v>555</v>
       </c>
@@ -13519,7 +14327,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="236" spans="2:4">
+    <row r="236" spans="1:4">
       <c r="B236" t="s">
         <v>556</v>
       </c>
@@ -13527,12 +14335,50 @@
         <v>550</v>
       </c>
     </row>
-    <row r="237" spans="2:4">
+    <row r="237" spans="1:4">
       <c r="B237" t="s">
         <v>555</v>
       </c>
       <c r="C237" t="s">
         <v>558</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="1">
+        <v>46258</v>
+      </c>
+      <c r="C239" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="C240" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="241" spans="3:3">
+      <c r="C241" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="243" spans="3:3">
+      <c r="C243" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="244" spans="3:3">
+      <c r="C244" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="245" spans="3:3">
+      <c r="C245" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="246" spans="3:3">
+      <c r="C246" t="s">
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -13542,6 +14388,232 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E218887-0FDF-44BB-AA49-E18A6D1E6450}">
+  <dimension ref="A2:B25"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>568</v>
+      </c>
+      <c r="B5" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>597</v>
+      </c>
+      <c r="B9" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>609</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368A907-596B-4B61-8CB6-45BC6EA11F46}">
+  <dimension ref="B2:B22"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="55" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="56" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="56" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="56" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="56" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="56" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="56" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="56" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="56" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="56" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="56" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="56" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="56" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="56" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="56" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="56" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="56" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="56" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="56" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="56" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="56" t="s">
+        <v>593</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{885D8AAA-735E-4C60-B6AA-AFC225D5AECF}">
   <dimension ref="D2:R17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -13668,7 +14740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
   <dimension ref="B2:E64"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -13946,7 +15018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -14132,406 +15204,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
-  <dimension ref="A1:AK43"/>
-  <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:33">
-      <c r="M1" t="s">
-        <v>101</v>
-      </c>
-      <c r="T1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33">
-      <c r="B2" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="M2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33">
-      <c r="B3" t="s">
-        <v>97</v>
-      </c>
-      <c r="M3" t="s">
-        <v>103</v>
-      </c>
-      <c r="R3" t="s">
-        <v>144</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33">
-      <c r="B4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M4" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33">
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33">
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
-      <c r="M6" t="s">
-        <v>105</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33">
-      <c r="B7" t="s">
-        <v>100</v>
-      </c>
-      <c r="M7" t="s">
-        <v>106</v>
-      </c>
-      <c r="R7" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33">
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33">
-      <c r="AE10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33">
-      <c r="M11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33">
-      <c r="M12" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33">
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33">
-      <c r="A14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33">
-      <c r="D15" t="s">
-        <v>140</v>
-      </c>
-      <c r="M15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33">
-      <c r="M16" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF16" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="AG16" s="39"/>
-    </row>
-    <row r="17" spans="1:37">
-      <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F17" t="s">
-        <v>111</v>
-      </c>
-      <c r="M17" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>147</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37">
-      <c r="M18" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37">
-      <c r="B19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" t="s">
-        <v>111</v>
-      </c>
-      <c r="M19" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37">
-      <c r="AF20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" spans="1:37">
-      <c r="B21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:37">
-      <c r="M22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:37">
-      <c r="D24" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="28" spans="1:37">
-      <c r="A28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
-      <c r="A38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
-      <c r="A41" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
-      <c r="A42" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
-      <c r="O43" t="s">
-        <v>216</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015F96B1-EBF5-4BB2-93CD-A0906537FC8C}">
-  <dimension ref="C2:X16"/>
-  <sheetFormatPr defaultColWidth="3.875" defaultRowHeight="18.75"/>
-  <cols>
-    <col min="25" max="25" width="3.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="3:24">
-      <c r="C2" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="Q2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="3:24">
-      <c r="C4" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="3:24">
-      <c r="C5" t="s">
-        <v>170</v>
-      </c>
-      <c r="I5" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="3:24">
-      <c r="C6" t="s">
-        <v>181</v>
-      </c>
-      <c r="I6" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>154</v>
-      </c>
-      <c r="S6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="3:24">
-      <c r="Q7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="3:24">
-      <c r="C8" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="9" spans="3:24">
-      <c r="C9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I9" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>175</v>
-      </c>
-      <c r="X9" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="10" spans="3:24">
-      <c r="C10" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="3:24">
-      <c r="C11" t="s">
-        <v>174</v>
-      </c>
-      <c r="I11" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="3:24">
-      <c r="Q12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="3:24">
-      <c r="C13" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>161</v>
-      </c>
-      <c r="S13" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="3:24">
-      <c r="C14" t="s">
-        <v>179</v>
-      </c>
-      <c r="I14" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>163</v>
-      </c>
-      <c r="S14" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="3:24">
-      <c r="Q15" t="s">
-        <v>165</v>
-      </c>
-      <c r="R15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" spans="3:24">
-      <c r="Q16" t="s">
-        <v>167</v>
-      </c>
-      <c r="S16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -14766,27 +15459,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14803,23 +15495,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFC3E55-861F-4371-8EF3-F8E4B6FAE338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB9E1E-EA22-46CF-BA13-D67F776A6414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="435" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="2475" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="637">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -6619,6 +6619,408 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑の処理をすべて終了</t>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今日からカメラステートに実装変更する</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラのツールを作る(アリかナシかでいうとナシより)</t>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラをUnity風ではなくて、CameraStateで動かすようにする</t>
+    <rPh sb="9" eb="10">
+      <t>フウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内部ターゲットの作りの変更</t>
+    <rPh sb="0" eb="2">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先にtargetの処理の修正をする</t>
+    <rPh sb="0" eb="1">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まずは、Playerの中で攻撃が初めて当たった時の処理、2回目以降の処理みたいな感じでまとめる</t>
+    <rPh sb="11" eb="12">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(これをすることで、カメラが毎回ぶれる問題もなくなるはず</t>
+    <rPh sb="14" eb="16">
+      <t>マイカイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃の移動と歩きの移動は分けて扱う</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃は速度が一定ではなく、加速度や、減速をしたりするから</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ゲンソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やられは初速とかを与えて、放物線に任せる</t>
+    <rPh sb="4" eb="6">
+      <t>ショソク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ホウブツセン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>マカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>速度の初期化問題について</t>
+    <rPh sb="0" eb="2">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="3" eb="8">
+      <t>ショキカモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>加速度はあったほうがいい</t>
+    <rPh sb="0" eb="3">
+      <t>カソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステート切り替え時に速度をリセットするかどうかのフラグはあったほうがいい</t>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stateを継承前提の作りにすることで、作らなくていいステートが生まれてくるからそういう設計にする(ジャンプとかは一緒になりやすい)</t>
+    <rPh sb="6" eb="8">
+      <t>ケイショウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>イッショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そもそもStateの中だと速度を毎フレーム初期化などをしなくていい可能性が高い</t>
+    <rPh sb="10" eb="11">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>マイ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ショキカ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(今回はEnemyをstateの分けていないからわけている</t>
+    <rPh sb="1" eb="3">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>速度をmapで持つのは管理しにくいからあらかじめ複数個持つのがいい</t>
+    <rPh sb="0" eb="2">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>フクスウコ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hit時もその敵のポインタ事態を渡すのではなく、敵のデータの構造体を渡す</t>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>コウゾウタイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中時には回転制御というのがあり、rateを設けることで、空中でぐるぐる動かない用にできる</t>
+    <rPh sb="0" eb="3">
+      <t>クウチュウジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>モウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それぞれのステートの時はこの移動速度、加速度を参照するというCSVを作るのがよい(かなりあり)</t>
+    <rPh sb="10" eb="11">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンしていないときのプレイやー挙動について聞いた</t>
+    <rPh sb="18" eb="20">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雑に言うと、基本はスティック移動を優先する</t>
+    <rPh sb="0" eb="1">
+      <t>ザツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ユウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>targetの処理の修正終わり</t>
+    <rPh sb="7" eb="9">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次は、cameraStateパターンの実装をする</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7001,7 +7403,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -7065,6 +7467,7 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -10489,11 +10892,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.3418803418803416E-2</v>
+        <v>5.3304904051172705E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -10511,7 +10914,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -10532,11 +10935,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-437</v>
+        <v>-438</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.38215102974828374</v>
+        <v>-0.38127853881278539</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -10549,11 +10952,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-417</v>
+        <v>-418</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.40047961630695444</v>
+        <v>-0.39952153110047844</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -10566,11 +10969,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-406</v>
+        <v>-407</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.41133004926108374</v>
+        <v>-0.41031941031941033</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -11258,11 +11661,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>14.428571428571429</v>
+        <v>16.833333333333332</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -11301,11 +11704,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-2.4736842105263159</v>
+        <v>-2.4102564102564101</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -11344,11 +11747,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-5.8571428571428568</v>
+        <v>-5.4666666666666668</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -11387,11 +11790,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>5.333333333333333</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13133,7 +13536,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D246"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -14253,17 +14656,17 @@
         <v>542</v>
       </c>
     </row>
-    <row r="225" spans="1:4">
+    <row r="225" spans="2:4">
       <c r="C225" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="2:4">
       <c r="C226" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="2:4">
       <c r="C228" t="s">
         <v>545</v>
       </c>
@@ -14271,31 +14674,31 @@
         <v>557</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="2:4">
       <c r="B229" t="s">
         <v>555</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="57" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="2:4">
       <c r="B230" t="s">
         <v>554</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C230" s="57" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="2:4">
       <c r="B231" t="s">
         <v>554</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C231" s="57" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="2:4">
       <c r="B232" t="s">
         <v>556</v>
       </c>
@@ -14303,7 +14706,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="2:4">
       <c r="B233" t="s">
         <v>556</v>
       </c>
@@ -14311,7 +14714,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="2:4">
       <c r="B234" t="s">
         <v>555</v>
       </c>
@@ -14319,7 +14722,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="2:4">
       <c r="B235" t="s">
         <v>555</v>
       </c>
@@ -14327,7 +14730,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="2:4">
       <c r="B236" t="s">
         <v>556</v>
       </c>
@@ -14335,7 +14738,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="2:4">
       <c r="B237" t="s">
         <v>555</v>
       </c>
@@ -14343,42 +14746,114 @@
         <v>558</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
-      <c r="A239" s="1">
+    <row r="238" spans="2:4">
+      <c r="B238" t="s">
+        <v>614</v>
+      </c>
+      <c r="C238" s="57" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4">
+      <c r="B239" t="s">
+        <v>614</v>
+      </c>
+      <c r="C239" s="57" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4">
+      <c r="B240" t="s">
+        <v>615</v>
+      </c>
+      <c r="C240" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" s="1">
         <v>46258</v>
       </c>
-      <c r="C239" t="s">
+      <c r="C241" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
-      <c r="C240" t="s">
+    <row r="242" spans="1:3">
+      <c r="C242" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="241" spans="3:3">
-      <c r="C241" t="s">
+    <row r="243" spans="1:3">
+      <c r="C243" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="243" spans="3:3">
-      <c r="C243" t="s">
+    <row r="245" spans="1:3">
+      <c r="C245" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="244" spans="3:3">
-      <c r="C244" t="s">
+    <row r="246" spans="1:3">
+      <c r="C246" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="245" spans="3:3">
-      <c r="C245" t="s">
+    <row r="247" spans="1:3">
+      <c r="C247" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="246" spans="3:3">
-      <c r="C246" t="s">
+    <row r="248" spans="1:3">
+      <c r="C248" t="s">
         <v>595</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="C249" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="1">
+        <v>46259</v>
+      </c>
+      <c r="C250" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="C251" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="C252" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="C253" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="C254" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="C255" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="C256" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="257" spans="3:3">
+      <c r="C257" t="s">
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -14389,7 +14864,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E218887-0FDF-44BB-AA49-E18A6D1E6450}">
-  <dimension ref="A2:B25"/>
+  <dimension ref="A2:B45"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:2">
@@ -14489,6 +14964,71 @@
     <row r="25" spans="2:2">
       <c r="B25" t="s">
         <v>609</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" t="s">
+        <v>632</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB9E1E-EA22-46CF-BA13-D67F776A6414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA25D79D-5EF5-4EED-8745-3D4AA6BC3ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="2475" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="315" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="642">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -7021,6 +7021,80 @@
     </rPh>
     <rPh sb="19" eb="21">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まずは、ゲームシーンでplayerCameraのみで移植をする</t>
+    <rPh sb="26" eb="28">
+      <t>イショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、ほかのカメラでの移植も終える、</t>
+    <rPh sb="13" eb="15">
+      <t>イショク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後にカメラのラープに関する関数を作る</t>
+    <rPh sb="0" eb="2">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル攻撃を振ったら血を地面にテクスチャを貼り付けるとかめちゃくちゃいい</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>草をポリゴンで表示させて、2分割して上部分を揺らすとぽい</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ウエブブン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ユ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -13536,7 +13610,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D257"/>
+  <dimension ref="A1:D263"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -14854,6 +14928,31 @@
     <row r="257" spans="3:3">
       <c r="C257" t="s">
         <v>636</v>
+      </c>
+    </row>
+    <row r="258" spans="3:3">
+      <c r="C258" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="259" spans="3:3">
+      <c r="C259" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="260" spans="3:3">
+      <c r="C260" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="262" spans="3:3">
+      <c r="C262" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="263" spans="3:3">
+      <c r="C263" t="s">
+        <v>641</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA25D79D-5EF5-4EED-8745-3D4AA6BC3ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A114082-4E26-45FF-9732-45AFD550A47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="315" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6000" yWindow="735" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="654">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -7095,6 +7095,162 @@
     </rPh>
     <rPh sb="22" eb="23">
       <t>ユ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンカメラの時のプレイヤーの入力方向などを直す</t>
+    <rPh sb="9" eb="10">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>ニュウリョクホウコウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直した</t>
+    <rPh sb="0" eb="1">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PlayerStateRun,Avoidを消した</t>
+    <rPh sb="21" eb="22">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今から、カメラの揺れ機能を追加しながら、UltCamのステートじっそうをする</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ユ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラの機能追加終わり、UltCamの実装も終わり、Titlecamの実装も終わり</t>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今から、基底クラスのラープ実装、各ステートの初期値などの細かい設定に入る</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラープについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Slerpするかどうか（その場合の基軸など),lerpするかどうか、どのくらいの割合でするか、強度などの項目をしらべないといけない</t>
+    <rPh sb="14" eb="16">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キジク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ワリアイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>キョウド</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Changeの時にだれがどこで設定するのかも決める</t>
+    <rPh sb="7" eb="8">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネズミけるときすろーにしてもいいかも(TitleScene上で</t>
+    <rPh sb="29" eb="30">
+      <t>ジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IMGUIを導入する</t>
+    <rPh sb="6" eb="8">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先度高</t>
+    <rPh sb="0" eb="3">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7477,7 +7633,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -7542,6 +7698,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -10966,11 +11123,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.3304904051172705E-2</v>
+        <v>5.3191489361702128E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -10988,7 +11145,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -11009,11 +11166,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-438</v>
+        <v>-439</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.38127853881278539</v>
+        <v>-0.38041002277904329</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -11026,11 +11183,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-418</v>
+        <v>-419</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.39952153110047844</v>
+        <v>-0.39856801909307876</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -11043,11 +11200,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-407</v>
+        <v>-408</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.41031941031941033</v>
+        <v>-0.40931372549019607</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -11735,11 +11892,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>16.833333333333332</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -11778,11 +11935,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-2.4102564102564101</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -11821,11 +11978,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-5.4666666666666668</v>
+        <v>-5.125</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -11864,11 +12021,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13610,7 +13767,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D263"/>
+  <dimension ref="A1:D275"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -14925,34 +15082,95 @@
         <v>635</v>
       </c>
     </row>
-    <row r="257" spans="3:3">
+    <row r="257" spans="1:3">
       <c r="C257" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="258" spans="3:3">
+    <row r="258" spans="1:3">
       <c r="C258" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="259" spans="3:3">
+    <row r="259" spans="1:3">
       <c r="C259" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="260" spans="3:3">
+    <row r="260" spans="1:3">
       <c r="C260" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="262" spans="3:3">
+    <row r="262" spans="1:3">
       <c r="C262" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="263" spans="3:3">
+    <row r="263" spans="1:3">
       <c r="C263" t="s">
         <v>641</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C264" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="C265" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="C266" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="C267" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="C268" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="C269" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="C270" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="C271" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="C272" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3">
+      <c r="C274" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3">
+      <c r="B275" s="58" t="s">
+        <v>653</v>
+      </c>
+      <c r="C275" s="58" t="s">
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -14963,7 +15181,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E218887-0FDF-44BB-AA49-E18A6D1E6450}">
-  <dimension ref="A2:B45"/>
+  <dimension ref="A2:B48"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:2">
@@ -15128,6 +15346,16 @@
     <row r="45" spans="2:2">
       <c r="B45" t="s">
         <v>632</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" t="s">
+        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -15855,15 +16083,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -16098,6 +16317,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
@@ -16110,14 +16338,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16134,4 +16354,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A114082-4E26-45FF-9732-45AFD550A47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F93672-3109-4A19-804E-63A37507048E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="735" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4365" yWindow="1845" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
     <sheet name="作業工数見積もり" sheetId="1" r:id="rId2"/>
     <sheet name="カレンダー" sheetId="6" r:id="rId3"/>
     <sheet name="日記" sheetId="12" r:id="rId4"/>
-    <sheet name="インターン中気になったこと" sheetId="18" r:id="rId5"/>
-    <sheet name="フィードバック" sheetId="19" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="16" r:id="rId7"/>
-    <sheet name="メモ" sheetId="9" r:id="rId8"/>
-    <sheet name="雑用" sheetId="10" r:id="rId9"/>
-    <sheet name="仕様書①" sheetId="13" r:id="rId10"/>
-    <sheet name="仕様書②" sheetId="15" r:id="rId11"/>
-    <sheet name="クラス設計" sheetId="14" r:id="rId12"/>
-    <sheet name="Sheet2" sheetId="17" r:id="rId13"/>
+    <sheet name="必要なUI,Effect" sheetId="20" r:id="rId5"/>
+    <sheet name="インターン中気になったこと" sheetId="18" r:id="rId6"/>
+    <sheet name="フィードバック" sheetId="19" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId8"/>
+    <sheet name="メモ" sheetId="9" r:id="rId9"/>
+    <sheet name="雑用" sheetId="10" r:id="rId10"/>
+    <sheet name="仕様書①" sheetId="13" r:id="rId11"/>
+    <sheet name="仕様書②" sheetId="15" r:id="rId12"/>
+    <sheet name="クラス設計" sheetId="14" r:id="rId13"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$B$2:$G$57</definedName>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="687">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -6138,16 +6139,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>boss登場時のカメラ演出</t>
-    <rPh sb="4" eb="7">
-      <t>トウジョウジ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>エンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>UIをしっかりしたのに変える</t>
     <rPh sb="11" eb="12">
       <t>カ</t>
@@ -7251,6 +7242,298 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>boss登場時のカメラ演出,フェーズ終わりのカメラ演出</t>
+    <rPh sb="4" eb="7">
+      <t>トウジョウジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終わり</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>途中</t>
+    <rPh sb="0" eb="2">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要なエフェクト制作（ステージ終わりのやつとか制限の壁とか</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字フォント</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンカーソル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Effect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>切り上げ攻撃時の足元から出すエフェクト</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>アシモト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃のHitEffect（剣と格闘で分ける</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクトウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージのフェーズ終わり時の解放エフェクト</t>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>細かい残りタスク</t>
+    <rPh sb="0" eb="1">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameOverの死</t>
+    <rPh sb="9" eb="10">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameOver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameClear</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pauseScene</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剣のヒット音</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打撃のヒット音</t>
+    <rPh sb="0" eb="2">
+      <t>ダゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のヒット音、攻撃音</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>コウゲキオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ制限の壁</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TitleScene</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameScene</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PauseScene</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameClearScene</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameOverScene</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルの時の音</t>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>血殺の時の音</t>
+    <rPh sb="0" eb="2">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カラス状態出現時のエフェクト</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>シュツゲンジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>導入官僚</t>
+    <rPh sb="0" eb="4">
+      <t>ドウニュウカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後の演出案</t>
+    <rPh sb="0" eb="2">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>倒れたボスに追い打ちで血殺をする</t>
+    <rPh sb="0" eb="1">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>チサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの時の敵ロックオンをかえないといけない←完了</t>
+    <rPh sb="3" eb="4">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>途中</t>
+    <rPh sb="0" eb="2">
+      <t>トチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -11123,11 +11406,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.3191489361702128E-2</v>
+        <v>5.3078556263269641E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -11145,7 +11428,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -11166,11 +11449,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-439</v>
+        <v>-440</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.38041002277904329</v>
+        <v>-0.37954545454545452</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -11183,11 +11466,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-419</v>
+        <v>-420</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.39856801909307876</v>
+        <v>-0.39761904761904759</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -11200,11 +11483,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-408</v>
+        <v>-409</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.40931372549019607</v>
+        <v>-0.40831295843520782</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -11287,6 +11570,192 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="44"/>
+      <c r="G2" s="45"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="44"/>
+      <c r="C3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G3" s="45"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="44"/>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="45"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="44"/>
+      <c r="C5" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="45"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="44"/>
+      <c r="C6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="44"/>
+      <c r="C7" t="s">
+        <v>194</v>
+      </c>
+      <c r="G7" s="45"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="44"/>
+      <c r="G8" s="45"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="44"/>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="45"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="44"/>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F10" t="s">
+        <v>193</v>
+      </c>
+      <c r="G10" s="45"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="44"/>
+      <c r="B11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" t="s">
+        <v>191</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="45"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="44"/>
+      <c r="B12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" t="s">
+        <v>188</v>
+      </c>
+      <c r="F12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G12" s="45"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="44"/>
+      <c r="B13" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F13" t="s">
+        <v>186</v>
+      </c>
+      <c r="G13" s="45"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1">
+      <c r="A14" s="46"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="48"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D17" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="D22" t="s">
+        <v>201</v>
+      </c>
+      <c r="F22" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F2B08E-4005-4196-B3E0-F413A5A01C4A}">
   <dimension ref="A1:AK43"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="18.75"/>
@@ -11536,7 +12005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015F96B1-EBF5-4BB2-93CD-A0906537FC8C}">
   <dimension ref="C2:X16"/>
   <sheetFormatPr defaultColWidth="3.875" defaultRowHeight="18.75"/>
@@ -11685,7 +12154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B1947F-A3A0-4027-965D-A484FB7F3C32}">
   <dimension ref="C1:AU33"/>
   <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
@@ -11757,29 +12226,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AB6BCA-2C55-4226-858C-6FF0248D7A91}">
   <dimension ref="B2:B5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -11892,11 +12361,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>20.2</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -11935,11 +12404,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-2.35</v>
+        <v>-2.2926829268292681</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -11978,11 +12447,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-5.125</v>
+        <v>-4.8235294117647056</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -12021,11 +12490,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="e">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13767,7 +14236,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D275"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -14902,20 +15371,23 @@
         <v>545</v>
       </c>
       <c r="D228" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="229" spans="2:4">
       <c r="B229" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C229" s="57" t="s">
         <v>546</v>
       </c>
+      <c r="D229" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="230" spans="2:4">
       <c r="B230" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C230" s="57" t="s">
         <v>547</v>
@@ -14923,254 +15395,300 @@
     </row>
     <row r="231" spans="2:4">
       <c r="B231" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C231" s="57" t="s">
-        <v>548</v>
+        <v>653</v>
+      </c>
+      <c r="D231" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="232" spans="2:4">
       <c r="B232" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C232" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="233" spans="2:4">
       <c r="B233" t="s">
-        <v>556</v>
-      </c>
-      <c r="C233" t="s">
-        <v>551</v>
+        <v>555</v>
+      </c>
+      <c r="C233" s="57" t="s">
+        <v>550</v>
+      </c>
+      <c r="D233" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="234" spans="2:4">
       <c r="B234" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C234" t="s">
-        <v>552</v>
+        <v>551</v>
+      </c>
+      <c r="D234" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="235" spans="2:4">
       <c r="B235" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C235" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="236" spans="2:4">
       <c r="B236" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C236" t="s">
-        <v>550</v>
+        <v>549</v>
+      </c>
+      <c r="D236" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="237" spans="2:4">
       <c r="B237" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C237" t="s">
-        <v>558</v>
+        <v>557</v>
+      </c>
+      <c r="D237" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="238" spans="2:4">
       <c r="B238" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C238" s="57" t="s">
-        <v>613</v>
+        <v>612</v>
+      </c>
+      <c r="D238" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="239" spans="2:4">
       <c r="B239" t="s">
+        <v>613</v>
+      </c>
+      <c r="C239" s="57" t="s">
+        <v>615</v>
+      </c>
+      <c r="D239" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4">
+      <c r="C240" s="32" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="B241" t="s">
         <v>614</v>
       </c>
-      <c r="C239" s="57" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="240" spans="2:4">
-      <c r="B240" t="s">
-        <v>615</v>
-      </c>
-      <c r="C240" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="1">
+      <c r="C241" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" s="1">
         <v>46258</v>
       </c>
-      <c r="C241" t="s">
+      <c r="C242" t="s">
         <v>530</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="C242" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="C243" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="C245" t="s">
-        <v>571</v>
+        <v>562</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="C244" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="C246" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="C247" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="C248" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="C249" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="C250" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="1">
+        <v>46259</v>
+      </c>
+      <c r="C251" t="s">
         <v>610</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250" s="1">
-        <v>46259</v>
-      </c>
-      <c r="C250" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="C251" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="C252" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="C253" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="C254" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="C255" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="C256" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="C257" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="C258" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="C259" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="C260" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3">
-      <c r="C262" t="s">
-        <v>640</v>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="C261" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="C263" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="C264" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C265" t="s">
         <v>641</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3">
-      <c r="A264" s="1">
-        <v>46260</v>
-      </c>
-      <c r="C264" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3">
-      <c r="C265" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="C266" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="C267" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="C268" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="C269" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="C270" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="C271" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="C272" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="273" spans="2:3">
+      <c r="C273" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3">
+      <c r="C275" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="274" spans="2:3">
-      <c r="C274" t="s">
+    <row r="276" spans="2:3">
+      <c r="B276" s="58" t="s">
+        <v>652</v>
+      </c>
+      <c r="C276" s="58" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="275" spans="2:3">
-      <c r="B275" s="58" t="s">
-        <v>653</v>
-      </c>
-      <c r="C275" s="58" t="s">
-        <v>652</v>
+    <row r="277" spans="2:3">
+      <c r="C277" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3">
+      <c r="C279" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3">
+      <c r="C280" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3">
+      <c r="C281" t="s">
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -15180,182 +15698,98 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E218887-0FDF-44BB-AA49-E18A6D1E6450}">
-  <dimension ref="A2:B48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B2C458A-D800-40F2-A389-E66EF82142B9}">
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>659</v>
+      </c>
+      <c r="L1" t="s">
+        <v>661</v>
+      </c>
+      <c r="O1" t="s">
+        <v>662</v>
+      </c>
+      <c r="R1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>568</v>
-      </c>
-      <c r="B2" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="B3" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="B4" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>568</v>
-      </c>
-      <c r="B5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="B6" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>597</v>
-      </c>
-      <c r="B9" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="B11" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="B13" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="B14" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="B15" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="B16" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" t="s">
-        <v>641</v>
+        <v>657</v>
+      </c>
+      <c r="F2" t="s">
+        <v>663</v>
+      </c>
+      <c r="L2" t="s">
+        <v>674</v>
+      </c>
+      <c r="O2" t="s">
+        <v>670</v>
+      </c>
+      <c r="R2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
+        <v>658</v>
+      </c>
+      <c r="F3" t="s">
+        <v>660</v>
+      </c>
+      <c r="L3" t="s">
+        <v>675</v>
+      </c>
+      <c r="O3" t="s">
+        <v>671</v>
+      </c>
+      <c r="R3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
+        <v>666</v>
+      </c>
+      <c r="F4" t="s">
+        <v>664</v>
+      </c>
+      <c r="L4" t="s">
+        <v>676</v>
+      </c>
+      <c r="O4" t="s">
+        <v>672</v>
+      </c>
+      <c r="R4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="F5" t="s">
+        <v>673</v>
+      </c>
+      <c r="L5" t="s">
+        <v>677</v>
+      </c>
+      <c r="O5" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="F6" t="s">
+        <v>681</v>
+      </c>
+      <c r="L6" t="s">
+        <v>678</v>
+      </c>
+      <c r="O6" t="s">
+        <v>680</v>
       </c>
     </row>
   </sheetData>
@@ -15365,113 +15799,182 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368A907-596B-4B61-8CB6-45BC6EA11F46}">
-  <dimension ref="B2:B22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E218887-0FDF-44BB-AA49-E18A6D1E6450}">
+  <dimension ref="A2:B48"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" s="55" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" s="56" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" s="56" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="56" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" s="56" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="56" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="56" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="56" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="56" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="56" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="56" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="56" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="56" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="56" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="56" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="56" t="s">
-        <v>588</v>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>567</v>
+      </c>
+      <c r="B5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>596</v>
+      </c>
+      <c r="B9" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="56" t="s">
-        <v>589</v>
+      <c r="B18" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="56" t="s">
-        <v>590</v>
+      <c r="B19" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="56" t="s">
-        <v>591</v>
+      <c r="B20" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="56" t="s">
-        <v>592</v>
+      <c r="B21" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="56" t="s">
-        <v>593</v>
+      <c r="B22" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" t="s">
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -15481,6 +15984,122 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368A907-596B-4B61-8CB6-45BC6EA11F46}">
+  <dimension ref="B2:B22"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="55" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="56" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="56" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="56" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="56" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="56" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="56" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="56" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="56" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="56" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="56" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="56" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="56" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="56" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="56" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="56" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="56" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="56" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="56" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="56" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="56" t="s">
+        <v>592</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{885D8AAA-735E-4C60-B6AA-AFC225D5AECF}">
   <dimension ref="D2:R17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -15607,7 +16226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF696AB-2B42-42A5-B99F-E70A812D4095}">
   <dimension ref="B2:E64"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -15877,192 +16496,6 @@
     <row r="64" spans="2:2">
       <c r="B64" t="s">
         <v>457</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E98AC8-7610-4AC5-B6A1-107905495902}">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="41"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="44"/>
-      <c r="G2" s="45"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="44"/>
-      <c r="C3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G3" s="45"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="44"/>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="45"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="44"/>
-      <c r="C5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G5" s="45"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="44"/>
-      <c r="C6" t="s">
-        <v>188</v>
-      </c>
-      <c r="G6" s="45"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="44"/>
-      <c r="C7" t="s">
-        <v>194</v>
-      </c>
-      <c r="G7" s="45"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="44"/>
-      <c r="G8" s="45"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="44"/>
-      <c r="B9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9" t="s">
-        <v>192</v>
-      </c>
-      <c r="G9" s="45"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="44"/>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>190</v>
-      </c>
-      <c r="F10" t="s">
-        <v>193</v>
-      </c>
-      <c r="G10" s="45"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="44"/>
-      <c r="B11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D11" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="45"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="44"/>
-      <c r="B12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" t="s">
-        <v>188</v>
-      </c>
-      <c r="F12" t="s">
-        <v>188</v>
-      </c>
-      <c r="G12" s="45"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="44"/>
-      <c r="B13" t="s">
-        <v>194</v>
-      </c>
-      <c r="D13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F13" t="s">
-        <v>186</v>
-      </c>
-      <c r="G13" s="45"/>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1">
-      <c r="A14" s="46"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="G14" s="48"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D17" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" t="s">
-        <v>196</v>
-      </c>
-      <c r="D20" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="D22" t="s">
-        <v>201</v>
-      </c>
-      <c r="F22" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F93672-3109-4A19-804E-63A37507048E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3969D629-FDF8-41C2-988C-4587FC4C3C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4365" yWindow="1845" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="701">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -7482,13 +7482,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>導入官僚</t>
-    <rPh sb="0" eb="4">
-      <t>ドウニュウカンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>最後の演出案</t>
     <rPh sb="0" eb="2">
       <t>サイゴ</t>
@@ -7535,6 +7528,129 @@
     <rPh sb="0" eb="2">
       <t>トチュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>導入完了</t>
+    <rPh sb="0" eb="2">
+      <t>ドウニュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベントムービー中はプレイヤーを動かさないようにしないといけない</t>
+    <rPh sb="8" eb="9">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーを動かさないようにする完了</t>
+    <rPh sb="6" eb="7">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次はボスを倒した時のアクションを作る</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EventManagerを作って、それが発火したとき</t>
+    <rPh sb="13" eb="14">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーとボスの動きをセット</t>
+    <rPh sb="9" eb="10">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まず、カメラ関係なくアクションが起こるようにする</t>
+    <rPh sb="6" eb="8">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあとにカメラをセッティングする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラストヒットシーン案</t>
+    <rPh sb="9" eb="10">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの背中を見るカメラ</t>
+    <rPh sb="3" eb="5">
+      <t>セナカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスが倒れる</t>
+    <rPh sb="3" eb="4">
+      <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーは切りかかる</t>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのあと、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>血殺</t>
+    <rPh sb="0" eb="2">
+      <t>チサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>する</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -14236,7 +14352,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D296"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -15382,7 +15498,7 @@
         <v>546</v>
       </c>
       <c r="D229" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="230" spans="2:4">
@@ -15401,7 +15517,7 @@
         <v>653</v>
       </c>
       <c r="D231" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="232" spans="2:4">
@@ -15653,17 +15769,17 @@
         <v>648</v>
       </c>
     </row>
-    <row r="273" spans="2:3">
+    <row r="273" spans="1:3">
       <c r="C273" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="275" spans="2:3">
+    <row r="275" spans="1:3">
       <c r="C275" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="276" spans="2:3">
+    <row r="276" spans="1:3">
       <c r="B276" s="58" t="s">
         <v>652</v>
       </c>
@@ -15671,24 +15787,97 @@
         <v>651</v>
       </c>
     </row>
-    <row r="277" spans="2:3">
+    <row r="277" spans="1:3">
+      <c r="A277" s="1">
+        <v>46261</v>
+      </c>
       <c r="C277" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="C279" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="C280" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="279" spans="2:3">
-      <c r="C279" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="280" spans="2:3">
-      <c r="C280" t="s">
+    <row r="281" spans="1:3">
+      <c r="C281" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="281" spans="2:3">
-      <c r="C281" t="s">
-        <v>684</v>
+    <row r="282" spans="1:3">
+      <c r="C282" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="C283" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="C284" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="C285" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="C286" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="C287" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="C288" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="290" spans="3:3">
+      <c r="C290" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="291" spans="3:3">
+      <c r="C291" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="292" spans="3:3">
+      <c r="C292" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="293" spans="3:3">
+      <c r="C293" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="294" spans="3:3">
+      <c r="C294" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="295" spans="3:3">
+      <c r="C295" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="296" spans="3:3">
+      <c r="C296" t="s">
+        <v>700</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3969D629-FDF8-41C2-988C-4587FC4C3C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FA6ED5-3452-4D34-9B0E-81AF39440CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4365" yWindow="1845" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="705">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -6116,13 +6116,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ボスを動かす</t>
-    <rPh sb="3" eb="4">
-      <t>ウゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ボス用の血殺を作る(最後の)</t>
     <rPh sb="2" eb="3">
       <t>ヨウ</t>
@@ -7246,22 +7239,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>boss登場時のカメラ演出,フェーズ終わりのカメラ演出</t>
-    <rPh sb="4" eb="7">
-      <t>トウジョウジ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>エンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>終わり</t>
     <rPh sb="0" eb="1">
       <t>オ</t>
@@ -7651,6 +7628,102 @@
   </si>
   <si>
     <t>する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラの動き：</t>
+    <rPh sb="4" eb="5">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後ろー＞プレイヤーのほうに回る(手の付近)ー＞敵のほうを見る(playerのうしろ)-&gt;血殺終わり</t>
+    <rPh sb="0" eb="1">
+      <t>ウシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>フキン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けっこうやった</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>boss登場時のカメラ演出←完了,フェーズ終わりのカメラ演出←未完</t>
+    <rPh sb="4" eb="7">
+      <t>トウジョウジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ミカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスを動かす←ほぼ完了←攻撃回りが変</t>
+    <rPh sb="3" eb="4">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>コウゲキマワ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Relaseでも、裏コマンド入力でデバックの描画が見れるようにすると便利</t>
+    <rPh sb="9" eb="10">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ベンリ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -12349,22 +12422,22 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -14352,7 +14425,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D296"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -15487,135 +15560,141 @@
         <v>545</v>
       </c>
       <c r="D228" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="229" spans="2:4">
       <c r="B229" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C229" s="57" t="s">
-        <v>546</v>
+        <v>703</v>
       </c>
       <c r="D229" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="230" spans="2:4">
       <c r="B230" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C230" s="57" t="s">
-        <v>547</v>
+        <v>546</v>
+      </c>
+      <c r="D230" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="231" spans="2:4">
       <c r="B231" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C231" s="57" t="s">
-        <v>653</v>
+        <v>702</v>
       </c>
       <c r="D231" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="232" spans="2:4">
       <c r="B232" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C232" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="233" spans="2:4">
       <c r="B233" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C233" s="57" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D233" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="234" spans="2:4">
       <c r="B234" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C234" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D234" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="235" spans="2:4">
       <c r="B235" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C235" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="236" spans="2:4">
       <c r="B236" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C236" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D236" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="237" spans="2:4">
       <c r="B237" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C237" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D237" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="238" spans="2:4">
       <c r="B238" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C238" s="57" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D238" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="239" spans="2:4">
       <c r="B239" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C239" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D239" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="240" spans="2:4">
       <c r="C240" s="32" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
       <c r="B241" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C241" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
+        <v>610</v>
+      </c>
+      <c r="D241" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
       <c r="A242" s="1">
         <v>46258</v>
       </c>
@@ -15623,107 +15702,107 @@
         <v>530</v>
       </c>
     </row>
-    <row r="243" spans="1:3">
+    <row r="243" spans="1:4">
       <c r="C243" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="C244" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="244" spans="1:3">
-      <c r="C244" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
+    <row r="246" spans="1:4">
       <c r="C246" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="C247" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
-      <c r="C247" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
+    <row r="248" spans="1:4">
       <c r="C248" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="C249" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="249" spans="1:3">
-      <c r="C249" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:4">
       <c r="C250" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
       <c r="A251" s="1">
         <v>46259</v>
       </c>
       <c r="C251" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
       <c r="C252" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="C253" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
-      <c r="C253" t="s">
+    <row r="254" spans="1:4">
+      <c r="C254" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
-      <c r="C254" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3">
+    <row r="255" spans="1:4">
       <c r="C255" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="C256" t="s">
         <v>632</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="C256" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="C257" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="C258" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="C259" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="C260" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="C261" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="C263" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="C264" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -15731,60 +15810,60 @@
         <v>46260</v>
       </c>
       <c r="C265" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="C266" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="C267" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="C268" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="C269" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="C270" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="C271" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="C272" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="C273" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="C275" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="B276" s="58" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C276" s="58" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -15792,92 +15871,107 @@
         <v>46261</v>
       </c>
       <c r="C277" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="C279" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="C280" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="C281" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="C282" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="C283" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="C284" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="C285" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="C286" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="C287" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="C288" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="290" spans="3:3">
       <c r="C290" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="291" spans="3:3">
       <c r="C291" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="292" spans="3:3">
       <c r="C292" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="293" spans="3:3">
       <c r="C293" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="294" spans="3:3">
       <c r="C294" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="295" spans="3:3">
       <c r="C295" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="296" spans="3:3">
       <c r="C296" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="297" spans="3:3">
+      <c r="C297" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="298" spans="3:3">
+      <c r="C298" t="s">
         <v>700</v>
+      </c>
+    </row>
+    <row r="300" spans="3:3">
+      <c r="C300" t="s">
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -15896,89 +15990,89 @@
         <v>42</v>
       </c>
       <c r="F1" t="s">
+        <v>657</v>
+      </c>
+      <c r="L1" t="s">
         <v>659</v>
       </c>
-      <c r="L1" t="s">
-        <v>661</v>
-      </c>
       <c r="O1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="R1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="L2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="O2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="R2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
+        <v>656</v>
+      </c>
+      <c r="F3" t="s">
         <v>658</v>
       </c>
-      <c r="F3" t="s">
-        <v>660</v>
-      </c>
       <c r="L3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="O3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="R3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F4" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="L4" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="O4" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="R4" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="F5" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L5" t="s">
+        <v>675</v>
+      </c>
+      <c r="O5" t="s">
         <v>677</v>
-      </c>
-      <c r="O5" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="F6" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="L6" t="s">
+        <v>676</v>
+      </c>
+      <c r="O6" t="s">
         <v>678</v>
-      </c>
-      <c r="O6" t="s">
-        <v>680</v>
       </c>
     </row>
   </sheetData>
@@ -15994,176 +16088,176 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>566</v>
+      </c>
+      <c r="B5" t="s">
         <v>567</v>
-      </c>
-      <c r="B5" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -16179,107 +16273,107 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="55" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="56" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="56" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="56" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="56" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" s="56" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" s="56" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="56" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" s="56" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" s="56" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" s="56" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="56" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="56" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="56" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="56" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="56" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="56" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="56" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="56" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="56" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="56" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>

--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FA6ED5-3452-4D34-9B0E-81AF39440CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4365" yWindow="1845" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8940" yWindow="4155" windowWidth="20625" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -16788,14 +16788,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17034,21 +17032,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17073,9 +17070,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FA6ED5-3452-4D34-9B0E-81AF39440CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A2B68D-4F77-408A-90C9-4FC4608710B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="4155" windowWidth="20625" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8205" yWindow="2685" windowWidth="20625" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="706">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -7723,6 +7723,16 @@
     </rPh>
     <rPh sb="34" eb="36">
       <t>ベンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bossを倒した後のTimeScaleがなぜかかからない</t>
+    <rPh sb="5" eb="6">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -14425,7 +14435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D300"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -15972,6 +15982,11 @@
     <row r="300" spans="3:3">
       <c r="C300" t="s">
         <v>704</v>
+      </c>
+    </row>
+    <row r="301" spans="3:3">
+      <c r="C301" t="s">
+        <v>705</v>
       </c>
     </row>
   </sheetData>
@@ -16788,12 +16803,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17032,20 +17049,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17070,12 +17088,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A2B68D-4F77-408A-90C9-4FC4608710B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EC7A12-9621-47B9-804F-D2AA1BABCAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8205" yWindow="2685" windowWidth="20625" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2670" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="724">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -7733,6 +7733,270 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直した</t>
+    <rPh sb="0" eb="1">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃の当たり判定を出すタイミングをそろそろCSVに取り入れないといけない</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題点</t>
+    <rPh sb="0" eb="3">
+      <t>モンダイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベント発火が死亡アニメーション途中なので、血殺で締めた場合、TimeScaleが上書きされてしまう←終わり</t>
+    <rPh sb="4" eb="6">
+      <t>ハッカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>チサツ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ウワガ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベント発火をその前の当たったタイミングにすると行けそうだが、他がどうなるかちょっと怪しいため決断できない←終わり</t>
+    <rPh sb="4" eb="6">
+      <t>ハッカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>アヤ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ケツダン</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスのそのイベントが発火したタイミングで敵を削除したい←終わり</t>
+    <rPh sb="10" eb="12">
+      <t>ハッカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヤジルシオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>血殺カメラ遷移をイベント発火中はやめたい←終わり</t>
+    <rPh sb="20" eb="22">
+      <t>ヤジルシオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定を団子上でする、でその時のoffsetなどをIMGUIでやるのがよい</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ダンゴ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーに対してのフィードバックが少ないので、それをしっかり考えること</t>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>達成感を一つ一つ与えてあげる</t>
+    <rPh sb="0" eb="3">
+      <t>タッセイカン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIをしっかりしたものにする(ゲームとして見られる)</t>
+    <rPh sb="21" eb="22">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の配置をIMGUIで調整してそれをcsvでだすようにするといい</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シングルトンおおすぎ問題</t>
+    <rPh sb="10" eb="12">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF242424"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t>→バトルマネージャーを作って解決</t>
+    </r>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF242424"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t>（バトルマネージャーをシングルトンで持ち、外部からは、バトルマネージャーから呼び出す</t>
+    </r>
+    <rPh sb="18" eb="19">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF242424"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t>ほかのマネージャーはバトルマネージャーが持っているという設計</t>
+    </r>
+    <rPh sb="20" eb="21">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7745,7 +8009,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7818,6 +8082,12 @@
       <color rgb="FF242424"/>
       <name val="Cascadia Mono"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="29">
@@ -8115,7 +8385,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -8181,6 +8451,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -11605,11 +11876,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.3078556263269641E-2</v>
+        <v>5.2966101694915252E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -11627,7 +11898,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -11648,11 +11919,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-440</v>
+        <v>-441</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.37954545454545452</v>
+        <v>-0.37868480725623582</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -11665,11 +11936,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-420</v>
+        <v>-421</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.39761904761904759</v>
+        <v>-0.39667458432304037</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -11682,11 +11953,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-409</v>
+        <v>-410</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.40831295843520782</v>
+        <v>-0.40731707317073168</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -12560,11 +12831,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>25.25</v>
+        <v>33.666666666666664</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -12603,11 +12874,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-2.2926829268292681</v>
+        <v>-2.2380952380952381</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -12646,11 +12917,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-4.8235294117647056</v>
+        <v>-4.5555555555555554</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -12689,11 +12960,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="10" t="e">
+        <v>-1</v>
+      </c>
+      <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -14435,7 +14706,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D309"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -15581,7 +15852,7 @@
         <v>703</v>
       </c>
       <c r="D229" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
     </row>
     <row r="230" spans="2:4">
@@ -15592,7 +15863,7 @@
         <v>546</v>
       </c>
       <c r="D230" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
     </row>
     <row r="231" spans="2:4">
@@ -15858,25 +16129,28 @@
         <v>647</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:4">
       <c r="C273" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:4">
       <c r="C275" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:4">
       <c r="B276" s="58" t="s">
         <v>651</v>
       </c>
       <c r="C276" s="58" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="277" spans="1:3">
+      <c r="D276" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
       <c r="A277" s="1">
         <v>46261</v>
       </c>
@@ -15884,52 +16158,52 @@
         <v>684</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:4">
       <c r="C279" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" spans="1:4">
       <c r="C280" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:4">
       <c r="C281" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:4">
       <c r="C282" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:4">
       <c r="C283" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:4">
       <c r="C284" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:4">
       <c r="C285" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:4">
       <c r="C286" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:4">
       <c r="C287" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
+    <row r="288" spans="1:4">
       <c r="C288" t="s">
         <v>691</v>
       </c>
@@ -15987,6 +16261,41 @@
     <row r="301" spans="3:3">
       <c r="C301" t="s">
         <v>705</v>
+      </c>
+    </row>
+    <row r="302" spans="3:3">
+      <c r="C302" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="303" spans="3:3">
+      <c r="C303" s="58" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="305" spans="3:3">
+      <c r="C305" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="306" spans="3:3">
+      <c r="C306" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="307" spans="3:3">
+      <c r="C307" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="308" spans="3:3">
+      <c r="C308" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="309" spans="3:3">
+      <c r="C309" t="s">
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -16098,7 +16407,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E218887-0FDF-44BB-AA49-E18A6D1E6450}">
-  <dimension ref="A2:B48"/>
+  <dimension ref="A2:B55"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:2">
@@ -16273,6 +16582,31 @@
     <row r="48" spans="2:2">
       <c r="B48" t="s">
         <v>639</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
+        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -16283,7 +16617,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368A907-596B-4B61-8CB6-45BC6EA11F46}">
-  <dimension ref="B2:B22"/>
+  <dimension ref="B2:B27"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:2">
@@ -16389,6 +16723,26 @@
     <row r="22" spans="2:2">
       <c r="B22" s="56" t="s">
         <v>591</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="59" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="56" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="56" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="56" t="s">
+        <v>723</v>
       </c>
     </row>
   </sheetData>
@@ -16803,14 +17157,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17049,21 +17401,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17088,9 +17439,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_hirao\Documents\GitHub\2026_summer\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EC7A12-9621-47B9-804F-D2AA1BABCAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB9FA85-4AD7-4E8E-A03E-F21790695C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2670" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="713">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -7287,56 +7287,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>切り上げ攻撃時の足元から出すエフェクト</t>
-    <rPh sb="0" eb="1">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>アシモト</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>BGM</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>SE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃のHitEffect（剣と格闘で分ける</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カクトウ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージのフェーズ終わり時の解放エフェクト</t>
-    <rPh sb="9" eb="10">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カイホウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7369,26 +7324,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>剣のヒット音</t>
-    <rPh sb="0" eb="1">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>オン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>打撃のヒット音</t>
-    <rPh sb="0" eb="2">
-      <t>ダゲキ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>敵のヒット音、攻撃音</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -7402,50 +7337,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ステージ制限の壁</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>TitleScene</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>GameScene</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>PauseScene</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>GameClearScene</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>GameOverScene</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スキルの時の音</t>
-    <rPh sb="4" eb="5">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>血殺の時の音</t>
-    <rPh sb="0" eb="2">
-      <t>チサツ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>オト</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -8385,7 +8281,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -8452,6 +8348,7 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -11876,11 +11773,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.2966101694915252E-2</v>
+        <v>5.2742616033755275E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -11898,7 +11795,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -11919,11 +11816,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-441</v>
+        <v>-443</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.37868480725623582</v>
+        <v>-0.37697516930022573</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -11936,11 +11833,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-421</v>
+        <v>-423</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.39667458432304037</v>
+        <v>-0.39479905437352247</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -11953,11 +11850,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-410</v>
+        <v>-412</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.40731707317073168</v>
+        <v>-0.4053398058252427</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -12831,11 +12728,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>33.666666666666664</v>
+        <v>-101</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -12874,11 +12771,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-42</v>
+        <v>-46</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-2.2380952380952381</v>
+        <v>-2.0434782608695654</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -12917,11 +12814,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-18</v>
+        <v>-22</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-4.5555555555555554</v>
+        <v>-3.7272727272727271</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -12960,11 +12857,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>-16</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -15849,10 +15746,10 @@
         <v>553</v>
       </c>
       <c r="C229" s="57" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="D229" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="230" spans="2:4">
@@ -15863,7 +15760,7 @@
         <v>546</v>
       </c>
       <c r="D230" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="231" spans="2:4">
@@ -15871,10 +15768,10 @@
         <v>552</v>
       </c>
       <c r="C231" s="57" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="D231" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
     </row>
     <row r="232" spans="2:4">
@@ -15972,7 +15869,7 @@
         <v>610</v>
       </c>
       <c r="D241" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -16147,7 +16044,7 @@
         <v>650</v>
       </c>
       <c r="D276" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -16155,147 +16052,147 @@
         <v>46261</v>
       </c>
       <c r="C277" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="C279" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="C280" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="C281" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="C282" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="C283" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="C284" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="C285" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="C286" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="C287" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="C288" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="290" spans="3:3">
       <c r="C290" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="291" spans="3:3">
       <c r="C291" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
     </row>
     <row r="292" spans="3:3">
       <c r="C292" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
     </row>
     <row r="293" spans="3:3">
       <c r="C293" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
     </row>
     <row r="294" spans="3:3">
       <c r="C294" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
     </row>
     <row r="295" spans="3:3">
       <c r="C295" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
     </row>
     <row r="296" spans="3:3">
       <c r="C296" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
     </row>
     <row r="297" spans="3:3">
       <c r="C297" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
     </row>
     <row r="298" spans="3:3">
       <c r="C298" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
     </row>
     <row r="300" spans="3:3">
       <c r="C300" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
     </row>
     <row r="301" spans="3:3">
       <c r="C301" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
     </row>
     <row r="302" spans="3:3">
       <c r="C302" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
     </row>
     <row r="303" spans="3:3">
       <c r="C303" s="58" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
     </row>
     <row r="305" spans="3:3">
       <c r="C305" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="306" spans="3:3">
       <c r="C306" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
     </row>
     <row r="307" spans="3:3">
       <c r="C307" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
     </row>
     <row r="308" spans="3:3">
       <c r="C308" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
     </row>
     <row r="309" spans="3:3">
       <c r="C309" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -16306,7 +16203,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B2C458A-D800-40F2-A389-E66EF82142B9}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -16317,13 +16214,13 @@
         <v>657</v>
       </c>
       <c r="L1" t="s">
+        <v>658</v>
+      </c>
+      <c r="O1" t="s">
         <v>659</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>660</v>
-      </c>
-      <c r="R1" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -16331,72 +16228,35 @@
         <v>655</v>
       </c>
       <c r="F2" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="L2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="O2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="R2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>656</v>
       </c>
-      <c r="F3" t="s">
-        <v>658</v>
-      </c>
-      <c r="L3" t="s">
-        <v>673</v>
-      </c>
-      <c r="O3" t="s">
-        <v>669</v>
-      </c>
       <c r="R3" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
+        <v>661</v>
+      </c>
+      <c r="L4" t="s">
+        <v>667</v>
+      </c>
+      <c r="R4" t="s">
         <v>664</v>
-      </c>
-      <c r="F4" t="s">
-        <v>662</v>
-      </c>
-      <c r="L4" t="s">
-        <v>674</v>
-      </c>
-      <c r="O4" t="s">
-        <v>670</v>
-      </c>
-      <c r="R4" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="F5" t="s">
-        <v>671</v>
-      </c>
-      <c r="L5" t="s">
-        <v>675</v>
-      </c>
-      <c r="O5" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="F6" t="s">
-        <v>679</v>
-      </c>
-      <c r="L6" t="s">
-        <v>676</v>
-      </c>
-      <c r="O6" t="s">
-        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -16586,27 +16446,27 @@
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>
@@ -16626,7 +16486,7 @@
       </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="60" t="s">
         <v>572</v>
       </c>
     </row>
@@ -16651,7 +16511,7 @@
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="60" t="s">
         <v>577</v>
       </c>
     </row>
@@ -16727,22 +16587,22 @@
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="59" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" s="56" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" s="56" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" s="56" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -17157,12 +17017,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17401,20 +17263,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17439,12 +17302,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_summer\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB9FA85-4AD7-4E8E-A03E-F21790695C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92160ED-4223-46D6-A277-FB99FDA10B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="717">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -7893,6 +7893,49 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトシーン案</t>
+    <rPh sb="7" eb="8">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーはずっと歩いている</t>
+    <rPh sb="9" eb="10">
+      <t>アル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>髪の毛だけ通常描画などペルソナにもう少し寄せる</t>
+    <rPh sb="0" eb="1">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルと表示させる</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -11773,11 +11816,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>5.2742616033755275E-2</v>
+        <v>5.2631578947368418E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -11795,7 +11838,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -11816,11 +11859,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-443</v>
+        <v>-444</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.37697516930022573</v>
+        <v>-0.37612612612612611</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -11833,11 +11876,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-423</v>
+        <v>-424</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-0.39479905437352247</v>
+        <v>-0.39386792452830188</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -11850,11 +11893,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-412</v>
+        <v>-413</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-0.4053398058252427</v>
+        <v>-0.40435835351089588</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -12728,11 +12771,11 @@
       </c>
       <c r="M3" s="10">
         <f ca="1">INT(J11 - TODAY())</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N3" s="10">
         <f ca="1">K3/M3</f>
-        <v>-101</v>
+        <v>-50.5</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="26.25" hidden="1" customHeight="1">
@@ -12771,11 +12814,11 @@
       </c>
       <c r="M4" s="10">
         <f ca="1">INT(J12-TODAY())</f>
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="N4" s="10">
         <f ca="1">J4/M4</f>
-        <v>-2.0434782608695654</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" hidden="1" customHeight="1">
@@ -12814,11 +12857,11 @@
       </c>
       <c r="M5" s="10">
         <f t="shared" ref="M5:M6" ca="1" si="0">INT(J13-TODAY())</f>
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N6" ca="1" si="1">J5/M5</f>
-        <v>-3.7272727272727271</v>
+        <v>-3.5652173913043477</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" hidden="1" customHeight="1">
@@ -12857,11 +12900,11 @@
       </c>
       <c r="M6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="N6" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>-3.2</v>
+        <v>-2.6666666666666665</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -14603,7 +14646,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5F4C71-EC53-4AC7-B05F-AE75E87F0C1C}">
-  <dimension ref="A1:D309"/>
+  <dimension ref="A1:D315"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
@@ -16193,6 +16236,26 @@
     <row r="309" spans="3:3">
       <c r="C309" t="s">
         <v>703</v>
+      </c>
+    </row>
+    <row r="312" spans="3:3">
+      <c r="C312" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="313" spans="3:3">
+      <c r="C313" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="314" spans="3:3">
+      <c r="C314" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="315" spans="3:3">
+      <c r="C315" t="s">
+        <v>716</v>
       </c>
     </row>
   </sheetData>
@@ -17017,14 +17080,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17263,21 +17324,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17302,9 +17362,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/進捗/コスト表_summer_2026.xlsx
+++ b/進捗/コスト表_summer_2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92160ED-4223-46D6-A277-FB99FDA10B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="5" r:id="rId1"/>
@@ -17080,12 +17080,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17324,20 +17326,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17362,12 +17365,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>